--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F04318B7-9E1E-4376-A110-F0D4A1362440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A459132-78B1-438F-AA16-9A84474043FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1603,7 +1603,7 @@
         <v>1</v>
       </c>
       <c r="E44" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F44" t="s">
         <v>9</v>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A459132-78B1-438F-AA16-9A84474043FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62EF403E-8770-41EE-94B8-014B7714BA91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="142">
   <si>
     <t>REFERENCIA INTERNA</t>
   </si>
@@ -455,13 +455,16 @@
   </si>
   <si>
     <t>Ventas Junio y transcurso de ventas Julio.pdf</t>
+  </si>
+  <si>
+    <t>100.0%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -471,6 +474,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -500,10 +510,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1590,7 +1600,7 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44" s="4">
+      <c r="A44" s="3">
         <v>134001</v>
       </c>
       <c r="B44" t="s">
@@ -1602,15 +1612,15 @@
       <c r="D44">
         <v>1</v>
       </c>
-      <c r="E44" s="3">
-        <v>1</v>
+      <c r="E44" s="4" t="s">
+        <v>141</v>
       </c>
       <c r="F44" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45" s="4">
+      <c r="A45" s="3">
         <v>134000</v>
       </c>
       <c r="B45" t="s">

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62EF403E-8770-41EE-94B8-014B7714BA91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{486C28C0-8D84-44D5-8878-46BFD7F80FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="102">
   <si>
     <t>REFERENCIA INTERNA</t>
   </si>
@@ -52,399 +52,129 @@
     <t>Estado de tendencia</t>
   </si>
   <si>
-    <t>110150</t>
-  </si>
-  <si>
     <t>Cremosillo Tradicional 150g</t>
   </si>
   <si>
-    <t>2.56%</t>
-  </si>
-  <si>
-    <t>SUBIÓ</t>
-  </si>
-  <si>
-    <t>110151</t>
-  </si>
-  <si>
     <t>Cremosillo Coco 150g</t>
   </si>
   <si>
-    <t>-20.0%</t>
-  </si>
-  <si>
     <t>BAJO</t>
   </si>
   <si>
-    <t>110230</t>
-  </si>
-  <si>
     <t>Cremosillo Tradicional 230g</t>
   </si>
   <si>
-    <t>4.43%</t>
-  </si>
-  <si>
-    <t>110400</t>
-  </si>
-  <si>
     <t>Cremosillo Tradicional 400g</t>
   </si>
   <si>
-    <t>-19.44%</t>
-  </si>
-  <si>
-    <t>111000</t>
-  </si>
-  <si>
     <t>Cremosillo Tradicional 1000g</t>
   </si>
   <si>
     <t>30.77%</t>
   </si>
   <si>
-    <t>120130</t>
-  </si>
-  <si>
     <t>Gelatina Saltarina Fresa 130g</t>
   </si>
   <si>
-    <t>-13.33%</t>
-  </si>
-  <si>
-    <t>120131</t>
-  </si>
-  <si>
     <t>Gelatina Saltarina Chicle 130g</t>
   </si>
   <si>
-    <t>-16.35%</t>
-  </si>
-  <si>
-    <t>120132</t>
-  </si>
-  <si>
     <t>Gelatina Saltarina Kolita 130g</t>
   </si>
   <si>
-    <t>-18.77%</t>
-  </si>
-  <si>
-    <t>130150</t>
-  </si>
-  <si>
     <t>Cremigurt Natural 150g</t>
   </si>
   <si>
-    <t>-15.86%</t>
-  </si>
-  <si>
-    <t>130151</t>
-  </si>
-  <si>
     <t>Cremigurt Dulce 150g</t>
   </si>
   <si>
-    <t>-27.39%</t>
-  </si>
-  <si>
-    <t>130152</t>
-  </si>
-  <si>
     <t>Cremigurt Griego Fresa 150g</t>
   </si>
   <si>
-    <t>-18.55%</t>
-  </si>
-  <si>
-    <t>130153</t>
-  </si>
-  <si>
     <t>Cremigurt Griego Durazno 150g</t>
   </si>
   <si>
-    <t>-13.18%</t>
-  </si>
-  <si>
-    <t>130154</t>
-  </si>
-  <si>
     <t>Cremigurt Griego Piña 150g</t>
   </si>
   <si>
-    <t>-18.21%</t>
-  </si>
-  <si>
-    <t>130155</t>
-  </si>
-  <si>
     <t>Cremigurt Griego 150g</t>
   </si>
   <si>
-    <t>-22.74%</t>
-  </si>
-  <si>
-    <t>130156</t>
-  </si>
-  <si>
     <t>Cremigurt Light 150g</t>
   </si>
   <si>
-    <t>-35.77%</t>
-  </si>
-  <si>
-    <t>130700</t>
-  </si>
-  <si>
     <t>Cremigurt Natural 700g</t>
   </si>
   <si>
-    <t>-4.73%</t>
-  </si>
-  <si>
-    <t>130701</t>
-  </si>
-  <si>
     <t>Cremigurt Dulce 700g</t>
   </si>
   <si>
-    <t>19.0%</t>
-  </si>
-  <si>
-    <t>130702</t>
-  </si>
-  <si>
     <t>Cremigurt Griego Fresa 700g</t>
   </si>
   <si>
-    <t>-8.42%</t>
-  </si>
-  <si>
-    <t>130703</t>
-  </si>
-  <si>
     <t>Cremigurt Griego 700g</t>
   </si>
   <si>
-    <t>-4.58%</t>
-  </si>
-  <si>
-    <t>130704</t>
-  </si>
-  <si>
     <t>Cremigurt Light 700g</t>
   </si>
   <si>
-    <t>-65.12%</t>
-  </si>
-  <si>
-    <t>130707</t>
-  </si>
-  <si>
     <t>Griego Mykonos 700g</t>
   </si>
   <si>
-    <t>-90.91%</t>
-  </si>
-  <si>
-    <t>131150</t>
-  </si>
-  <si>
     <t>Cremigurt Power Natural 150g</t>
   </si>
   <si>
-    <t>-39.3%</t>
-  </si>
-  <si>
-    <t>131151</t>
-  </si>
-  <si>
     <t>Cremigurt Power Mantecado 150g</t>
   </si>
   <si>
-    <t>-30.02%</t>
-  </si>
-  <si>
-    <t>131152</t>
-  </si>
-  <si>
     <t>Cremigurt Power CheesseCake Fresa 150g</t>
   </si>
   <si>
-    <t>-18.18%</t>
-  </si>
-  <si>
-    <t>131153</t>
-  </si>
-  <si>
     <t>Cremigurt Power Cookies and Cream 150g</t>
   </si>
   <si>
-    <t>-34.6%</t>
-  </si>
-  <si>
-    <t>131700</t>
-  </si>
-  <si>
     <t>Cremigurt Power Natural 700g</t>
   </si>
   <si>
-    <t>-7.84%</t>
-  </si>
-  <si>
-    <t>131701</t>
-  </si>
-  <si>
     <t>Cremigurt Power Mantecado 700g</t>
   </si>
   <si>
-    <t>-8.93%</t>
-  </si>
-  <si>
-    <t>132150</t>
-  </si>
-  <si>
     <t>Cremigurt Griego Fresa S/A 150g</t>
   </si>
   <si>
-    <t>-6.43%</t>
-  </si>
-  <si>
-    <t>132151</t>
-  </si>
-  <si>
     <t>Cremigurt Griego Coco Vainilla S/A 150g</t>
   </si>
   <si>
-    <t>-17.06%</t>
-  </si>
-  <si>
-    <t>132152</t>
-  </si>
-  <si>
     <t>Cremigurt Griego Pie de Limón S/A 150g</t>
   </si>
   <si>
-    <t>-17.04%</t>
-  </si>
-  <si>
-    <t>132153</t>
-  </si>
-  <si>
     <t>Cremigurt Griego Caramelo Salado S/A 150g</t>
   </si>
   <si>
-    <t>-17.29%</t>
-  </si>
-  <si>
-    <t>140230</t>
-  </si>
-  <si>
     <t>Cremigurt Líquido Dulce 230g</t>
   </si>
   <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>140231</t>
-  </si>
-  <si>
     <t>Cremigurt Líquido Fresa 230g</t>
   </si>
   <si>
-    <t>-93.27%</t>
-  </si>
-  <si>
-    <t>140232</t>
-  </si>
-  <si>
     <t>Cremigurt Líquido Durazno 230g</t>
   </si>
   <si>
-    <t>-48.45%</t>
-  </si>
-  <si>
-    <t>150360</t>
-  </si>
-  <si>
-    <t>Tevia Limón 360ml</t>
-  </si>
-  <si>
-    <t>-28.73%</t>
-  </si>
-  <si>
-    <t>150361</t>
-  </si>
-  <si>
     <t>Tevia Durazno 360ml</t>
   </si>
   <si>
-    <t>-31.66%</t>
-  </si>
-  <si>
-    <t>150362</t>
-  </si>
-  <si>
     <t>Tevia Blueberry 360ml</t>
   </si>
   <si>
-    <t>-24.77%</t>
-  </si>
-  <si>
-    <t>150363</t>
-  </si>
-  <si>
     <t>Tevia Tropical Punch 360ml</t>
   </si>
   <si>
-    <t>-32.47%</t>
-  </si>
-  <si>
-    <t>151500</t>
-  </si>
-  <si>
-    <t>Tevia Limón 1.5L</t>
-  </si>
-  <si>
-    <t>-28.57%</t>
-  </si>
-  <si>
-    <t>151501</t>
-  </si>
-  <si>
-    <t>Tevia Durazno 1.5L</t>
-  </si>
-  <si>
-    <t>-37.8%</t>
-  </si>
-  <si>
-    <t>151502</t>
-  </si>
-  <si>
-    <t>Tevia Blueberry 1.5L</t>
-  </si>
-  <si>
-    <t>-21.05%</t>
-  </si>
-  <si>
-    <t>151503</t>
-  </si>
-  <si>
-    <t>Tevia Tropical Punch 1.5L</t>
-  </si>
-  <si>
-    <t>-27.03%</t>
-  </si>
-  <si>
     <t>Cremigurt Griego Dulce 4 Kg</t>
   </si>
   <si>
     <t>Cremigurt Griego Natural 4 Kg</t>
   </si>
   <si>
-    <t>-50.0%</t>
-  </si>
-  <si>
     <t>Índice</t>
   </si>
   <si>
@@ -457,7 +187,157 @@
     <t>Ventas Junio y transcurso de ventas Julio.pdf</t>
   </si>
   <si>
-    <t>100.0%</t>
+    <t>31.55%</t>
+  </si>
+  <si>
+    <t>SUBIO</t>
+  </si>
+  <si>
+    <t>38.33%</t>
+  </si>
+  <si>
+    <t>25.52%</t>
+  </si>
+  <si>
+    <t>38.89%</t>
+  </si>
+  <si>
+    <t>6.35%</t>
+  </si>
+  <si>
+    <t>8.65%</t>
+  </si>
+  <si>
+    <t>3.07%</t>
+  </si>
+  <si>
+    <t>ESTABLE</t>
+  </si>
+  <si>
+    <t>10.87%</t>
+  </si>
+  <si>
+    <t>0.27%</t>
+  </si>
+  <si>
+    <t>3.32%</t>
+  </si>
+  <si>
+    <t>9.19%</t>
+  </si>
+  <si>
+    <t>4.53%</t>
+  </si>
+  <si>
+    <t>0.33%</t>
+  </si>
+  <si>
+    <t>-5.84%</t>
+  </si>
+  <si>
+    <t>11.24%</t>
+  </si>
+  <si>
+    <t>82.00%</t>
+  </si>
+  <si>
+    <t>17.37%</t>
+  </si>
+  <si>
+    <t>22.88%</t>
+  </si>
+  <si>
+    <t>-67.44%</t>
+  </si>
+  <si>
+    <t>9.09%</t>
+  </si>
+  <si>
+    <t>-24.49%</t>
+  </si>
+  <si>
+    <t>-13.90%</t>
+  </si>
+  <si>
+    <t>1.40%</t>
+  </si>
+  <si>
+    <t>-16.92%</t>
+  </si>
+  <si>
+    <t>13.73%</t>
+  </si>
+  <si>
+    <t>16.07%</t>
+  </si>
+  <si>
+    <t>18.98%</t>
+  </si>
+  <si>
+    <t>-2.23%</t>
+  </si>
+  <si>
+    <t>1.67%</t>
+  </si>
+  <si>
+    <t>6.69%</t>
+  </si>
+  <si>
+    <t>29.27%</t>
+  </si>
+  <si>
+    <t>-93.02%</t>
+  </si>
+  <si>
+    <t>-2.25%</t>
+  </si>
+  <si>
+    <t>Tevia Limon 360ml</t>
+  </si>
+  <si>
+    <t>-13.06%</t>
+  </si>
+  <si>
+    <t>19.60%</t>
+  </si>
+  <si>
+    <t>18.35%</t>
+  </si>
+  <si>
+    <t>38.53%</t>
+  </si>
+  <si>
+    <t>Tevia Limon 1.5L</t>
+  </si>
+  <si>
+    <t>37.50%</t>
+  </si>
+  <si>
+    <t>Tevia Durazno 1.5 L</t>
+  </si>
+  <si>
+    <t>-25.61%</t>
+  </si>
+  <si>
+    <t>Tevia Blueberry 1.5 L</t>
+  </si>
+  <si>
+    <t>44.74%</t>
+  </si>
+  <si>
+    <t>Tevia Tropical Punch 1.5 L</t>
+  </si>
+  <si>
+    <t>-16.22%</t>
+  </si>
+  <si>
+    <t>Not in source</t>
+  </si>
+  <si>
+    <t>No disponible</t>
+  </si>
+  <si>
+    <t>0.00%</t>
   </si>
 </sst>
 </file>
@@ -506,7 +386,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
@@ -516,6 +396,7 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -760,91 +641,91 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2">
+        <v>110150</v>
+      </c>
+      <c r="B2" t="s">
         <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
       </c>
       <c r="C2">
         <v>821</v>
       </c>
-      <c r="D2">
-        <v>842</v>
+      <c r="D2" s="5">
+        <v>1080</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>10</v>
+      <c r="A3">
+        <v>110151</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C3">
         <v>60</v>
       </c>
       <c r="D3">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>14</v>
+      <c r="A4">
+        <v>110230</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>384</v>
       </c>
       <c r="D4">
-        <v>401</v>
+        <v>482</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>17</v>
+      <c r="A5">
+        <v>110400</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>72</v>
       </c>
       <c r="D5">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>20</v>
+      <c r="A6">
+        <v>111000</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C6">
         <v>13</v>
@@ -853,758 +734,758 @@
         <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>23</v>
+      <c r="A7">
+        <v>120130</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7">
+        <v>13</v>
+      </c>
+      <c r="C7" s="5">
         <v>1133</v>
       </c>
-      <c r="D7">
-        <v>982</v>
+      <c r="D7" s="5">
+        <v>1205</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>26</v>
+      <c r="A8">
+        <v>120131</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C8">
         <v>104</v>
       </c>
       <c r="D8">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>29</v>
+      <c r="A9">
+        <v>120132</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C9">
         <v>261</v>
       </c>
       <c r="D9">
-        <v>212</v>
+        <v>269</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>32</v>
+      <c r="A10">
+        <v>130150</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C10">
         <v>561</v>
       </c>
       <c r="D10">
-        <v>472</v>
+        <v>622</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>35</v>
+      <c r="A11">
+        <v>130151</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C11">
         <v>376</v>
       </c>
       <c r="D11">
-        <v>273</v>
+        <v>377</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>38</v>
+      <c r="A12">
+        <v>130152</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12">
+        <v>18</v>
+      </c>
+      <c r="C12" s="5">
         <v>2744</v>
       </c>
-      <c r="D12">
-        <v>2235</v>
+      <c r="D12" s="5">
+        <v>2835</v>
       </c>
       <c r="E12" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>41</v>
+      <c r="A13">
+        <v>130153</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13">
+        <v>19</v>
+      </c>
+      <c r="C13" s="5">
         <v>1752</v>
       </c>
-      <c r="D13">
-        <v>1521</v>
+      <c r="D13" s="5">
+        <v>1913</v>
       </c>
       <c r="E13" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>44</v>
+      <c r="A14">
+        <v>130154</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14">
+        <v>20</v>
+      </c>
+      <c r="C14" s="5">
         <v>1812</v>
       </c>
-      <c r="D14">
-        <v>1482</v>
+      <c r="D14" s="5">
+        <v>1894</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>47</v>
+      <c r="A15">
+        <v>130155</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15">
+        <v>21</v>
+      </c>
+      <c r="C15" s="5">
         <v>2128</v>
       </c>
-      <c r="D15">
-        <v>1644</v>
+      <c r="D15" s="5">
+        <v>2135</v>
       </c>
       <c r="E15" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>50</v>
+      <c r="A16">
+        <v>130156</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="C16">
         <v>137</v>
       </c>
       <c r="D16">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="E16" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>53</v>
+      <c r="A17">
+        <v>130700</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="C17">
         <v>169</v>
       </c>
       <c r="D17">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="E17" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F17" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>56</v>
+      <c r="A18">
+        <v>130701</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="C18">
         <v>100</v>
       </c>
       <c r="D18">
-        <v>119</v>
+        <v>182</v>
       </c>
       <c r="E18" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F18" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>59</v>
+      <c r="A19">
+        <v>130702</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="C19">
         <v>380</v>
       </c>
       <c r="D19">
-        <v>348</v>
+        <v>446</v>
       </c>
       <c r="E19" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F19" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>62</v>
+      <c r="A20">
+        <v>130703</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="C20">
         <v>612</v>
       </c>
       <c r="D20">
-        <v>584</v>
+        <v>752</v>
       </c>
       <c r="E20" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F20" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>65</v>
+      <c r="A21">
+        <v>130704</v>
       </c>
       <c r="B21" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="C21">
         <v>43</v>
       </c>
       <c r="D21">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E21" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F21" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>68</v>
+      <c r="A22">
+        <v>130707</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="C22">
         <v>33</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="E22" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F22" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>71</v>
+      <c r="A23">
+        <v>131150</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="C23">
         <v>682</v>
       </c>
       <c r="D23">
-        <v>414</v>
+        <v>515</v>
       </c>
       <c r="E23" t="s">
         <v>73</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+      <c r="A24">
+        <v>131151</v>
+      </c>
+      <c r="B24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="5">
+        <v>1086</v>
+      </c>
+      <c r="D24">
+        <v>935</v>
+      </c>
+      <c r="E24" t="s">
         <v>74</v>
       </c>
-      <c r="B24" t="s">
-        <v>75</v>
-      </c>
-      <c r="C24">
-        <v>1086</v>
-      </c>
-      <c r="D24">
-        <v>760</v>
-      </c>
-      <c r="E24" t="s">
-        <v>76</v>
-      </c>
       <c r="F24" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>77</v>
+      <c r="A25">
+        <v>131152</v>
       </c>
       <c r="B25" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="C25">
         <v>429</v>
       </c>
       <c r="D25">
-        <v>351</v>
+        <v>435</v>
       </c>
       <c r="E25" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F25" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>80</v>
+      <c r="A26">
+        <v>131153</v>
       </c>
       <c r="B26" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="C26">
         <v>396</v>
       </c>
       <c r="D26">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="E26" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F26" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>83</v>
+      <c r="A27">
+        <v>131700</v>
       </c>
       <c r="B27" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="C27">
         <v>102</v>
       </c>
       <c r="D27">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="E27" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="F27" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>86</v>
+      <c r="A28">
+        <v>131701</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="C28">
         <v>112</v>
       </c>
       <c r="D28">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="E28" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F28" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>89</v>
+      <c r="A29">
+        <v>132150</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="C29">
         <v>669</v>
       </c>
       <c r="D29">
-        <v>626</v>
+        <v>796</v>
       </c>
       <c r="E29" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="F29" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>92</v>
+      <c r="A30">
+        <v>132151</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="C30">
         <v>674</v>
       </c>
       <c r="D30">
-        <v>559</v>
+        <v>659</v>
       </c>
       <c r="E30" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="F30" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>95</v>
+      <c r="A31">
+        <v>132152</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>37</v>
       </c>
       <c r="C31">
         <v>839</v>
       </c>
       <c r="D31">
-        <v>696</v>
+        <v>853</v>
       </c>
       <c r="E31" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="F31" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>98</v>
+      <c r="A32">
+        <v>132153</v>
       </c>
       <c r="B32" t="s">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="C32">
         <v>538</v>
       </c>
       <c r="D32">
-        <v>445</v>
+        <v>574</v>
       </c>
       <c r="E32" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="F32" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>101</v>
+      <c r="A33">
+        <v>140230</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>39</v>
       </c>
       <c r="C33">
         <v>164</v>
       </c>
       <c r="D33">
-        <v>164</v>
+        <v>212</v>
       </c>
       <c r="E33" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="F33" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>104</v>
+      <c r="A34">
+        <v>140231</v>
       </c>
       <c r="B34" t="s">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="C34">
         <v>401</v>
       </c>
       <c r="D34">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E34" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="F34" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>107</v>
+      <c r="A35">
+        <v>140232</v>
       </c>
       <c r="B35" t="s">
-        <v>108</v>
+        <v>41</v>
       </c>
       <c r="C35">
         <v>355</v>
       </c>
       <c r="D35">
-        <v>183</v>
+        <v>347</v>
       </c>
       <c r="E35" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="F35" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>110</v>
+      <c r="A36">
+        <v>150360</v>
       </c>
       <c r="B36" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="C36">
         <v>268</v>
       </c>
       <c r="D36">
-        <v>191</v>
+        <v>233</v>
       </c>
       <c r="E36" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="F36" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>113</v>
+      <c r="A37">
+        <v>150361</v>
       </c>
       <c r="B37" t="s">
-        <v>114</v>
+        <v>42</v>
       </c>
       <c r="C37">
         <v>398</v>
       </c>
       <c r="D37">
-        <v>272</v>
+        <v>476</v>
       </c>
       <c r="E37" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="F37" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>116</v>
+      <c r="A38">
+        <v>150362</v>
       </c>
       <c r="B38" t="s">
-        <v>117</v>
+        <v>43</v>
       </c>
       <c r="C38">
         <v>218</v>
       </c>
       <c r="D38">
-        <v>164</v>
+        <v>258</v>
       </c>
       <c r="E38" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="F38" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>119</v>
+      <c r="A39">
+        <v>150363</v>
       </c>
       <c r="B39" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="C39">
         <v>231</v>
       </c>
       <c r="D39">
-        <v>156</v>
+        <v>320</v>
       </c>
       <c r="E39" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="F39" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>122</v>
+      <c r="A40">
+        <v>151500</v>
       </c>
       <c r="B40" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="C40">
         <v>56</v>
       </c>
       <c r="D40">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="E40" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="F40" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>125</v>
+      <c r="A41">
+        <v>151501</v>
       </c>
       <c r="B41" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="C41">
         <v>82</v>
       </c>
       <c r="D41">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E41" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="F41" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>128</v>
+      <c r="A42">
+        <v>151502</v>
       </c>
       <c r="B42" t="s">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="C42">
         <v>38</v>
       </c>
       <c r="D42">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="E42" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="F42" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>131</v>
+      <c r="A43">
+        <v>151503</v>
       </c>
       <c r="B43" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="C43">
         <v>37</v>
       </c>
       <c r="D43">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E43" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="F43" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44" s="3">
-        <v>134001</v>
+      <c r="A44" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="B44" t="s">
-        <v>134</v>
+        <v>45</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -1613,30 +1494,30 @@
         <v>1</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="F44" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45" s="3">
-        <v>134000</v>
+      <c r="A45" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="B45" t="s">
-        <v>135</v>
+        <v>46</v>
       </c>
       <c r="C45">
         <v>2</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="F45" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1654,18 +1535,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>137</v>
+        <v>47</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>138</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>139</v>
+        <v>49</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>140</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{486C28C0-8D84-44D5-8878-46BFD7F80FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CF4478-9320-499D-9821-853EBEAF2268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="101">
   <si>
     <t>REFERENCIA INTERNA</t>
   </si>
@@ -209,9 +209,6 @@
   </si>
   <si>
     <t>3.07%</t>
-  </si>
-  <si>
-    <t>ESTABLE</t>
   </si>
   <si>
     <t>10.87%</t>
@@ -797,7 +794,7 @@
         <v>58</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -814,7 +811,7 @@
         <v>622</v>
       </c>
       <c r="E10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F10" t="s">
         <v>52</v>
@@ -834,10 +831,10 @@
         <v>377</v>
       </c>
       <c r="E11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -854,10 +851,10 @@
         <v>2835</v>
       </c>
       <c r="E12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -874,7 +871,7 @@
         <v>1913</v>
       </c>
       <c r="E13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F13" t="s">
         <v>52</v>
@@ -894,10 +891,10 @@
         <v>1894</v>
       </c>
       <c r="E14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -914,10 +911,10 @@
         <v>2135</v>
       </c>
       <c r="E15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
@@ -934,7 +931,7 @@
         <v>129</v>
       </c>
       <c r="E16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F16" t="s">
         <v>8</v>
@@ -954,7 +951,7 @@
         <v>188</v>
       </c>
       <c r="E17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F17" t="s">
         <v>52</v>
@@ -974,7 +971,7 @@
         <v>182</v>
       </c>
       <c r="E18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F18" t="s">
         <v>52</v>
@@ -994,7 +991,7 @@
         <v>446</v>
       </c>
       <c r="E19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F19" t="s">
         <v>52</v>
@@ -1014,7 +1011,7 @@
         <v>752</v>
       </c>
       <c r="E20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F20" t="s">
         <v>52</v>
@@ -1034,7 +1031,7 @@
         <v>14</v>
       </c>
       <c r="E21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F21" t="s">
         <v>8</v>
@@ -1054,7 +1051,7 @@
         <v>36</v>
       </c>
       <c r="E22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F22" t="s">
         <v>52</v>
@@ -1074,7 +1071,7 @@
         <v>515</v>
       </c>
       <c r="E23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F23" t="s">
         <v>8</v>
@@ -1094,7 +1091,7 @@
         <v>935</v>
       </c>
       <c r="E24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F24" t="s">
         <v>8</v>
@@ -1114,10 +1111,10 @@
         <v>435</v>
       </c>
       <c r="E25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F25" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
@@ -1134,7 +1131,7 @@
         <v>329</v>
       </c>
       <c r="E26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F26" t="s">
         <v>8</v>
@@ -1154,7 +1151,7 @@
         <v>116</v>
       </c>
       <c r="E27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F27" t="s">
         <v>52</v>
@@ -1174,7 +1171,7 @@
         <v>130</v>
       </c>
       <c r="E28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F28" t="s">
         <v>52</v>
@@ -1194,7 +1191,7 @@
         <v>796</v>
       </c>
       <c r="E29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F29" t="s">
         <v>52</v>
@@ -1214,10 +1211,10 @@
         <v>659</v>
       </c>
       <c r="E30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F30" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
@@ -1234,10 +1231,10 @@
         <v>853</v>
       </c>
       <c r="E31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F31" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
@@ -1254,7 +1251,7 @@
         <v>574</v>
       </c>
       <c r="E32" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F32" t="s">
         <v>52</v>
@@ -1274,7 +1271,7 @@
         <v>212</v>
       </c>
       <c r="E33" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F33" t="s">
         <v>52</v>
@@ -1294,7 +1291,7 @@
         <v>28</v>
       </c>
       <c r="E34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F34" t="s">
         <v>8</v>
@@ -1314,10 +1311,10 @@
         <v>347</v>
       </c>
       <c r="E35" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F35" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
@@ -1325,7 +1322,7 @@
         <v>150360</v>
       </c>
       <c r="B36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C36">
         <v>268</v>
@@ -1334,7 +1331,7 @@
         <v>233</v>
       </c>
       <c r="E36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F36" t="s">
         <v>8</v>
@@ -1354,7 +1351,7 @@
         <v>476</v>
       </c>
       <c r="E37" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F37" t="s">
         <v>52</v>
@@ -1374,7 +1371,7 @@
         <v>258</v>
       </c>
       <c r="E38" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F38" t="s">
         <v>52</v>
@@ -1394,7 +1391,7 @@
         <v>320</v>
       </c>
       <c r="E39" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F39" t="s">
         <v>52</v>
@@ -1405,7 +1402,7 @@
         <v>151500</v>
       </c>
       <c r="B40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C40">
         <v>56</v>
@@ -1414,7 +1411,7 @@
         <v>77</v>
       </c>
       <c r="E40" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F40" t="s">
         <v>52</v>
@@ -1425,7 +1422,7 @@
         <v>151501</v>
       </c>
       <c r="B41" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C41">
         <v>82</v>
@@ -1434,7 +1431,7 @@
         <v>61</v>
       </c>
       <c r="E41" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F41" t="s">
         <v>8</v>
@@ -1445,7 +1442,7 @@
         <v>151502</v>
       </c>
       <c r="B42" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C42">
         <v>38</v>
@@ -1454,7 +1451,7 @@
         <v>55</v>
       </c>
       <c r="E42" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F42" t="s">
         <v>52</v>
@@ -1465,7 +1462,7 @@
         <v>151503</v>
       </c>
       <c r="B43" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C43">
         <v>37</v>
@@ -1474,7 +1471,7 @@
         <v>31</v>
       </c>
       <c r="E43" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F43" t="s">
         <v>8</v>
@@ -1482,7 +1479,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B44" t="s">
         <v>45</v>
@@ -1494,7 +1491,7 @@
         <v>1</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F44" t="s">
         <v>52</v>
@@ -1502,7 +1499,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B45" t="s">
         <v>46</v>
@@ -1514,10 +1511,10 @@
         <v>2</v>
       </c>
       <c r="E45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F45" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CF4478-9320-499D-9821-853EBEAF2268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D59131E9-B18F-4997-AA35-F3858DB5998D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="100">
   <si>
     <t>REFERENCIA INTERNA</t>
   </si>
@@ -329,9 +329,6 @@
   </si>
   <si>
     <t>Not in source</t>
-  </si>
-  <si>
-    <t>No disponible</t>
   </si>
   <si>
     <t>0.00%</t>
@@ -341,7 +338,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -351,13 +348,6 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -383,14 +373,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -647,7 +634,7 @@
       <c r="C2">
         <v>821</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="4">
         <v>1080</v>
       </c>
       <c r="E2" t="s">
@@ -744,10 +731,10 @@
       <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="4">
         <v>1133</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="4">
         <v>1205</v>
       </c>
       <c r="E7" t="s">
@@ -844,10 +831,10 @@
       <c r="B12" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="4">
         <v>2744</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="4">
         <v>2835</v>
       </c>
       <c r="E12" t="s">
@@ -864,10 +851,10 @@
       <c r="B13" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="4">
         <v>1752</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="4">
         <v>1913</v>
       </c>
       <c r="E13" t="s">
@@ -884,10 +871,10 @@
       <c r="B14" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="4">
         <v>1812</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="4">
         <v>1894</v>
       </c>
       <c r="E14" t="s">
@@ -904,10 +891,10 @@
       <c r="B15" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="4">
         <v>2128</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="4">
         <v>2135</v>
       </c>
       <c r="E15" t="s">
@@ -1084,7 +1071,7 @@
       <c r="B24" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="4">
         <v>1086</v>
       </c>
       <c r="D24">
@@ -1490,7 +1477,7 @@
       <c r="D44">
         <v>1</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" t="s">
         <v>99</v>
       </c>
       <c r="F44" t="s">
@@ -1511,7 +1498,7 @@
         <v>2</v>
       </c>
       <c r="E45" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F45" t="s">
         <v>52</v>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D59131E9-B18F-4997-AA35-F3858DB5998D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95CA6E4-0535-4824-AB20-49F78A0BD881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="101">
   <si>
     <t>REFERENCIA INTERNA</t>
   </si>
@@ -58,9 +58,6 @@
     <t>Cremosillo Coco 150g</t>
   </si>
   <si>
-    <t>BAJO</t>
-  </si>
-  <si>
     <t>Cremosillo Tradicional 230g</t>
   </si>
   <si>
@@ -332,13 +329,19 @@
   </si>
   <si>
     <t>0.00%</t>
+  </si>
+  <si>
+    <t>SUBIÓ</t>
+  </si>
+  <si>
+    <t>BAJÓ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -348,6 +351,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -373,7 +383,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
@@ -381,6 +391,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -638,10 +649,10 @@
         <v>1080</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -658,10 +669,10 @@
         <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" t="s">
         <v>52</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -669,7 +680,7 @@
         <v>110230</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>384</v>
@@ -678,10 +689,10 @@
         <v>482</v>
       </c>
       <c r="E4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" t="s">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -689,7 +700,7 @@
         <v>110400</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <v>72</v>
@@ -698,10 +709,10 @@
         <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F5" t="s">
-        <v>52</v>
+        <v>54</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -709,7 +720,7 @@
         <v>111000</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <v>13</v>
@@ -718,10 +729,10 @@
         <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
-        <v>52</v>
+        <v>11</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -729,7 +740,7 @@
         <v>120130</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="4">
         <v>1133</v>
@@ -738,10 +749,10 @@
         <v>1205</v>
       </c>
       <c r="E7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" t="s">
-        <v>52</v>
+        <v>55</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -749,7 +760,7 @@
         <v>120131</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8">
         <v>104</v>
@@ -758,10 +769,10 @@
         <v>113</v>
       </c>
       <c r="E8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8" t="s">
-        <v>52</v>
+        <v>56</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -769,7 +780,7 @@
         <v>120132</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9">
         <v>261</v>
@@ -778,10 +789,10 @@
         <v>269</v>
       </c>
       <c r="E9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F9" t="s">
-        <v>52</v>
+        <v>57</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -789,7 +800,7 @@
         <v>130150</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10">
         <v>561</v>
@@ -798,10 +809,10 @@
         <v>622</v>
       </c>
       <c r="E10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F10" t="s">
-        <v>52</v>
+        <v>58</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -809,7 +820,7 @@
         <v>130151</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11">
         <v>376</v>
@@ -818,10 +829,10 @@
         <v>377</v>
       </c>
       <c r="E11" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" t="s">
-        <v>52</v>
+        <v>59</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -829,7 +840,7 @@
         <v>130152</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" s="4">
         <v>2744</v>
@@ -838,10 +849,10 @@
         <v>2835</v>
       </c>
       <c r="E12" t="s">
-        <v>61</v>
-      </c>
-      <c r="F12" t="s">
-        <v>52</v>
+        <v>60</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -849,7 +860,7 @@
         <v>130153</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" s="4">
         <v>1752</v>
@@ -858,10 +869,10 @@
         <v>1913</v>
       </c>
       <c r="E13" t="s">
-        <v>62</v>
-      </c>
-      <c r="F13" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -869,7 +880,7 @@
         <v>130154</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C14" s="4">
         <v>1812</v>
@@ -878,10 +889,10 @@
         <v>1894</v>
       </c>
       <c r="E14" t="s">
-        <v>63</v>
-      </c>
-      <c r="F14" t="s">
-        <v>52</v>
+        <v>62</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -889,7 +900,7 @@
         <v>130155</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" s="4">
         <v>2128</v>
@@ -898,10 +909,10 @@
         <v>2135</v>
       </c>
       <c r="E15" t="s">
-        <v>64</v>
-      </c>
-      <c r="F15" t="s">
-        <v>52</v>
+        <v>63</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
@@ -909,7 +920,7 @@
         <v>130156</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16">
         <v>137</v>
@@ -918,10 +929,10 @@
         <v>129</v>
       </c>
       <c r="E16" t="s">
-        <v>65</v>
-      </c>
-      <c r="F16" t="s">
-        <v>8</v>
+        <v>64</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -929,7 +940,7 @@
         <v>130700</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17">
         <v>169</v>
@@ -938,10 +949,10 @@
         <v>188</v>
       </c>
       <c r="E17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -949,7 +960,7 @@
         <v>130701</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18">
         <v>100</v>
@@ -958,10 +969,10 @@
         <v>182</v>
       </c>
       <c r="E18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -969,7 +980,7 @@
         <v>130702</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19">
         <v>380</v>
@@ -978,10 +989,10 @@
         <v>446</v>
       </c>
       <c r="E19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -989,7 +1000,7 @@
         <v>130703</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C20">
         <v>612</v>
@@ -998,10 +1009,10 @@
         <v>752</v>
       </c>
       <c r="E20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -1009,7 +1020,7 @@
         <v>130704</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C21">
         <v>43</v>
@@ -1018,10 +1029,10 @@
         <v>14</v>
       </c>
       <c r="E21" t="s">
-        <v>70</v>
-      </c>
-      <c r="F21" t="s">
-        <v>8</v>
+        <v>69</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -1029,7 +1040,7 @@
         <v>130707</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C22">
         <v>33</v>
@@ -1038,10 +1049,10 @@
         <v>36</v>
       </c>
       <c r="E22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -1049,7 +1060,7 @@
         <v>131150</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C23">
         <v>682</v>
@@ -1058,10 +1069,10 @@
         <v>515</v>
       </c>
       <c r="E23" t="s">
-        <v>72</v>
-      </c>
-      <c r="F23" t="s">
-        <v>8</v>
+        <v>71</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
@@ -1069,7 +1080,7 @@
         <v>131151</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C24" s="4">
         <v>1086</v>
@@ -1078,10 +1089,10 @@
         <v>935</v>
       </c>
       <c r="E24" t="s">
-        <v>73</v>
-      </c>
-      <c r="F24" t="s">
-        <v>8</v>
+        <v>72</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
@@ -1089,7 +1100,7 @@
         <v>131152</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C25">
         <v>429</v>
@@ -1098,10 +1109,10 @@
         <v>435</v>
       </c>
       <c r="E25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
@@ -1109,7 +1120,7 @@
         <v>131153</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C26">
         <v>396</v>
@@ -1118,10 +1129,10 @@
         <v>329</v>
       </c>
       <c r="E26" t="s">
-        <v>75</v>
-      </c>
-      <c r="F26" t="s">
-        <v>8</v>
+        <v>74</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
@@ -1129,7 +1140,7 @@
         <v>131700</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C27">
         <v>102</v>
@@ -1138,10 +1149,10 @@
         <v>116</v>
       </c>
       <c r="E27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
@@ -1149,7 +1160,7 @@
         <v>131701</v>
       </c>
       <c r="B28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C28">
         <v>112</v>
@@ -1158,10 +1169,10 @@
         <v>130</v>
       </c>
       <c r="E28" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
@@ -1169,7 +1180,7 @@
         <v>132150</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C29">
         <v>669</v>
@@ -1178,10 +1189,10 @@
         <v>796</v>
       </c>
       <c r="E29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
@@ -1189,7 +1200,7 @@
         <v>132151</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C30">
         <v>674</v>
@@ -1198,10 +1209,10 @@
         <v>659</v>
       </c>
       <c r="E30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
@@ -1209,7 +1220,7 @@
         <v>132152</v>
       </c>
       <c r="B31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C31">
         <v>839</v>
@@ -1218,10 +1229,10 @@
         <v>853</v>
       </c>
       <c r="E31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
@@ -1229,7 +1240,7 @@
         <v>132153</v>
       </c>
       <c r="B32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C32">
         <v>538</v>
@@ -1238,10 +1249,10 @@
         <v>574</v>
       </c>
       <c r="E32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
@@ -1249,7 +1260,7 @@
         <v>140230</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C33">
         <v>164</v>
@@ -1258,10 +1269,10 @@
         <v>212</v>
       </c>
       <c r="E33" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
@@ -1269,7 +1280,7 @@
         <v>140231</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C34">
         <v>401</v>
@@ -1278,10 +1289,10 @@
         <v>28</v>
       </c>
       <c r="E34" t="s">
-        <v>83</v>
-      </c>
-      <c r="F34" t="s">
-        <v>8</v>
+        <v>82</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
@@ -1289,7 +1300,7 @@
         <v>140232</v>
       </c>
       <c r="B35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C35">
         <v>355</v>
@@ -1298,10 +1309,10 @@
         <v>347</v>
       </c>
       <c r="E35" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
@@ -1309,7 +1320,7 @@
         <v>150360</v>
       </c>
       <c r="B36" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C36">
         <v>268</v>
@@ -1318,10 +1329,10 @@
         <v>233</v>
       </c>
       <c r="E36" t="s">
-        <v>86</v>
-      </c>
-      <c r="F36" t="s">
-        <v>8</v>
+        <v>85</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
@@ -1329,7 +1340,7 @@
         <v>150361</v>
       </c>
       <c r="B37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C37">
         <v>398</v>
@@ -1338,10 +1349,10 @@
         <v>476</v>
       </c>
       <c r="E37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F37" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
@@ -1349,7 +1360,7 @@
         <v>150362</v>
       </c>
       <c r="B38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C38">
         <v>218</v>
@@ -1358,10 +1369,10 @@
         <v>258</v>
       </c>
       <c r="E38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
@@ -1369,7 +1380,7 @@
         <v>150363</v>
       </c>
       <c r="B39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C39">
         <v>231</v>
@@ -1378,10 +1389,10 @@
         <v>320</v>
       </c>
       <c r="E39" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F39" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
@@ -1389,7 +1400,7 @@
         <v>151500</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C40">
         <v>56</v>
@@ -1398,10 +1409,10 @@
         <v>77</v>
       </c>
       <c r="E40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
@@ -1409,7 +1420,7 @@
         <v>151501</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C41">
         <v>82</v>
@@ -1418,10 +1429,10 @@
         <v>61</v>
       </c>
       <c r="E41" t="s">
-        <v>93</v>
-      </c>
-      <c r="F41" t="s">
-        <v>8</v>
+        <v>92</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
@@ -1429,7 +1440,7 @@
         <v>151502</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C42">
         <v>38</v>
@@ -1438,10 +1449,10 @@
         <v>55</v>
       </c>
       <c r="E42" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
@@ -1449,7 +1460,7 @@
         <v>151503</v>
       </c>
       <c r="B43" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C43">
         <v>37</v>
@@ -1458,18 +1469,18 @@
         <v>31</v>
       </c>
       <c r="E43" t="s">
-        <v>97</v>
-      </c>
-      <c r="F43" t="s">
-        <v>8</v>
+        <v>96</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -1478,18 +1489,18 @@
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F44" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C45">
         <v>2</v>
@@ -1498,10 +1509,10 @@
         <v>2</v>
       </c>
       <c r="E45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F45" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1519,18 +1530,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95CA6E4-0535-4824-AB20-49F78A0BD881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A489E57C-CFA9-45D8-8191-BA71BD6E461B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -334,7 +334,7 @@
     <t>SUBIÓ</t>
   </si>
   <si>
-    <t>BAJÓ</t>
+    <t>BAJO</t>
   </si>
 </sst>
 </file>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A489E57C-CFA9-45D8-8191-BA71BD6E461B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8AFB948-E77B-46E5-B7F7-F3A1C4C18F19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="100">
   <si>
     <t>REFERENCIA INTERNA</t>
   </si>
@@ -185,9 +185,6 @@
   </si>
   <si>
     <t>31.55%</t>
-  </si>
-  <si>
-    <t>SUBIO</t>
   </si>
   <si>
     <t>38.33%</t>
@@ -652,7 +649,7 @@
         <v>50</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -669,10 +666,10 @@
         <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -689,10 +686,10 @@
         <v>482</v>
       </c>
       <c r="E4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -709,10 +706,10 @@
         <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -732,7 +729,7 @@
         <v>11</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -749,10 +746,10 @@
         <v>1205</v>
       </c>
       <c r="E7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -769,10 +766,10 @@
         <v>113</v>
       </c>
       <c r="E8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -789,10 +786,10 @@
         <v>269</v>
       </c>
       <c r="E9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -809,10 +806,10 @@
         <v>622</v>
       </c>
       <c r="E10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -829,10 +826,10 @@
         <v>377</v>
       </c>
       <c r="E11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -849,10 +846,10 @@
         <v>2835</v>
       </c>
       <c r="E12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -869,10 +866,10 @@
         <v>1913</v>
       </c>
       <c r="E13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -889,10 +886,10 @@
         <v>1894</v>
       </c>
       <c r="E14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -909,10 +906,10 @@
         <v>2135</v>
       </c>
       <c r="E15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
@@ -929,10 +926,10 @@
         <v>129</v>
       </c>
       <c r="E16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -949,10 +946,10 @@
         <v>188</v>
       </c>
       <c r="E17" t="s">
-        <v>65</v>
-      </c>
-      <c r="F17" t="s">
-        <v>51</v>
+        <v>64</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -969,10 +966,10 @@
         <v>182</v>
       </c>
       <c r="E18" t="s">
-        <v>66</v>
-      </c>
-      <c r="F18" t="s">
-        <v>51</v>
+        <v>65</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -989,10 +986,10 @@
         <v>446</v>
       </c>
       <c r="E19" t="s">
-        <v>67</v>
-      </c>
-      <c r="F19" t="s">
-        <v>51</v>
+        <v>66</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -1009,10 +1006,10 @@
         <v>752</v>
       </c>
       <c r="E20" t="s">
-        <v>68</v>
-      </c>
-      <c r="F20" t="s">
-        <v>51</v>
+        <v>67</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -1029,10 +1026,10 @@
         <v>14</v>
       </c>
       <c r="E21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -1049,10 +1046,10 @@
         <v>36</v>
       </c>
       <c r="E22" t="s">
-        <v>70</v>
-      </c>
-      <c r="F22" t="s">
-        <v>51</v>
+        <v>69</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -1069,10 +1066,10 @@
         <v>515</v>
       </c>
       <c r="E23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
@@ -1089,10 +1086,10 @@
         <v>935</v>
       </c>
       <c r="E24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
@@ -1109,10 +1106,10 @@
         <v>435</v>
       </c>
       <c r="E25" t="s">
-        <v>73</v>
-      </c>
-      <c r="F25" t="s">
-        <v>51</v>
+        <v>72</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
@@ -1129,10 +1126,10 @@
         <v>329</v>
       </c>
       <c r="E26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
@@ -1149,10 +1146,10 @@
         <v>116</v>
       </c>
       <c r="E27" t="s">
-        <v>75</v>
-      </c>
-      <c r="F27" t="s">
-        <v>51</v>
+        <v>74</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
@@ -1169,10 +1166,10 @@
         <v>130</v>
       </c>
       <c r="E28" t="s">
-        <v>76</v>
-      </c>
-      <c r="F28" t="s">
-        <v>51</v>
+        <v>75</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
@@ -1189,10 +1186,10 @@
         <v>796</v>
       </c>
       <c r="E29" t="s">
-        <v>77</v>
-      </c>
-      <c r="F29" t="s">
-        <v>51</v>
+        <v>76</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
@@ -1209,10 +1206,10 @@
         <v>659</v>
       </c>
       <c r="E30" t="s">
-        <v>78</v>
-      </c>
-      <c r="F30" t="s">
-        <v>51</v>
+        <v>77</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
@@ -1229,10 +1226,10 @@
         <v>853</v>
       </c>
       <c r="E31" t="s">
-        <v>79</v>
-      </c>
-      <c r="F31" t="s">
-        <v>51</v>
+        <v>78</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
@@ -1249,10 +1246,10 @@
         <v>574</v>
       </c>
       <c r="E32" t="s">
-        <v>80</v>
-      </c>
-      <c r="F32" t="s">
-        <v>51</v>
+        <v>79</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
@@ -1269,10 +1266,10 @@
         <v>212</v>
       </c>
       <c r="E33" t="s">
-        <v>81</v>
-      </c>
-      <c r="F33" t="s">
-        <v>51</v>
+        <v>80</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
@@ -1289,10 +1286,10 @@
         <v>28</v>
       </c>
       <c r="E34" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
@@ -1309,10 +1306,10 @@
         <v>347</v>
       </c>
       <c r="E35" t="s">
-        <v>83</v>
-      </c>
-      <c r="F35" t="s">
-        <v>51</v>
+        <v>82</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
@@ -1320,7 +1317,7 @@
         <v>150360</v>
       </c>
       <c r="B36" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C36">
         <v>268</v>
@@ -1329,10 +1326,10 @@
         <v>233</v>
       </c>
       <c r="E36" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
@@ -1349,10 +1346,10 @@
         <v>476</v>
       </c>
       <c r="E37" t="s">
-        <v>86</v>
-      </c>
-      <c r="F37" t="s">
-        <v>51</v>
+        <v>85</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
@@ -1369,10 +1366,10 @@
         <v>258</v>
       </c>
       <c r="E38" t="s">
-        <v>87</v>
-      </c>
-      <c r="F38" t="s">
-        <v>51</v>
+        <v>86</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
@@ -1389,10 +1386,10 @@
         <v>320</v>
       </c>
       <c r="E39" t="s">
-        <v>88</v>
-      </c>
-      <c r="F39" t="s">
-        <v>51</v>
+        <v>87</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
@@ -1400,7 +1397,7 @@
         <v>151500</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C40">
         <v>56</v>
@@ -1409,10 +1406,10 @@
         <v>77</v>
       </c>
       <c r="E40" t="s">
-        <v>90</v>
-      </c>
-      <c r="F40" t="s">
-        <v>51</v>
+        <v>89</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
@@ -1420,7 +1417,7 @@
         <v>151501</v>
       </c>
       <c r="B41" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C41">
         <v>82</v>
@@ -1429,10 +1426,10 @@
         <v>61</v>
       </c>
       <c r="E41" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
@@ -1440,7 +1437,7 @@
         <v>151502</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C42">
         <v>38</v>
@@ -1449,10 +1446,10 @@
         <v>55</v>
       </c>
       <c r="E42" t="s">
-        <v>94</v>
-      </c>
-      <c r="F42" t="s">
-        <v>51</v>
+        <v>93</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
@@ -1460,7 +1457,7 @@
         <v>151503</v>
       </c>
       <c r="B43" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C43">
         <v>37</v>
@@ -1469,15 +1466,15 @@
         <v>31</v>
       </c>
       <c r="E43" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B44" t="s">
         <v>44</v>
@@ -1489,15 +1486,15 @@
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>98</v>
-      </c>
-      <c r="F44" t="s">
-        <v>51</v>
+        <v>97</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B45" t="s">
         <v>45</v>
@@ -1509,10 +1506,10 @@
         <v>2</v>
       </c>
       <c r="E45" t="s">
-        <v>98</v>
-      </c>
-      <c r="F45" t="s">
-        <v>51</v>
+        <v>97</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8AFB948-E77B-46E5-B7F7-F3A1C4C18F19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68FAF54-191E-4593-9235-A5C5A66A94D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="101">
   <si>
     <t>REFERENCIA INTERNA</t>
   </si>
@@ -332,6 +332,9 @@
   </si>
   <si>
     <t>BAJO</t>
+  </si>
+  <si>
+    <t>PRECIO UNITARIO</t>
   </si>
 </sst>
 </file>
@@ -604,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.7109375" customWidth="1"/>
@@ -612,7 +615,7 @@
     <col min="3" max="9" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -631,8 +634,11 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G1" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>110150</v>
       </c>
@@ -651,8 +657,11 @@
       <c r="F2" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G2">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>110151</v>
       </c>
@@ -671,8 +680,11 @@
       <c r="F3" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G3">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>110230</v>
       </c>
@@ -691,8 +703,11 @@
       <c r="F4" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G4">
+        <v>2.0299999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>110400</v>
       </c>
@@ -711,8 +726,11 @@
       <c r="F5" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G5">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>111000</v>
       </c>
@@ -731,8 +749,11 @@
       <c r="F6" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G6">
+        <v>8.7799999999999994</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>120130</v>
       </c>
@@ -751,8 +772,11 @@
       <c r="F7" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G7">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>120131</v>
       </c>
@@ -771,8 +795,11 @@
       <c r="F8" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G8">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>120132</v>
       </c>
@@ -791,8 +818,11 @@
       <c r="F9" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G9">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>130150</v>
       </c>
@@ -811,8 +841,11 @@
       <c r="F10" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G10">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>130151</v>
       </c>
@@ -831,8 +864,11 @@
       <c r="F11" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G11">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>130152</v>
       </c>
@@ -851,8 +887,11 @@
       <c r="F12" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G12">
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>130153</v>
       </c>
@@ -871,8 +910,11 @@
       <c r="F13" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G13">
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>130154</v>
       </c>
@@ -891,8 +933,11 @@
       <c r="F14" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G14">
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>130155</v>
       </c>
@@ -911,8 +956,11 @@
       <c r="F15" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G15">
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>130156</v>
       </c>
@@ -931,8 +979,11 @@
       <c r="F16" s="5" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G16">
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>130700</v>
       </c>
@@ -951,8 +1002,11 @@
       <c r="F17" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G17">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>130701</v>
       </c>
@@ -971,8 +1025,11 @@
       <c r="F18" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G18">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>130702</v>
       </c>
@@ -991,8 +1048,11 @@
       <c r="F19" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G19">
+        <v>4.1500000000000004</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>130703</v>
       </c>
@@ -1011,8 +1071,11 @@
       <c r="F20" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G20">
+        <v>4.1500000000000004</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>130704</v>
       </c>
@@ -1031,8 +1094,11 @@
       <c r="F21" s="5" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G21">
+        <v>4.1500000000000004</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>130707</v>
       </c>
@@ -1051,8 +1117,11 @@
       <c r="F22" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G22">
+        <v>4.1500000000000004</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>131150</v>
       </c>
@@ -1071,8 +1140,11 @@
       <c r="F23" s="5" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G23">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>131151</v>
       </c>
@@ -1091,8 +1163,11 @@
       <c r="F24" s="5" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G24">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>131152</v>
       </c>
@@ -1111,8 +1186,11 @@
       <c r="F25" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G25">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>131153</v>
       </c>
@@ -1131,8 +1209,11 @@
       <c r="F26" s="5" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G26">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>131700</v>
       </c>
@@ -1151,8 +1232,11 @@
       <c r="F27" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G27">
+        <v>6.15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>131701</v>
       </c>
@@ -1171,8 +1255,11 @@
       <c r="F28" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G28">
+        <v>6.15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>132150</v>
       </c>
@@ -1191,8 +1278,11 @@
       <c r="F29" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G29">
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>132151</v>
       </c>
@@ -1211,8 +1301,11 @@
       <c r="F30" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G30">
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>132152</v>
       </c>
@@ -1231,8 +1324,11 @@
       <c r="F31" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G31">
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>132153</v>
       </c>
@@ -1251,8 +1347,11 @@
       <c r="F32" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G32">
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>140230</v>
       </c>
@@ -1271,8 +1370,11 @@
       <c r="F33" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G33">
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>140231</v>
       </c>
@@ -1291,8 +1393,11 @@
       <c r="F34" s="5" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G34">
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>140232</v>
       </c>
@@ -1311,8 +1416,11 @@
       <c r="F35" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G35">
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>150360</v>
       </c>
@@ -1331,8 +1439,11 @@
       <c r="F36" s="5" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G36">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>150361</v>
       </c>
@@ -1351,8 +1462,11 @@
       <c r="F37" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G37">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>150362</v>
       </c>
@@ -1371,8 +1485,11 @@
       <c r="F38" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G38">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>150363</v>
       </c>
@@ -1391,8 +1508,11 @@
       <c r="F39" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G39">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>151500</v>
       </c>
@@ -1411,8 +1531,11 @@
       <c r="F40" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G40">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>151501</v>
       </c>
@@ -1431,8 +1554,11 @@
       <c r="F41" s="5" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G41">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>151502</v>
       </c>
@@ -1451,8 +1577,11 @@
       <c r="F42" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G42">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>151503</v>
       </c>
@@ -1471,8 +1600,11 @@
       <c r="F43" s="5" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G43">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>96</v>
       </c>
@@ -1491,8 +1623,11 @@
       <c r="F44" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G44">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>96</v>
       </c>
@@ -1510,6 +1645,9 @@
       </c>
       <c r="F45" s="5" t="s">
         <v>98</v>
+      </c>
+      <c r="G45">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68FAF54-191E-4593-9235-A5C5A66A94D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E4125CC-6BA8-4566-8E02-20255DDEA9EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1414,7 +1414,7 @@
         <v>82</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G35">
         <v>1.1599999999999999</v>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E4125CC-6BA8-4566-8E02-20255DDEA9EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B6219D1-5575-425A-85B3-88ACD6C2F800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="58">
   <si>
     <t>REFERENCIA INTERNA</t>
   </si>
@@ -67,9 +67,6 @@
     <t>Cremosillo Tradicional 1000g</t>
   </si>
   <si>
-    <t>30.77%</t>
-  </si>
-  <si>
     <t>Gelatina Saltarina Fresa 130g</t>
   </si>
   <si>
@@ -184,148 +181,22 @@
     <t>Ventas Junio y transcurso de ventas Julio.pdf</t>
   </si>
   <si>
-    <t>31.55%</t>
-  </si>
-  <si>
-    <t>38.33%</t>
-  </si>
-  <si>
-    <t>25.52%</t>
-  </si>
-  <si>
-    <t>38.89%</t>
-  </si>
-  <si>
-    <t>6.35%</t>
-  </si>
-  <si>
-    <t>8.65%</t>
-  </si>
-  <si>
-    <t>3.07%</t>
-  </si>
-  <si>
-    <t>10.87%</t>
-  </si>
-  <si>
-    <t>0.27%</t>
-  </si>
-  <si>
-    <t>3.32%</t>
-  </si>
-  <si>
-    <t>9.19%</t>
-  </si>
-  <si>
-    <t>4.53%</t>
-  </si>
-  <si>
-    <t>0.33%</t>
-  </si>
-  <si>
-    <t>-5.84%</t>
-  </si>
-  <si>
-    <t>11.24%</t>
-  </si>
-  <si>
-    <t>82.00%</t>
-  </si>
-  <si>
-    <t>17.37%</t>
-  </si>
-  <si>
-    <t>22.88%</t>
-  </si>
-  <si>
-    <t>-67.44%</t>
-  </si>
-  <si>
-    <t>9.09%</t>
-  </si>
-  <si>
-    <t>-24.49%</t>
-  </si>
-  <si>
-    <t>-13.90%</t>
-  </si>
-  <si>
-    <t>1.40%</t>
-  </si>
-  <si>
-    <t>-16.92%</t>
-  </si>
-  <si>
-    <t>13.73%</t>
-  </si>
-  <si>
-    <t>16.07%</t>
-  </si>
-  <si>
-    <t>18.98%</t>
-  </si>
-  <si>
-    <t>-2.23%</t>
-  </si>
-  <si>
-    <t>1.67%</t>
-  </si>
-  <si>
-    <t>6.69%</t>
-  </si>
-  <si>
-    <t>29.27%</t>
-  </si>
-  <si>
-    <t>-93.02%</t>
-  </si>
-  <si>
-    <t>-2.25%</t>
-  </si>
-  <si>
     <t>Tevia Limon 360ml</t>
   </si>
   <si>
-    <t>-13.06%</t>
-  </si>
-  <si>
-    <t>19.60%</t>
-  </si>
-  <si>
-    <t>18.35%</t>
-  </si>
-  <si>
-    <t>38.53%</t>
-  </si>
-  <si>
     <t>Tevia Limon 1.5L</t>
   </si>
   <si>
-    <t>37.50%</t>
-  </si>
-  <si>
     <t>Tevia Durazno 1.5 L</t>
   </si>
   <si>
-    <t>-25.61%</t>
-  </si>
-  <si>
     <t>Tevia Blueberry 1.5 L</t>
   </si>
   <si>
-    <t>44.74%</t>
-  </si>
-  <si>
     <t>Tevia Tropical Punch 1.5 L</t>
   </si>
   <si>
-    <t>-16.22%</t>
-  </si>
-  <si>
     <t>Not in source</t>
-  </si>
-  <si>
-    <t>0.00%</t>
   </si>
   <si>
     <t>SUBIÓ</t>
@@ -341,7 +212,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="171" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -351,6 +225,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -380,21 +261,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -634,8 +518,8 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>100</v>
+      <c r="G1" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -645,17 +529,17 @@
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2">
-        <v>821</v>
-      </c>
-      <c r="D2" s="4">
-        <v>1080</v>
-      </c>
-      <c r="E2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>98</v>
+      <c r="C2" s="5">
+        <v>1045.090909090909</v>
+      </c>
+      <c r="D2" s="5">
+        <v>1065.5</v>
+      </c>
+      <c r="E2" s="6">
+        <v>1.9528531663187243E-2</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="G2">
         <v>1.36</v>
@@ -668,17 +552,17 @@
       <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3">
-        <v>60</v>
-      </c>
-      <c r="D3">
-        <v>83</v>
-      </c>
-      <c r="E3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>98</v>
+      <c r="C3" s="5">
+        <v>75.954545454545453</v>
+      </c>
+      <c r="D3" s="5">
+        <v>76.75</v>
+      </c>
+      <c r="E3" s="6">
+        <v>1.0472770795930675E-2</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="G3">
         <v>1.59</v>
@@ -691,17 +575,17 @@
       <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C4">
-        <v>384</v>
-      </c>
-      <c r="D4">
-        <v>482</v>
-      </c>
-      <c r="E4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>98</v>
+      <c r="C4" s="5">
+        <v>488.77272727272725</v>
+      </c>
+      <c r="D4" s="5">
+        <v>469.5</v>
+      </c>
+      <c r="E4" s="6">
+        <v>-3.9430856505161316E-2</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G4">
         <v>2.0299999999999998</v>
@@ -714,17 +598,17 @@
       <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="C5">
-        <v>72</v>
-      </c>
-      <c r="D5">
-        <v>100</v>
-      </c>
-      <c r="E5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>98</v>
+      <c r="C5" s="5">
+        <v>91.36363636363636</v>
+      </c>
+      <c r="D5" s="5">
+        <v>91.25</v>
+      </c>
+      <c r="E5" s="6">
+        <v>-1.2437810945272743E-3</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G5">
         <v>3.61</v>
@@ -737,17 +621,17 @@
       <c r="B6" t="s">
         <v>10</v>
       </c>
-      <c r="C6">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>17</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>98</v>
+      <c r="C6" s="5">
+        <v>15.954545454545455</v>
+      </c>
+      <c r="D6" s="5">
+        <v>15.75</v>
+      </c>
+      <c r="E6" s="6">
+        <v>-1.2820512820512886E-2</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G6">
         <v>8.7799999999999994</v>
@@ -758,19 +642,19 @@
         <v>120130</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="4">
-        <v>1133</v>
-      </c>
-      <c r="D7" s="4">
-        <v>1205</v>
-      </c>
-      <c r="E7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>98</v>
+        <v>11</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1441.409090909091</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1124.375</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.21994733688625401</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G7">
         <v>0.63</v>
@@ -781,19 +665,19 @@
         <v>120131</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8">
-        <v>104</v>
-      </c>
-      <c r="D8">
-        <v>113</v>
-      </c>
-      <c r="E8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>98</v>
+        <v>12</v>
+      </c>
+      <c r="C8" s="5">
+        <v>132.90909090909091</v>
+      </c>
+      <c r="D8" s="5">
+        <v>105.25</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-0.20810533515731877</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G8">
         <v>0.63</v>
@@ -804,19 +688,19 @@
         <v>120132</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9">
-        <v>261</v>
-      </c>
-      <c r="D9">
-        <v>269</v>
-      </c>
-      <c r="E9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>98</v>
+        <v>13</v>
+      </c>
+      <c r="C9" s="5">
+        <v>332.59090909090907</v>
+      </c>
+      <c r="D9" s="5">
+        <v>255</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-0.23329233292332918</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G9">
         <v>0.63</v>
@@ -827,19 +711,19 @@
         <v>130150</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10">
-        <v>561</v>
-      </c>
-      <c r="D10">
-        <v>622</v>
-      </c>
-      <c r="E10" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>98</v>
+        <v>14</v>
+      </c>
+      <c r="C10" s="5">
+        <v>713.77272727272725</v>
+      </c>
+      <c r="D10" s="5">
+        <v>569</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-0.20282748519391192</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G10">
         <v>1.0900000000000001</v>
@@ -850,19 +734,19 @@
         <v>130151</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11">
-        <v>376</v>
-      </c>
-      <c r="D11">
-        <v>377</v>
-      </c>
-      <c r="E11" t="s">
-        <v>58</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>98</v>
+        <v>15</v>
+      </c>
+      <c r="C11" s="5">
+        <v>478.40909090909093</v>
+      </c>
+      <c r="D11" s="5">
+        <v>334.25</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-0.30133016627078391</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G11">
         <v>1.0900000000000001</v>
@@ -873,19 +757,19 @@
         <v>130152</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="4">
-        <v>2744</v>
-      </c>
-      <c r="D12" s="4">
-        <v>2835</v>
-      </c>
-      <c r="E12" t="s">
-        <v>59</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>98</v>
+        <v>16</v>
+      </c>
+      <c r="C12" s="5">
+        <v>3492.9545454545455</v>
+      </c>
+      <c r="D12" s="5">
+        <v>2759.875</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-0.20987377187845668</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G12">
         <v>1.1599999999999999</v>
@@ -896,19 +780,19 @@
         <v>130153</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="4">
-        <v>1752</v>
-      </c>
-      <c r="D13" s="4">
-        <v>1913</v>
-      </c>
-      <c r="E13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>98</v>
+        <v>17</v>
+      </c>
+      <c r="C13" s="5">
+        <v>2229.7272727272725</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1883.375</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-0.15533391772332528</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G13">
         <v>1.1599999999999999</v>
@@ -919,19 +803,19 @@
         <v>130154</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="4">
-        <v>1812</v>
-      </c>
-      <c r="D14" s="4">
-        <v>1894</v>
-      </c>
-      <c r="E14" t="s">
-        <v>61</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>98</v>
+        <v>18</v>
+      </c>
+      <c r="C14" s="5">
+        <v>2305.9545454545455</v>
+      </c>
+      <c r="D14" s="5">
+        <v>1856.125</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-0.19507303226823836</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G14">
         <v>1.1599999999999999</v>
@@ -942,19 +826,19 @@
         <v>130155</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="4">
-        <v>2128</v>
-      </c>
-      <c r="D15" s="4">
-        <v>2135</v>
-      </c>
-      <c r="E15" t="s">
-        <v>62</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>98</v>
+        <v>19</v>
+      </c>
+      <c r="C15" s="5">
+        <v>2708.2272727272725</v>
+      </c>
+      <c r="D15" s="5">
+        <v>2025.625</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.25204763263456464</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G15">
         <v>1.1599999999999999</v>
@@ -965,19 +849,19 @@
         <v>130156</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16">
-        <v>137</v>
-      </c>
-      <c r="D16">
-        <v>129</v>
-      </c>
-      <c r="E16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>99</v>
+        <v>20</v>
+      </c>
+      <c r="C16" s="5">
+        <v>174.04545454545453</v>
+      </c>
+      <c r="D16" s="5">
+        <v>113</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-0.35074431966570896</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G16">
         <v>1.1599999999999999</v>
@@ -988,19 +872,19 @@
         <v>130700</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17">
-        <v>169</v>
-      </c>
-      <c r="D17">
-        <v>188</v>
-      </c>
-      <c r="E17" t="s">
-        <v>64</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>98</v>
+        <v>21</v>
+      </c>
+      <c r="C17" s="5">
+        <v>214.59090909090909</v>
+      </c>
+      <c r="D17" s="5">
+        <v>169.5</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-0.21012497352255877</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G17">
         <v>3.68</v>
@@ -1011,19 +895,19 @@
         <v>130701</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18">
-        <v>100</v>
-      </c>
-      <c r="D18">
-        <v>182</v>
-      </c>
-      <c r="E18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>98</v>
+        <v>22</v>
+      </c>
+      <c r="C18" s="5">
+        <v>127.22727272727273</v>
+      </c>
+      <c r="D18" s="5">
+        <v>164.375</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.29197927831368342</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="G18">
         <v>3.68</v>
@@ -1034,19 +918,19 @@
         <v>130702</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19">
-        <v>380</v>
-      </c>
-      <c r="D19">
-        <v>446</v>
-      </c>
-      <c r="E19" t="s">
-        <v>66</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>98</v>
+        <v>23</v>
+      </c>
+      <c r="C19" s="5">
+        <v>484.18181818181819</v>
+      </c>
+      <c r="D19" s="5">
+        <v>412.25</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-0.14856365001877581</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G19">
         <v>4.1500000000000004</v>
@@ -1057,19 +941,19 @@
         <v>130703</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20">
-        <v>612</v>
-      </c>
-      <c r="D20">
-        <v>752</v>
-      </c>
-      <c r="E20" t="s">
-        <v>67</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>98</v>
+        <v>24</v>
+      </c>
+      <c r="C20" s="5">
+        <v>778.81818181818187</v>
+      </c>
+      <c r="D20" s="5">
+        <v>685</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-0.12046223882339213</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G20">
         <v>4.1500000000000004</v>
@@ -1080,19 +964,19 @@
         <v>130704</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21">
-        <v>43</v>
-      </c>
-      <c r="D21">
-        <v>14</v>
-      </c>
-      <c r="E21" t="s">
-        <v>68</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>99</v>
+        <v>25</v>
+      </c>
+      <c r="C21" s="5">
+        <v>54.772727272727273</v>
+      </c>
+      <c r="D21" s="5">
+        <v>12.625</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-0.76950207468879672</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G21">
         <v>4.1500000000000004</v>
@@ -1103,19 +987,19 @@
         <v>130707</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22">
-        <v>33</v>
-      </c>
-      <c r="D22">
-        <v>36</v>
-      </c>
-      <c r="E22" t="s">
-        <v>69</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>98</v>
+        <v>26</v>
+      </c>
+      <c r="C22" s="5">
+        <v>41.590909090909093</v>
+      </c>
+      <c r="D22" s="5">
+        <v>31.25</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-0.24863387978142082</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G22">
         <v>4.1500000000000004</v>
@@ -1126,19 +1010,19 @@
         <v>131150</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23">
-        <v>682</v>
-      </c>
-      <c r="D23">
-        <v>515</v>
-      </c>
-      <c r="E23" t="s">
-        <v>70</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>99</v>
+        <v>27</v>
+      </c>
+      <c r="C23" s="5">
+        <v>867.86363636363637</v>
+      </c>
+      <c r="D23" s="5">
+        <v>557</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-0.35819410255067308</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G23">
         <v>1.63</v>
@@ -1149,19 +1033,19 @@
         <v>131151</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="4">
-        <v>1086</v>
-      </c>
-      <c r="D24">
-        <v>935</v>
-      </c>
-      <c r="E24" t="s">
-        <v>71</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>99</v>
+        <v>28</v>
+      </c>
+      <c r="C24" s="5">
+        <v>1382.5454545454545</v>
+      </c>
+      <c r="D24" s="5">
+        <v>934.125</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-0.32434409521304575</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G24">
         <v>1.63</v>
@@ -1172,19 +1056,19 @@
         <v>131152</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
-      </c>
-      <c r="C25">
-        <v>429</v>
-      </c>
-      <c r="D25">
-        <v>435</v>
-      </c>
-      <c r="E25" t="s">
-        <v>72</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>98</v>
+        <v>29</v>
+      </c>
+      <c r="C25" s="5">
+        <v>545.59090909090912</v>
+      </c>
+      <c r="D25" s="5">
+        <v>401.5</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-0.26410064150629009</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G25">
         <v>1.63</v>
@@ -1195,19 +1079,19 @@
         <v>131153</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
-      </c>
-      <c r="C26">
-        <v>396</v>
-      </c>
-      <c r="D26">
-        <v>329</v>
-      </c>
-      <c r="E26" t="s">
-        <v>73</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>99</v>
+        <v>30</v>
+      </c>
+      <c r="C26" s="5">
+        <v>504</v>
+      </c>
+      <c r="D26" s="5">
+        <v>305.75</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-0.39335317460317465</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G26">
         <v>1.63</v>
@@ -1218,19 +1102,19 @@
         <v>131700</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27">
-        <v>102</v>
-      </c>
-      <c r="D27">
-        <v>116</v>
-      </c>
-      <c r="E27" t="s">
-        <v>74</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>98</v>
+        <v>31</v>
+      </c>
+      <c r="C27" s="5">
+        <v>130.27272727272728</v>
+      </c>
+      <c r="D27" s="5">
+        <v>104.125</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-0.20071528262386606</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G27">
         <v>6.15</v>
@@ -1241,19 +1125,19 @@
         <v>131701</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
-      </c>
-      <c r="C28">
-        <v>112</v>
-      </c>
-      <c r="D28">
-        <v>130</v>
-      </c>
-      <c r="E28" t="s">
-        <v>75</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>98</v>
+        <v>32</v>
+      </c>
+      <c r="C28" s="5">
+        <v>142.77272727272728</v>
+      </c>
+      <c r="D28" s="5">
+        <v>116.875</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-0.18139127666348298</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G28">
         <v>6.15</v>
@@ -1264,19 +1148,19 @@
         <v>132150</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
-      </c>
-      <c r="C29">
-        <v>669</v>
-      </c>
-      <c r="D29">
-        <v>796</v>
-      </c>
-      <c r="E29" t="s">
-        <v>76</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>98</v>
+        <v>33</v>
+      </c>
+      <c r="C29" s="5">
+        <v>851.81818181818187</v>
+      </c>
+      <c r="D29" s="5">
+        <v>727.5</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-0.14594450373532553</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G29">
         <v>1.1599999999999999</v>
@@ -1287,19 +1171,19 @@
         <v>132151</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30">
-        <v>674</v>
-      </c>
-      <c r="D30">
-        <v>659</v>
-      </c>
-      <c r="E30" t="s">
-        <v>77</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>98</v>
+        <v>34</v>
+      </c>
+      <c r="C30" s="5">
+        <v>857.40909090909088</v>
+      </c>
+      <c r="D30" s="5">
+        <v>607.25</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-0.29176164979059527</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G30">
         <v>1.1599999999999999</v>
@@ -1310,19 +1194,19 @@
         <v>132152</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
-      </c>
-      <c r="C31">
-        <v>839</v>
-      </c>
-      <c r="D31">
-        <v>853</v>
-      </c>
-      <c r="E31" t="s">
-        <v>78</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>98</v>
+        <v>35</v>
+      </c>
+      <c r="C31" s="5">
+        <v>1067.7272727272727</v>
+      </c>
+      <c r="D31" s="5">
+        <v>788.125</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-0.26186675180928054</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G31">
         <v>1.1599999999999999</v>
@@ -1333,19 +1217,19 @@
         <v>132153</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
-      </c>
-      <c r="C32">
-        <v>538</v>
-      </c>
-      <c r="D32">
-        <v>574</v>
-      </c>
-      <c r="E32" t="s">
-        <v>79</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>98</v>
+        <v>36</v>
+      </c>
+      <c r="C32" s="5">
+        <v>685.09090909090912</v>
+      </c>
+      <c r="D32" s="5">
+        <v>521.5</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-0.2387871549893843</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G32">
         <v>1.1599999999999999</v>
@@ -1356,19 +1240,19 @@
         <v>140230</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
-      </c>
-      <c r="C33">
-        <v>164</v>
-      </c>
-      <c r="D33">
-        <v>212</v>
-      </c>
-      <c r="E33" t="s">
-        <v>80</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>98</v>
+        <v>37</v>
+      </c>
+      <c r="C33" s="5">
+        <v>208.72727272727272</v>
+      </c>
+      <c r="D33" s="5">
+        <v>189.375</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-9.2715592334494779E-2</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G33">
         <v>1.1599999999999999</v>
@@ -1379,19 +1263,19 @@
         <v>140231</v>
       </c>
       <c r="B34" t="s">
-        <v>39</v>
-      </c>
-      <c r="C34">
-        <v>401</v>
-      </c>
-      <c r="D34">
-        <v>28</v>
-      </c>
-      <c r="E34" t="s">
-        <v>81</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>99</v>
+        <v>38</v>
+      </c>
+      <c r="C34" s="5">
+        <v>510.77272727272725</v>
+      </c>
+      <c r="D34" s="5">
+        <v>24.375</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-0.95227818812850407</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G34">
         <v>1.1599999999999999</v>
@@ -1402,19 +1286,19 @@
         <v>140232</v>
       </c>
       <c r="B35" t="s">
-        <v>40</v>
-      </c>
-      <c r="C35">
-        <v>355</v>
-      </c>
-      <c r="D35">
-        <v>347</v>
-      </c>
-      <c r="E35" t="s">
-        <v>82</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>99</v>
+        <v>39</v>
+      </c>
+      <c r="C35" s="5">
+        <v>452.40909090909093</v>
+      </c>
+      <c r="D35" s="5">
+        <v>319.375</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-0.29405706822063704</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G35">
         <v>1.1599999999999999</v>
@@ -1425,19 +1309,19 @@
         <v>150360</v>
       </c>
       <c r="B36" t="s">
-        <v>83</v>
-      </c>
-      <c r="C36">
-        <v>268</v>
-      </c>
-      <c r="D36">
-        <v>233</v>
-      </c>
-      <c r="E36" t="s">
-        <v>84</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>99</v>
+        <v>49</v>
+      </c>
+      <c r="C36" s="5">
+        <v>340.90909090909093</v>
+      </c>
+      <c r="D36" s="5">
+        <v>213.375</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-0.3741000000000001</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G36">
         <v>0.81</v>
@@ -1448,19 +1332,19 @@
         <v>150361</v>
       </c>
       <c r="B37" t="s">
-        <v>41</v>
-      </c>
-      <c r="C37">
-        <v>398</v>
-      </c>
-      <c r="D37">
-        <v>476</v>
-      </c>
-      <c r="E37" t="s">
-        <v>85</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>98</v>
+        <v>40</v>
+      </c>
+      <c r="C37" s="5">
+        <v>506.36363636363637</v>
+      </c>
+      <c r="D37" s="5">
+        <v>430</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-0.15080789946140039</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G37">
         <v>0.81</v>
@@ -1471,19 +1355,19 @@
         <v>150362</v>
       </c>
       <c r="B38" t="s">
-        <v>42</v>
-      </c>
-      <c r="C38">
-        <v>218</v>
-      </c>
-      <c r="D38">
-        <v>258</v>
-      </c>
-      <c r="E38" t="s">
-        <v>86</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>98</v>
+        <v>41</v>
+      </c>
+      <c r="C38" s="5">
+        <v>277.18181818181819</v>
+      </c>
+      <c r="D38" s="5">
+        <v>230.875</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-0.16706297146605442</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G38">
         <v>0.81</v>
@@ -1494,19 +1378,19 @@
         <v>150363</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
-      </c>
-      <c r="C39">
-        <v>231</v>
-      </c>
-      <c r="D39">
-        <v>320</v>
-      </c>
-      <c r="E39" t="s">
-        <v>87</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>98</v>
+        <v>42</v>
+      </c>
+      <c r="C39" s="5">
+        <v>294.59090909090907</v>
+      </c>
+      <c r="D39" s="5">
+        <v>286.125</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-2.8737849097361434E-2</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G39">
         <v>0.81</v>
@@ -1517,19 +1401,19 @@
         <v>151500</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
-      </c>
-      <c r="C40">
-        <v>56</v>
-      </c>
-      <c r="D40">
-        <v>77</v>
-      </c>
-      <c r="E40" t="s">
-        <v>89</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>98</v>
+        <v>50</v>
+      </c>
+      <c r="C40" s="5">
+        <v>71.454545454545453</v>
+      </c>
+      <c r="D40" s="5">
+        <v>67.125</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-6.0591603053435139E-2</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G40">
         <v>2.62</v>
@@ -1540,19 +1424,19 @@
         <v>151501</v>
       </c>
       <c r="B41" t="s">
-        <v>90</v>
-      </c>
-      <c r="C41">
-        <v>82</v>
-      </c>
-      <c r="D41">
-        <v>61</v>
-      </c>
-      <c r="E41" t="s">
-        <v>91</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>99</v>
+        <v>51</v>
+      </c>
+      <c r="C41" s="5">
+        <v>104.59090909090909</v>
+      </c>
+      <c r="D41" s="5">
+        <v>55.625</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-0.46816601477618425</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G41">
         <v>2.62</v>
@@ -1563,19 +1447,19 @@
         <v>151502</v>
       </c>
       <c r="B42" t="s">
-        <v>92</v>
-      </c>
-      <c r="C42">
-        <v>38</v>
-      </c>
-      <c r="D42">
-        <v>55</v>
-      </c>
-      <c r="E42" t="s">
-        <v>93</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>98</v>
+        <v>52</v>
+      </c>
+      <c r="C42" s="5">
+        <v>48.68181818181818</v>
+      </c>
+      <c r="D42" s="5">
+        <v>47.75</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-1.9140989729224955E-2</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G42">
         <v>2.62</v>
@@ -1586,19 +1470,19 @@
         <v>151503</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
-      </c>
-      <c r="C43">
-        <v>37</v>
-      </c>
-      <c r="D43">
-        <v>31</v>
-      </c>
-      <c r="E43" t="s">
-        <v>95</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>99</v>
+        <v>53</v>
+      </c>
+      <c r="C43" s="5">
+        <v>47.636363636363633</v>
+      </c>
+      <c r="D43" s="5">
+        <v>27.75</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-0.41746183206106868</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G43">
         <v>2.62</v>
@@ -1606,22 +1490,22 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
-      </c>
-      <c r="C44">
-        <v>0</v>
-      </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-      <c r="E44" t="s">
-        <v>97</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>98</v>
+        <v>43</v>
+      </c>
+      <c r="C44" s="5">
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="D44" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-8.3333333333333259E-2</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G44">
         <v>18</v>
@@ -1629,22 +1513,22 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
-      </c>
-      <c r="C45">
-        <v>2</v>
-      </c>
-      <c r="D45">
-        <v>2</v>
-      </c>
-      <c r="E45" t="s">
-        <v>97</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>98</v>
+        <v>44</v>
+      </c>
+      <c r="C45" s="5">
+        <v>2.7727272727272698</v>
+      </c>
+      <c r="D45" s="5">
+        <v>3.125</v>
+      </c>
+      <c r="E45" s="6">
+        <v>0.12704918032786994</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="G45">
         <v>18</v>
@@ -1665,18 +1549,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B6219D1-5575-425A-85B3-88ACD6C2F800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F272887-5432-4171-AA76-930E8D85B448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -213,13 +213,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="171" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -238,21 +245,31 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F9FA"/>
+        <bgColor rgb="FFF8F9FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -260,25 +277,45 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE0E0E0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{6A46E9E3-F881-4AFA-9613-5EAED1E58279}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -506,13 +543,13 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -530,13 +567,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="5">
-        <v>1045.090909090909</v>
+        <v>1045</v>
       </c>
       <c r="D2" s="5">
-        <v>1065.5</v>
+        <v>1066</v>
       </c>
       <c r="E2" s="6">
-        <v>1.9528531663187243E-2</v>
+        <v>1.9528531660000001E-2</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>55</v>
@@ -553,13 +590,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="5">
-        <v>75.954545454545453</v>
+        <v>76</v>
       </c>
       <c r="D3" s="5">
-        <v>76.75</v>
-      </c>
-      <c r="E3" s="6">
-        <v>1.0472770795930675E-2</v>
+        <v>77</v>
+      </c>
+      <c r="E3" s="7">
+        <v>1.04727708E-2</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>55</v>
@@ -576,13 +613,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="5">
-        <v>488.77272727272725</v>
+        <v>489</v>
       </c>
       <c r="D4" s="5">
-        <v>469.5</v>
+        <v>470</v>
       </c>
       <c r="E4" s="6">
-        <v>-3.9430856505161316E-2</v>
+        <v>-3.9430856510000001E-2</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>56</v>
@@ -599,13 +636,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="5">
-        <v>91.36363636363636</v>
+        <v>91</v>
       </c>
       <c r="D5" s="5">
-        <v>91.25</v>
-      </c>
-      <c r="E5" s="6">
-        <v>-1.2437810945272743E-3</v>
+        <v>91</v>
+      </c>
+      <c r="E5" s="7">
+        <v>-1.2437810900000001E-3</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>56</v>
@@ -622,13 +659,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="5">
-        <v>15.954545454545455</v>
+        <v>16</v>
       </c>
       <c r="D6" s="5">
-        <v>15.75</v>
+        <v>16</v>
       </c>
       <c r="E6" s="6">
-        <v>-1.2820512820512886E-2</v>
+        <v>-1.2820512819999999E-2</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>56</v>
@@ -645,13 +682,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="5">
-        <v>1441.409090909091</v>
+        <v>1441</v>
       </c>
       <c r="D7" s="5">
-        <v>1124.375</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-0.21994733688625401</v>
+        <v>1124</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.21994733689000001</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>56</v>
@@ -668,13 +705,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="5">
-        <v>132.90909090909091</v>
+        <v>133</v>
       </c>
       <c r="D8" s="5">
-        <v>105.25</v>
+        <v>105</v>
       </c>
       <c r="E8" s="6">
-        <v>-0.20810533515731877</v>
+        <v>-0.20810533515999999</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>56</v>
@@ -691,13 +728,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="5">
-        <v>332.59090909090907</v>
+        <v>333</v>
       </c>
       <c r="D9" s="5">
         <v>255</v>
       </c>
-      <c r="E9" s="6">
-        <v>-0.23329233292332918</v>
+      <c r="E9" s="7">
+        <v>-0.23329233292000001</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>56</v>
@@ -714,13 +751,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="5">
-        <v>713.77272727272725</v>
+        <v>714</v>
       </c>
       <c r="D10" s="5">
         <v>569</v>
       </c>
       <c r="E10" s="6">
-        <v>-0.20282748519391192</v>
+        <v>-0.20282874814999999</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>56</v>
@@ -737,13 +774,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="5">
-        <v>478.40909090909093</v>
+        <v>478</v>
       </c>
       <c r="D11" s="5">
-        <v>334.25</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-0.30133016627078391</v>
+        <v>334</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.30133016626999998</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>56</v>
@@ -760,13 +797,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="5">
-        <v>3492.9545454545455</v>
+        <v>3493</v>
       </c>
       <c r="D12" s="5">
-        <v>2759.875</v>
+        <v>2760</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.20987377187845668</v>
+        <v>-0.20987377188</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>56</v>
@@ -783,13 +820,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="5">
-        <v>2229.7272727272725</v>
+        <v>2230</v>
       </c>
       <c r="D13" s="5">
-        <v>1883.375</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-0.15533391772332528</v>
+        <v>1883</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.15533391771999999</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>56</v>
@@ -806,13 +843,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="5">
-        <v>2305.9545454545455</v>
+        <v>2306</v>
       </c>
       <c r="D14" s="5">
-        <v>1856.125</v>
+        <v>1856</v>
       </c>
       <c r="E14" s="6">
-        <v>-0.19507303226823836</v>
+        <v>-0.15907303227</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>56</v>
@@ -829,13 +866,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="5">
-        <v>2708.2272727272725</v>
+        <v>2708</v>
       </c>
       <c r="D15" s="5">
-        <v>2025.625</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-0.25204763263456464</v>
+        <v>2026</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.25204763263000002</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>56</v>
@@ -852,13 +889,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="5">
-        <v>174.04545454545453</v>
+        <v>174</v>
       </c>
       <c r="D16" s="5">
         <v>113</v>
       </c>
       <c r="E16" s="6">
-        <v>-0.35074431966570896</v>
+        <v>-0.35074431967000003</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>56</v>
@@ -875,13 +912,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="5">
-        <v>214.59090909090909</v>
+        <v>215</v>
       </c>
       <c r="D17" s="5">
-        <v>169.5</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-0.21012497352255877</v>
+        <v>170</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.21012497352000001</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>56</v>
@@ -898,13 +935,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="5">
-        <v>127.22727272727273</v>
+        <v>127</v>
       </c>
       <c r="D18" s="5">
-        <v>164.375</v>
+        <v>164</v>
       </c>
       <c r="E18" s="6">
-        <v>0.29197927831368342</v>
+        <v>0.29197927830999998</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>55</v>
@@ -921,13 +958,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="5">
-        <v>484.18181818181819</v>
+        <v>484</v>
       </c>
       <c r="D19" s="5">
-        <v>412.25</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-0.14856365001877581</v>
+        <v>412</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.14856365001999999</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>56</v>
@@ -944,13 +981,13 @@
         <v>24</v>
       </c>
       <c r="C20" s="5">
-        <v>778.81818181818187</v>
+        <v>779</v>
       </c>
       <c r="D20" s="5">
         <v>685</v>
       </c>
       <c r="E20" s="6">
-        <v>-0.12046223882339213</v>
+        <v>-0.12046223882</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>56</v>
@@ -967,13 +1004,13 @@
         <v>25</v>
       </c>
       <c r="C21" s="5">
-        <v>54.772727272727273</v>
+        <v>55</v>
       </c>
       <c r="D21" s="5">
-        <v>12.625</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-0.76950207468879672</v>
+        <v>13</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.76950207468999998</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>56</v>
@@ -990,13 +1027,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="5">
-        <v>41.590909090909093</v>
+        <v>42</v>
       </c>
       <c r="D22" s="5">
-        <v>31.25</v>
+        <v>31</v>
       </c>
       <c r="E22" s="6">
-        <v>-0.24863387978142082</v>
+        <v>-0.24863387978000001</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>56</v>
@@ -1013,13 +1050,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="5">
-        <v>867.86363636363637</v>
+        <v>868</v>
       </c>
       <c r="D23" s="5">
         <v>557</v>
       </c>
-      <c r="E23" s="6">
-        <v>-0.35819410255067308</v>
+      <c r="E23" s="7">
+        <v>-0.35819410255</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>56</v>
@@ -1036,13 +1073,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="5">
-        <v>1382.5454545454545</v>
+        <v>1383</v>
       </c>
       <c r="D24" s="5">
-        <v>934.125</v>
+        <v>934</v>
       </c>
       <c r="E24" s="6">
-        <v>-0.32434409521304575</v>
+        <v>-0.32434440951999999</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>56</v>
@@ -1059,13 +1096,13 @@
         <v>29</v>
       </c>
       <c r="C25" s="5">
-        <v>545.59090909090912</v>
+        <v>546</v>
       </c>
       <c r="D25" s="5">
-        <v>401.5</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-0.26410064150629009</v>
+        <v>402</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.26410064151000001</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>56</v>
@@ -1085,10 +1122,10 @@
         <v>504</v>
       </c>
       <c r="D26" s="5">
-        <v>305.75</v>
+        <v>306</v>
       </c>
       <c r="E26" s="6">
-        <v>-0.39335317460317465</v>
+        <v>-0.39335317460000002</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>56</v>
@@ -1105,13 +1142,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="5">
-        <v>130.27272727272728</v>
+        <v>130</v>
       </c>
       <c r="D27" s="5">
-        <v>104.125</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-0.20071528262386606</v>
+        <v>104</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.20071528261999999</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>56</v>
@@ -1128,13 +1165,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="5">
-        <v>142.77272727272728</v>
+        <v>143</v>
       </c>
       <c r="D28" s="5">
-        <v>116.875</v>
+        <v>117</v>
       </c>
       <c r="E28" s="6">
-        <v>-0.18139127666348298</v>
+        <v>-0.18319127666000001</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>56</v>
@@ -1151,13 +1188,13 @@
         <v>33</v>
       </c>
       <c r="C29" s="5">
-        <v>851.81818181818187</v>
+        <v>852</v>
       </c>
       <c r="D29" s="5">
-        <v>727.5</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-0.14594450373532553</v>
+        <v>728</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.14594450374000001</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>56</v>
@@ -1174,13 +1211,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="5">
-        <v>857.40909090909088</v>
+        <v>857</v>
       </c>
       <c r="D30" s="5">
-        <v>607.25</v>
+        <v>607</v>
       </c>
       <c r="E30" s="6">
-        <v>-0.29176164979059527</v>
+        <v>-0.29176164979000002</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>56</v>
@@ -1197,13 +1234,13 @@
         <v>35</v>
       </c>
       <c r="C31" s="5">
-        <v>1067.7272727272727</v>
+        <v>1068</v>
       </c>
       <c r="D31" s="5">
-        <v>788.125</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-0.26186675180928054</v>
+        <v>788</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.26186675181000002</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>56</v>
@@ -1220,13 +1257,13 @@
         <v>36</v>
       </c>
       <c r="C32" s="5">
-        <v>685.09090909090912</v>
+        <v>685</v>
       </c>
       <c r="D32" s="5">
-        <v>521.5</v>
+        <v>522</v>
       </c>
       <c r="E32" s="6">
-        <v>-0.2387871549893843</v>
+        <v>-0.23878715499</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>56</v>
@@ -1243,13 +1280,13 @@
         <v>37</v>
       </c>
       <c r="C33" s="5">
-        <v>208.72727272727272</v>
+        <v>209</v>
       </c>
       <c r="D33" s="5">
-        <v>189.375</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-9.2715592334494779E-2</v>
+        <v>189</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-9.2715592329999999E-2</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>56</v>
@@ -1266,13 +1303,13 @@
         <v>38</v>
       </c>
       <c r="C34" s="5">
-        <v>510.77272727272725</v>
+        <v>511</v>
       </c>
       <c r="D34" s="5">
-        <v>24.375</v>
+        <v>24</v>
       </c>
       <c r="E34" s="6">
-        <v>-0.95227818812850407</v>
+        <v>-0.95227818812999998</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>56</v>
@@ -1289,13 +1326,13 @@
         <v>39</v>
       </c>
       <c r="C35" s="5">
-        <v>452.40909090909093</v>
+        <v>452</v>
       </c>
       <c r="D35" s="5">
-        <v>319.375</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-0.29405706822063704</v>
+        <v>319</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.29405706822</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>56</v>
@@ -1312,13 +1349,13 @@
         <v>49</v>
       </c>
       <c r="C36" s="5">
-        <v>340.90909090909093</v>
+        <v>341</v>
       </c>
       <c r="D36" s="5">
-        <v>213.375</v>
+        <v>213</v>
       </c>
       <c r="E36" s="6">
-        <v>-0.3741000000000001</v>
+        <v>-0.374</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>56</v>
@@ -1335,13 +1372,13 @@
         <v>40</v>
       </c>
       <c r="C37" s="5">
-        <v>506.36363636363637</v>
+        <v>506</v>
       </c>
       <c r="D37" s="5">
         <v>430</v>
       </c>
-      <c r="E37" s="6">
-        <v>-0.15080789946140039</v>
+      <c r="E37" s="7">
+        <v>-0.15080789946000001</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>56</v>
@@ -1358,13 +1395,13 @@
         <v>41</v>
       </c>
       <c r="C38" s="5">
-        <v>277.18181818181819</v>
+        <v>277</v>
       </c>
       <c r="D38" s="5">
-        <v>230.875</v>
+        <v>231</v>
       </c>
       <c r="E38" s="6">
-        <v>-0.16706297146605442</v>
+        <v>-0.16706297146999999</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>56</v>
@@ -1381,13 +1418,13 @@
         <v>42</v>
       </c>
       <c r="C39" s="5">
-        <v>294.59090909090907</v>
+        <v>295</v>
       </c>
       <c r="D39" s="5">
-        <v>286.125</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-2.8737849097361434E-2</v>
+        <v>286</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-2.8737849100000001E-2</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>56</v>
@@ -1404,13 +1441,13 @@
         <v>50</v>
       </c>
       <c r="C40" s="5">
-        <v>71.454545454545453</v>
+        <v>71</v>
       </c>
       <c r="D40" s="5">
-        <v>67.125</v>
+        <v>67</v>
       </c>
       <c r="E40" s="6">
-        <v>-6.0591603053435139E-2</v>
+        <v>-6.0591603049999998E-2</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>56</v>
@@ -1427,13 +1464,13 @@
         <v>51</v>
       </c>
       <c r="C41" s="5">
-        <v>104.59090909090909</v>
+        <v>105</v>
       </c>
       <c r="D41" s="5">
-        <v>55.625</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-0.46816601477618425</v>
+        <v>56</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.46816601477999997</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>56</v>
@@ -1450,13 +1487,13 @@
         <v>52</v>
       </c>
       <c r="C42" s="5">
-        <v>48.68181818181818</v>
+        <v>49</v>
       </c>
       <c r="D42" s="5">
-        <v>47.75</v>
+        <v>48</v>
       </c>
       <c r="E42" s="6">
-        <v>-1.9140989729224955E-2</v>
+        <v>-1.9140989729999999E-2</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>56</v>
@@ -1473,13 +1510,13 @@
         <v>53</v>
       </c>
       <c r="C43" s="5">
-        <v>47.636363636363633</v>
+        <v>48</v>
       </c>
       <c r="D43" s="5">
-        <v>27.75</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-0.41746183206106868</v>
+        <v>28</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-0.41746183205999998</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>56</v>
@@ -1496,13 +1533,13 @@
         <v>43</v>
       </c>
       <c r="C44" s="5">
-        <v>0.54545454545454541</v>
+        <v>1</v>
       </c>
       <c r="D44" s="5">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E44" s="6">
-        <v>-8.3333333333333259E-2</v>
+        <v>-8.3333333329999995E-2</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>56</v>
@@ -1519,13 +1556,13 @@
         <v>44</v>
       </c>
       <c r="C45" s="5">
-        <v>2.7727272727272698</v>
+        <v>3</v>
       </c>
       <c r="D45" s="5">
-        <v>3.125</v>
-      </c>
-      <c r="E45" s="6">
-        <v>0.12704918032786994</v>
+        <v>3</v>
+      </c>
+      <c r="E45" s="7">
+        <v>0.12704918033000001</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>55</v>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F272887-5432-4171-AA76-930E8D85B448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA949A48-6F04-45CD-9A82-27A06B9B13AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -573,7 +573,7 @@
         <v>1066</v>
       </c>
       <c r="E2" s="6">
-        <v>1.9528531660000001E-2</v>
+        <v>0.02</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>55</v>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA949A48-6F04-45CD-9A82-27A06B9B13AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78E1AB11-8828-4349-8FE3-7C95B72311CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="59">
   <si>
     <t>REFERENCIA INTERNA</t>
   </si>
@@ -206,6 +206,9 @@
   </si>
   <si>
     <t>PRECIO UNITARIO</t>
+  </si>
+  <si>
+    <t>2.0%</t>
   </si>
 </sst>
 </file>
@@ -572,8 +575,8 @@
       <c r="D2" s="5">
         <v>1066</v>
       </c>
-      <c r="E2" s="6">
-        <v>0.02</v>
+      <c r="E2" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>55</v>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78E1AB11-8828-4349-8FE3-7C95B72311CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{555771A8-9245-4CA0-8F61-C8811EE0D781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="101">
   <si>
     <t>REFERENCIA INTERNA</t>
   </si>
@@ -209,6 +209,132 @@
   </si>
   <si>
     <t>2.0%</t>
+  </si>
+  <si>
+    <t>1.0%</t>
+  </si>
+  <si>
+    <t>-3.9%</t>
+  </si>
+  <si>
+    <t>-0.1%</t>
+  </si>
+  <si>
+    <t>-1.3%</t>
+  </si>
+  <si>
+    <t>-22.0%</t>
+  </si>
+  <si>
+    <t>-20.8%</t>
+  </si>
+  <si>
+    <t>-23.3%</t>
+  </si>
+  <si>
+    <t>-20.3%</t>
+  </si>
+  <si>
+    <t>-30.1%</t>
+  </si>
+  <si>
+    <t>-21.0%</t>
+  </si>
+  <si>
+    <t>-15.5%</t>
+  </si>
+  <si>
+    <t>-15.9%</t>
+  </si>
+  <si>
+    <t>-25.2%</t>
+  </si>
+  <si>
+    <t>-35.1%</t>
+  </si>
+  <si>
+    <t>29.2%</t>
+  </si>
+  <si>
+    <t>-14.9%</t>
+  </si>
+  <si>
+    <t>-12.0%</t>
+  </si>
+  <si>
+    <t>-77.0%</t>
+  </si>
+  <si>
+    <t>-24.9%</t>
+  </si>
+  <si>
+    <t>-35.8%</t>
+  </si>
+  <si>
+    <t>-32.4%</t>
+  </si>
+  <si>
+    <t>-26.4%</t>
+  </si>
+  <si>
+    <t>-39.3%</t>
+  </si>
+  <si>
+    <t>-20.1%</t>
+  </si>
+  <si>
+    <t>-18.3%</t>
+  </si>
+  <si>
+    <t>-14.6%</t>
+  </si>
+  <si>
+    <t>-29.2%</t>
+  </si>
+  <si>
+    <t>-26.2%</t>
+  </si>
+  <si>
+    <t>-23.9%</t>
+  </si>
+  <si>
+    <t>-9.3%</t>
+  </si>
+  <si>
+    <t>-95.2%</t>
+  </si>
+  <si>
+    <t>-29.4%</t>
+  </si>
+  <si>
+    <t>-37.4%</t>
+  </si>
+  <si>
+    <t>-15.1%</t>
+  </si>
+  <si>
+    <t>-16.7%</t>
+  </si>
+  <si>
+    <t>-2.9%</t>
+  </si>
+  <si>
+    <t>-6.1%</t>
+  </si>
+  <si>
+    <t>-46.8%</t>
+  </si>
+  <si>
+    <t>-1.9%</t>
+  </si>
+  <si>
+    <t>-41.7%</t>
+  </si>
+  <si>
+    <t>-8.3%</t>
+  </si>
+  <si>
+    <t>12.7%</t>
   </si>
 </sst>
 </file>
@@ -598,8 +724,8 @@
       <c r="D3" s="5">
         <v>77</v>
       </c>
-      <c r="E3" s="7">
-        <v>1.04727708E-2</v>
+      <c r="E3" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>55</v>
@@ -621,8 +747,8 @@
       <c r="D4" s="5">
         <v>470</v>
       </c>
-      <c r="E4" s="6">
-        <v>-3.9430856510000001E-2</v>
+      <c r="E4" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>56</v>
@@ -644,8 +770,8 @@
       <c r="D5" s="5">
         <v>91</v>
       </c>
-      <c r="E5" s="7">
-        <v>-1.2437810900000001E-3</v>
+      <c r="E5" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>56</v>
@@ -667,8 +793,8 @@
       <c r="D6" s="5">
         <v>16</v>
       </c>
-      <c r="E6" s="6">
-        <v>-1.2820512819999999E-2</v>
+      <c r="E6" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>56</v>
@@ -690,8 +816,8 @@
       <c r="D7" s="5">
         <v>1124</v>
       </c>
-      <c r="E7" s="7">
-        <v>-0.21994733689000001</v>
+      <c r="E7" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>56</v>
@@ -713,8 +839,8 @@
       <c r="D8" s="5">
         <v>105</v>
       </c>
-      <c r="E8" s="6">
-        <v>-0.20810533515999999</v>
+      <c r="E8" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>56</v>
@@ -736,8 +862,8 @@
       <c r="D9" s="5">
         <v>255</v>
       </c>
-      <c r="E9" s="7">
-        <v>-0.23329233292000001</v>
+      <c r="E9" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>56</v>
@@ -759,8 +885,8 @@
       <c r="D10" s="5">
         <v>569</v>
       </c>
-      <c r="E10" s="6">
-        <v>-0.20282874814999999</v>
+      <c r="E10" s="6" t="s">
+        <v>66</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>56</v>
@@ -782,8 +908,8 @@
       <c r="D11" s="5">
         <v>334</v>
       </c>
-      <c r="E11" s="7">
-        <v>-0.30133016626999998</v>
+      <c r="E11" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>56</v>
@@ -805,8 +931,8 @@
       <c r="D12" s="5">
         <v>2760</v>
       </c>
-      <c r="E12" s="6">
-        <v>-0.20987377188</v>
+      <c r="E12" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>56</v>
@@ -828,8 +954,8 @@
       <c r="D13" s="5">
         <v>1883</v>
       </c>
-      <c r="E13" s="7">
-        <v>-0.15533391771999999</v>
+      <c r="E13" s="7" t="s">
+        <v>69</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>56</v>
@@ -851,8 +977,8 @@
       <c r="D14" s="5">
         <v>1856</v>
       </c>
-      <c r="E14" s="6">
-        <v>-0.15907303227</v>
+      <c r="E14" s="6" t="s">
+        <v>70</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>56</v>
@@ -874,8 +1000,8 @@
       <c r="D15" s="5">
         <v>2026</v>
       </c>
-      <c r="E15" s="7">
-        <v>-0.25204763263000002</v>
+      <c r="E15" s="7" t="s">
+        <v>71</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>56</v>
@@ -897,8 +1023,8 @@
       <c r="D16" s="5">
         <v>113</v>
       </c>
-      <c r="E16" s="6">
-        <v>-0.35074431967000003</v>
+      <c r="E16" s="6" t="s">
+        <v>72</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>56</v>
@@ -920,8 +1046,8 @@
       <c r="D17" s="5">
         <v>170</v>
       </c>
-      <c r="E17" s="7">
-        <v>-0.21012497352000001</v>
+      <c r="E17" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>56</v>
@@ -943,8 +1069,8 @@
       <c r="D18" s="5">
         <v>164</v>
       </c>
-      <c r="E18" s="6">
-        <v>0.29197927830999998</v>
+      <c r="E18" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>55</v>
@@ -966,8 +1092,8 @@
       <c r="D19" s="5">
         <v>412</v>
       </c>
-      <c r="E19" s="7">
-        <v>-0.14856365001999999</v>
+      <c r="E19" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>56</v>
@@ -989,8 +1115,8 @@
       <c r="D20" s="5">
         <v>685</v>
       </c>
-      <c r="E20" s="6">
-        <v>-0.12046223882</v>
+      <c r="E20" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>56</v>
@@ -1012,8 +1138,8 @@
       <c r="D21" s="5">
         <v>13</v>
       </c>
-      <c r="E21" s="7">
-        <v>-0.76950207468999998</v>
+      <c r="E21" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>56</v>
@@ -1035,8 +1161,8 @@
       <c r="D22" s="5">
         <v>31</v>
       </c>
-      <c r="E22" s="6">
-        <v>-0.24863387978000001</v>
+      <c r="E22" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>56</v>
@@ -1058,8 +1184,8 @@
       <c r="D23" s="5">
         <v>557</v>
       </c>
-      <c r="E23" s="7">
-        <v>-0.35819410255</v>
+      <c r="E23" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>56</v>
@@ -1081,8 +1207,8 @@
       <c r="D24" s="5">
         <v>934</v>
       </c>
-      <c r="E24" s="6">
-        <v>-0.32434440951999999</v>
+      <c r="E24" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>56</v>
@@ -1104,8 +1230,8 @@
       <c r="D25" s="5">
         <v>402</v>
       </c>
-      <c r="E25" s="7">
-        <v>-0.26410064151000001</v>
+      <c r="E25" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>56</v>
@@ -1127,8 +1253,8 @@
       <c r="D26" s="5">
         <v>306</v>
       </c>
-      <c r="E26" s="6">
-        <v>-0.39335317460000002</v>
+      <c r="E26" s="6" t="s">
+        <v>81</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>56</v>
@@ -1150,8 +1276,8 @@
       <c r="D27" s="5">
         <v>104</v>
       </c>
-      <c r="E27" s="7">
-        <v>-0.20071528261999999</v>
+      <c r="E27" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>56</v>
@@ -1173,8 +1299,8 @@
       <c r="D28" s="5">
         <v>117</v>
       </c>
-      <c r="E28" s="6">
-        <v>-0.18319127666000001</v>
+      <c r="E28" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>56</v>
@@ -1196,8 +1322,8 @@
       <c r="D29" s="5">
         <v>728</v>
       </c>
-      <c r="E29" s="7">
-        <v>-0.14594450374000001</v>
+      <c r="E29" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>56</v>
@@ -1219,8 +1345,8 @@
       <c r="D30" s="5">
         <v>607</v>
       </c>
-      <c r="E30" s="6">
-        <v>-0.29176164979000002</v>
+      <c r="E30" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>56</v>
@@ -1242,8 +1368,8 @@
       <c r="D31" s="5">
         <v>788</v>
       </c>
-      <c r="E31" s="7">
-        <v>-0.26186675181000002</v>
+      <c r="E31" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>56</v>
@@ -1265,8 +1391,8 @@
       <c r="D32" s="5">
         <v>522</v>
       </c>
-      <c r="E32" s="6">
-        <v>-0.23878715499</v>
+      <c r="E32" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>56</v>
@@ -1288,8 +1414,8 @@
       <c r="D33" s="5">
         <v>189</v>
       </c>
-      <c r="E33" s="7">
-        <v>-9.2715592329999999E-2</v>
+      <c r="E33" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>56</v>
@@ -1311,8 +1437,8 @@
       <c r="D34" s="5">
         <v>24</v>
       </c>
-      <c r="E34" s="6">
-        <v>-0.95227818812999998</v>
+      <c r="E34" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>56</v>
@@ -1334,8 +1460,8 @@
       <c r="D35" s="5">
         <v>319</v>
       </c>
-      <c r="E35" s="7">
-        <v>-0.29405706822</v>
+      <c r="E35" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>56</v>
@@ -1357,8 +1483,8 @@
       <c r="D36" s="5">
         <v>213</v>
       </c>
-      <c r="E36" s="6">
-        <v>-0.374</v>
+      <c r="E36" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>56</v>
@@ -1380,8 +1506,8 @@
       <c r="D37" s="5">
         <v>430</v>
       </c>
-      <c r="E37" s="7">
-        <v>-0.15080789946000001</v>
+      <c r="E37" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>56</v>
@@ -1403,8 +1529,8 @@
       <c r="D38" s="5">
         <v>231</v>
       </c>
-      <c r="E38" s="6">
-        <v>-0.16706297146999999</v>
+      <c r="E38" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>56</v>
@@ -1426,8 +1552,8 @@
       <c r="D39" s="5">
         <v>286</v>
       </c>
-      <c r="E39" s="7">
-        <v>-2.8737849100000001E-2</v>
+      <c r="E39" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>56</v>
@@ -1449,8 +1575,8 @@
       <c r="D40" s="5">
         <v>67</v>
       </c>
-      <c r="E40" s="6">
-        <v>-6.0591603049999998E-2</v>
+      <c r="E40" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>56</v>
@@ -1472,8 +1598,8 @@
       <c r="D41" s="5">
         <v>56</v>
       </c>
-      <c r="E41" s="7">
-        <v>-0.46816601477999997</v>
+      <c r="E41" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>56</v>
@@ -1495,8 +1621,8 @@
       <c r="D42" s="5">
         <v>48</v>
       </c>
-      <c r="E42" s="6">
-        <v>-1.9140989729999999E-2</v>
+      <c r="E42" s="6" t="s">
+        <v>97</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>56</v>
@@ -1518,8 +1644,8 @@
       <c r="D43" s="5">
         <v>28</v>
       </c>
-      <c r="E43" s="7">
-        <v>-0.41746183205999998</v>
+      <c r="E43" s="7" t="s">
+        <v>98</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>56</v>
@@ -1541,8 +1667,8 @@
       <c r="D44" s="5">
         <v>0</v>
       </c>
-      <c r="E44" s="6">
-        <v>-8.3333333329999995E-2</v>
+      <c r="E44" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>56</v>
@@ -1564,8 +1690,8 @@
       <c r="D45" s="5">
         <v>3</v>
       </c>
-      <c r="E45" s="7">
-        <v>0.12704918033000001</v>
+      <c r="E45" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>55</v>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{555771A8-9245-4CA0-8F61-C8811EE0D781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6212A2C5-06DF-4E37-A27B-64732A3626FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="107">
   <si>
     <t>REFERENCIA INTERNA</t>
   </si>
@@ -335,6 +335,24 @@
   </si>
   <si>
     <t>12.7%</t>
+  </si>
+  <si>
+    <t>CATEGORIA</t>
+  </si>
+  <si>
+    <t>CREMOSILLO</t>
+  </si>
+  <si>
+    <t>CREMIGURT</t>
+  </si>
+  <si>
+    <t>TEVIA</t>
+  </si>
+  <si>
+    <t>SALTARINA</t>
+  </si>
+  <si>
+    <t>CREMIGURT POWER</t>
   </si>
 </sst>
 </file>
@@ -657,7 +675,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.7109375" customWidth="1"/>
@@ -665,7 +683,7 @@
     <col min="3" max="9" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -687,8 +705,11 @@
       <c r="G1" s="4" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H1" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>110150</v>
       </c>
@@ -710,8 +731,11 @@
       <c r="G2">
         <v>1.36</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H2" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>110151</v>
       </c>
@@ -733,8 +757,11 @@
       <c r="G3">
         <v>1.59</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H3" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>110230</v>
       </c>
@@ -756,8 +783,11 @@
       <c r="G4">
         <v>2.0299999999999998</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H4" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>110400</v>
       </c>
@@ -779,8 +809,11 @@
       <c r="G5">
         <v>3.61</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H5" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>111000</v>
       </c>
@@ -802,8 +835,11 @@
       <c r="G6">
         <v>8.7799999999999994</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H6" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>120130</v>
       </c>
@@ -825,8 +861,11 @@
       <c r="G7">
         <v>0.63</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H7" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>120131</v>
       </c>
@@ -848,8 +887,11 @@
       <c r="G8">
         <v>0.63</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H8" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>120132</v>
       </c>
@@ -871,8 +913,11 @@
       <c r="G9">
         <v>0.63</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H9" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>130150</v>
       </c>
@@ -894,8 +939,11 @@
       <c r="G10">
         <v>1.0900000000000001</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H10" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>130151</v>
       </c>
@@ -917,8 +965,11 @@
       <c r="G11">
         <v>1.0900000000000001</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H11" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>130152</v>
       </c>
@@ -940,8 +991,11 @@
       <c r="G12">
         <v>1.1599999999999999</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H12" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>130153</v>
       </c>
@@ -963,8 +1017,11 @@
       <c r="G13">
         <v>1.1599999999999999</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H13" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>130154</v>
       </c>
@@ -986,8 +1043,11 @@
       <c r="G14">
         <v>1.1599999999999999</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H14" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>130155</v>
       </c>
@@ -1009,8 +1069,11 @@
       <c r="G15">
         <v>1.1599999999999999</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H15" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>130156</v>
       </c>
@@ -1032,8 +1095,11 @@
       <c r="G16">
         <v>1.1599999999999999</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H16" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>130700</v>
       </c>
@@ -1055,8 +1121,11 @@
       <c r="G17">
         <v>3.68</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H17" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>130701</v>
       </c>
@@ -1078,8 +1147,11 @@
       <c r="G18">
         <v>3.68</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H18" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>130702</v>
       </c>
@@ -1101,8 +1173,11 @@
       <c r="G19">
         <v>4.1500000000000004</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H19" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>130703</v>
       </c>
@@ -1124,8 +1199,11 @@
       <c r="G20">
         <v>4.1500000000000004</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H20" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>130704</v>
       </c>
@@ -1147,8 +1225,11 @@
       <c r="G21">
         <v>4.1500000000000004</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H21" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>130707</v>
       </c>
@@ -1170,8 +1251,11 @@
       <c r="G22">
         <v>4.1500000000000004</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H22" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>131150</v>
       </c>
@@ -1193,8 +1277,11 @@
       <c r="G23">
         <v>1.63</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H23" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>131151</v>
       </c>
@@ -1216,8 +1303,11 @@
       <c r="G24">
         <v>1.63</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H24" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>131152</v>
       </c>
@@ -1239,8 +1329,11 @@
       <c r="G25">
         <v>1.63</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H25" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>131153</v>
       </c>
@@ -1262,8 +1355,11 @@
       <c r="G26">
         <v>1.63</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H26" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>131700</v>
       </c>
@@ -1285,8 +1381,11 @@
       <c r="G27">
         <v>6.15</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H27" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>131701</v>
       </c>
@@ -1308,8 +1407,11 @@
       <c r="G28">
         <v>6.15</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H28" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>132150</v>
       </c>
@@ -1331,8 +1433,11 @@
       <c r="G29">
         <v>1.1599999999999999</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H29" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>132151</v>
       </c>
@@ -1354,8 +1459,11 @@
       <c r="G30">
         <v>1.1599999999999999</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H30" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>132152</v>
       </c>
@@ -1377,8 +1485,11 @@
       <c r="G31">
         <v>1.1599999999999999</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H31" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>132153</v>
       </c>
@@ -1400,8 +1511,11 @@
       <c r="G32">
         <v>1.1599999999999999</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H32" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>140230</v>
       </c>
@@ -1423,8 +1537,11 @@
       <c r="G33">
         <v>1.1599999999999999</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H33" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>140231</v>
       </c>
@@ -1446,8 +1563,11 @@
       <c r="G34">
         <v>1.1599999999999999</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H34" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>140232</v>
       </c>
@@ -1469,8 +1589,11 @@
       <c r="G35">
         <v>1.1599999999999999</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H35" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>150360</v>
       </c>
@@ -1492,8 +1615,11 @@
       <c r="G36">
         <v>0.81</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H36" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>150361</v>
       </c>
@@ -1515,8 +1641,11 @@
       <c r="G37">
         <v>0.81</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H37" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>150362</v>
       </c>
@@ -1538,8 +1667,11 @@
       <c r="G38">
         <v>0.81</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H38" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>150363</v>
       </c>
@@ -1561,8 +1693,11 @@
       <c r="G39">
         <v>0.81</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H39" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>151500</v>
       </c>
@@ -1584,8 +1719,11 @@
       <c r="G40">
         <v>2.62</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H40" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>151501</v>
       </c>
@@ -1607,8 +1745,11 @@
       <c r="G41">
         <v>2.62</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H41" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>151502</v>
       </c>
@@ -1630,8 +1771,11 @@
       <c r="G42">
         <v>2.62</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H42" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>151503</v>
       </c>
@@ -1653,8 +1797,11 @@
       <c r="G43">
         <v>2.62</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H43" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>54</v>
       </c>
@@ -1676,8 +1823,11 @@
       <c r="G44">
         <v>18</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H44" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>54</v>
       </c>
@@ -1698,6 +1848,9 @@
       </c>
       <c r="G45">
         <v>18</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6212A2C5-06DF-4E37-A27B-64732A3626FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{249BDBEE-3F1A-4518-9626-48CEF63F544F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -680,7 +680,8 @@
   <cols>
     <col min="1" max="1" width="17.7109375" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
-    <col min="3" max="9" width="17.7109375" customWidth="1"/>
+    <col min="3" max="8" width="17.7109375" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -691,22 +692,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -716,23 +717,23 @@
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="5">
         <v>1045</v>
       </c>
-      <c r="D2" s="5">
+      <c r="E2" s="5">
         <v>1066</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>1.36</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -742,23 +743,23 @@
       <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="5">
         <v>76</v>
       </c>
-      <c r="D3" s="5">
+      <c r="E3" s="5">
         <v>77</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>1.59</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -768,23 +769,23 @@
       <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" s="5">
         <v>489</v>
       </c>
-      <c r="D4" s="5">
+      <c r="E4" s="5">
         <v>470</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="F4" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G4">
+      <c r="G4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4">
         <v>2.0299999999999998</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -794,23 +795,23 @@
       <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="5">
-        <v>91</v>
+      <c r="C5" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="D5" s="5">
         <v>91</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="5">
+        <v>91</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G5">
+      <c r="G5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5">
         <v>3.61</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -820,23 +821,23 @@
       <c r="B6" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="5">
-        <v>16</v>
+      <c r="C6" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="D6" s="5">
         <v>16</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5">
+        <v>16</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6">
+      <c r="G6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H6">
         <v>8.7799999999999994</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -846,23 +847,23 @@
       <c r="B7" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" s="5">
         <v>1441</v>
       </c>
-      <c r="D7" s="5">
+      <c r="E7" s="5">
         <v>1124</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7">
+      <c r="G7" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H7">
         <v>0.63</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -872,23 +873,23 @@
       <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="5">
         <v>133</v>
       </c>
-      <c r="D8" s="5">
+      <c r="E8" s="5">
         <v>105</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8">
+      <c r="G8" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8">
         <v>0.63</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -898,23 +899,23 @@
       <c r="B9" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" s="5">
         <v>333</v>
       </c>
-      <c r="D9" s="5">
+      <c r="E9" s="5">
         <v>255</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="F9" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9">
+      <c r="G9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9">
         <v>0.63</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -924,23 +925,23 @@
       <c r="B10" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" s="5">
         <v>714</v>
       </c>
-      <c r="D10" s="5">
+      <c r="E10" s="5">
         <v>569</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="F10" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10">
+      <c r="G10" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10">
         <v>1.0900000000000001</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -950,23 +951,23 @@
       <c r="B11" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" s="5">
         <v>478</v>
       </c>
-      <c r="D11" s="5">
+      <c r="E11" s="5">
         <v>334</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="F11" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11">
+      <c r="G11" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H11">
         <v>1.0900000000000001</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -976,23 +977,23 @@
       <c r="B12" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="5">
         <v>3493</v>
       </c>
-      <c r="D12" s="5">
+      <c r="E12" s="5">
         <v>2760</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="F12" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12">
+      <c r="G12" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H12">
         <v>1.1599999999999999</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -1002,23 +1003,23 @@
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" s="5">
         <v>2230</v>
       </c>
-      <c r="D13" s="5">
+      <c r="E13" s="5">
         <v>1883</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="F13" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13">
+      <c r="G13" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H13">
         <v>1.1599999999999999</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -1028,23 +1029,23 @@
       <c r="B14" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D14" s="5">
         <v>2306</v>
       </c>
-      <c r="D14" s="5">
+      <c r="E14" s="5">
         <v>1856</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="F14" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G14">
+      <c r="G14" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H14">
         <v>1.1599999999999999</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -1054,23 +1055,23 @@
       <c r="B15" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" s="5">
         <v>2708</v>
       </c>
-      <c r="D15" s="5">
+      <c r="E15" s="5">
         <v>2026</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="F15" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G15">
+      <c r="G15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15">
         <v>1.1599999999999999</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -1080,23 +1081,23 @@
       <c r="B16" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" s="5">
         <v>174</v>
       </c>
-      <c r="D16" s="5">
+      <c r="E16" s="5">
         <v>113</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="F16" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G16">
+      <c r="G16" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H16">
         <v>1.1599999999999999</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -1106,23 +1107,23 @@
       <c r="B17" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" s="5">
         <v>215</v>
       </c>
-      <c r="D17" s="5">
+      <c r="E17" s="5">
         <v>170</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="F17" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G17">
+      <c r="G17" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H17">
         <v>3.68</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -1132,23 +1133,23 @@
       <c r="B18" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18" s="5">
         <v>127</v>
       </c>
-      <c r="D18" s="5">
+      <c r="E18" s="5">
         <v>164</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="F18" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="G18" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>3.68</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -1158,23 +1159,23 @@
       <c r="B19" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" s="5">
         <v>484</v>
       </c>
-      <c r="D19" s="5">
+      <c r="E19" s="5">
         <v>412</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="F19" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G19">
+      <c r="G19" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H19">
         <v>4.1500000000000004</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -1184,23 +1185,23 @@
       <c r="B20" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D20" s="5">
         <v>779</v>
       </c>
-      <c r="D20" s="5">
+      <c r="E20" s="5">
         <v>685</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="F20" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G20">
+      <c r="G20" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20">
         <v>4.1500000000000004</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -1210,23 +1211,23 @@
       <c r="B21" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" s="5">
         <v>55</v>
       </c>
-      <c r="D21" s="5">
+      <c r="E21" s="5">
         <v>13</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="F21" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G21">
+      <c r="G21" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H21">
         <v>4.1500000000000004</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
@@ -1236,23 +1237,23 @@
       <c r="B22" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" s="5">
         <v>42</v>
       </c>
-      <c r="D22" s="5">
+      <c r="E22" s="5">
         <v>31</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="F22" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G22">
+      <c r="G22" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H22">
         <v>4.1500000000000004</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -1262,23 +1263,23 @@
       <c r="B23" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D23" s="5">
         <v>868</v>
       </c>
-      <c r="D23" s="5">
+      <c r="E23" s="5">
         <v>557</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="F23" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G23">
+      <c r="G23" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H23">
         <v>1.63</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
@@ -1288,23 +1289,23 @@
       <c r="B24" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24" s="5">
         <v>1383</v>
       </c>
-      <c r="D24" s="5">
+      <c r="E24" s="5">
         <v>934</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="F24" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G24">
+      <c r="G24" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H24">
         <v>1.63</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -1314,23 +1315,23 @@
       <c r="B25" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" s="5">
         <v>546</v>
       </c>
-      <c r="D25" s="5">
+      <c r="E25" s="5">
         <v>402</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="F25" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G25">
+      <c r="G25" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H25">
         <v>1.63</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
@@ -1340,23 +1341,23 @@
       <c r="B26" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" s="5">
         <v>504</v>
       </c>
-      <c r="D26" s="5">
+      <c r="E26" s="5">
         <v>306</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="F26" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F26" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G26">
+      <c r="G26" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H26">
         <v>1.63</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -1366,23 +1367,23 @@
       <c r="B27" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C27" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27" s="5">
         <v>130</v>
       </c>
-      <c r="D27" s="5">
+      <c r="E27" s="5">
         <v>104</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="F27" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G27">
+      <c r="G27" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H27">
         <v>6.15</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
@@ -1392,23 +1393,23 @@
       <c r="B28" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28" s="5">
         <v>143</v>
       </c>
-      <c r="D28" s="5">
+      <c r="E28" s="5">
         <v>117</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="F28" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G28">
+      <c r="G28" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H28">
         <v>6.15</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -1418,23 +1419,23 @@
       <c r="B29" t="s">
         <v>33</v>
       </c>
-      <c r="C29" s="5">
+      <c r="C29" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D29" s="5">
         <v>852</v>
       </c>
-      <c r="D29" s="5">
+      <c r="E29" s="5">
         <v>728</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="F29" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="F29" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G29">
+      <c r="G29" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H29">
         <v>1.1599999999999999</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -1444,23 +1445,23 @@
       <c r="B30" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D30" s="5">
         <v>857</v>
       </c>
-      <c r="D30" s="5">
+      <c r="E30" s="5">
         <v>607</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="F30" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F30" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G30">
+      <c r="G30" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H30">
         <v>1.1599999999999999</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -1470,23 +1471,23 @@
       <c r="B31" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="5">
+      <c r="C31" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" s="5">
         <v>1068</v>
       </c>
-      <c r="D31" s="5">
+      <c r="E31" s="5">
         <v>788</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="F31" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G31">
+      <c r="G31" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H31">
         <v>1.1599999999999999</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -1496,23 +1497,23 @@
       <c r="B32" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C32" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D32" s="5">
         <v>685</v>
       </c>
-      <c r="D32" s="5">
+      <c r="E32" s="5">
         <v>522</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="F32" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G32">
+      <c r="G32" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H32">
         <v>1.1599999999999999</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -1522,23 +1523,23 @@
       <c r="B33" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="5">
+      <c r="C33" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D33" s="5">
         <v>209</v>
       </c>
-      <c r="D33" s="5">
+      <c r="E33" s="5">
         <v>189</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="F33" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="F33" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G33">
+      <c r="G33" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H33">
         <v>1.1599999999999999</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
@@ -1548,23 +1549,23 @@
       <c r="B34" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="5">
+      <c r="C34" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D34" s="5">
         <v>511</v>
       </c>
-      <c r="D34" s="5">
+      <c r="E34" s="5">
         <v>24</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="F34" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="F34" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G34">
+      <c r="G34" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H34">
         <v>1.1599999999999999</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
@@ -1574,23 +1575,23 @@
       <c r="B35" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="5">
+      <c r="C35" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D35" s="5">
         <v>452</v>
       </c>
-      <c r="D35" s="5">
+      <c r="E35" s="5">
         <v>319</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="F35" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="F35" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G35">
+      <c r="G35" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H35">
         <v>1.1599999999999999</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
@@ -1600,23 +1601,23 @@
       <c r="B36" t="s">
         <v>49</v>
       </c>
-      <c r="C36" s="5">
+      <c r="C36" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D36" s="5">
         <v>341</v>
       </c>
-      <c r="D36" s="5">
+      <c r="E36" s="5">
         <v>213</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="F36" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="F36" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G36">
+      <c r="G36" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H36">
         <v>0.81</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -1626,23 +1627,23 @@
       <c r="B37" t="s">
         <v>40</v>
       </c>
-      <c r="C37" s="5">
+      <c r="C37" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D37" s="5">
         <v>506</v>
       </c>
-      <c r="D37" s="5">
+      <c r="E37" s="5">
         <v>430</v>
       </c>
-      <c r="E37" s="7" t="s">
+      <c r="F37" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="F37" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G37">
+      <c r="G37" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H37">
         <v>0.81</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
@@ -1652,23 +1653,23 @@
       <c r="B38" t="s">
         <v>41</v>
       </c>
-      <c r="C38" s="5">
+      <c r="C38" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D38" s="5">
         <v>277</v>
       </c>
-      <c r="D38" s="5">
+      <c r="E38" s="5">
         <v>231</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="F38" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="F38" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G38">
+      <c r="G38" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H38">
         <v>0.81</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -1678,23 +1679,23 @@
       <c r="B39" t="s">
         <v>42</v>
       </c>
-      <c r="C39" s="5">
+      <c r="C39" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D39" s="5">
         <v>295</v>
       </c>
-      <c r="D39" s="5">
+      <c r="E39" s="5">
         <v>286</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="F39" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="F39" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G39">
+      <c r="G39" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H39">
         <v>0.81</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -1704,23 +1705,23 @@
       <c r="B40" t="s">
         <v>50</v>
       </c>
-      <c r="C40" s="5">
+      <c r="C40" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D40" s="5">
         <v>71</v>
       </c>
-      <c r="D40" s="5">
+      <c r="E40" s="5">
         <v>67</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="F40" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="F40" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G40">
+      <c r="G40" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H40">
         <v>2.62</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
@@ -1730,23 +1731,23 @@
       <c r="B41" t="s">
         <v>51</v>
       </c>
-      <c r="C41" s="5">
+      <c r="C41" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D41" s="5">
         <v>105</v>
       </c>
-      <c r="D41" s="5">
-        <v>56</v>
-      </c>
-      <c r="E41" s="7" t="s">
+      <c r="E41" s="5">
+        <v>56</v>
+      </c>
+      <c r="F41" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="F41" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G41">
+      <c r="G41" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H41">
         <v>2.62</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
@@ -1756,23 +1757,23 @@
       <c r="B42" t="s">
         <v>52</v>
       </c>
-      <c r="C42" s="5">
+      <c r="C42" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D42" s="5">
         <v>49</v>
       </c>
-      <c r="D42" s="5">
+      <c r="E42" s="5">
         <v>48</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="F42" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="F42" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G42">
+      <c r="G42" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H42">
         <v>2.62</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -1782,23 +1783,23 @@
       <c r="B43" t="s">
         <v>53</v>
       </c>
-      <c r="C43" s="5">
+      <c r="C43" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D43" s="5">
         <v>48</v>
       </c>
-      <c r="D43" s="5">
+      <c r="E43" s="5">
         <v>28</v>
       </c>
-      <c r="E43" s="7" t="s">
+      <c r="F43" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="F43" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G43">
+      <c r="G43" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H43">
         <v>2.62</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -1808,23 +1809,23 @@
       <c r="B44" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="5">
+      <c r="C44" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D44" s="5">
         <v>1</v>
       </c>
-      <c r="D44" s="5">
+      <c r="E44" s="5">
         <v>0</v>
       </c>
-      <c r="E44" s="6" t="s">
+      <c r="F44" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="F44" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G44">
+      <c r="G44" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H44">
         <v>18</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -1834,23 +1835,23 @@
       <c r="B45" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="5">
-        <v>3</v>
+      <c r="C45" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="D45" s="5">
         <v>3</v>
       </c>
-      <c r="E45" s="7" t="s">
+      <c r="E45" s="5">
+        <v>3</v>
+      </c>
+      <c r="F45" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="G45" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G45">
+      <c r="H45">
         <v>18</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{249BDBEE-3F1A-4518-9626-48CEF63F544F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CFE3D1-ED13-4228-8639-BE384772F250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -337,9 +337,6 @@
     <t>12.7%</t>
   </si>
   <si>
-    <t>CATEGORIA</t>
-  </si>
-  <si>
     <t>CREMOSILLO</t>
   </si>
   <si>
@@ -353,6 +350,9 @@
   </si>
   <si>
     <t>CREMIGURT POWER</t>
+  </si>
+  <si>
+    <t>CATEGORÍA</t>
   </si>
 </sst>
 </file>
@@ -692,7 +692,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>2</v>
@@ -718,7 +718,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D2" s="5">
         <v>1045</v>
@@ -744,7 +744,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D3" s="5">
         <v>76</v>
@@ -770,7 +770,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" s="5">
         <v>489</v>
@@ -796,7 +796,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D5" s="5">
         <v>91</v>
@@ -822,7 +822,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D6" s="5">
         <v>16</v>
@@ -848,7 +848,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D7" s="5">
         <v>1441</v>
@@ -874,7 +874,7 @@
         <v>12</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D8" s="5">
         <v>133</v>
@@ -900,7 +900,7 @@
         <v>13</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D9" s="5">
         <v>333</v>
@@ -926,7 +926,7 @@
         <v>14</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D10" s="5">
         <v>714</v>
@@ -952,7 +952,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D11" s="5">
         <v>478</v>
@@ -978,7 +978,7 @@
         <v>16</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D12" s="5">
         <v>3493</v>
@@ -1004,7 +1004,7 @@
         <v>17</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D13" s="5">
         <v>2230</v>
@@ -1030,7 +1030,7 @@
         <v>18</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D14" s="5">
         <v>2306</v>
@@ -1056,7 +1056,7 @@
         <v>19</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D15" s="5">
         <v>2708</v>
@@ -1082,7 +1082,7 @@
         <v>20</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D16" s="5">
         <v>174</v>
@@ -1108,7 +1108,7 @@
         <v>21</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D17" s="5">
         <v>215</v>
@@ -1134,7 +1134,7 @@
         <v>22</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D18" s="5">
         <v>127</v>
@@ -1160,7 +1160,7 @@
         <v>23</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D19" s="5">
         <v>484</v>
@@ -1186,7 +1186,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D20" s="5">
         <v>779</v>
@@ -1212,7 +1212,7 @@
         <v>25</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D21" s="5">
         <v>55</v>
@@ -1238,7 +1238,7 @@
         <v>26</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D22" s="5">
         <v>42</v>
@@ -1264,7 +1264,7 @@
         <v>27</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D23" s="5">
         <v>868</v>
@@ -1290,7 +1290,7 @@
         <v>28</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D24" s="5">
         <v>1383</v>
@@ -1316,7 +1316,7 @@
         <v>29</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D25" s="5">
         <v>546</v>
@@ -1342,7 +1342,7 @@
         <v>30</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" s="5">
         <v>504</v>
@@ -1368,7 +1368,7 @@
         <v>31</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D27" s="5">
         <v>130</v>
@@ -1394,7 +1394,7 @@
         <v>32</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D28" s="5">
         <v>143</v>
@@ -1420,7 +1420,7 @@
         <v>33</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D29" s="5">
         <v>852</v>
@@ -1446,7 +1446,7 @@
         <v>34</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D30" s="5">
         <v>857</v>
@@ -1472,7 +1472,7 @@
         <v>35</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D31" s="5">
         <v>1068</v>
@@ -1498,7 +1498,7 @@
         <v>36</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D32" s="5">
         <v>685</v>
@@ -1524,7 +1524,7 @@
         <v>37</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D33" s="5">
         <v>209</v>
@@ -1550,7 +1550,7 @@
         <v>38</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D34" s="5">
         <v>511</v>
@@ -1576,7 +1576,7 @@
         <v>39</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D35" s="5">
         <v>452</v>
@@ -1602,7 +1602,7 @@
         <v>49</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D36" s="5">
         <v>341</v>
@@ -1628,7 +1628,7 @@
         <v>40</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D37" s="5">
         <v>506</v>
@@ -1654,7 +1654,7 @@
         <v>41</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D38" s="5">
         <v>277</v>
@@ -1680,7 +1680,7 @@
         <v>42</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D39" s="5">
         <v>295</v>
@@ -1706,7 +1706,7 @@
         <v>50</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D40" s="5">
         <v>71</v>
@@ -1732,7 +1732,7 @@
         <v>51</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D41" s="5">
         <v>105</v>
@@ -1758,7 +1758,7 @@
         <v>52</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D42" s="5">
         <v>49</v>
@@ -1784,7 +1784,7 @@
         <v>53</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D43" s="5">
         <v>48</v>
@@ -1810,7 +1810,7 @@
         <v>43</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D44" s="5">
         <v>1</v>
@@ -1836,7 +1836,7 @@
         <v>44</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D45" s="5">
         <v>3</v>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CFE3D1-ED13-4228-8639-BE384772F250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2106A901-6B61-4F15-B811-F5588D293DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
     <sheet name="Referencias de fuentes" sheetId="2" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -32,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="62">
   <si>
     <t>REFERENCIA INTERNA</t>
   </si>
@@ -199,142 +202,7 @@
     <t>Not in source</t>
   </si>
   <si>
-    <t>SUBIÓ</t>
-  </si>
-  <si>
-    <t>BAJO</t>
-  </si>
-  <si>
     <t>PRECIO UNITARIO</t>
-  </si>
-  <si>
-    <t>2.0%</t>
-  </si>
-  <si>
-    <t>1.0%</t>
-  </si>
-  <si>
-    <t>-3.9%</t>
-  </si>
-  <si>
-    <t>-0.1%</t>
-  </si>
-  <si>
-    <t>-1.3%</t>
-  </si>
-  <si>
-    <t>-22.0%</t>
-  </si>
-  <si>
-    <t>-20.8%</t>
-  </si>
-  <si>
-    <t>-23.3%</t>
-  </si>
-  <si>
-    <t>-20.3%</t>
-  </si>
-  <si>
-    <t>-30.1%</t>
-  </si>
-  <si>
-    <t>-21.0%</t>
-  </si>
-  <si>
-    <t>-15.5%</t>
-  </si>
-  <si>
-    <t>-15.9%</t>
-  </si>
-  <si>
-    <t>-25.2%</t>
-  </si>
-  <si>
-    <t>-35.1%</t>
-  </si>
-  <si>
-    <t>29.2%</t>
-  </si>
-  <si>
-    <t>-14.9%</t>
-  </si>
-  <si>
-    <t>-12.0%</t>
-  </si>
-  <si>
-    <t>-77.0%</t>
-  </si>
-  <si>
-    <t>-24.9%</t>
-  </si>
-  <si>
-    <t>-35.8%</t>
-  </si>
-  <si>
-    <t>-32.4%</t>
-  </si>
-  <si>
-    <t>-26.4%</t>
-  </si>
-  <si>
-    <t>-39.3%</t>
-  </si>
-  <si>
-    <t>-20.1%</t>
-  </si>
-  <si>
-    <t>-18.3%</t>
-  </si>
-  <si>
-    <t>-14.6%</t>
-  </si>
-  <si>
-    <t>-29.2%</t>
-  </si>
-  <si>
-    <t>-26.2%</t>
-  </si>
-  <si>
-    <t>-23.9%</t>
-  </si>
-  <si>
-    <t>-9.3%</t>
-  </si>
-  <si>
-    <t>-95.2%</t>
-  </si>
-  <si>
-    <t>-29.4%</t>
-  </si>
-  <si>
-    <t>-37.4%</t>
-  </si>
-  <si>
-    <t>-15.1%</t>
-  </si>
-  <si>
-    <t>-16.7%</t>
-  </si>
-  <si>
-    <t>-2.9%</t>
-  </si>
-  <si>
-    <t>-6.1%</t>
-  </si>
-  <si>
-    <t>-46.8%</t>
-  </si>
-  <si>
-    <t>-1.9%</t>
-  </si>
-  <si>
-    <t>-41.7%</t>
-  </si>
-  <si>
-    <t>-8.3%</t>
-  </si>
-  <si>
-    <t>12.7%</t>
   </si>
   <si>
     <t>CREMOSILLO</t>
@@ -444,7 +312,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
@@ -459,6 +327,7 @@
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -475,6 +344,529 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="INVENTARIO NACIONAL 03-07-26"/>
+      <sheetName val="VINCULO VTS BY SKU JUNIO"/>
+      <sheetName val="VINCULO VTS BY SKU OPEN"/>
+      <sheetName val="DESV. VTS BY SKU"/>
+      <sheetName val="INVENTARIO NACIONAL 03-07-26-2"/>
+      <sheetName val="INVENTARIO NACIONAL 06-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 07-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 08-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 09-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 10-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 13-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 14-07-26"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="4">
+          <cell r="F4">
+            <v>1047.7777777777778</v>
+          </cell>
+          <cell r="G4">
+            <v>2.5709425500659577E-3</v>
+          </cell>
+          <cell r="H4" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="F5">
+            <v>75</v>
+          </cell>
+          <cell r="G5">
+            <v>-1.2567324955116699E-2</v>
+          </cell>
+          <cell r="H5" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="F6">
+            <v>473.44444444444446</v>
+          </cell>
+          <cell r="G6">
+            <v>-3.1360757204707657E-2</v>
+          </cell>
+          <cell r="H6" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="F7">
+            <v>88.555555555555557</v>
+          </cell>
+          <cell r="G7">
+            <v>-3.073521282476499E-2</v>
+          </cell>
+          <cell r="H7" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="F8">
+            <v>15.444444444444445</v>
+          </cell>
+          <cell r="G8">
+            <v>-3.1972143083254245E-2</v>
+          </cell>
+          <cell r="H8" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="F9">
+            <v>1142</v>
+          </cell>
+          <cell r="G9">
+            <v>-0.20771971870959605</v>
+          </cell>
+          <cell r="H9" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="F10">
+            <v>101.44444444444444</v>
+          </cell>
+          <cell r="G10">
+            <v>-0.23673810609515122</v>
+          </cell>
+          <cell r="H10" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="F11">
+            <v>257.11111111111109</v>
+          </cell>
+          <cell r="G11">
+            <v>-0.226944862041213</v>
+          </cell>
+          <cell r="H11" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="F12">
+            <v>560</v>
+          </cell>
+          <cell r="G12">
+            <v>-0.21543654078838437</v>
+          </cell>
+          <cell r="H12" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="F13">
+            <v>325.88888888888891</v>
+          </cell>
+          <cell r="G13">
+            <v>-0.31880707310636047</v>
+          </cell>
+          <cell r="H13" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="F14">
+            <v>2734.7777777777778</v>
+          </cell>
+          <cell r="G14">
+            <v>-0.21705887030891913</v>
+          </cell>
+          <cell r="H14" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="F15">
+            <v>1864.2222222222222</v>
+          </cell>
+          <cell r="G15">
+            <v>-0.16392365782833429</v>
+          </cell>
+          <cell r="H15" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="F16">
+            <v>1825.4444444444443</v>
+          </cell>
+          <cell r="G16">
+            <v>-0.2083779586884198</v>
+          </cell>
+          <cell r="H16" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="F17">
+            <v>2000</v>
+          </cell>
+          <cell r="G17">
+            <v>-0.26150954163239959</v>
+          </cell>
+          <cell r="H17" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="F18">
+            <v>106.88888888888889</v>
+          </cell>
+          <cell r="G18">
+            <v>-0.3858564754360001</v>
+          </cell>
+          <cell r="H18" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="F19">
+            <v>165.11111111111111</v>
+          </cell>
+          <cell r="G19">
+            <v>-0.23057732589611424</v>
+          </cell>
+          <cell r="H19" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="F20">
+            <v>154.22222222222223</v>
+          </cell>
+          <cell r="G20">
+            <v>0.21217895280060328</v>
+          </cell>
+          <cell r="H20" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="F21">
+            <v>396.66666666666669</v>
+          </cell>
+          <cell r="G21">
+            <v>-0.18074852922768803</v>
+          </cell>
+          <cell r="H21" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="F22">
+            <v>643.77777777777783</v>
+          </cell>
+          <cell r="G22">
+            <v>-0.17339143742785623</v>
+          </cell>
+          <cell r="H22" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="F23">
+            <v>11.222222222222221</v>
+          </cell>
+          <cell r="G23">
+            <v>-0.79511295527893044</v>
+          </cell>
+          <cell r="H23" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="F24">
+            <v>27.777777777777779</v>
+          </cell>
+          <cell r="G24">
+            <v>-0.33211900425015184</v>
+          </cell>
+          <cell r="H24" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="F25">
+            <v>555.77777777777783</v>
+          </cell>
+          <cell r="G25">
+            <v>-0.35960241391551295</v>
+          </cell>
+          <cell r="H25" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="F26">
+            <v>944</v>
+          </cell>
+          <cell r="G26">
+            <v>-0.31720147290899525</v>
+          </cell>
+          <cell r="H26" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="F27">
+            <v>391.33333333333331</v>
+          </cell>
+          <cell r="G27">
+            <v>-0.28273487183759627</v>
+          </cell>
+          <cell r="H27" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="F28">
+            <v>310.66666666666669</v>
+          </cell>
+          <cell r="G28">
+            <v>-0.3835978835978836</v>
+          </cell>
+          <cell r="H28" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="F29">
+            <v>99.555555555555557</v>
+          </cell>
+          <cell r="G29">
+            <v>-0.23579126928743122</v>
+          </cell>
+          <cell r="H29" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="F30">
+            <v>112.88888888888889</v>
+          </cell>
+          <cell r="G30">
+            <v>-0.20931055219498396</v>
+          </cell>
+          <cell r="H30" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="F31">
+            <v>706.33333333333337</v>
+          </cell>
+          <cell r="G31">
+            <v>-0.17079331198861614</v>
+          </cell>
+          <cell r="H31" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="F32">
+            <v>586.77777777777783</v>
+          </cell>
+          <cell r="G32">
+            <v>-0.31563849275772082</v>
+          </cell>
+          <cell r="H32" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="F33">
+            <v>764.11111111111109</v>
+          </cell>
+          <cell r="G33">
+            <v>-0.28435740977248003</v>
+          </cell>
+          <cell r="H33" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="F34">
+            <v>506.44444444444446</v>
+          </cell>
+          <cell r="G34">
+            <v>-0.2607631516867186</v>
+          </cell>
+          <cell r="H34" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="F35">
+            <v>188.33333333333334</v>
+          </cell>
+          <cell r="G35">
+            <v>-9.7706155632984792E-2</v>
+          </cell>
+          <cell r="H35" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="F36">
+            <v>47</v>
+          </cell>
+          <cell r="G36">
+            <v>-0.9079825576221412</v>
+          </cell>
+          <cell r="H36" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="F37">
+            <v>320.88888888888891</v>
+          </cell>
+          <cell r="G37">
+            <v>-0.29071078513457693</v>
+          </cell>
+          <cell r="H37" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="F38">
+            <v>224.77777777777777</v>
+          </cell>
+          <cell r="G38">
+            <v>-0.34065185185185187</v>
+          </cell>
+          <cell r="H38" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="F39">
+            <v>422.22222222222223</v>
+          </cell>
+          <cell r="G39">
+            <v>-0.16616796329543193</v>
+          </cell>
+          <cell r="H39" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="F40">
+            <v>229.11111111111111</v>
+          </cell>
+          <cell r="G40">
+            <v>-0.17342662439415468</v>
+          </cell>
+          <cell r="H40" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="F41">
+            <v>276</v>
+          </cell>
+          <cell r="G41">
+            <v>-6.3107545131923959E-2</v>
+          </cell>
+          <cell r="H41" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="F42">
+            <v>60.333333333333336</v>
+          </cell>
+          <cell r="G42">
+            <v>-0.15564037319762503</v>
+          </cell>
+          <cell r="H42" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="F43">
+            <v>52.777777777777779</v>
+          </cell>
+          <cell r="G43">
+            <v>-0.49538847843932587</v>
+          </cell>
+          <cell r="H43" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="F44">
+            <v>43.777777777777779</v>
+          </cell>
+          <cell r="G44">
+            <v>-0.10073659093266929</v>
+          </cell>
+          <cell r="H44" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="F45">
+            <v>28.888888888888889</v>
+          </cell>
+          <cell r="G45">
+            <v>-0.39355385920271413</v>
+          </cell>
+          <cell r="H45" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="F46">
+            <v>0.44444444444444442</v>
+          </cell>
+          <cell r="G46">
+            <v>-0.18518518518518512</v>
+          </cell>
+          <cell r="H46" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="F47">
+            <v>3</v>
+          </cell>
+          <cell r="G47">
+            <v>8.19672131147553E-2</v>
+          </cell>
+          <cell r="H47" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -692,7 +1084,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>2</v>
@@ -707,7 +1099,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -718,19 +1110,22 @@
         <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="D2" s="5">
         <v>1045</v>
       </c>
       <c r="E2" s="5">
-        <v>1066</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>55</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
+        <v>1047.7777777777778</v>
+      </c>
+      <c r="F2" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
+        <v>2.5709425500659577E-3</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
+        <v>SUBIÓ</v>
       </c>
       <c r="H2">
         <v>1.36</v>
@@ -744,19 +1139,22 @@
         <v>7</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="D3" s="5">
         <v>76</v>
       </c>
       <c r="E3" s="5">
-        <v>77</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>55</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
+        <v>75</v>
+      </c>
+      <c r="F3" s="7">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
+        <v>-1.2567324955116699E-2</v>
+      </c>
+      <c r="G3" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
+        <v>BAJO</v>
       </c>
       <c r="H3">
         <v>1.59</v>
@@ -770,19 +1168,22 @@
         <v>8</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="D4" s="5">
         <v>489</v>
       </c>
       <c r="E4" s="5">
-        <v>470</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
+        <v>473.44444444444446</v>
+      </c>
+      <c r="F4" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
+        <v>-3.1360757204707657E-2</v>
+      </c>
+      <c r="G4" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
+        <v>BAJO</v>
       </c>
       <c r="H4">
         <v>2.0299999999999998</v>
@@ -796,19 +1197,22 @@
         <v>9</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="D5" s="5">
         <v>91</v>
       </c>
       <c r="E5" s="5">
-        <v>91</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
+        <v>88.555555555555557</v>
+      </c>
+      <c r="F5" s="7">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
+        <v>-3.073521282476499E-2</v>
+      </c>
+      <c r="G5" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
+        <v>BAJO</v>
       </c>
       <c r="H5">
         <v>3.61</v>
@@ -822,19 +1226,22 @@
         <v>10</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="D6" s="5">
         <v>16</v>
       </c>
       <c r="E6" s="5">
-        <v>16</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
+        <v>15.444444444444445</v>
+      </c>
+      <c r="F6" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
+        <v>-3.1972143083254245E-2</v>
+      </c>
+      <c r="G6" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
+        <v>BAJO</v>
       </c>
       <c r="H6">
         <v>8.7799999999999994</v>
@@ -848,19 +1255,22 @@
         <v>11</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="D7" s="5">
         <v>1441</v>
       </c>
       <c r="E7" s="5">
-        <v>1124</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
+        <v>1142</v>
+      </c>
+      <c r="F7" s="7">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
+        <v>-0.20771971870959605</v>
+      </c>
+      <c r="G7" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
+        <v>BAJO</v>
       </c>
       <c r="H7">
         <v>0.63</v>
@@ -874,19 +1284,22 @@
         <v>12</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="D8" s="5">
         <v>133</v>
       </c>
       <c r="E8" s="5">
-        <v>105</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
+        <v>101.44444444444444</v>
+      </c>
+      <c r="F8" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
+        <v>-0.23673810609515122</v>
+      </c>
+      <c r="G8" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
+        <v>BAJO</v>
       </c>
       <c r="H8">
         <v>0.63</v>
@@ -900,19 +1313,22 @@
         <v>13</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="D9" s="5">
         <v>333</v>
       </c>
       <c r="E9" s="5">
-        <v>255</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
+        <v>257.11111111111109</v>
+      </c>
+      <c r="F9" s="7">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
+        <v>-0.226944862041213</v>
+      </c>
+      <c r="G9" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
+        <v>BAJO</v>
       </c>
       <c r="H9">
         <v>0.63</v>
@@ -926,19 +1342,22 @@
         <v>14</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D10" s="5">
         <v>714</v>
       </c>
       <c r="E10" s="5">
-        <v>569</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
+        <v>560</v>
+      </c>
+      <c r="F10" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
+        <v>-0.21543654078838437</v>
+      </c>
+      <c r="G10" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
+        <v>BAJO</v>
       </c>
       <c r="H10">
         <v>1.0900000000000001</v>
@@ -952,19 +1371,22 @@
         <v>15</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D11" s="5">
         <v>478</v>
       </c>
       <c r="E11" s="5">
-        <v>334</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
+        <v>325.88888888888891</v>
+      </c>
+      <c r="F11" s="7">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
+        <v>-0.31880707310636047</v>
+      </c>
+      <c r="G11" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
+        <v>BAJO</v>
       </c>
       <c r="H11">
         <v>1.0900000000000001</v>
@@ -978,19 +1400,22 @@
         <v>16</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D12" s="5">
         <v>3493</v>
       </c>
       <c r="E12" s="5">
-        <v>2760</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
+        <v>2734.7777777777778</v>
+      </c>
+      <c r="F12" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
+        <v>-0.21705887030891913</v>
+      </c>
+      <c r="G12" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
+        <v>BAJO</v>
       </c>
       <c r="H12">
         <v>1.1599999999999999</v>
@@ -1004,19 +1429,22 @@
         <v>17</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D13" s="5">
         <v>2230</v>
       </c>
       <c r="E13" s="5">
-        <v>1883</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
+        <v>1864.2222222222222</v>
+      </c>
+      <c r="F13" s="7">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
+        <v>-0.16392365782833429</v>
+      </c>
+      <c r="G13" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
+        <v>BAJO</v>
       </c>
       <c r="H13">
         <v>1.1599999999999999</v>
@@ -1030,19 +1458,22 @@
         <v>18</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D14" s="5">
         <v>2306</v>
       </c>
       <c r="E14" s="5">
-        <v>1856</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
+        <v>1825.4444444444443</v>
+      </c>
+      <c r="F14" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
+        <v>-0.2083779586884198</v>
+      </c>
+      <c r="G14" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
+        <v>BAJO</v>
       </c>
       <c r="H14">
         <v>1.1599999999999999</v>
@@ -1056,19 +1487,22 @@
         <v>19</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D15" s="5">
         <v>2708</v>
       </c>
       <c r="E15" s="5">
-        <v>2026</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
+        <v>2000</v>
+      </c>
+      <c r="F15" s="7">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
+        <v>-0.26150954163239959</v>
+      </c>
+      <c r="G15" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
+        <v>BAJO</v>
       </c>
       <c r="H15">
         <v>1.1599999999999999</v>
@@ -1082,19 +1516,22 @@
         <v>20</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D16" s="5">
         <v>174</v>
       </c>
       <c r="E16" s="5">
-        <v>113</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
+        <v>106.88888888888889</v>
+      </c>
+      <c r="F16" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
+        <v>-0.3858564754360001</v>
+      </c>
+      <c r="G16" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
+        <v>BAJO</v>
       </c>
       <c r="H16">
         <v>1.1599999999999999</v>
@@ -1108,19 +1545,22 @@
         <v>21</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D17" s="5">
         <v>215</v>
       </c>
       <c r="E17" s="5">
-        <v>170</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
+        <v>165.11111111111111</v>
+      </c>
+      <c r="F17" s="7">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
+        <v>-0.23057732589611424</v>
+      </c>
+      <c r="G17" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
+        <v>BAJO</v>
       </c>
       <c r="H17">
         <v>3.68</v>
@@ -1134,19 +1574,22 @@
         <v>22</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D18" s="5">
         <v>127</v>
       </c>
       <c r="E18" s="5">
-        <v>164</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>55</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
+        <v>154.22222222222223</v>
+      </c>
+      <c r="F18" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
+        <v>0.21217895280060328</v>
+      </c>
+      <c r="G18" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
+        <v>SUBIÓ</v>
       </c>
       <c r="H18">
         <v>3.68</v>
@@ -1160,19 +1603,22 @@
         <v>23</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D19" s="5">
         <v>484</v>
       </c>
       <c r="E19" s="5">
-        <v>412</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
+        <v>396.66666666666669</v>
+      </c>
+      <c r="F19" s="7">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
+        <v>-0.18074852922768803</v>
+      </c>
+      <c r="G19" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
+        <v>BAJO</v>
       </c>
       <c r="H19">
         <v>4.1500000000000004</v>
@@ -1186,19 +1632,22 @@
         <v>24</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D20" s="5">
         <v>779</v>
       </c>
       <c r="E20" s="5">
-        <v>685</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
+        <v>643.77777777777783</v>
+      </c>
+      <c r="F20" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
+        <v>-0.17339143742785623</v>
+      </c>
+      <c r="G20" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
+        <v>BAJO</v>
       </c>
       <c r="H20">
         <v>4.1500000000000004</v>
@@ -1212,19 +1661,22 @@
         <v>25</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D21" s="5">
         <v>55</v>
       </c>
       <c r="E21" s="5">
-        <v>13</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
+        <v>11.222222222222221</v>
+      </c>
+      <c r="F21" s="7">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
+        <v>-0.79511295527893044</v>
+      </c>
+      <c r="G21" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
+        <v>BAJO</v>
       </c>
       <c r="H21">
         <v>4.1500000000000004</v>
@@ -1238,19 +1690,22 @@
         <v>26</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D22" s="5">
         <v>42</v>
       </c>
       <c r="E22" s="5">
-        <v>31</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
+        <v>27.777777777777779</v>
+      </c>
+      <c r="F22" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
+        <v>-0.33211900425015184</v>
+      </c>
+      <c r="G22" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
+        <v>BAJO</v>
       </c>
       <c r="H22">
         <v>4.1500000000000004</v>
@@ -1264,19 +1719,22 @@
         <v>27</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="D23" s="5">
         <v>868</v>
       </c>
       <c r="E23" s="5">
-        <v>557</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
+        <v>555.77777777777783</v>
+      </c>
+      <c r="F23" s="7">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
+        <v>-0.35960241391551295</v>
+      </c>
+      <c r="G23" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
+        <v>BAJO</v>
       </c>
       <c r="H23">
         <v>1.63</v>
@@ -1290,19 +1748,22 @@
         <v>28</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="D24" s="5">
         <v>1383</v>
       </c>
       <c r="E24" s="5">
-        <v>934</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
+        <v>944</v>
+      </c>
+      <c r="F24" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
+        <v>-0.31720147290899525</v>
+      </c>
+      <c r="G24" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
+        <v>BAJO</v>
       </c>
       <c r="H24">
         <v>1.63</v>
@@ -1316,19 +1777,22 @@
         <v>29</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="D25" s="5">
         <v>546</v>
       </c>
       <c r="E25" s="5">
-        <v>402</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
+        <v>391.33333333333331</v>
+      </c>
+      <c r="F25" s="7">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
+        <v>-0.28273487183759627</v>
+      </c>
+      <c r="G25" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
+        <v>BAJO</v>
       </c>
       <c r="H25">
         <v>1.63</v>
@@ -1342,19 +1806,22 @@
         <v>30</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="D26" s="5">
         <v>504</v>
       </c>
       <c r="E26" s="5">
-        <v>306</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
+        <v>310.66666666666669</v>
+      </c>
+      <c r="F26" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
+        <v>-0.3835978835978836</v>
+      </c>
+      <c r="G26" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
+        <v>BAJO</v>
       </c>
       <c r="H26">
         <v>1.63</v>
@@ -1368,19 +1835,22 @@
         <v>31</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="D27" s="5">
         <v>130</v>
       </c>
       <c r="E27" s="5">
-        <v>104</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
+        <v>99.555555555555557</v>
+      </c>
+      <c r="F27" s="7">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
+        <v>-0.23579126928743122</v>
+      </c>
+      <c r="G27" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
+        <v>BAJO</v>
       </c>
       <c r="H27">
         <v>6.15</v>
@@ -1394,19 +1864,22 @@
         <v>32</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="D28" s="5">
         <v>143</v>
       </c>
       <c r="E28" s="5">
-        <v>117</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
+        <v>112.88888888888889</v>
+      </c>
+      <c r="F28" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
+        <v>-0.20931055219498396</v>
+      </c>
+      <c r="G28" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
+        <v>BAJO</v>
       </c>
       <c r="H28">
         <v>6.15</v>
@@ -1420,19 +1893,22 @@
         <v>33</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D29" s="5">
         <v>852</v>
       </c>
       <c r="E29" s="5">
-        <v>728</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
+        <v>706.33333333333337</v>
+      </c>
+      <c r="F29" s="7">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
+        <v>-0.17079331198861614</v>
+      </c>
+      <c r="G29" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
+        <v>BAJO</v>
       </c>
       <c r="H29">
         <v>1.1599999999999999</v>
@@ -1446,19 +1922,22 @@
         <v>34</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D30" s="5">
         <v>857</v>
       </c>
       <c r="E30" s="5">
-        <v>607</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
+        <v>586.77777777777783</v>
+      </c>
+      <c r="F30" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
+        <v>-0.31563849275772082</v>
+      </c>
+      <c r="G30" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
+        <v>BAJO</v>
       </c>
       <c r="H30">
         <v>1.1599999999999999</v>
@@ -1472,19 +1951,22 @@
         <v>35</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D31" s="5">
         <v>1068</v>
       </c>
       <c r="E31" s="5">
-        <v>788</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
+        <v>764.11111111111109</v>
+      </c>
+      <c r="F31" s="7">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
+        <v>-0.28435740977248003</v>
+      </c>
+      <c r="G31" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
+        <v>BAJO</v>
       </c>
       <c r="H31">
         <v>1.1599999999999999</v>
@@ -1498,19 +1980,22 @@
         <v>36</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D32" s="5">
         <v>685</v>
       </c>
       <c r="E32" s="5">
-        <v>522</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
+        <v>506.44444444444446</v>
+      </c>
+      <c r="F32" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
+        <v>-0.2607631516867186</v>
+      </c>
+      <c r="G32" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
+        <v>BAJO</v>
       </c>
       <c r="H32">
         <v>1.1599999999999999</v>
@@ -1524,19 +2009,22 @@
         <v>37</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D33" s="5">
         <v>209</v>
       </c>
       <c r="E33" s="5">
-        <v>189</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
+        <v>188.33333333333334</v>
+      </c>
+      <c r="F33" s="7">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
+        <v>-9.7706155632984792E-2</v>
+      </c>
+      <c r="G33" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
+        <v>BAJO</v>
       </c>
       <c r="H33">
         <v>1.1599999999999999</v>
@@ -1550,19 +2038,22 @@
         <v>38</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D34" s="5">
         <v>511</v>
       </c>
       <c r="E34" s="5">
-        <v>24</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
+        <v>47</v>
+      </c>
+      <c r="F34" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
+        <v>-0.9079825576221412</v>
+      </c>
+      <c r="G34" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
+        <v>BAJO</v>
       </c>
       <c r="H34">
         <v>1.1599999999999999</v>
@@ -1576,19 +2067,22 @@
         <v>39</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D35" s="5">
         <v>452</v>
       </c>
       <c r="E35" s="5">
-        <v>319</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
+        <v>320.88888888888891</v>
+      </c>
+      <c r="F35" s="7">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
+        <v>-0.29071078513457693</v>
+      </c>
+      <c r="G35" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
+        <v>BAJO</v>
       </c>
       <c r="H35">
         <v>1.1599999999999999</v>
@@ -1602,19 +2096,22 @@
         <v>49</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="D36" s="5">
         <v>341</v>
       </c>
       <c r="E36" s="5">
-        <v>213</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
+        <v>224.77777777777777</v>
+      </c>
+      <c r="F36" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
+        <v>-0.34065185185185187</v>
+      </c>
+      <c r="G36" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
+        <v>BAJO</v>
       </c>
       <c r="H36">
         <v>0.81</v>
@@ -1628,19 +2125,22 @@
         <v>40</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="D37" s="5">
         <v>506</v>
       </c>
       <c r="E37" s="5">
-        <v>430</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
+        <v>422.22222222222223</v>
+      </c>
+      <c r="F37" s="7">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
+        <v>-0.16616796329543193</v>
+      </c>
+      <c r="G37" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
+        <v>BAJO</v>
       </c>
       <c r="H37">
         <v>0.81</v>
@@ -1654,19 +2154,22 @@
         <v>41</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="D38" s="5">
         <v>277</v>
       </c>
       <c r="E38" s="5">
-        <v>231</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
+        <v>229.11111111111111</v>
+      </c>
+      <c r="F38" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
+        <v>-0.17342662439415468</v>
+      </c>
+      <c r="G38" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
+        <v>BAJO</v>
       </c>
       <c r="H38">
         <v>0.81</v>
@@ -1680,19 +2183,22 @@
         <v>42</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="D39" s="5">
         <v>295</v>
       </c>
       <c r="E39" s="5">
-        <v>286</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
+        <v>276</v>
+      </c>
+      <c r="F39" s="7">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
+        <v>-6.3107545131923959E-2</v>
+      </c>
+      <c r="G39" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
+        <v>BAJO</v>
       </c>
       <c r="H39">
         <v>0.81</v>
@@ -1706,19 +2212,22 @@
         <v>50</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="D40" s="5">
         <v>71</v>
       </c>
       <c r="E40" s="5">
-        <v>67</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
+        <v>60.333333333333336</v>
+      </c>
+      <c r="F40" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
+        <v>-0.15564037319762503</v>
+      </c>
+      <c r="G40" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
+        <v>BAJO</v>
       </c>
       <c r="H40">
         <v>2.62</v>
@@ -1732,19 +2241,22 @@
         <v>51</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="D41" s="5">
         <v>105</v>
       </c>
       <c r="E41" s="5">
-        <v>56</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
+        <v>52.777777777777779</v>
+      </c>
+      <c r="F41" s="7">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
+        <v>-0.49538847843932587</v>
+      </c>
+      <c r="G41" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
+        <v>BAJO</v>
       </c>
       <c r="H41">
         <v>2.62</v>
@@ -1758,19 +2270,22 @@
         <v>52</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="D42" s="5">
         <v>49</v>
       </c>
       <c r="E42" s="5">
-        <v>48</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
+        <v>43.777777777777779</v>
+      </c>
+      <c r="F42" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
+        <v>-0.10073659093266929</v>
+      </c>
+      <c r="G42" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
+        <v>BAJO</v>
       </c>
       <c r="H42">
         <v>2.62</v>
@@ -1784,19 +2299,22 @@
         <v>53</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="D43" s="5">
         <v>48</v>
       </c>
       <c r="E43" s="5">
-        <v>28</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
+        <v>28.888888888888889</v>
+      </c>
+      <c r="F43" s="7">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
+        <v>-0.39355385920271413</v>
+      </c>
+      <c r="G43" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
+        <v>BAJO</v>
       </c>
       <c r="H43">
         <v>2.62</v>
@@ -1810,19 +2328,22 @@
         <v>43</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D44" s="5">
         <v>1</v>
       </c>
       <c r="E44" s="5">
-        <v>0</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>56</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="F44" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
+        <v>-0.18518518518518512</v>
+      </c>
+      <c r="G44" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
+        <v>BAJO</v>
       </c>
       <c r="H44">
         <v>18</v>
@@ -1836,19 +2357,22 @@
         <v>44</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D45" s="5">
         <v>3</v>
       </c>
       <c r="E45" s="5">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
         <v>3</v>
       </c>
-      <c r="F45" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>55</v>
+      <c r="F45" s="7">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
+        <v>8.19672131147553E-2</v>
+      </c>
+      <c r="G45" s="8" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
+        <v>SUBIÓ</v>
       </c>
       <c r="H45">
         <v>18</v>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2106A901-6B61-4F15-B811-F5588D293DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{682E183E-C311-4137-81BE-522A59A8C017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1116,8 +1116,8 @@
         <v>1045</v>
       </c>
       <c r="E2" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1047.7777777777778</v>
+        <f ca="1">ROUND('[1]DESV. VTS BY SKU'!$F$4,'[1]DESV. VTS BY SKU'!$F$4)</f>
+        <v>1047.7777777777801</v>
       </c>
       <c r="F2" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{682E183E-C311-4137-81BE-522A59A8C017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{684841E5-1537-46DF-A9DD-51FBC995C8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -365,6 +365,7 @@
       <sheetName val="INVENTARIO NACIONAL 10-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 13-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 14-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 15-07-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -373,10 +374,10 @@
       <sheetData sheetId="3">
         <row r="4">
           <cell r="F4">
-            <v>1047.7777777777778</v>
+            <v>1056.2</v>
           </cell>
           <cell r="G4">
-            <v>2.5709425500659577E-3</v>
+            <v>1.062978427279071E-2</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -384,10 +385,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>75</v>
+            <v>75.7</v>
           </cell>
           <cell r="G5">
-            <v>-1.2567324955116699E-2</v>
+            <v>-3.3512866546977493E-3</v>
           </cell>
           <cell r="H5" t="str">
             <v>BAJO</v>
@@ -395,10 +396,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>473.44444444444446</v>
+            <v>470.1</v>
           </cell>
           <cell r="G6">
-            <v>-3.1360757204707657E-2</v>
+            <v>-3.8203292104528885E-2</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -406,32 +407,32 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>88.555555555555557</v>
+            <v>94.7</v>
           </cell>
           <cell r="G7">
-            <v>-3.073521282476499E-2</v>
+            <v>3.6517412935323401E-2</v>
           </cell>
           <cell r="H7" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="8">
           <cell r="F8">
-            <v>15.444444444444445</v>
+            <v>16.399999999999999</v>
           </cell>
           <cell r="G8">
-            <v>-3.1972143083254245E-2</v>
+            <v>2.7920227920227747E-2</v>
           </cell>
           <cell r="H8" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1142</v>
+            <v>1143.7</v>
           </cell>
           <cell r="G9">
-            <v>-0.20771971870959605</v>
+            <v>-0.20654031724007449</v>
           </cell>
           <cell r="H9" t="str">
             <v>BAJO</v>
@@ -439,10 +440,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>101.44444444444444</v>
+            <v>109.2</v>
           </cell>
           <cell r="G10">
-            <v>-0.23673810609515122</v>
+            <v>-0.17838577291381663</v>
           </cell>
           <cell r="H10" t="str">
             <v>BAJO</v>
@@ -450,10 +451,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>257.11111111111109</v>
+            <v>276.3</v>
           </cell>
           <cell r="G11">
-            <v>-0.226944862041213</v>
+            <v>-0.1692496924969249</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -461,10 +462,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>560</v>
+            <v>582.29999999999995</v>
           </cell>
           <cell r="G12">
-            <v>-0.21543654078838437</v>
+            <v>-0.18419410303763617</v>
           </cell>
           <cell r="H12" t="str">
             <v>BAJO</v>
@@ -472,10 +473,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>325.88888888888891</v>
+            <v>346.8</v>
           </cell>
           <cell r="G13">
-            <v>-0.31880707310636047</v>
+            <v>-0.27509738717339671</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -483,10 +484,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>2734.7777777777778</v>
+            <v>2825.6</v>
           </cell>
           <cell r="G14">
-            <v>-0.21705887030891913</v>
+            <v>-0.19105732318303081</v>
           </cell>
           <cell r="H14" t="str">
             <v>BAJO</v>
@@ -494,10 +495,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>1864.2222222222222</v>
+            <v>1950.2</v>
           </cell>
           <cell r="G15">
-            <v>-0.16392365782833429</v>
+            <v>-0.12536388469849546</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -505,10 +506,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>1825.4444444444443</v>
+            <v>1891.7</v>
           </cell>
           <cell r="G16">
-            <v>-0.2083779586884198</v>
+            <v>-0.17964558159705113</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -516,10 +517,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2000</v>
+            <v>2103.1</v>
           </cell>
           <cell r="G17">
-            <v>-0.26150954163239959</v>
+            <v>-0.22344035850354982</v>
           </cell>
           <cell r="H17" t="str">
             <v>BAJO</v>
@@ -527,10 +528,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>106.88888888888889</v>
+            <v>113.2</v>
           </cell>
           <cell r="G18">
-            <v>-0.3858564754360001</v>
+            <v>-0.34959519456777222</v>
           </cell>
           <cell r="H18" t="str">
             <v>BAJO</v>
@@ -538,10 +539,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>165.11111111111111</v>
+            <v>180.3</v>
           </cell>
           <cell r="G19">
-            <v>-0.23057732589611424</v>
+            <v>-0.15979665325142978</v>
           </cell>
           <cell r="H19" t="str">
             <v>BAJO</v>
@@ -549,10 +550,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>154.22222222222223</v>
+            <v>153.6</v>
           </cell>
           <cell r="G20">
-            <v>0.21217895280060328</v>
+            <v>0.20728831725616281</v>
           </cell>
           <cell r="H20" t="str">
             <v>SUBIÓ</v>
@@ -560,10 +561,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>396.66666666666669</v>
+            <v>436.6</v>
           </cell>
           <cell r="G21">
-            <v>-0.18074852922768803</v>
+            <v>-9.8272624859181312E-2</v>
           </cell>
           <cell r="H21" t="str">
             <v>BAJO</v>
@@ -571,10 +572,10 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>643.77777777777783</v>
+            <v>664.1</v>
           </cell>
           <cell r="G22">
-            <v>-0.17339143742785623</v>
+            <v>-0.147297770514766</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -582,10 +583,10 @@
         </row>
         <row r="23">
           <cell r="F23">
-            <v>11.222222222222221</v>
+            <v>10.3</v>
           </cell>
           <cell r="G23">
-            <v>-0.79511295527893044</v>
+            <v>-0.81195020746887969</v>
           </cell>
           <cell r="H23" t="str">
             <v>BAJO</v>
@@ -593,21 +594,21 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>27.777777777777779</v>
+            <v>60</v>
           </cell>
           <cell r="G24">
-            <v>-0.33211900425015184</v>
+            <v>0.44262295081967196</v>
           </cell>
           <cell r="H24" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="25">
           <cell r="F25">
-            <v>555.77777777777783</v>
+            <v>565.1</v>
           </cell>
           <cell r="G25">
-            <v>-0.35960241391551295</v>
+            <v>-0.3488608390509611</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -626,10 +627,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>391.33333333333331</v>
+            <v>418.4</v>
           </cell>
           <cell r="G27">
-            <v>-0.28273487183759627</v>
+            <v>-0.23312505207031586</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -637,10 +638,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>310.66666666666669</v>
+            <v>327.60000000000002</v>
           </cell>
           <cell r="G28">
-            <v>-0.3835978835978836</v>
+            <v>-0.35</v>
           </cell>
           <cell r="H28" t="str">
             <v>BAJO</v>
@@ -648,10 +649,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>99.555555555555557</v>
+            <v>104.7</v>
           </cell>
           <cell r="G29">
-            <v>-0.23579126928743122</v>
+            <v>-0.19630146545708305</v>
           </cell>
           <cell r="H29" t="str">
             <v>BAJO</v>
@@ -659,10 +660,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>112.88888888888889</v>
+            <v>117.3</v>
           </cell>
           <cell r="G30">
-            <v>-0.20931055219498396</v>
+            <v>-0.17841451766953209</v>
           </cell>
           <cell r="H30" t="str">
             <v>BAJO</v>
@@ -670,10 +671,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>706.33333333333337</v>
+            <v>731</v>
           </cell>
           <cell r="G31">
-            <v>-0.17079331198861614</v>
+            <v>-0.1418356456776948</v>
           </cell>
           <cell r="H31" t="str">
             <v>BAJO</v>
@@ -681,10 +682,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>586.77777777777783</v>
+            <v>614</v>
           </cell>
           <cell r="G32">
-            <v>-0.31563849275772082</v>
+            <v>-0.28388909505380899</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -692,10 +693,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>764.11111111111109</v>
+            <v>770.4</v>
           </cell>
           <cell r="G33">
-            <v>-0.28435740977248003</v>
+            <v>-0.27846743295019161</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -703,10 +704,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>506.44444444444446</v>
+            <v>512.9</v>
           </cell>
           <cell r="G34">
-            <v>-0.2607631516867186</v>
+            <v>-0.25134023354564761</v>
           </cell>
           <cell r="H34" t="str">
             <v>BAJO</v>
@@ -714,10 +715,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>188.33333333333334</v>
+            <v>193.7</v>
           </cell>
           <cell r="G35">
-            <v>-9.7706155632984792E-2</v>
+            <v>-7.1994773519163835E-2</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -725,10 +726,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>47</v>
+            <v>64.7</v>
           </cell>
           <cell r="G36">
-            <v>-0.9079825576221412</v>
+            <v>-0.87332918038622409</v>
           </cell>
           <cell r="H36" t="str">
             <v>BAJO</v>
@@ -736,10 +737,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>320.88888888888891</v>
+            <v>364.9</v>
           </cell>
           <cell r="G37">
-            <v>-0.29071078513457693</v>
+            <v>-0.19342911684919128</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -747,10 +748,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>224.77777777777777</v>
+            <v>241.8</v>
           </cell>
           <cell r="G38">
-            <v>-0.34065185185185187</v>
+            <v>-0.29071999999999998</v>
           </cell>
           <cell r="H38" t="str">
             <v>BAJO</v>
@@ -758,10 +759,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>422.22222222222223</v>
+            <v>428.4</v>
           </cell>
           <cell r="G39">
-            <v>-0.16616796329543193</v>
+            <v>-0.15396768402154404</v>
           </cell>
           <cell r="H39" t="str">
             <v>BAJO</v>
@@ -769,10 +770,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>229.11111111111111</v>
+            <v>238.2</v>
           </cell>
           <cell r="G40">
-            <v>-0.17342662439415468</v>
+            <v>-0.14063627418825853</v>
           </cell>
           <cell r="H40" t="str">
             <v>BAJO</v>
@@ -780,10 +781,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>276</v>
+            <v>277.2</v>
           </cell>
           <cell r="G41">
-            <v>-6.3107545131923959E-2</v>
+            <v>-5.9034099675975837E-2</v>
           </cell>
           <cell r="H41" t="str">
             <v>BAJO</v>
@@ -791,10 +792,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>60.333333333333336</v>
+            <v>62.6</v>
           </cell>
           <cell r="G42">
-            <v>-0.15564037319762503</v>
+            <v>-0.12391857506361315</v>
           </cell>
           <cell r="H42" t="str">
             <v>BAJO</v>
@@ -802,10 +803,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>52.777777777777779</v>
+            <v>57.1</v>
           </cell>
           <cell r="G43">
-            <v>-0.49538847843932587</v>
+            <v>-0.45406345067362019</v>
           </cell>
           <cell r="H43" t="str">
             <v>BAJO</v>
@@ -813,10 +814,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>43.777777777777779</v>
+            <v>46.6</v>
           </cell>
           <cell r="G44">
-            <v>-0.10073659093266929</v>
+            <v>-4.2763772175536841E-2</v>
           </cell>
           <cell r="H44" t="str">
             <v>BAJO</v>
@@ -824,10 +825,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>28.888888888888889</v>
+            <v>32.299999999999997</v>
           </cell>
           <cell r="G45">
-            <v>-0.39355385920271413</v>
+            <v>-0.32194656488549622</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -835,10 +836,10 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>0.44444444444444442</v>
+            <v>0.4</v>
           </cell>
           <cell r="G46">
-            <v>-0.18518518518518512</v>
+            <v>-0.26666666666666661</v>
           </cell>
           <cell r="H46" t="str">
             <v>BAJO</v>
@@ -846,13 +847,13 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>3</v>
+            <v>2.7</v>
           </cell>
           <cell r="G47">
-            <v>8.19672131147553E-2</v>
+            <v>-2.6229508196720208E-2</v>
           </cell>
           <cell r="H47" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
       </sheetData>
@@ -864,6 +865,7 @@
       <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1116,12 +1118,12 @@
         <v>1045</v>
       </c>
       <c r="E2" s="5">
-        <f ca="1">ROUND('[1]DESV. VTS BY SKU'!$F$4,'[1]DESV. VTS BY SKU'!$F$4)</f>
-        <v>1047.7777777777801</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!$F$4</f>
+        <v>1056.2</v>
       </c>
       <c r="F2" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>2.5709425500659577E-3</v>
+        <v>1.062978427279071E-2</v>
       </c>
       <c r="G2" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1146,11 +1148,11 @@
       </c>
       <c r="E3" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>75</v>
+        <v>75.7</v>
       </c>
       <c r="F3" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-1.2567324955116699E-2</v>
+        <v>-3.3512866546977493E-3</v>
       </c>
       <c r="G3" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1175,11 +1177,11 @@
       </c>
       <c r="E4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>473.44444444444446</v>
+        <v>470.1</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-3.1360757204707657E-2</v>
+        <v>-3.8203292104528885E-2</v>
       </c>
       <c r="G4" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1204,15 +1206,15 @@
       </c>
       <c r="E5" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>88.555555555555557</v>
+        <v>94.7</v>
       </c>
       <c r="F5" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>-3.073521282476499E-2</v>
+        <v>3.6517412935323401E-2</v>
       </c>
       <c r="G5" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H5">
         <v>3.61</v>
@@ -1233,15 +1235,15 @@
       </c>
       <c r="E6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>15.444444444444445</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="F6" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>-3.1972143083254245E-2</v>
+        <v>2.7920227920227747E-2</v>
       </c>
       <c r="G6" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H6">
         <v>8.7799999999999994</v>
@@ -1262,11 +1264,11 @@
       </c>
       <c r="E7" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1142</v>
+        <v>1143.7</v>
       </c>
       <c r="F7" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>-0.20771971870959605</v>
+        <v>-0.20654031724007449</v>
       </c>
       <c r="G7" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1291,11 +1293,11 @@
       </c>
       <c r="E8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>101.44444444444444</v>
+        <v>109.2</v>
       </c>
       <c r="F8" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-0.23673810609515122</v>
+        <v>-0.17838577291381663</v>
       </c>
       <c r="G8" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1320,11 +1322,11 @@
       </c>
       <c r="E9" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>257.11111111111109</v>
+        <v>276.3</v>
       </c>
       <c r="F9" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-0.226944862041213</v>
+        <v>-0.1692496924969249</v>
       </c>
       <c r="G9" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1349,11 +1351,11 @@
       </c>
       <c r="E10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>560</v>
+        <v>582.29999999999995</v>
       </c>
       <c r="F10" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>-0.21543654078838437</v>
+        <v>-0.18419410303763617</v>
       </c>
       <c r="G10" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1378,11 +1380,11 @@
       </c>
       <c r="E11" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>325.88888888888891</v>
+        <v>346.8</v>
       </c>
       <c r="F11" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.31880707310636047</v>
+        <v>-0.27509738717339671</v>
       </c>
       <c r="G11" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1407,11 +1409,11 @@
       </c>
       <c r="E12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>2734.7777777777778</v>
+        <v>2825.6</v>
       </c>
       <c r="F12" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-0.21705887030891913</v>
+        <v>-0.19105732318303081</v>
       </c>
       <c r="G12" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1436,11 +1438,11 @@
       </c>
       <c r="E13" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>1864.2222222222222</v>
+        <v>1950.2</v>
       </c>
       <c r="F13" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-0.16392365782833429</v>
+        <v>-0.12536388469849546</v>
       </c>
       <c r="G13" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1465,11 +1467,11 @@
       </c>
       <c r="E14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>1825.4444444444443</v>
+        <v>1891.7</v>
       </c>
       <c r="F14" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-0.2083779586884198</v>
+        <v>-0.17964558159705113</v>
       </c>
       <c r="G14" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1494,11 +1496,11 @@
       </c>
       <c r="E15" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2000</v>
+        <v>2103.1</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-0.26150954163239959</v>
+        <v>-0.22344035850354982</v>
       </c>
       <c r="G15" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1523,11 +1525,11 @@
       </c>
       <c r="E16" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>106.88888888888889</v>
+        <v>113.2</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.3858564754360001</v>
+        <v>-0.34959519456777222</v>
       </c>
       <c r="G16" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1552,11 +1554,11 @@
       </c>
       <c r="E17" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>165.11111111111111</v>
+        <v>180.3</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>-0.23057732589611424</v>
+        <v>-0.15979665325142978</v>
       </c>
       <c r="G17" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1581,11 +1583,11 @@
       </c>
       <c r="E18" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>154.22222222222223</v>
+        <v>153.6</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>0.21217895280060328</v>
+        <v>0.20728831725616281</v>
       </c>
       <c r="G18" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1610,11 +1612,11 @@
       </c>
       <c r="E19" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>396.66666666666669</v>
+        <v>436.6</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>-0.18074852922768803</v>
+        <v>-9.8272624859181312E-2</v>
       </c>
       <c r="G19" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1639,11 +1641,11 @@
       </c>
       <c r="E20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>643.77777777777783</v>
+        <v>664.1</v>
       </c>
       <c r="F20" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-0.17339143742785623</v>
+        <v>-0.147297770514766</v>
       </c>
       <c r="G20" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1668,11 +1670,11 @@
       </c>
       <c r="E21" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>11.222222222222221</v>
+        <v>10.3</v>
       </c>
       <c r="F21" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>-0.79511295527893044</v>
+        <v>-0.81195020746887969</v>
       </c>
       <c r="G21" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
@@ -1697,15 +1699,15 @@
       </c>
       <c r="E22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>27.777777777777779</v>
+        <v>60</v>
       </c>
       <c r="F22" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>-0.33211900425015184</v>
+        <v>0.44262295081967196</v>
       </c>
       <c r="G22" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H22">
         <v>4.1500000000000004</v>
@@ -1726,11 +1728,11 @@
       </c>
       <c r="E23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>555.77777777777783</v>
+        <v>565.1</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-0.35960241391551295</v>
+        <v>-0.3488608390509611</v>
       </c>
       <c r="G23" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1784,11 +1786,11 @@
       </c>
       <c r="E25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>391.33333333333331</v>
+        <v>418.4</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.28273487183759627</v>
+        <v>-0.23312505207031586</v>
       </c>
       <c r="G25" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1813,11 +1815,11 @@
       </c>
       <c r="E26" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>310.66666666666669</v>
+        <v>327.60000000000002</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-0.3835978835978836</v>
+        <v>-0.35</v>
       </c>
       <c r="G26" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1842,11 +1844,11 @@
       </c>
       <c r="E27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>99.555555555555557</v>
+        <v>104.7</v>
       </c>
       <c r="F27" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>-0.23579126928743122</v>
+        <v>-0.19630146545708305</v>
       </c>
       <c r="G27" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1871,11 +1873,11 @@
       </c>
       <c r="E28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>112.88888888888889</v>
+        <v>117.3</v>
       </c>
       <c r="F28" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>-0.20931055219498396</v>
+        <v>-0.17841451766953209</v>
       </c>
       <c r="G28" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1900,11 +1902,11 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>706.33333333333337</v>
+        <v>731</v>
       </c>
       <c r="F29" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-0.17079331198861614</v>
+        <v>-0.1418356456776948</v>
       </c>
       <c r="G29" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1929,11 +1931,11 @@
       </c>
       <c r="E30" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>586.77777777777783</v>
+        <v>614</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-0.31563849275772082</v>
+        <v>-0.28388909505380899</v>
       </c>
       <c r="G30" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -1958,11 +1960,11 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>764.11111111111109</v>
+        <v>770.4</v>
       </c>
       <c r="F31" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-0.28435740977248003</v>
+        <v>-0.27846743295019161</v>
       </c>
       <c r="G31" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -1987,11 +1989,11 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>506.44444444444446</v>
+        <v>512.9</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-0.2607631516867186</v>
+        <v>-0.25134023354564761</v>
       </c>
       <c r="G32" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2016,11 +2018,11 @@
       </c>
       <c r="E33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>188.33333333333334</v>
+        <v>193.7</v>
       </c>
       <c r="F33" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-9.7706155632984792E-2</v>
+        <v>-7.1994773519163835E-2</v>
       </c>
       <c r="G33" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2045,11 +2047,11 @@
       </c>
       <c r="E34" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>47</v>
+        <v>64.7</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-0.9079825576221412</v>
+        <v>-0.87332918038622409</v>
       </c>
       <c r="G34" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2074,11 +2076,11 @@
       </c>
       <c r="E35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>320.88888888888891</v>
+        <v>364.9</v>
       </c>
       <c r="F35" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.29071078513457693</v>
+        <v>-0.19342911684919128</v>
       </c>
       <c r="G35" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2103,11 +2105,11 @@
       </c>
       <c r="E36" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>224.77777777777777</v>
+        <v>241.8</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>-0.34065185185185187</v>
+        <v>-0.29071999999999998</v>
       </c>
       <c r="G36" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2132,11 +2134,11 @@
       </c>
       <c r="E37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>422.22222222222223</v>
+        <v>428.4</v>
       </c>
       <c r="F37" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>-0.16616796329543193</v>
+        <v>-0.15396768402154404</v>
       </c>
       <c r="G37" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2161,11 +2163,11 @@
       </c>
       <c r="E38" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>229.11111111111111</v>
+        <v>238.2</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>-0.17342662439415468</v>
+        <v>-0.14063627418825853</v>
       </c>
       <c r="G38" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2190,11 +2192,11 @@
       </c>
       <c r="E39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>276</v>
+        <v>277.2</v>
       </c>
       <c r="F39" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-6.3107545131923959E-2</v>
+        <v>-5.9034099675975837E-2</v>
       </c>
       <c r="G39" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2219,11 +2221,11 @@
       </c>
       <c r="E40" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>60.333333333333336</v>
+        <v>62.6</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>-0.15564037319762503</v>
+        <v>-0.12391857506361315</v>
       </c>
       <c r="G40" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2248,11 +2250,11 @@
       </c>
       <c r="E41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>52.777777777777779</v>
+        <v>57.1</v>
       </c>
       <c r="F41" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.49538847843932587</v>
+        <v>-0.45406345067362019</v>
       </c>
       <c r="G41" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2277,11 +2279,11 @@
       </c>
       <c r="E42" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>43.777777777777779</v>
+        <v>46.6</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-0.10073659093266929</v>
+        <v>-4.2763772175536841E-2</v>
       </c>
       <c r="G42" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2306,11 +2308,11 @@
       </c>
       <c r="E43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>28.888888888888889</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="F43" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-0.39355385920271413</v>
+        <v>-0.32194656488549622</v>
       </c>
       <c r="G43" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2335,11 +2337,11 @@
       </c>
       <c r="E44" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>0.44444444444444442</v>
+        <v>0.4</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>-0.18518518518518512</v>
+        <v>-0.26666666666666661</v>
       </c>
       <c r="G44" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
@@ -2364,15 +2366,15 @@
       </c>
       <c r="E45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="F45" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>8.19672131147553E-2</v>
+        <v>-2.6229508196720208E-2</v>
       </c>
       <c r="G45" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H45">
         <v>18</v>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{684841E5-1537-46DF-A9DD-51FBC995C8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C67290D-6BD4-4F10-988A-039B1DDE532F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -366,6 +366,8 @@
       <sheetName val="INVENTARIO NACIONAL 13-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 14-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 15-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 16-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 17-07-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -374,10 +376,10 @@
       <sheetData sheetId="3">
         <row r="4">
           <cell r="F4">
-            <v>1056.2</v>
+            <v>1045.5</v>
           </cell>
           <cell r="G4">
-            <v>1.062978427279071E-2</v>
+            <v>3.9144050104389372E-4</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -385,10 +387,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>75.7</v>
+            <v>72.5</v>
           </cell>
           <cell r="G5">
-            <v>-3.3512866546977493E-3</v>
+            <v>-4.548174745661282E-2</v>
           </cell>
           <cell r="H5" t="str">
             <v>BAJO</v>
@@ -396,10 +398,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>470.1</v>
+            <v>477.08333333333331</v>
           </cell>
           <cell r="G6">
-            <v>-3.8203292104528885E-2</v>
+            <v>-2.3915806441613174E-2</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -407,10 +409,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>94.7</v>
+            <v>99.916666666666671</v>
           </cell>
           <cell r="G7">
-            <v>3.6517412935323401E-2</v>
+            <v>9.3615257048093037E-2</v>
           </cell>
           <cell r="H7" t="str">
             <v>SUBIÓ</v>
@@ -418,10 +420,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>16.399999999999999</v>
+            <v>17.833333333333332</v>
           </cell>
           <cell r="G8">
-            <v>2.7920227920227747E-2</v>
+            <v>0.11775878442545107</v>
           </cell>
           <cell r="H8" t="str">
             <v>SUBIÓ</v>
@@ -429,10 +431,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1143.7</v>
+            <v>1160.0833333333333</v>
           </cell>
           <cell r="G9">
-            <v>-0.20654031724007449</v>
+            <v>-0.1951741246465476</v>
           </cell>
           <cell r="H9" t="str">
             <v>BAJO</v>
@@ -440,10 +442,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>109.2</v>
+            <v>121.91666666666667</v>
           </cell>
           <cell r="G10">
-            <v>-0.17838577291381663</v>
+            <v>-8.2706338349293196E-2</v>
           </cell>
           <cell r="H10" t="str">
             <v>BAJO</v>
@@ -451,10 +453,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>276.3</v>
+            <v>290.75</v>
           </cell>
           <cell r="G11">
-            <v>-0.1692496924969249</v>
+            <v>-0.12580292469591359</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -462,10 +464,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>582.29999999999995</v>
+            <v>608.58333333333337</v>
           </cell>
           <cell r="G12">
-            <v>-0.18419410303763617</v>
+            <v>-0.14737099068118609</v>
           </cell>
           <cell r="H12" t="str">
             <v>BAJO</v>
@@ -473,10 +475,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>346.8</v>
+            <v>350.08333333333331</v>
           </cell>
           <cell r="G13">
-            <v>-0.27509738717339671</v>
+            <v>-0.26823436262866196</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -484,10 +486,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>2825.6</v>
+            <v>2874.6666666666665</v>
           </cell>
           <cell r="G14">
-            <v>-0.19105732318303081</v>
+            <v>-0.17700999848179244</v>
           </cell>
           <cell r="H14" t="str">
             <v>BAJO</v>
@@ -495,10 +497,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>1950.2</v>
+            <v>1975.1666666666667</v>
           </cell>
           <cell r="G15">
-            <v>-0.12536388469849546</v>
+            <v>-0.11416670064282886</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -506,10 +508,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>1891.7</v>
+            <v>1911.6666666666667</v>
           </cell>
           <cell r="G16">
-            <v>-0.17964558159705113</v>
+            <v>-0.17098683907932688</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -517,10 +519,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2103.1</v>
+            <v>2135.8333333333335</v>
           </cell>
           <cell r="G17">
-            <v>-0.22344035850354982</v>
+            <v>-0.21135373133493329</v>
           </cell>
           <cell r="H17" t="str">
             <v>BAJO</v>
@@ -528,10 +530,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>113.2</v>
+            <v>121.16666666666667</v>
           </cell>
           <cell r="G18">
-            <v>-0.34959519456777222</v>
+            <v>-0.3038217114999564</v>
           </cell>
           <cell r="H18" t="str">
             <v>BAJO</v>
@@ -539,10 +541,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>180.3</v>
+            <v>192.66666666666666</v>
           </cell>
           <cell r="G19">
-            <v>-0.15979665325142978</v>
+            <v>-0.1021676198545507</v>
           </cell>
           <cell r="H19" t="str">
             <v>BAJO</v>
@@ -550,10 +552,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>153.6</v>
+            <v>153.5</v>
           </cell>
           <cell r="G20">
-            <v>0.20728831725616281</v>
+            <v>0.20650232225794918</v>
           </cell>
           <cell r="H20" t="str">
             <v>SUBIÓ</v>
@@ -561,10 +563,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>436.6</v>
+            <v>452.25</v>
           </cell>
           <cell r="G21">
-            <v>-9.8272624859181312E-2</v>
+            <v>-6.5950056327450213E-2</v>
           </cell>
           <cell r="H21" t="str">
             <v>BAJO</v>
@@ -572,10 +574,10 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>664.1</v>
+            <v>766.66666666666663</v>
           </cell>
           <cell r="G22">
-            <v>-0.147297770514766</v>
+            <v>-1.56025057390764E-2</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -583,10 +585,10 @@
         </row>
         <row r="23">
           <cell r="F23">
-            <v>10.3</v>
+            <v>9</v>
           </cell>
           <cell r="G23">
-            <v>-0.81195020746887969</v>
+            <v>-0.83568464730290459</v>
           </cell>
           <cell r="H23" t="str">
             <v>BAJO</v>
@@ -594,10 +596,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>60</v>
+            <v>50</v>
           </cell>
           <cell r="G24">
-            <v>0.44262295081967196</v>
+            <v>0.20218579234972678</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -605,10 +607,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>565.1</v>
+            <v>573</v>
           </cell>
           <cell r="G25">
-            <v>-0.3488608390509611</v>
+            <v>-0.33975802650185938</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -616,10 +618,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>944</v>
+            <v>949</v>
           </cell>
           <cell r="G26">
-            <v>-0.31720147290899525</v>
+            <v>-0.31358495528669117</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -627,10 +629,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>418.4</v>
+            <v>430.66666666666669</v>
           </cell>
           <cell r="G27">
-            <v>-0.23312505207031586</v>
+            <v>-0.2106417839984448</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -638,10 +640,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>327.60000000000002</v>
+            <v>343.41666666666669</v>
           </cell>
           <cell r="G28">
-            <v>-0.35</v>
+            <v>-0.31861772486772488</v>
           </cell>
           <cell r="H28" t="str">
             <v>BAJO</v>
@@ -649,10 +651,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>104.7</v>
+            <v>107.41666666666667</v>
           </cell>
           <cell r="G29">
-            <v>-0.19630146545708305</v>
+            <v>-0.17544777855315186</v>
           </cell>
           <cell r="H29" t="str">
             <v>BAJO</v>
@@ -660,10 +662,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>117.3</v>
+            <v>111.83333333333333</v>
           </cell>
           <cell r="G30">
-            <v>-0.17841451766953209</v>
+            <v>-0.21670380982701909</v>
           </cell>
           <cell r="H30" t="str">
             <v>BAJO</v>
@@ -671,10 +673,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>731</v>
+            <v>747.75</v>
           </cell>
           <cell r="G31">
-            <v>-0.1418356456776948</v>
+            <v>-0.12217182497331913</v>
           </cell>
           <cell r="H31" t="str">
             <v>BAJO</v>
@@ -682,10 +684,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>614</v>
+            <v>628.41666666666663</v>
           </cell>
           <cell r="G32">
-            <v>-0.28388909505380899</v>
+            <v>-0.26707487320857415</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -693,10 +695,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>770.4</v>
+            <v>798.16666666666663</v>
           </cell>
           <cell r="G33">
-            <v>-0.27846743295019161</v>
+            <v>-0.25246204058464605</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -704,10 +706,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>512.9</v>
+            <v>525.25</v>
           </cell>
           <cell r="G34">
-            <v>-0.25134023354564761</v>
+            <v>-0.23331342887473461</v>
           </cell>
           <cell r="H34" t="str">
             <v>BAJO</v>
@@ -715,10 +717,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>193.7</v>
+            <v>205.16666666666666</v>
           </cell>
           <cell r="G35">
-            <v>-7.1994773519163835E-2</v>
+            <v>-1.7058652729384449E-2</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -726,10 +728,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>64.7</v>
+            <v>58.5</v>
           </cell>
           <cell r="G36">
-            <v>-0.87332918038622409</v>
+            <v>-0.88546765150840967</v>
           </cell>
           <cell r="H36" t="str">
             <v>BAJO</v>
@@ -737,10 +739,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>364.9</v>
+            <v>357.58333333333331</v>
           </cell>
           <cell r="G37">
-            <v>-0.19342911684919128</v>
+            <v>-0.20960179510365395</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -748,10 +750,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>241.8</v>
+            <v>249.5</v>
           </cell>
           <cell r="G38">
-            <v>-0.29071999999999998</v>
+            <v>-0.26813333333333333</v>
           </cell>
           <cell r="H38" t="str">
             <v>BAJO</v>
@@ -759,10 +761,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>428.4</v>
+            <v>414.58333333333331</v>
           </cell>
           <cell r="G39">
-            <v>-0.15396768402154404</v>
+            <v>-0.18125374027528429</v>
           </cell>
           <cell r="H39" t="str">
             <v>BAJO</v>
@@ -770,10 +772,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>238.2</v>
+            <v>234.91666666666666</v>
           </cell>
           <cell r="G40">
-            <v>-0.14063627418825853</v>
+            <v>-0.15248168798513184</v>
           </cell>
           <cell r="H40" t="str">
             <v>BAJO</v>
@@ -781,10 +783,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>277.2</v>
+            <v>275.25</v>
           </cell>
           <cell r="G41">
-            <v>-5.9034099675975837E-2</v>
+            <v>-6.565344854189159E-2</v>
           </cell>
           <cell r="H41" t="str">
             <v>BAJO</v>
@@ -792,10 +794,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>62.6</v>
+            <v>58.75</v>
           </cell>
           <cell r="G42">
-            <v>-0.12391857506361315</v>
+            <v>-0.17779898218829515</v>
           </cell>
           <cell r="H42" t="str">
             <v>BAJO</v>
@@ -803,10 +805,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>57.1</v>
+            <v>64.083333333333329</v>
           </cell>
           <cell r="G43">
-            <v>-0.45406345067362019</v>
+            <v>-0.38729537882080256</v>
           </cell>
           <cell r="H43" t="str">
             <v>BAJO</v>
@@ -814,10 +816,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>46.6</v>
+            <v>43.583333333333336</v>
           </cell>
           <cell r="G44">
-            <v>-4.2763772175536841E-2</v>
+            <v>-0.10473078120136936</v>
           </cell>
           <cell r="H44" t="str">
             <v>BAJO</v>
@@ -825,10 +827,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>32.299999999999997</v>
+            <v>32.416666666666664</v>
           </cell>
           <cell r="G45">
-            <v>-0.32194656488549622</v>
+            <v>-0.31949745547073793</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -836,24 +838,24 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>0.4</v>
+            <v>0.75</v>
           </cell>
           <cell r="G46">
-            <v>-0.26666666666666661</v>
+            <v>0.375</v>
           </cell>
           <cell r="H46" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="47">
           <cell r="F47">
-            <v>2.7</v>
+            <v>3</v>
           </cell>
           <cell r="G47">
-            <v>-2.6229508196720208E-2</v>
+            <v>8.19672131147553E-2</v>
           </cell>
           <cell r="H47" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
       </sheetData>
@@ -866,6 +868,8 @@
       <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
       <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1119,11 +1123,11 @@
       </c>
       <c r="E2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!$F$4</f>
-        <v>1056.2</v>
+        <v>1045.5</v>
       </c>
       <c r="F2" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>1.062978427279071E-2</v>
+        <v>3.9144050104389372E-4</v>
       </c>
       <c r="G2" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1148,11 +1152,11 @@
       </c>
       <c r="E3" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>75.7</v>
+        <v>72.5</v>
       </c>
       <c r="F3" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-3.3512866546977493E-3</v>
+        <v>-4.548174745661282E-2</v>
       </c>
       <c r="G3" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1177,11 +1181,11 @@
       </c>
       <c r="E4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>470.1</v>
+        <v>477.08333333333331</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-3.8203292104528885E-2</v>
+        <v>-2.3915806441613174E-2</v>
       </c>
       <c r="G4" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1206,11 +1210,11 @@
       </c>
       <c r="E5" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>94.7</v>
+        <v>99.916666666666671</v>
       </c>
       <c r="F5" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>3.6517412935323401E-2</v>
+        <v>9.3615257048093037E-2</v>
       </c>
       <c r="G5" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1235,11 +1239,11 @@
       </c>
       <c r="E6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>16.399999999999999</v>
+        <v>17.833333333333332</v>
       </c>
       <c r="F6" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>2.7920227920227747E-2</v>
+        <v>0.11775878442545107</v>
       </c>
       <c r="G6" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1264,11 +1268,11 @@
       </c>
       <c r="E7" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1143.7</v>
+        <v>1160.0833333333333</v>
       </c>
       <c r="F7" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>-0.20654031724007449</v>
+        <v>-0.1951741246465476</v>
       </c>
       <c r="G7" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1293,11 +1297,11 @@
       </c>
       <c r="E8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>109.2</v>
+        <v>121.91666666666667</v>
       </c>
       <c r="F8" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-0.17838577291381663</v>
+        <v>-8.2706338349293196E-2</v>
       </c>
       <c r="G8" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1322,11 +1326,11 @@
       </c>
       <c r="E9" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>276.3</v>
+        <v>290.75</v>
       </c>
       <c r="F9" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-0.1692496924969249</v>
+        <v>-0.12580292469591359</v>
       </c>
       <c r="G9" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1351,11 +1355,11 @@
       </c>
       <c r="E10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>582.29999999999995</v>
+        <v>608.58333333333337</v>
       </c>
       <c r="F10" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>-0.18419410303763617</v>
+        <v>-0.14737099068118609</v>
       </c>
       <c r="G10" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1380,11 +1384,11 @@
       </c>
       <c r="E11" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>346.8</v>
+        <v>350.08333333333331</v>
       </c>
       <c r="F11" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.27509738717339671</v>
+        <v>-0.26823436262866196</v>
       </c>
       <c r="G11" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1409,11 +1413,11 @@
       </c>
       <c r="E12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>2825.6</v>
+        <v>2874.6666666666665</v>
       </c>
       <c r="F12" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-0.19105732318303081</v>
+        <v>-0.17700999848179244</v>
       </c>
       <c r="G12" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1438,11 +1442,11 @@
       </c>
       <c r="E13" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>1950.2</v>
+        <v>1975.1666666666667</v>
       </c>
       <c r="F13" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-0.12536388469849546</v>
+        <v>-0.11416670064282886</v>
       </c>
       <c r="G13" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1467,11 +1471,11 @@
       </c>
       <c r="E14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>1891.7</v>
+        <v>1911.6666666666667</v>
       </c>
       <c r="F14" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-0.17964558159705113</v>
+        <v>-0.17098683907932688</v>
       </c>
       <c r="G14" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1496,11 +1500,11 @@
       </c>
       <c r="E15" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2103.1</v>
+        <v>2135.8333333333335</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-0.22344035850354982</v>
+        <v>-0.21135373133493329</v>
       </c>
       <c r="G15" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1525,11 +1529,11 @@
       </c>
       <c r="E16" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>113.2</v>
+        <v>121.16666666666667</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.34959519456777222</v>
+        <v>-0.3038217114999564</v>
       </c>
       <c r="G16" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1554,11 +1558,11 @@
       </c>
       <c r="E17" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>180.3</v>
+        <v>192.66666666666666</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>-0.15979665325142978</v>
+        <v>-0.1021676198545507</v>
       </c>
       <c r="G17" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1583,11 +1587,11 @@
       </c>
       <c r="E18" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>153.6</v>
+        <v>153.5</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>0.20728831725616281</v>
+        <v>0.20650232225794918</v>
       </c>
       <c r="G18" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1612,11 +1616,11 @@
       </c>
       <c r="E19" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>436.6</v>
+        <v>452.25</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>-9.8272624859181312E-2</v>
+        <v>-6.5950056327450213E-2</v>
       </c>
       <c r="G19" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1641,11 +1645,11 @@
       </c>
       <c r="E20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>664.1</v>
+        <v>766.66666666666663</v>
       </c>
       <c r="F20" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-0.147297770514766</v>
+        <v>-1.56025057390764E-2</v>
       </c>
       <c r="G20" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1670,11 +1674,11 @@
       </c>
       <c r="E21" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>10.3</v>
+        <v>9</v>
       </c>
       <c r="F21" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>-0.81195020746887969</v>
+        <v>-0.83568464730290459</v>
       </c>
       <c r="G21" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
@@ -1699,11 +1703,11 @@
       </c>
       <c r="E22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F22" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>0.44262295081967196</v>
+        <v>0.20218579234972678</v>
       </c>
       <c r="G22" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1728,11 +1732,11 @@
       </c>
       <c r="E23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>565.1</v>
+        <v>573</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-0.3488608390509611</v>
+        <v>-0.33975802650185938</v>
       </c>
       <c r="G23" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1757,11 +1761,11 @@
       </c>
       <c r="E24" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.31720147290899525</v>
+        <v>-0.31358495528669117</v>
       </c>
       <c r="G24" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1786,11 +1790,11 @@
       </c>
       <c r="E25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>418.4</v>
+        <v>430.66666666666669</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.23312505207031586</v>
+        <v>-0.2106417839984448</v>
       </c>
       <c r="G25" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1815,11 +1819,11 @@
       </c>
       <c r="E26" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>327.60000000000002</v>
+        <v>343.41666666666669</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-0.35</v>
+        <v>-0.31861772486772488</v>
       </c>
       <c r="G26" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1844,11 +1848,11 @@
       </c>
       <c r="E27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>104.7</v>
+        <v>107.41666666666667</v>
       </c>
       <c r="F27" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>-0.19630146545708305</v>
+        <v>-0.17544777855315186</v>
       </c>
       <c r="G27" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1873,11 +1877,11 @@
       </c>
       <c r="E28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>117.3</v>
+        <v>111.83333333333333</v>
       </c>
       <c r="F28" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>-0.17841451766953209</v>
+        <v>-0.21670380982701909</v>
       </c>
       <c r="G28" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1902,11 +1906,11 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>731</v>
+        <v>747.75</v>
       </c>
       <c r="F29" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-0.1418356456776948</v>
+        <v>-0.12217182497331913</v>
       </c>
       <c r="G29" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1931,11 +1935,11 @@
       </c>
       <c r="E30" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>614</v>
+        <v>628.41666666666663</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-0.28388909505380899</v>
+        <v>-0.26707487320857415</v>
       </c>
       <c r="G30" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -1960,11 +1964,11 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>770.4</v>
+        <v>798.16666666666663</v>
       </c>
       <c r="F31" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-0.27846743295019161</v>
+        <v>-0.25246204058464605</v>
       </c>
       <c r="G31" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -1989,11 +1993,11 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>512.9</v>
+        <v>525.25</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-0.25134023354564761</v>
+        <v>-0.23331342887473461</v>
       </c>
       <c r="G32" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2018,11 +2022,11 @@
       </c>
       <c r="E33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>193.7</v>
+        <v>205.16666666666666</v>
       </c>
       <c r="F33" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-7.1994773519163835E-2</v>
+        <v>-1.7058652729384449E-2</v>
       </c>
       <c r="G33" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2047,11 +2051,11 @@
       </c>
       <c r="E34" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>64.7</v>
+        <v>58.5</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-0.87332918038622409</v>
+        <v>-0.88546765150840967</v>
       </c>
       <c r="G34" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2076,11 +2080,11 @@
       </c>
       <c r="E35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>364.9</v>
+        <v>357.58333333333331</v>
       </c>
       <c r="F35" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.19342911684919128</v>
+        <v>-0.20960179510365395</v>
       </c>
       <c r="G35" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2105,11 +2109,11 @@
       </c>
       <c r="E36" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>241.8</v>
+        <v>249.5</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>-0.29071999999999998</v>
+        <v>-0.26813333333333333</v>
       </c>
       <c r="G36" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2134,11 +2138,11 @@
       </c>
       <c r="E37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>428.4</v>
+        <v>414.58333333333331</v>
       </c>
       <c r="F37" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>-0.15396768402154404</v>
+        <v>-0.18125374027528429</v>
       </c>
       <c r="G37" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2163,11 +2167,11 @@
       </c>
       <c r="E38" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>238.2</v>
+        <v>234.91666666666666</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>-0.14063627418825853</v>
+        <v>-0.15248168798513184</v>
       </c>
       <c r="G38" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2192,11 +2196,11 @@
       </c>
       <c r="E39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>277.2</v>
+        <v>275.25</v>
       </c>
       <c r="F39" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-5.9034099675975837E-2</v>
+        <v>-6.565344854189159E-2</v>
       </c>
       <c r="G39" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2221,11 +2225,11 @@
       </c>
       <c r="E40" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>62.6</v>
+        <v>58.75</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>-0.12391857506361315</v>
+        <v>-0.17779898218829515</v>
       </c>
       <c r="G40" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2250,11 +2254,11 @@
       </c>
       <c r="E41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>57.1</v>
+        <v>64.083333333333329</v>
       </c>
       <c r="F41" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.45406345067362019</v>
+        <v>-0.38729537882080256</v>
       </c>
       <c r="G41" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2279,11 +2283,11 @@
       </c>
       <c r="E42" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>46.6</v>
+        <v>43.583333333333336</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-4.2763772175536841E-2</v>
+        <v>-0.10473078120136936</v>
       </c>
       <c r="G42" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2308,11 +2312,11 @@
       </c>
       <c r="E43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>32.299999999999997</v>
+        <v>32.416666666666664</v>
       </c>
       <c r="F43" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-0.32194656488549622</v>
+        <v>-0.31949745547073793</v>
       </c>
       <c r="G43" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2337,15 +2341,15 @@
       </c>
       <c r="E44" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>-0.26666666666666661</v>
+        <v>0.375</v>
       </c>
       <c r="G44" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H44">
         <v>18</v>
@@ -2366,15 +2370,15 @@
       </c>
       <c r="E45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="F45" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-2.6229508196720208E-2</v>
+        <v>8.19672131147553E-2</v>
       </c>
       <c r="G45" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H45">
         <v>18</v>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C67290D-6BD4-4F10-988A-039B1DDE532F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CEDFA11-258C-4EBC-BD51-D90CBE6F796B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -368,6 +368,9 @@
       <sheetName val="INVENTARIO NACIONAL 15-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 16-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 17-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 20-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 21-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 22-07-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -376,10 +379,10 @@
       <sheetData sheetId="3">
         <row r="4">
           <cell r="F4">
-            <v>1045.5</v>
+            <v>1053.5333333333333</v>
           </cell>
           <cell r="G4">
-            <v>3.9144050104389372E-4</v>
+            <v>8.0781721178382337E-3</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -387,10 +390,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>72.5</v>
+            <v>72.266666666666666</v>
           </cell>
           <cell r="G5">
-            <v>-4.548174745661282E-2</v>
+            <v>-4.8553760223419062E-2</v>
           </cell>
           <cell r="H5" t="str">
             <v>BAJO</v>
@@ -398,21 +401,21 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>477.08333333333331</v>
+            <v>490.2</v>
           </cell>
           <cell r="G6">
-            <v>-2.3915806441613174E-2</v>
+            <v>2.9201153166558136E-3</v>
           </cell>
           <cell r="H6" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="7">
           <cell r="F7">
-            <v>99.916666666666671</v>
+            <v>95.8</v>
           </cell>
           <cell r="G7">
-            <v>9.3615257048093037E-2</v>
+            <v>4.8557213930348286E-2</v>
           </cell>
           <cell r="H7" t="str">
             <v>SUBIÓ</v>
@@ -420,10 +423,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>17.833333333333332</v>
+            <v>16.466666666666665</v>
           </cell>
           <cell r="G8">
-            <v>0.11775878442545107</v>
+            <v>3.2098765432098553E-2</v>
           </cell>
           <cell r="H8" t="str">
             <v>SUBIÓ</v>
@@ -431,10 +434,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1160.0833333333333</v>
+            <v>1199.6666666666667</v>
           </cell>
           <cell r="G9">
-            <v>-0.1951741246465476</v>
+            <v>-0.16771257082190194</v>
           </cell>
           <cell r="H9" t="str">
             <v>BAJO</v>
@@ -442,10 +445,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>121.91666666666667</v>
+            <v>112.66666666666667</v>
           </cell>
           <cell r="G10">
-            <v>-8.2706338349293196E-2</v>
+            <v>-0.15230278157774735</v>
           </cell>
           <cell r="H10" t="str">
             <v>BAJO</v>
@@ -453,10 +456,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>290.75</v>
+            <v>271</v>
           </cell>
           <cell r="G11">
-            <v>-0.12580292469591359</v>
+            <v>-0.18518518518518512</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -464,10 +467,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>608.58333333333337</v>
+            <v>611.33333333333337</v>
           </cell>
           <cell r="G12">
-            <v>-0.14737099068118609</v>
+            <v>-0.14351822369398626</v>
           </cell>
           <cell r="H12" t="str">
             <v>BAJO</v>
@@ -475,10 +478,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>350.08333333333331</v>
+            <v>349.53333333333336</v>
           </cell>
           <cell r="G13">
-            <v>-0.26823436262866196</v>
+            <v>-0.26938400633412507</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -486,10 +489,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>2874.6666666666665</v>
+            <v>2966.2666666666669</v>
           </cell>
           <cell r="G14">
-            <v>-0.17700999848179244</v>
+            <v>-0.15078578090094774</v>
           </cell>
           <cell r="H14" t="str">
             <v>BAJO</v>
@@ -497,10 +500,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>1975.1666666666667</v>
+            <v>2006.0666666666666</v>
           </cell>
           <cell r="G15">
-            <v>-0.11416670064282886</v>
+            <v>-0.10030850355390653</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -508,10 +511,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>1911.6666666666667</v>
+            <v>1976.4</v>
           </cell>
           <cell r="G16">
-            <v>-0.17098683907932688</v>
+            <v>-0.14291458871301566</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -519,10 +522,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2135.8333333333335</v>
+            <v>2202.1999999999998</v>
           </cell>
           <cell r="G17">
-            <v>-0.21135373133493329</v>
+            <v>-0.18684815629143514</v>
           </cell>
           <cell r="H17" t="str">
             <v>BAJO</v>
@@ -530,10 +533,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>121.16666666666667</v>
+            <v>131.66666666666666</v>
           </cell>
           <cell r="G18">
-            <v>-0.3038217114999564</v>
+            <v>-0.24349264385827452</v>
           </cell>
           <cell r="H18" t="str">
             <v>BAJO</v>
@@ -541,10 +544,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>192.66666666666666</v>
+            <v>192.33333333333334</v>
           </cell>
           <cell r="G19">
-            <v>-0.1021676198545507</v>
+            <v>-0.10372096307279532</v>
           </cell>
           <cell r="H19" t="str">
             <v>BAJO</v>
@@ -552,10 +555,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>153.5</v>
+            <v>146.86666666666667</v>
           </cell>
           <cell r="G20">
-            <v>0.20650232225794918</v>
+            <v>0.15436465404311073</v>
           </cell>
           <cell r="H20" t="str">
             <v>SUBIÓ</v>
@@ -563,10 +566,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>452.25</v>
+            <v>452.53333333333336</v>
           </cell>
           <cell r="G21">
-            <v>-6.5950056327450213E-2</v>
+            <v>-6.5364876705469976E-2</v>
           </cell>
           <cell r="H21" t="str">
             <v>BAJO</v>
@@ -574,10 +577,10 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>766.66666666666663</v>
+            <v>764.06666666666672</v>
           </cell>
           <cell r="G22">
-            <v>-1.56025057390764E-2</v>
+            <v>-1.8940897241352506E-2</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -585,10 +588,10 @@
         </row>
         <row r="23">
           <cell r="F23">
-            <v>9</v>
+            <v>7.333333333333333</v>
           </cell>
           <cell r="G23">
-            <v>-0.83568464730290459</v>
+            <v>-0.86611341632088523</v>
           </cell>
           <cell r="H23" t="str">
             <v>BAJO</v>
@@ -596,10 +599,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>50</v>
+            <v>58</v>
           </cell>
           <cell r="G24">
-            <v>0.20218579234972678</v>
+            <v>0.39453551912568297</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -607,10 +610,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>573</v>
+            <v>613.06666666666672</v>
           </cell>
           <cell r="G25">
-            <v>-0.33975802650185938</v>
+            <v>-0.29359101939628829</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -618,10 +621,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>949</v>
+            <v>991</v>
           </cell>
           <cell r="G26">
-            <v>-0.31358495528669117</v>
+            <v>-0.28320620725933721</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -629,10 +632,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>430.66666666666669</v>
+            <v>439.6</v>
           </cell>
           <cell r="G27">
-            <v>-0.2106417839984448</v>
+            <v>-0.19426809964175629</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -640,10 +643,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>343.41666666666669</v>
+            <v>345.4</v>
           </cell>
           <cell r="G28">
-            <v>-0.31861772486772488</v>
+            <v>-0.31468253968253967</v>
           </cell>
           <cell r="H28" t="str">
             <v>BAJO</v>
@@ -651,10 +654,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>107.41666666666667</v>
+            <v>104.73333333333333</v>
           </cell>
           <cell r="G29">
-            <v>-0.17544777855315186</v>
+            <v>-0.19604559199813909</v>
           </cell>
           <cell r="H29" t="str">
             <v>BAJO</v>
@@ -662,10 +665,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>111.83333333333333</v>
+            <v>111.2</v>
           </cell>
           <cell r="G30">
-            <v>-0.21670380982701909</v>
+            <v>-0.22113976440624006</v>
           </cell>
           <cell r="H30" t="str">
             <v>BAJO</v>
@@ -673,10 +676,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>747.75</v>
+            <v>732.73333333333335</v>
           </cell>
           <cell r="G31">
-            <v>-0.12217182497331913</v>
+            <v>-0.13980078263963003</v>
           </cell>
           <cell r="H31" t="str">
             <v>BAJO</v>
@@ -684,10 +687,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>628.41666666666663</v>
+            <v>616.5333333333333</v>
           </cell>
           <cell r="G32">
-            <v>-0.26707487320857415</v>
+            <v>-0.28093445722666954</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -695,10 +698,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>798.16666666666663</v>
+            <v>775.66666666666663</v>
           </cell>
           <cell r="G33">
-            <v>-0.25246204058464605</v>
+            <v>-0.27353483751951191</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -706,10 +709,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>525.25</v>
+            <v>519.4</v>
           </cell>
           <cell r="G34">
-            <v>-0.23331342887473461</v>
+            <v>-0.24185244161358821</v>
           </cell>
           <cell r="H34" t="str">
             <v>BAJO</v>
@@ -717,10 +720,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>205.16666666666666</v>
+            <v>199.4</v>
           </cell>
           <cell r="G35">
-            <v>-1.7058652729384449E-2</v>
+            <v>-4.4686411149825744E-2</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -728,10 +731,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>58.5</v>
+            <v>144.13333333333333</v>
           </cell>
           <cell r="G36">
-            <v>-0.88546765150840967</v>
+            <v>-0.71781317670789946</v>
           </cell>
           <cell r="H36" t="str">
             <v>BAJO</v>
@@ -739,10 +742,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>357.58333333333331</v>
+            <v>355</v>
           </cell>
           <cell r="G37">
-            <v>-0.20960179510365395</v>
+            <v>-0.21531196624133431</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -750,10 +753,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>249.5</v>
+            <v>274.53333333333336</v>
           </cell>
           <cell r="G38">
-            <v>-0.26813333333333333</v>
+            <v>-0.19470222222222222</v>
           </cell>
           <cell r="H38" t="str">
             <v>BAJO</v>
@@ -761,10 +764,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>414.58333333333331</v>
+            <v>388</v>
           </cell>
           <cell r="G39">
-            <v>-0.18125374027528429</v>
+            <v>-0.2337522441651706</v>
           </cell>
           <cell r="H39" t="str">
             <v>BAJO</v>
@@ -772,10 +775,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>234.91666666666666</v>
+            <v>238.73333333333332</v>
           </cell>
           <cell r="G40">
-            <v>-0.15248168798513184</v>
+            <v>-0.13871214605881721</v>
           </cell>
           <cell r="H40" t="str">
             <v>BAJO</v>
@@ -783,10 +786,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>275.25</v>
+            <v>254.53333333333333</v>
           </cell>
           <cell r="G41">
-            <v>-6.565344854189159E-2</v>
+            <v>-0.1359769582883299</v>
           </cell>
           <cell r="H41" t="str">
             <v>BAJO</v>
@@ -794,10 +797,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>58.75</v>
+            <v>50.2</v>
           </cell>
           <cell r="G42">
-            <v>-0.17779898218829515</v>
+            <v>-0.29745547073791345</v>
           </cell>
           <cell r="H42" t="str">
             <v>BAJO</v>
@@ -805,10 +808,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>64.083333333333329</v>
+            <v>84.466666666666669</v>
           </cell>
           <cell r="G43">
-            <v>-0.38729537882080256</v>
+            <v>-0.19240909749384327</v>
           </cell>
           <cell r="H43" t="str">
             <v>BAJO</v>
@@ -816,10 +819,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>43.583333333333336</v>
+            <v>36.466666666666669</v>
           </cell>
           <cell r="G44">
-            <v>-0.10473078120136936</v>
+            <v>-0.25091814503579202</v>
           </cell>
           <cell r="H44" t="str">
             <v>BAJO</v>
@@ -827,10 +830,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>32.416666666666664</v>
+            <v>44.06666666666667</v>
           </cell>
           <cell r="G45">
-            <v>-0.31949745547073793</v>
+            <v>-7.4936386768447716E-2</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -838,10 +841,10 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>0.75</v>
+            <v>0.6</v>
           </cell>
           <cell r="G46">
-            <v>0.375</v>
+            <v>0.10000000000000009</v>
           </cell>
           <cell r="H46" t="str">
             <v>SUBIÓ</v>
@@ -849,10 +852,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>3</v>
+            <v>3.2</v>
           </cell>
           <cell r="G47">
-            <v>8.19672131147553E-2</v>
+            <v>0.1540983606557389</v>
           </cell>
           <cell r="H47" t="str">
             <v>SUBIÓ</v>
@@ -870,6 +873,9 @@
       <sheetData sheetId="12"/>
       <sheetData sheetId="13"/>
       <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1123,11 +1129,11 @@
       </c>
       <c r="E2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!$F$4</f>
-        <v>1045.5</v>
+        <v>1053.5333333333333</v>
       </c>
       <c r="F2" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>3.9144050104389372E-4</v>
+        <v>8.0781721178382337E-3</v>
       </c>
       <c r="G2" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1152,11 +1158,11 @@
       </c>
       <c r="E3" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>72.5</v>
+        <v>72.266666666666666</v>
       </c>
       <c r="F3" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-4.548174745661282E-2</v>
+        <v>-4.8553760223419062E-2</v>
       </c>
       <c r="G3" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1181,15 +1187,15 @@
       </c>
       <c r="E4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>477.08333333333331</v>
+        <v>490.2</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-2.3915806441613174E-2</v>
+        <v>2.9201153166558136E-3</v>
       </c>
       <c r="G4" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H4">
         <v>2.0299999999999998</v>
@@ -1210,11 +1216,11 @@
       </c>
       <c r="E5" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>99.916666666666671</v>
+        <v>95.8</v>
       </c>
       <c r="F5" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>9.3615257048093037E-2</v>
+        <v>4.8557213930348286E-2</v>
       </c>
       <c r="G5" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1239,11 +1245,11 @@
       </c>
       <c r="E6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>17.833333333333332</v>
+        <v>16.466666666666665</v>
       </c>
       <c r="F6" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>0.11775878442545107</v>
+        <v>3.2098765432098553E-2</v>
       </c>
       <c r="G6" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1268,11 +1274,11 @@
       </c>
       <c r="E7" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1160.0833333333333</v>
+        <v>1199.6666666666667</v>
       </c>
       <c r="F7" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>-0.1951741246465476</v>
+        <v>-0.16771257082190194</v>
       </c>
       <c r="G7" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1297,11 +1303,11 @@
       </c>
       <c r="E8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>121.91666666666667</v>
+        <v>112.66666666666667</v>
       </c>
       <c r="F8" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-8.2706338349293196E-2</v>
+        <v>-0.15230278157774735</v>
       </c>
       <c r="G8" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1326,11 +1332,11 @@
       </c>
       <c r="E9" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>290.75</v>
+        <v>271</v>
       </c>
       <c r="F9" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-0.12580292469591359</v>
+        <v>-0.18518518518518512</v>
       </c>
       <c r="G9" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1355,11 +1361,11 @@
       </c>
       <c r="E10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>608.58333333333337</v>
+        <v>611.33333333333337</v>
       </c>
       <c r="F10" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>-0.14737099068118609</v>
+        <v>-0.14351822369398626</v>
       </c>
       <c r="G10" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1384,11 +1390,11 @@
       </c>
       <c r="E11" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>350.08333333333331</v>
+        <v>349.53333333333336</v>
       </c>
       <c r="F11" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.26823436262866196</v>
+        <v>-0.26938400633412507</v>
       </c>
       <c r="G11" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1413,11 +1419,11 @@
       </c>
       <c r="E12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>2874.6666666666665</v>
+        <v>2966.2666666666669</v>
       </c>
       <c r="F12" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-0.17700999848179244</v>
+        <v>-0.15078578090094774</v>
       </c>
       <c r="G12" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1442,11 +1448,11 @@
       </c>
       <c r="E13" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>1975.1666666666667</v>
+        <v>2006.0666666666666</v>
       </c>
       <c r="F13" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-0.11416670064282886</v>
+        <v>-0.10030850355390653</v>
       </c>
       <c r="G13" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1471,11 +1477,11 @@
       </c>
       <c r="E14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>1911.6666666666667</v>
+        <v>1976.4</v>
       </c>
       <c r="F14" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-0.17098683907932688</v>
+        <v>-0.14291458871301566</v>
       </c>
       <c r="G14" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1500,11 +1506,11 @@
       </c>
       <c r="E15" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2135.8333333333335</v>
+        <v>2202.1999999999998</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-0.21135373133493329</v>
+        <v>-0.18684815629143514</v>
       </c>
       <c r="G15" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1529,11 +1535,11 @@
       </c>
       <c r="E16" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>121.16666666666667</v>
+        <v>131.66666666666666</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.3038217114999564</v>
+        <v>-0.24349264385827452</v>
       </c>
       <c r="G16" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1558,11 +1564,11 @@
       </c>
       <c r="E17" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>192.66666666666666</v>
+        <v>192.33333333333334</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>-0.1021676198545507</v>
+        <v>-0.10372096307279532</v>
       </c>
       <c r="G17" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1587,11 +1593,11 @@
       </c>
       <c r="E18" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>153.5</v>
+        <v>146.86666666666667</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>0.20650232225794918</v>
+        <v>0.15436465404311073</v>
       </c>
       <c r="G18" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1616,11 +1622,11 @@
       </c>
       <c r="E19" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>452.25</v>
+        <v>452.53333333333336</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>-6.5950056327450213E-2</v>
+        <v>-6.5364876705469976E-2</v>
       </c>
       <c r="G19" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1645,11 +1651,11 @@
       </c>
       <c r="E20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>766.66666666666663</v>
+        <v>764.06666666666672</v>
       </c>
       <c r="F20" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-1.56025057390764E-2</v>
+        <v>-1.8940897241352506E-2</v>
       </c>
       <c r="G20" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1674,11 +1680,11 @@
       </c>
       <c r="E21" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>9</v>
+        <v>7.333333333333333</v>
       </c>
       <c r="F21" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>-0.83568464730290459</v>
+        <v>-0.86611341632088523</v>
       </c>
       <c r="G21" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
@@ -1703,11 +1709,11 @@
       </c>
       <c r="E22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F22" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>0.20218579234972678</v>
+        <v>0.39453551912568297</v>
       </c>
       <c r="G22" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1732,11 +1738,11 @@
       </c>
       <c r="E23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>573</v>
+        <v>613.06666666666672</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-0.33975802650185938</v>
+        <v>-0.29359101939628829</v>
       </c>
       <c r="G23" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1761,11 +1767,11 @@
       </c>
       <c r="E24" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>949</v>
+        <v>991</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.31358495528669117</v>
+        <v>-0.28320620725933721</v>
       </c>
       <c r="G24" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1790,11 +1796,11 @@
       </c>
       <c r="E25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>430.66666666666669</v>
+        <v>439.6</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.2106417839984448</v>
+        <v>-0.19426809964175629</v>
       </c>
       <c r="G25" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1819,11 +1825,11 @@
       </c>
       <c r="E26" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>343.41666666666669</v>
+        <v>345.4</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-0.31861772486772488</v>
+        <v>-0.31468253968253967</v>
       </c>
       <c r="G26" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1848,11 +1854,11 @@
       </c>
       <c r="E27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>107.41666666666667</v>
+        <v>104.73333333333333</v>
       </c>
       <c r="F27" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>-0.17544777855315186</v>
+        <v>-0.19604559199813909</v>
       </c>
       <c r="G27" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1877,11 +1883,11 @@
       </c>
       <c r="E28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>111.83333333333333</v>
+        <v>111.2</v>
       </c>
       <c r="F28" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>-0.21670380982701909</v>
+        <v>-0.22113976440624006</v>
       </c>
       <c r="G28" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1906,11 +1912,11 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>747.75</v>
+        <v>732.73333333333335</v>
       </c>
       <c r="F29" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-0.12217182497331913</v>
+        <v>-0.13980078263963003</v>
       </c>
       <c r="G29" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1935,11 +1941,11 @@
       </c>
       <c r="E30" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>628.41666666666663</v>
+        <v>616.5333333333333</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-0.26707487320857415</v>
+        <v>-0.28093445722666954</v>
       </c>
       <c r="G30" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -1964,11 +1970,11 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>798.16666666666663</v>
+        <v>775.66666666666663</v>
       </c>
       <c r="F31" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-0.25246204058464605</v>
+        <v>-0.27353483751951191</v>
       </c>
       <c r="G31" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -1993,11 +1999,11 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>525.25</v>
+        <v>519.4</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-0.23331342887473461</v>
+        <v>-0.24185244161358821</v>
       </c>
       <c r="G32" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2022,11 +2028,11 @@
       </c>
       <c r="E33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>205.16666666666666</v>
+        <v>199.4</v>
       </c>
       <c r="F33" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-1.7058652729384449E-2</v>
+        <v>-4.4686411149825744E-2</v>
       </c>
       <c r="G33" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2051,11 +2057,11 @@
       </c>
       <c r="E34" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>58.5</v>
+        <v>144.13333333333333</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-0.88546765150840967</v>
+        <v>-0.71781317670789946</v>
       </c>
       <c r="G34" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2080,11 +2086,11 @@
       </c>
       <c r="E35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>357.58333333333331</v>
+        <v>355</v>
       </c>
       <c r="F35" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.20960179510365395</v>
+        <v>-0.21531196624133431</v>
       </c>
       <c r="G35" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2109,11 +2115,11 @@
       </c>
       <c r="E36" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>249.5</v>
+        <v>274.53333333333336</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>-0.26813333333333333</v>
+        <v>-0.19470222222222222</v>
       </c>
       <c r="G36" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2138,11 +2144,11 @@
       </c>
       <c r="E37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>414.58333333333331</v>
+        <v>388</v>
       </c>
       <c r="F37" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>-0.18125374027528429</v>
+        <v>-0.2337522441651706</v>
       </c>
       <c r="G37" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2167,11 +2173,11 @@
       </c>
       <c r="E38" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>234.91666666666666</v>
+        <v>238.73333333333332</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>-0.15248168798513184</v>
+        <v>-0.13871214605881721</v>
       </c>
       <c r="G38" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2196,11 +2202,11 @@
       </c>
       <c r="E39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>275.25</v>
+        <v>254.53333333333333</v>
       </c>
       <c r="F39" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-6.565344854189159E-2</v>
+        <v>-0.1359769582883299</v>
       </c>
       <c r="G39" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2225,11 +2231,11 @@
       </c>
       <c r="E40" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>58.75</v>
+        <v>50.2</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>-0.17779898218829515</v>
+        <v>-0.29745547073791345</v>
       </c>
       <c r="G40" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2254,11 +2260,11 @@
       </c>
       <c r="E41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>64.083333333333329</v>
+        <v>84.466666666666669</v>
       </c>
       <c r="F41" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.38729537882080256</v>
+        <v>-0.19240909749384327</v>
       </c>
       <c r="G41" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2283,11 +2289,11 @@
       </c>
       <c r="E42" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>43.583333333333336</v>
+        <v>36.466666666666669</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-0.10473078120136936</v>
+        <v>-0.25091814503579202</v>
       </c>
       <c r="G42" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2312,11 +2318,11 @@
       </c>
       <c r="E43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>32.416666666666664</v>
+        <v>44.06666666666667</v>
       </c>
       <c r="F43" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-0.31949745547073793</v>
+        <v>-7.4936386768447716E-2</v>
       </c>
       <c r="G43" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2341,11 +2347,11 @@
       </c>
       <c r="E44" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>0.375</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="G44" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
@@ -2370,11 +2376,11 @@
       </c>
       <c r="E45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="F45" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>8.19672131147553E-2</v>
+        <v>0.1540983606557389</v>
       </c>
       <c r="G45" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CEDFA11-258C-4EBC-BD51-D90CBE6F796B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCCF65ED-CDDC-49C2-817D-02B95BB1994C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -371,6 +371,8 @@
       <sheetName val="INVENTARIO NACIONAL 20-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 21-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 22-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 23-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 27-07-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -379,10 +381,10 @@
       <sheetData sheetId="3">
         <row r="4">
           <cell r="F4">
-            <v>1053.5333333333333</v>
+            <v>1069.1111111111111</v>
           </cell>
           <cell r="G4">
-            <v>8.0781721178382337E-3</v>
+            <v>2.2983839789685323E-2</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -390,10 +392,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>72.266666666666666</v>
+            <v>71.222222222222229</v>
           </cell>
           <cell r="G5">
-            <v>-4.8553760223419062E-2</v>
+            <v>-6.2304674512932978E-2</v>
           </cell>
           <cell r="H5" t="str">
             <v>BAJO</v>
@@ -401,10 +403,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>490.2</v>
+            <v>514.66666666666663</v>
           </cell>
           <cell r="G6">
-            <v>2.9201153166558136E-3</v>
+            <v>5.2977463653554047E-2</v>
           </cell>
           <cell r="H6" t="str">
             <v>SUBIÓ</v>
@@ -412,10 +414,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>95.8</v>
+            <v>92.277777777777771</v>
           </cell>
           <cell r="G7">
-            <v>4.8557213930348286E-2</v>
+            <v>1.0005527915975643E-2</v>
           </cell>
           <cell r="H7" t="str">
             <v>SUBIÓ</v>
@@ -423,10 +425,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>16.466666666666665</v>
+            <v>16.055555555555557</v>
           </cell>
           <cell r="G8">
-            <v>3.2098765432098553E-2</v>
+            <v>6.3311174422286953E-3</v>
           </cell>
           <cell r="H8" t="str">
             <v>SUBIÓ</v>
@@ -434,10 +436,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1199.6666666666667</v>
+            <v>1190.4444444444443</v>
           </cell>
           <cell r="G9">
-            <v>-0.16771257082190194</v>
+            <v>-0.17411063108139846</v>
           </cell>
           <cell r="H9" t="str">
             <v>BAJO</v>
@@ -445,10 +447,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>112.66666666666667</v>
+            <v>112.05555555555556</v>
           </cell>
           <cell r="G10">
-            <v>-0.15230278157774735</v>
+            <v>-0.15690074479404159</v>
           </cell>
           <cell r="H10" t="str">
             <v>BAJO</v>
@@ -456,10 +458,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>271</v>
+            <v>267</v>
           </cell>
           <cell r="G11">
-            <v>-0.18518518518518512</v>
+            <v>-0.19721197211972108</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -467,10 +469,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>611.33333333333337</v>
+            <v>606.94444444444446</v>
           </cell>
           <cell r="G12">
-            <v>-0.14351822369398626</v>
+            <v>-0.14966708413820429</v>
           </cell>
           <cell r="H12" t="str">
             <v>BAJO</v>
@@ -478,10 +480,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>349.53333333333336</v>
+            <v>351.38888888888891</v>
           </cell>
           <cell r="G13">
-            <v>-0.26938400633412507</v>
+            <v>-0.26550541039852205</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -489,10 +491,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>2966.2666666666669</v>
+            <v>3036.6666666666665</v>
           </cell>
           <cell r="G14">
-            <v>-0.15078578090094774</v>
+            <v>-0.13063092372091012</v>
           </cell>
           <cell r="H14" t="str">
             <v>BAJO</v>
@@ -500,10 +502,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2006.0666666666666</v>
+            <v>2045.8333333333333</v>
           </cell>
           <cell r="G15">
-            <v>-0.10030850355390653</v>
+            <v>-8.2473736426523114E-2</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -511,10 +513,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>1976.4</v>
+            <v>2033.6666666666667</v>
           </cell>
           <cell r="G16">
-            <v>-0.14291458871301566</v>
+            <v>-0.11808033220976</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -522,10 +524,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2202.1999999999998</v>
+            <v>2252.3888888888887</v>
           </cell>
           <cell r="G17">
-            <v>-0.18684815629143514</v>
+            <v>-0.16831614851117715</v>
           </cell>
           <cell r="H17" t="str">
             <v>BAJO</v>
@@ -533,10 +535,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>131.66666666666666</v>
+            <v>126.72222222222223</v>
           </cell>
           <cell r="G18">
-            <v>-0.24349264385827452</v>
+            <v>-0.27190156989060088</v>
           </cell>
           <cell r="H18" t="str">
             <v>BAJO</v>
@@ -544,10 +546,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>192.33333333333334</v>
+            <v>200.72222222222223</v>
           </cell>
           <cell r="G19">
-            <v>-0.10372096307279532</v>
+            <v>-6.4628492080303079E-2</v>
           </cell>
           <cell r="H19" t="str">
             <v>BAJO</v>
@@ -555,10 +557,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>146.86666666666667</v>
+            <v>147</v>
           </cell>
           <cell r="G20">
-            <v>0.15436465404311073</v>
+            <v>0.15541264737406202</v>
           </cell>
           <cell r="H20" t="str">
             <v>SUBIÓ</v>
@@ -566,10 +568,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>452.53333333333336</v>
+            <v>456.16666666666669</v>
           </cell>
           <cell r="G21">
-            <v>-6.5364876705469976E-2</v>
+            <v>-5.7860808611841286E-2</v>
           </cell>
           <cell r="H21" t="str">
             <v>BAJO</v>
@@ -577,10 +579,10 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>764.06666666666672</v>
+            <v>762</v>
           </cell>
           <cell r="G22">
-            <v>-1.8940897241352506E-2</v>
+            <v>-2.159449048675155E-2</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -588,10 +590,10 @@
         </row>
         <row r="23">
           <cell r="F23">
-            <v>7.333333333333333</v>
+            <v>6.1111111111111107</v>
           </cell>
           <cell r="G23">
-            <v>-0.86611341632088523</v>
+            <v>-0.88842784693407095</v>
           </cell>
           <cell r="H23" t="str">
             <v>BAJO</v>
@@ -599,10 +601,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>58</v>
+            <v>49.444444444444443</v>
           </cell>
           <cell r="G24">
-            <v>0.39453551912568297</v>
+            <v>0.1888281724347296</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -610,10 +612,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>613.06666666666672</v>
+            <v>659.22222222222217</v>
           </cell>
           <cell r="G25">
-            <v>-0.29359101939628829</v>
+            <v>-0.24040806112769664</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -621,10 +623,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>991</v>
+            <v>1024.4444444444443</v>
           </cell>
           <cell r="G26">
-            <v>-0.28320620725933721</v>
+            <v>-0.25901572271903683</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -632,10 +634,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>439.6</v>
+            <v>447.05555555555554</v>
           </cell>
           <cell r="G27">
-            <v>-0.19426809964175629</v>
+            <v>-0.18060299739879848</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -643,10 +645,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>345.4</v>
+            <v>347.44444444444446</v>
           </cell>
           <cell r="G28">
-            <v>-0.31468253968253967</v>
+            <v>-0.31062610229276888</v>
           </cell>
           <cell r="H28" t="str">
             <v>BAJO</v>
@@ -654,10 +656,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>104.73333333333333</v>
+            <v>102.27777777777777</v>
           </cell>
           <cell r="G29">
-            <v>-0.19604559199813909</v>
+            <v>-0.21489493680700944</v>
           </cell>
           <cell r="H29" t="str">
             <v>BAJO</v>
@@ -665,10 +667,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>111.2</v>
+            <v>111.61111111111111</v>
           </cell>
           <cell r="G30">
-            <v>-0.22113976440624006</v>
+            <v>-0.2182602851179738</v>
           </cell>
           <cell r="H30" t="str">
             <v>BAJO</v>
@@ -676,10 +678,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>732.73333333333335</v>
+            <v>753.94444444444446</v>
           </cell>
           <cell r="G31">
-            <v>-0.13980078263963003</v>
+            <v>-0.11489979841100439</v>
           </cell>
           <cell r="H31" t="str">
             <v>BAJO</v>
@@ -687,10 +689,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>616.5333333333333</v>
+            <v>632.55555555555554</v>
           </cell>
           <cell r="G32">
-            <v>-0.28093445722666954</v>
+            <v>-0.26224766886379569</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -698,10 +700,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>775.66666666666663</v>
+            <v>788.22222222222217</v>
           </cell>
           <cell r="G33">
-            <v>-0.27353483751951191</v>
+            <v>-0.26177569651388299</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -709,10 +711,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>519.4</v>
+            <v>535.16666666666663</v>
           </cell>
           <cell r="G34">
-            <v>-0.24185244161358821</v>
+            <v>-0.21883846426043885</v>
           </cell>
           <cell r="H34" t="str">
             <v>BAJO</v>
@@ -720,10 +722,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>199.4</v>
+            <v>203.83333333333334</v>
           </cell>
           <cell r="G35">
-            <v>-4.4686411149825744E-2</v>
+            <v>-2.344657375145176E-2</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -731,10 +733,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>144.13333333333333</v>
+            <v>176.16666666666666</v>
           </cell>
           <cell r="G36">
-            <v>-0.71781317670789946</v>
+            <v>-0.65509774257660702</v>
           </cell>
           <cell r="H36" t="str">
             <v>BAJO</v>
@@ -742,10 +744,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>355</v>
+            <v>330.66666666666669</v>
           </cell>
           <cell r="G37">
-            <v>-0.21531196624133431</v>
+            <v>-0.2690980943769048</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -753,10 +755,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>274.53333333333336</v>
+            <v>256.72222222222223</v>
           </cell>
           <cell r="G38">
-            <v>-0.19470222222222222</v>
+            <v>-0.24694814814814814</v>
           </cell>
           <cell r="H38" t="str">
             <v>BAJO</v>
@@ -764,10 +766,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>388</v>
+            <v>378.5</v>
           </cell>
           <cell r="G39">
-            <v>-0.2337522441651706</v>
+            <v>-0.25251346499102334</v>
           </cell>
           <cell r="H39" t="str">
             <v>BAJO</v>
@@ -775,10 +777,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>238.73333333333332</v>
+            <v>234.11111111111111</v>
           </cell>
           <cell r="G40">
-            <v>-0.13871214605881721</v>
+            <v>-0.1553879231806421</v>
           </cell>
           <cell r="H40" t="str">
             <v>BAJO</v>
@@ -786,10 +788,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>254.53333333333333</v>
+            <v>241.16666666666666</v>
           </cell>
           <cell r="G41">
-            <v>-0.1359769582883299</v>
+            <v>-0.18135061461708579</v>
           </cell>
           <cell r="H41" t="str">
             <v>BAJO</v>
@@ -797,10 +799,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>50.2</v>
+            <v>46.777777777777779</v>
           </cell>
           <cell r="G42">
-            <v>-0.29745547073791345</v>
+            <v>-0.34534916595985299</v>
           </cell>
           <cell r="H42" t="str">
             <v>BAJO</v>
@@ -808,10 +810,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>84.466666666666669</v>
+            <v>76.111111111111114</v>
           </cell>
           <cell r="G43">
-            <v>-0.19240909749384327</v>
+            <v>-0.27229706890723837</v>
           </cell>
           <cell r="H43" t="str">
             <v>BAJO</v>
@@ -819,10 +821,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>36.466666666666669</v>
+            <v>33.444444444444443</v>
           </cell>
           <cell r="G44">
-            <v>-0.25091814503579202</v>
+            <v>-0.31299927378358749</v>
           </cell>
           <cell r="H44" t="str">
             <v>BAJO</v>
@@ -830,10 +832,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>44.06666666666667</v>
+            <v>40</v>
           </cell>
           <cell r="G45">
-            <v>-7.4936386768447716E-2</v>
+            <v>-0.16030534351145032</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -841,10 +843,10 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>0.6</v>
+            <v>0.55555555555555558</v>
           </cell>
           <cell r="G46">
-            <v>0.10000000000000009</v>
+            <v>1.8518518518518601E-2</v>
           </cell>
           <cell r="H46" t="str">
             <v>SUBIÓ</v>
@@ -852,10 +854,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>3.2</v>
+            <v>3</v>
           </cell>
           <cell r="G47">
-            <v>0.1540983606557389</v>
+            <v>8.19672131147553E-2</v>
           </cell>
           <cell r="H47" t="str">
             <v>SUBIÓ</v>
@@ -876,6 +878,8 @@
       <sheetData sheetId="15"/>
       <sheetData sheetId="16"/>
       <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1129,11 +1133,11 @@
       </c>
       <c r="E2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!$F$4</f>
-        <v>1053.5333333333333</v>
+        <v>1069.1111111111111</v>
       </c>
       <c r="F2" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>8.0781721178382337E-3</v>
+        <v>2.2983839789685323E-2</v>
       </c>
       <c r="G2" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1158,11 +1162,11 @@
       </c>
       <c r="E3" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>72.266666666666666</v>
+        <v>71.222222222222229</v>
       </c>
       <c r="F3" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-4.8553760223419062E-2</v>
+        <v>-6.2304674512932978E-2</v>
       </c>
       <c r="G3" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1187,11 +1191,11 @@
       </c>
       <c r="E4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>490.2</v>
+        <v>514.66666666666663</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>2.9201153166558136E-3</v>
+        <v>5.2977463653554047E-2</v>
       </c>
       <c r="G4" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1216,11 +1220,11 @@
       </c>
       <c r="E5" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>95.8</v>
+        <v>92.277777777777771</v>
       </c>
       <c r="F5" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>4.8557213930348286E-2</v>
+        <v>1.0005527915975643E-2</v>
       </c>
       <c r="G5" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1245,11 +1249,11 @@
       </c>
       <c r="E6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>16.466666666666665</v>
+        <v>16.055555555555557</v>
       </c>
       <c r="F6" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>3.2098765432098553E-2</v>
+        <v>6.3311174422286953E-3</v>
       </c>
       <c r="G6" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1274,11 +1278,11 @@
       </c>
       <c r="E7" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1199.6666666666667</v>
+        <v>1190.4444444444443</v>
       </c>
       <c r="F7" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>-0.16771257082190194</v>
+        <v>-0.17411063108139846</v>
       </c>
       <c r="G7" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1303,11 +1307,11 @@
       </c>
       <c r="E8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>112.66666666666667</v>
+        <v>112.05555555555556</v>
       </c>
       <c r="F8" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-0.15230278157774735</v>
+        <v>-0.15690074479404159</v>
       </c>
       <c r="G8" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1332,11 +1336,11 @@
       </c>
       <c r="E9" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="F9" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-0.18518518518518512</v>
+        <v>-0.19721197211972108</v>
       </c>
       <c r="G9" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1361,11 +1365,11 @@
       </c>
       <c r="E10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>611.33333333333337</v>
+        <v>606.94444444444446</v>
       </c>
       <c r="F10" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>-0.14351822369398626</v>
+        <v>-0.14966708413820429</v>
       </c>
       <c r="G10" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1390,11 +1394,11 @@
       </c>
       <c r="E11" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>349.53333333333336</v>
+        <v>351.38888888888891</v>
       </c>
       <c r="F11" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.26938400633412507</v>
+        <v>-0.26550541039852205</v>
       </c>
       <c r="G11" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1419,11 +1423,11 @@
       </c>
       <c r="E12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>2966.2666666666669</v>
+        <v>3036.6666666666665</v>
       </c>
       <c r="F12" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-0.15078578090094774</v>
+        <v>-0.13063092372091012</v>
       </c>
       <c r="G12" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1448,11 +1452,11 @@
       </c>
       <c r="E13" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2006.0666666666666</v>
+        <v>2045.8333333333333</v>
       </c>
       <c r="F13" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-0.10030850355390653</v>
+        <v>-8.2473736426523114E-2</v>
       </c>
       <c r="G13" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1477,11 +1481,11 @@
       </c>
       <c r="E14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>1976.4</v>
+        <v>2033.6666666666667</v>
       </c>
       <c r="F14" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-0.14291458871301566</v>
+        <v>-0.11808033220976</v>
       </c>
       <c r="G14" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1506,11 +1510,11 @@
       </c>
       <c r="E15" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2202.1999999999998</v>
+        <v>2252.3888888888887</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-0.18684815629143514</v>
+        <v>-0.16831614851117715</v>
       </c>
       <c r="G15" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1535,11 +1539,11 @@
       </c>
       <c r="E16" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>131.66666666666666</v>
+        <v>126.72222222222223</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.24349264385827452</v>
+        <v>-0.27190156989060088</v>
       </c>
       <c r="G16" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1564,11 +1568,11 @@
       </c>
       <c r="E17" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>192.33333333333334</v>
+        <v>200.72222222222223</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>-0.10372096307279532</v>
+        <v>-6.4628492080303079E-2</v>
       </c>
       <c r="G17" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1593,11 +1597,11 @@
       </c>
       <c r="E18" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>146.86666666666667</v>
+        <v>147</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>0.15436465404311073</v>
+        <v>0.15541264737406202</v>
       </c>
       <c r="G18" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1622,11 +1626,11 @@
       </c>
       <c r="E19" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>452.53333333333336</v>
+        <v>456.16666666666669</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>-6.5364876705469976E-2</v>
+        <v>-5.7860808611841286E-2</v>
       </c>
       <c r="G19" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1651,11 +1655,11 @@
       </c>
       <c r="E20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>764.06666666666672</v>
+        <v>762</v>
       </c>
       <c r="F20" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-1.8940897241352506E-2</v>
+        <v>-2.159449048675155E-2</v>
       </c>
       <c r="G20" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1680,11 +1684,11 @@
       </c>
       <c r="E21" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>7.333333333333333</v>
+        <v>6.1111111111111107</v>
       </c>
       <c r="F21" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>-0.86611341632088523</v>
+        <v>-0.88842784693407095</v>
       </c>
       <c r="G21" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
@@ -1709,11 +1713,11 @@
       </c>
       <c r="E22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>58</v>
+        <v>49.444444444444443</v>
       </c>
       <c r="F22" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>0.39453551912568297</v>
+        <v>0.1888281724347296</v>
       </c>
       <c r="G22" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1738,11 +1742,11 @@
       </c>
       <c r="E23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>613.06666666666672</v>
+        <v>659.22222222222217</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-0.29359101939628829</v>
+        <v>-0.24040806112769664</v>
       </c>
       <c r="G23" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1767,11 +1771,11 @@
       </c>
       <c r="E24" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>991</v>
+        <v>1024.4444444444443</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.28320620725933721</v>
+        <v>-0.25901572271903683</v>
       </c>
       <c r="G24" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1796,11 +1800,11 @@
       </c>
       <c r="E25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>439.6</v>
+        <v>447.05555555555554</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.19426809964175629</v>
+        <v>-0.18060299739879848</v>
       </c>
       <c r="G25" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1825,11 +1829,11 @@
       </c>
       <c r="E26" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>345.4</v>
+        <v>347.44444444444446</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-0.31468253968253967</v>
+        <v>-0.31062610229276888</v>
       </c>
       <c r="G26" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1854,11 +1858,11 @@
       </c>
       <c r="E27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>104.73333333333333</v>
+        <v>102.27777777777777</v>
       </c>
       <c r="F27" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>-0.19604559199813909</v>
+        <v>-0.21489493680700944</v>
       </c>
       <c r="G27" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1883,11 +1887,11 @@
       </c>
       <c r="E28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>111.2</v>
+        <v>111.61111111111111</v>
       </c>
       <c r="F28" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>-0.22113976440624006</v>
+        <v>-0.2182602851179738</v>
       </c>
       <c r="G28" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1912,11 +1916,11 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>732.73333333333335</v>
+        <v>753.94444444444446</v>
       </c>
       <c r="F29" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-0.13980078263963003</v>
+        <v>-0.11489979841100439</v>
       </c>
       <c r="G29" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1941,11 +1945,11 @@
       </c>
       <c r="E30" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>616.5333333333333</v>
+        <v>632.55555555555554</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-0.28093445722666954</v>
+        <v>-0.26224766886379569</v>
       </c>
       <c r="G30" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -1970,11 +1974,11 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>775.66666666666663</v>
+        <v>788.22222222222217</v>
       </c>
       <c r="F31" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-0.27353483751951191</v>
+        <v>-0.26177569651388299</v>
       </c>
       <c r="G31" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -1999,11 +2003,11 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>519.4</v>
+        <v>535.16666666666663</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-0.24185244161358821</v>
+        <v>-0.21883846426043885</v>
       </c>
       <c r="G32" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2028,11 +2032,11 @@
       </c>
       <c r="E33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>199.4</v>
+        <v>203.83333333333334</v>
       </c>
       <c r="F33" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-4.4686411149825744E-2</v>
+        <v>-2.344657375145176E-2</v>
       </c>
       <c r="G33" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2057,11 +2061,11 @@
       </c>
       <c r="E34" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>144.13333333333333</v>
+        <v>176.16666666666666</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-0.71781317670789946</v>
+        <v>-0.65509774257660702</v>
       </c>
       <c r="G34" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2086,11 +2090,11 @@
       </c>
       <c r="E35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>355</v>
+        <v>330.66666666666669</v>
       </c>
       <c r="F35" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.21531196624133431</v>
+        <v>-0.2690980943769048</v>
       </c>
       <c r="G35" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2115,11 +2119,11 @@
       </c>
       <c r="E36" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>274.53333333333336</v>
+        <v>256.72222222222223</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>-0.19470222222222222</v>
+        <v>-0.24694814814814814</v>
       </c>
       <c r="G36" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2144,11 +2148,11 @@
       </c>
       <c r="E37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>388</v>
+        <v>378.5</v>
       </c>
       <c r="F37" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>-0.2337522441651706</v>
+        <v>-0.25251346499102334</v>
       </c>
       <c r="G37" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2173,11 +2177,11 @@
       </c>
       <c r="E38" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>238.73333333333332</v>
+        <v>234.11111111111111</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>-0.13871214605881721</v>
+        <v>-0.1553879231806421</v>
       </c>
       <c r="G38" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2202,11 +2206,11 @@
       </c>
       <c r="E39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>254.53333333333333</v>
+        <v>241.16666666666666</v>
       </c>
       <c r="F39" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-0.1359769582883299</v>
+        <v>-0.18135061461708579</v>
       </c>
       <c r="G39" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2231,11 +2235,11 @@
       </c>
       <c r="E40" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>50.2</v>
+        <v>46.777777777777779</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>-0.29745547073791345</v>
+        <v>-0.34534916595985299</v>
       </c>
       <c r="G40" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2260,11 +2264,11 @@
       </c>
       <c r="E41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>84.466666666666669</v>
+        <v>76.111111111111114</v>
       </c>
       <c r="F41" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.19240909749384327</v>
+        <v>-0.27229706890723837</v>
       </c>
       <c r="G41" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2289,11 +2293,11 @@
       </c>
       <c r="E42" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>36.466666666666669</v>
+        <v>33.444444444444443</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-0.25091814503579202</v>
+        <v>-0.31299927378358749</v>
       </c>
       <c r="G42" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2318,11 +2322,11 @@
       </c>
       <c r="E43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>44.06666666666667</v>
+        <v>40</v>
       </c>
       <c r="F43" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-7.4936386768447716E-2</v>
+        <v>-0.16030534351145032</v>
       </c>
       <c r="G43" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2347,11 +2351,11 @@
       </c>
       <c r="E44" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>0.6</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>0.10000000000000009</v>
+        <v>1.8518518518518601E-2</v>
       </c>
       <c r="G44" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
@@ -2376,11 +2380,11 @@
       </c>
       <c r="E45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="F45" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>0.1540983606557389</v>
+        <v>8.19672131147553E-2</v>
       </c>
       <c r="G45" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCCF65ED-CDDC-49C2-817D-02B95BB1994C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D279F48B-8479-4F69-BD32-C84F0154010F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -373,6 +373,7 @@
       <sheetName val="INVENTARIO NACIONAL 22-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 23-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 27-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 28-07-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -381,10 +382,10 @@
       <sheetData sheetId="3">
         <row r="4">
           <cell r="F4">
-            <v>1069.1111111111111</v>
+            <v>1128.9444444444443</v>
           </cell>
           <cell r="G4">
-            <v>2.2983839789685323E-2</v>
+            <v>8.0235637516430813E-2</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -392,21 +393,21 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>71.222222222222229</v>
+            <v>76.833333333333329</v>
           </cell>
           <cell r="G5">
-            <v>-6.2304674512932978E-2</v>
+            <v>1.1569918212646968E-2</v>
           </cell>
           <cell r="H5" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="6">
           <cell r="F6">
-            <v>514.66666666666663</v>
+            <v>541.22222222222217</v>
           </cell>
           <cell r="G6">
-            <v>5.2977463653554047E-2</v>
+            <v>0.1073085547185797</v>
           </cell>
           <cell r="H6" t="str">
             <v>SUBIÓ</v>
@@ -414,10 +415,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>92.277777777777771</v>
+            <v>94.888888888888886</v>
           </cell>
           <cell r="G7">
-            <v>1.0005527915975643E-2</v>
+            <v>3.8584853510226669E-2</v>
           </cell>
           <cell r="H7" t="str">
             <v>SUBIÓ</v>
@@ -425,10 +426,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>16.055555555555557</v>
+            <v>17.111111111111111</v>
           </cell>
           <cell r="G8">
-            <v>6.3311174422286953E-3</v>
+            <v>7.2491294713516785E-2</v>
           </cell>
           <cell r="H8" t="str">
             <v>SUBIÓ</v>
@@ -436,10 +437,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1190.4444444444443</v>
+            <v>1261.8333333333333</v>
           </cell>
           <cell r="G9">
-            <v>-0.17411063108139846</v>
+            <v>-0.1245834778678272</v>
           </cell>
           <cell r="H9" t="str">
             <v>BAJO</v>
@@ -447,10 +448,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>112.05555555555556</v>
+            <v>117.05555555555556</v>
           </cell>
           <cell r="G10">
-            <v>-0.15690074479404159</v>
+            <v>-0.11928104575163401</v>
           </cell>
           <cell r="H10" t="str">
             <v>BAJO</v>
@@ -458,10 +459,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>267</v>
+            <v>283</v>
           </cell>
           <cell r="G11">
-            <v>-0.19721197211972108</v>
+            <v>-0.14910482438157713</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -469,10 +470,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>606.94444444444446</v>
+            <v>635.83333333333337</v>
           </cell>
           <cell r="G12">
-            <v>-0.14966708413820429</v>
+            <v>-0.10919357235347804</v>
           </cell>
           <cell r="H12" t="str">
             <v>BAJO</v>
@@ -480,10 +481,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>351.38888888888891</v>
+            <v>364.27777777777777</v>
           </cell>
           <cell r="G13">
-            <v>-0.26550541039852205</v>
+            <v>-0.23856426497756666</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -491,10 +492,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3036.6666666666665</v>
+            <v>3228.2777777777778</v>
           </cell>
           <cell r="G14">
-            <v>-0.13063092372091012</v>
+            <v>-7.5774466639194293E-2</v>
           </cell>
           <cell r="H14" t="str">
             <v>BAJO</v>
@@ -502,10 +503,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2045.8333333333333</v>
+            <v>2163</v>
           </cell>
           <cell r="G15">
-            <v>-8.2473736426523114E-2</v>
+            <v>-2.9926203775431093E-2</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -513,10 +514,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2033.6666666666667</v>
+            <v>2146.5555555555557</v>
           </cell>
           <cell r="G16">
-            <v>-0.11808033220976</v>
+            <v>-6.9124948804040409E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -524,10 +525,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2252.3888888888887</v>
+            <v>2385.1111111111113</v>
           </cell>
           <cell r="G17">
-            <v>-0.16831614851117715</v>
+            <v>-0.11930910114894933</v>
           </cell>
           <cell r="H17" t="str">
             <v>BAJO</v>
@@ -535,10 +536,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>126.72222222222223</v>
+            <v>132.61111111111111</v>
           </cell>
           <cell r="G18">
-            <v>-0.27190156989060088</v>
+            <v>-0.23806621978468401</v>
           </cell>
           <cell r="H18" t="str">
             <v>BAJO</v>
@@ -546,10 +547,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>200.72222222222223</v>
+            <v>214.33333333333334</v>
           </cell>
           <cell r="G19">
-            <v>-6.4628492080303079E-2</v>
+            <v>-1.2003106686435672E-3</v>
           </cell>
           <cell r="H19" t="str">
             <v>BAJO</v>
@@ -557,10 +558,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>147</v>
+            <v>150.66666666666666</v>
           </cell>
           <cell r="G20">
-            <v>0.15541264737406202</v>
+            <v>0.18423246397522908</v>
           </cell>
           <cell r="H20" t="str">
             <v>SUBIÓ</v>
@@ -568,10 +569,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>456.16666666666669</v>
+            <v>476.11111111111109</v>
           </cell>
           <cell r="G21">
-            <v>-5.7860808611841286E-2</v>
+            <v>-1.6668752868527648E-2</v>
           </cell>
           <cell r="H21" t="str">
             <v>BAJO</v>
@@ -579,13 +580,13 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>762</v>
+            <v>795</v>
           </cell>
           <cell r="G22">
-            <v>-2.159449048675155E-2</v>
+            <v>2.0777401657523065E-2</v>
           </cell>
           <cell r="H22" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="23">
@@ -612,10 +613,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>659.22222222222217</v>
+            <v>691</v>
           </cell>
           <cell r="G25">
-            <v>-0.24040806112769664</v>
+            <v>-0.20379196564185831</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -623,10 +624,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>1024.4444444444443</v>
+            <v>1094.5</v>
           </cell>
           <cell r="G26">
-            <v>-0.25901572271903683</v>
+            <v>-0.2083442924776433</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -634,10 +635,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>447.05555555555554</v>
+            <v>466.72222222222223</v>
           </cell>
           <cell r="G27">
-            <v>-0.18060299739879848</v>
+            <v>-0.14455645347922286</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -645,10 +646,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>347.44444444444446</v>
+            <v>367.77777777777777</v>
           </cell>
           <cell r="G28">
-            <v>-0.31062610229276888</v>
+            <v>-0.27028218694885364</v>
           </cell>
           <cell r="H28" t="str">
             <v>BAJO</v>
@@ -656,10 +657,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>102.27777777777777</v>
+            <v>106.72222222222223</v>
           </cell>
           <cell r="G29">
-            <v>-0.21489493680700944</v>
+            <v>-0.18077847561448401</v>
           </cell>
           <cell r="H29" t="str">
             <v>BAJO</v>
@@ -667,10 +668,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>111.61111111111111</v>
+            <v>118</v>
           </cell>
           <cell r="G30">
-            <v>-0.2182602851179738</v>
+            <v>-0.1735116205030246</v>
           </cell>
           <cell r="H30" t="str">
             <v>BAJO</v>
@@ -678,10 +679,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>753.94444444444446</v>
+            <v>792.33333333333337</v>
           </cell>
           <cell r="G31">
-            <v>-0.11489979841100439</v>
+            <v>-6.9832799715403793E-2</v>
           </cell>
           <cell r="H31" t="str">
             <v>BAJO</v>
@@ -689,10 +690,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>632.55555555555554</v>
+            <v>655.38888888888891</v>
           </cell>
           <cell r="G32">
-            <v>-0.26224766886379569</v>
+            <v>-0.23561705160602464</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -700,10 +701,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>788.22222222222217</v>
+            <v>825.94444444444446</v>
           </cell>
           <cell r="G33">
-            <v>-0.26177569651388299</v>
+            <v>-0.22644624189962637</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -711,10 +712,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>535.16666666666663</v>
+            <v>560.27777777777783</v>
           </cell>
           <cell r="G34">
-            <v>-0.21883846426043885</v>
+            <v>-0.18218477235196973</v>
           </cell>
           <cell r="H34" t="str">
             <v>BAJO</v>
@@ -722,21 +723,21 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>203.83333333333334</v>
+            <v>211.27777777777777</v>
           </cell>
           <cell r="G35">
-            <v>-2.344657375145176E-2</v>
+            <v>1.2219318621757624E-2</v>
           </cell>
           <cell r="H35" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="36">
           <cell r="F36">
-            <v>176.16666666666666</v>
+            <v>211.55555555555554</v>
           </cell>
           <cell r="G36">
-            <v>-0.65509774257660702</v>
+            <v>-0.58581274163724995</v>
           </cell>
           <cell r="H36" t="str">
             <v>BAJO</v>
@@ -744,10 +745,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>330.66666666666669</v>
+            <v>354.44444444444446</v>
           </cell>
           <cell r="G37">
-            <v>-0.2690980943769048</v>
+            <v>-0.2165399600343838</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -755,10 +756,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>256.72222222222223</v>
+            <v>270.88888888888891</v>
           </cell>
           <cell r="G38">
-            <v>-0.24694814814814814</v>
+            <v>-0.20539259259259257</v>
           </cell>
           <cell r="H38" t="str">
             <v>BAJO</v>
@@ -766,10 +767,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>378.5</v>
+            <v>407.22222222222223</v>
           </cell>
           <cell r="G39">
-            <v>-0.25251346499102334</v>
+            <v>-0.1957909435467784</v>
           </cell>
           <cell r="H39" t="str">
             <v>BAJO</v>
@@ -777,10 +778,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>234.11111111111111</v>
+            <v>242.72222222222223</v>
           </cell>
           <cell r="G40">
-            <v>-0.1553879231806421</v>
+            <v>-0.12432127109070368</v>
           </cell>
           <cell r="H40" t="str">
             <v>BAJO</v>
@@ -788,10 +789,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>241.16666666666666</v>
+            <v>256.77777777777777</v>
           </cell>
           <cell r="G41">
-            <v>-0.18135061461708579</v>
+            <v>-0.1283581066022047</v>
           </cell>
           <cell r="H41" t="str">
             <v>BAJO</v>
@@ -799,10 +800,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>46.777777777777779</v>
+            <v>52.111111111111114</v>
           </cell>
           <cell r="G42">
-            <v>-0.34534916595985299</v>
+            <v>-0.27070964093864847</v>
           </cell>
           <cell r="H42" t="str">
             <v>BAJO</v>
@@ -810,10 +811,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>76.111111111111114</v>
+            <v>85.222222222222229</v>
           </cell>
           <cell r="G43">
-            <v>-0.27229706890723837</v>
+            <v>-0.18518518518518512</v>
           </cell>
           <cell r="H43" t="str">
             <v>BAJO</v>
@@ -821,10 +822,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>33.444444444444443</v>
+            <v>35.444444444444443</v>
           </cell>
           <cell r="G44">
-            <v>-0.31299927378358749</v>
+            <v>-0.27191617387695821</v>
           </cell>
           <cell r="H44" t="str">
             <v>BAJO</v>
@@ -832,10 +833,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>40</v>
+            <v>41.666666666666664</v>
           </cell>
           <cell r="G45">
-            <v>-0.16030534351145032</v>
+            <v>-0.12531806615776075</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -854,10 +855,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>3</v>
+            <v>3.0555555555555554</v>
           </cell>
           <cell r="G47">
-            <v>8.19672131147553E-2</v>
+            <v>0.10200364298725062</v>
           </cell>
           <cell r="H47" t="str">
             <v>SUBIÓ</v>
@@ -880,6 +881,7 @@
       <sheetData sheetId="17"/>
       <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1133,11 +1135,11 @@
       </c>
       <c r="E2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!$F$4</f>
-        <v>1069.1111111111111</v>
+        <v>1128.9444444444443</v>
       </c>
       <c r="F2" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>2.2983839789685323E-2</v>
+        <v>8.0235637516430813E-2</v>
       </c>
       <c r="G2" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1162,15 +1164,15 @@
       </c>
       <c r="E3" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>71.222222222222229</v>
+        <v>76.833333333333329</v>
       </c>
       <c r="F3" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-6.2304674512932978E-2</v>
+        <v>1.1569918212646968E-2</v>
       </c>
       <c r="G3" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H3">
         <v>1.59</v>
@@ -1191,11 +1193,11 @@
       </c>
       <c r="E4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>514.66666666666663</v>
+        <v>541.22222222222217</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>5.2977463653554047E-2</v>
+        <v>0.1073085547185797</v>
       </c>
       <c r="G4" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1220,11 +1222,11 @@
       </c>
       <c r="E5" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>92.277777777777771</v>
+        <v>94.888888888888886</v>
       </c>
       <c r="F5" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>1.0005527915975643E-2</v>
+        <v>3.8584853510226669E-2</v>
       </c>
       <c r="G5" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1249,11 +1251,11 @@
       </c>
       <c r="E6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>16.055555555555557</v>
+        <v>17.111111111111111</v>
       </c>
       <c r="F6" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>6.3311174422286953E-3</v>
+        <v>7.2491294713516785E-2</v>
       </c>
       <c r="G6" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1278,11 +1280,11 @@
       </c>
       <c r="E7" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1190.4444444444443</v>
+        <v>1261.8333333333333</v>
       </c>
       <c r="F7" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>-0.17411063108139846</v>
+        <v>-0.1245834778678272</v>
       </c>
       <c r="G7" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1307,11 +1309,11 @@
       </c>
       <c r="E8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>112.05555555555556</v>
+        <v>117.05555555555556</v>
       </c>
       <c r="F8" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-0.15690074479404159</v>
+        <v>-0.11928104575163401</v>
       </c>
       <c r="G8" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1336,11 +1338,11 @@
       </c>
       <c r="E9" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="F9" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-0.19721197211972108</v>
+        <v>-0.14910482438157713</v>
       </c>
       <c r="G9" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1365,11 +1367,11 @@
       </c>
       <c r="E10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>606.94444444444446</v>
+        <v>635.83333333333337</v>
       </c>
       <c r="F10" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>-0.14966708413820429</v>
+        <v>-0.10919357235347804</v>
       </c>
       <c r="G10" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1394,11 +1396,11 @@
       </c>
       <c r="E11" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>351.38888888888891</v>
+        <v>364.27777777777777</v>
       </c>
       <c r="F11" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.26550541039852205</v>
+        <v>-0.23856426497756666</v>
       </c>
       <c r="G11" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1423,11 +1425,11 @@
       </c>
       <c r="E12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3036.6666666666665</v>
+        <v>3228.2777777777778</v>
       </c>
       <c r="F12" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-0.13063092372091012</v>
+        <v>-7.5774466639194293E-2</v>
       </c>
       <c r="G12" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1452,11 +1454,11 @@
       </c>
       <c r="E13" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2045.8333333333333</v>
+        <v>2163</v>
       </c>
       <c r="F13" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-8.2473736426523114E-2</v>
+        <v>-2.9926203775431093E-2</v>
       </c>
       <c r="G13" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1481,11 +1483,11 @@
       </c>
       <c r="E14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2033.6666666666667</v>
+        <v>2146.5555555555557</v>
       </c>
       <c r="F14" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-0.11808033220976</v>
+        <v>-6.9124948804040409E-2</v>
       </c>
       <c r="G14" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1510,11 +1512,11 @@
       </c>
       <c r="E15" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2252.3888888888887</v>
+        <v>2385.1111111111113</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-0.16831614851117715</v>
+        <v>-0.11930910114894933</v>
       </c>
       <c r="G15" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1539,11 +1541,11 @@
       </c>
       <c r="E16" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>126.72222222222223</v>
+        <v>132.61111111111111</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.27190156989060088</v>
+        <v>-0.23806621978468401</v>
       </c>
       <c r="G16" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1568,11 +1570,11 @@
       </c>
       <c r="E17" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>200.72222222222223</v>
+        <v>214.33333333333334</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>-6.4628492080303079E-2</v>
+        <v>-1.2003106686435672E-3</v>
       </c>
       <c r="G17" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1597,11 +1599,11 @@
       </c>
       <c r="E18" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>147</v>
+        <v>150.66666666666666</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>0.15541264737406202</v>
+        <v>0.18423246397522908</v>
       </c>
       <c r="G18" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1626,11 +1628,11 @@
       </c>
       <c r="E19" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>456.16666666666669</v>
+        <v>476.11111111111109</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>-5.7860808611841286E-2</v>
+        <v>-1.6668752868527648E-2</v>
       </c>
       <c r="G19" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1655,15 +1657,15 @@
       </c>
       <c r="E20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>762</v>
+        <v>795</v>
       </c>
       <c r="F20" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-2.159449048675155E-2</v>
+        <v>2.0777401657523065E-2</v>
       </c>
       <c r="G20" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H20">
         <v>4.1500000000000004</v>
@@ -1742,11 +1744,11 @@
       </c>
       <c r="E23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>659.22222222222217</v>
+        <v>691</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-0.24040806112769664</v>
+        <v>-0.20379196564185831</v>
       </c>
       <c r="G23" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1771,11 +1773,11 @@
       </c>
       <c r="E24" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>1024.4444444444443</v>
+        <v>1094.5</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.25901572271903683</v>
+        <v>-0.2083442924776433</v>
       </c>
       <c r="G24" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1800,11 +1802,11 @@
       </c>
       <c r="E25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>447.05555555555554</v>
+        <v>466.72222222222223</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.18060299739879848</v>
+        <v>-0.14455645347922286</v>
       </c>
       <c r="G25" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1829,11 +1831,11 @@
       </c>
       <c r="E26" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>347.44444444444446</v>
+        <v>367.77777777777777</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-0.31062610229276888</v>
+        <v>-0.27028218694885364</v>
       </c>
       <c r="G26" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1858,11 +1860,11 @@
       </c>
       <c r="E27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>102.27777777777777</v>
+        <v>106.72222222222223</v>
       </c>
       <c r="F27" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>-0.21489493680700944</v>
+        <v>-0.18077847561448401</v>
       </c>
       <c r="G27" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1887,11 +1889,11 @@
       </c>
       <c r="E28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>111.61111111111111</v>
+        <v>118</v>
       </c>
       <c r="F28" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>-0.2182602851179738</v>
+        <v>-0.1735116205030246</v>
       </c>
       <c r="G28" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1916,11 +1918,11 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>753.94444444444446</v>
+        <v>792.33333333333337</v>
       </c>
       <c r="F29" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-0.11489979841100439</v>
+        <v>-6.9832799715403793E-2</v>
       </c>
       <c r="G29" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1945,11 +1947,11 @@
       </c>
       <c r="E30" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>632.55555555555554</v>
+        <v>655.38888888888891</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-0.26224766886379569</v>
+        <v>-0.23561705160602464</v>
       </c>
       <c r="G30" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -1974,11 +1976,11 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>788.22222222222217</v>
+        <v>825.94444444444446</v>
       </c>
       <c r="F31" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-0.26177569651388299</v>
+        <v>-0.22644624189962637</v>
       </c>
       <c r="G31" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2003,11 +2005,11 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>535.16666666666663</v>
+        <v>560.27777777777783</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-0.21883846426043885</v>
+        <v>-0.18218477235196973</v>
       </c>
       <c r="G32" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2032,15 +2034,15 @@
       </c>
       <c r="E33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>203.83333333333334</v>
+        <v>211.27777777777777</v>
       </c>
       <c r="F33" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-2.344657375145176E-2</v>
+        <v>1.2219318621757624E-2</v>
       </c>
       <c r="G33" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H33">
         <v>1.1599999999999999</v>
@@ -2061,11 +2063,11 @@
       </c>
       <c r="E34" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>176.16666666666666</v>
+        <v>211.55555555555554</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-0.65509774257660702</v>
+        <v>-0.58581274163724995</v>
       </c>
       <c r="G34" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2090,11 +2092,11 @@
       </c>
       <c r="E35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>330.66666666666669</v>
+        <v>354.44444444444446</v>
       </c>
       <c r="F35" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.2690980943769048</v>
+        <v>-0.2165399600343838</v>
       </c>
       <c r="G35" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2119,11 +2121,11 @@
       </c>
       <c r="E36" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>256.72222222222223</v>
+        <v>270.88888888888891</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>-0.24694814814814814</v>
+        <v>-0.20539259259259257</v>
       </c>
       <c r="G36" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2148,11 +2150,11 @@
       </c>
       <c r="E37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>378.5</v>
+        <v>407.22222222222223</v>
       </c>
       <c r="F37" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>-0.25251346499102334</v>
+        <v>-0.1957909435467784</v>
       </c>
       <c r="G37" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2177,11 +2179,11 @@
       </c>
       <c r="E38" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>234.11111111111111</v>
+        <v>242.72222222222223</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>-0.1553879231806421</v>
+        <v>-0.12432127109070368</v>
       </c>
       <c r="G38" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2206,11 +2208,11 @@
       </c>
       <c r="E39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>241.16666666666666</v>
+        <v>256.77777777777777</v>
       </c>
       <c r="F39" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-0.18135061461708579</v>
+        <v>-0.1283581066022047</v>
       </c>
       <c r="G39" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2235,11 +2237,11 @@
       </c>
       <c r="E40" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>46.777777777777779</v>
+        <v>52.111111111111114</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>-0.34534916595985299</v>
+        <v>-0.27070964093864847</v>
       </c>
       <c r="G40" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2264,11 +2266,11 @@
       </c>
       <c r="E41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>76.111111111111114</v>
+        <v>85.222222222222229</v>
       </c>
       <c r="F41" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.27229706890723837</v>
+        <v>-0.18518518518518512</v>
       </c>
       <c r="G41" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2293,11 +2295,11 @@
       </c>
       <c r="E42" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>33.444444444444443</v>
+        <v>35.444444444444443</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-0.31299927378358749</v>
+        <v>-0.27191617387695821</v>
       </c>
       <c r="G42" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2322,11 +2324,11 @@
       </c>
       <c r="E43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>40</v>
+        <v>41.666666666666664</v>
       </c>
       <c r="F43" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-0.16030534351145032</v>
+        <v>-0.12531806615776075</v>
       </c>
       <c r="G43" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2380,11 +2382,11 @@
       </c>
       <c r="E45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>3</v>
+        <v>3.0555555555555554</v>
       </c>
       <c r="F45" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>8.19672131147553E-2</v>
+        <v>0.10200364298725062</v>
       </c>
       <c r="G45" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D279F48B-8479-4F69-BD32-C84F0154010F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B7FF445-DB7E-4D3F-801E-50BAFA15E06D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -374,6 +374,7 @@
       <sheetName val="INVENTARIO NACIONAL 23-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 27-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 28-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 29-07-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -382,10 +383,10 @@
       <sheetData sheetId="3">
         <row r="4">
           <cell r="F4">
-            <v>1128.9444444444443</v>
+            <v>1133.578947368421</v>
           </cell>
           <cell r="G4">
-            <v>8.0235637516430813E-2</v>
+            <v>8.4670182763799007E-2</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -393,10 +394,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>76.833333333333329</v>
+            <v>77.15789473684211</v>
           </cell>
           <cell r="G5">
-            <v>1.1569918212646968E-2</v>
+            <v>1.5843018677753617E-2</v>
           </cell>
           <cell r="H5" t="str">
             <v>SUBIÓ</v>
@@ -404,10 +405,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>541.22222222222217</v>
+            <v>543.84210526315792</v>
           </cell>
           <cell r="G6">
-            <v>0.1073085547185797</v>
+            <v>0.11266867997670182</v>
           </cell>
           <cell r="H6" t="str">
             <v>SUBIÓ</v>
@@ -415,10 +416,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>94.888888888888886</v>
+            <v>95.15789473684211</v>
           </cell>
           <cell r="G7">
-            <v>3.8584853510226669E-2</v>
+            <v>4.1529196124640011E-2</v>
           </cell>
           <cell r="H7" t="str">
             <v>SUBIÓ</v>
@@ -426,10 +427,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>17.111111111111111</v>
+            <v>17.315789473684209</v>
           </cell>
           <cell r="G8">
-            <v>7.2491294713516785E-2</v>
+            <v>8.5320137951716779E-2</v>
           </cell>
           <cell r="H8" t="str">
             <v>SUBIÓ</v>
@@ -437,10 +438,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1261.8333333333333</v>
+            <v>1256.9473684210527</v>
           </cell>
           <cell r="G9">
-            <v>-0.1245834778678272</v>
+            <v>-0.12797319210169478</v>
           </cell>
           <cell r="H9" t="str">
             <v>BAJO</v>
@@ -448,10 +449,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>117.05555555555556</v>
+            <v>121.26315789473684</v>
           </cell>
           <cell r="G10">
-            <v>-0.11928104575163401</v>
+            <v>-8.762329901360788E-2</v>
           </cell>
           <cell r="H10" t="str">
             <v>BAJO</v>
@@ -459,10 +460,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>283</v>
+            <v>287.78947368421052</v>
           </cell>
           <cell r="G11">
-            <v>-0.14910482438157713</v>
+            <v>-0.13470432949943534</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -470,10 +471,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>635.83333333333337</v>
+            <v>671.10526315789468</v>
           </cell>
           <cell r="G12">
-            <v>-0.10919357235347804</v>
+            <v>-5.9777380788786583E-2</v>
           </cell>
           <cell r="H12" t="str">
             <v>BAJO</v>
@@ -481,10 +482,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>364.27777777777777</v>
+            <v>393.31578947368422</v>
           </cell>
           <cell r="G13">
-            <v>-0.23856426497756666</v>
+            <v>-0.17786723340417554</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -492,10 +493,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3228.2777777777778</v>
+            <v>3267.8421052631579</v>
           </cell>
           <cell r="G14">
-            <v>-7.5774466639194293E-2</v>
+            <v>-6.4447572180500012E-2</v>
           </cell>
           <cell r="H14" t="str">
             <v>BAJO</v>
@@ -503,10 +504,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2163</v>
+            <v>2184.6842105263158</v>
           </cell>
           <cell r="G15">
-            <v>-2.9926203775431093E-2</v>
+            <v>-2.0201153186713561E-2</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -514,10 +515,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2146.5555555555557</v>
+            <v>2175.8947368421054</v>
           </cell>
           <cell r="G16">
-            <v>-6.9124948804040409E-2</v>
+            <v>-5.6401722604988658E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -525,10 +526,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2385.1111111111113</v>
+            <v>2428.3684210526317</v>
           </cell>
           <cell r="G17">
-            <v>-0.11930910114894933</v>
+            <v>-0.10333654582571794</v>
           </cell>
           <cell r="H17" t="str">
             <v>BAJO</v>
@@ -536,10 +537,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>132.61111111111111</v>
+            <v>136.10526315789474</v>
           </cell>
           <cell r="G18">
-            <v>-0.23806621978468401</v>
+            <v>-0.21799013071985263</v>
           </cell>
           <cell r="H18" t="str">
             <v>BAJO</v>
@@ -547,21 +548,21 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>214.33333333333334</v>
+            <v>224</v>
           </cell>
           <cell r="G19">
-            <v>-1.2003106686435672E-3</v>
+            <v>4.384664266045335E-2</v>
           </cell>
           <cell r="H19" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="20">
           <cell r="F20">
-            <v>150.66666666666666</v>
+            <v>153.52631578947367</v>
           </cell>
           <cell r="G20">
-            <v>0.18423246397522908</v>
+            <v>0.20670916304695264</v>
           </cell>
           <cell r="H20" t="str">
             <v>SUBIÓ</v>
@@ -569,21 +570,21 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>476.11111111111109</v>
+            <v>493.42105263157896</v>
           </cell>
           <cell r="G21">
-            <v>-1.6668752868527648E-2</v>
+            <v>1.908215902128596E-2</v>
           </cell>
           <cell r="H21" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="22">
           <cell r="F22">
-            <v>795</v>
+            <v>823.63157894736844</v>
           </cell>
           <cell r="G22">
-            <v>2.0777401657523065E-2</v>
+            <v>5.7540255447770861E-2</v>
           </cell>
           <cell r="H22" t="str">
             <v>SUBIÓ</v>
@@ -591,10 +592,10 @@
         </row>
         <row r="23">
           <cell r="F23">
-            <v>6.1111111111111107</v>
+            <v>5.7894736842105265</v>
           </cell>
           <cell r="G23">
-            <v>-0.88842784693407095</v>
+            <v>-0.89430006551648833</v>
           </cell>
           <cell r="H23" t="str">
             <v>BAJO</v>
@@ -602,10 +603,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>49.444444444444443</v>
+            <v>53.157894736842103</v>
           </cell>
           <cell r="G24">
-            <v>0.1888281724347296</v>
+            <v>0.2781133160770779</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -613,10 +614,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>691</v>
+            <v>688.84210526315792</v>
           </cell>
           <cell r="G25">
-            <v>-0.20379196564185831</v>
+            <v>-0.20627841010896797</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -624,10 +625,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>1094.5</v>
+            <v>1093.6842105263158</v>
           </cell>
           <cell r="G26">
-            <v>-0.2083442924776433</v>
+            <v>-0.20893435587917708</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -635,10 +636,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>466.72222222222223</v>
+            <v>476.5263157894737</v>
           </cell>
           <cell r="G27">
-            <v>-0.14455645347922286</v>
+            <v>-0.12658677435904186</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -646,10 +647,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>367.77777777777777</v>
+            <v>377.68421052631578</v>
           </cell>
           <cell r="G28">
-            <v>-0.27028218694885364</v>
+            <v>-0.25062656641604009</v>
           </cell>
           <cell r="H28" t="str">
             <v>BAJO</v>
@@ -657,10 +658,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>106.72222222222223</v>
+            <v>111.26315789473684</v>
           </cell>
           <cell r="G29">
-            <v>-0.18077847561448401</v>
+            <v>-0.14592132809343672</v>
           </cell>
           <cell r="H29" t="str">
             <v>BAJO</v>
@@ -668,10 +669,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>118</v>
+            <v>124.47368421052632</v>
           </cell>
           <cell r="G30">
-            <v>-0.1735116205030246</v>
+            <v>-0.12816903768494781</v>
           </cell>
           <cell r="H30" t="str">
             <v>BAJO</v>
@@ -679,10 +680,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>792.33333333333337</v>
+            <v>801.31578947368416</v>
           </cell>
           <cell r="G31">
-            <v>-6.9832799715403793E-2</v>
+            <v>-5.9287760489805219E-2</v>
           </cell>
           <cell r="H31" t="str">
             <v>BAJO</v>
@@ -690,10 +691,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>655.38888888888891</v>
+            <v>658.10526315789468</v>
           </cell>
           <cell r="G32">
-            <v>-0.23561705160602464</v>
+            <v>-0.23244893232923269</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -701,10 +702,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>825.94444444444446</v>
+            <v>841.47368421052636</v>
           </cell>
           <cell r="G33">
-            <v>-0.22644624189962637</v>
+            <v>-0.21190204118213796</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -712,10 +713,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>560.27777777777783</v>
+            <v>562.0526315789474</v>
           </cell>
           <cell r="G34">
-            <v>-0.18218477235196973</v>
+            <v>-0.17959408872499716</v>
           </cell>
           <cell r="H34" t="str">
             <v>BAJO</v>
@@ -723,10 +724,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>211.27777777777777</v>
+            <v>213.21052631578948</v>
           </cell>
           <cell r="G35">
-            <v>1.2219318621757624E-2</v>
+            <v>2.1479002384008794E-2</v>
           </cell>
           <cell r="H35" t="str">
             <v>SUBIÓ</v>
@@ -734,10 +735,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>211.55555555555554</v>
+            <v>236.10526315789474</v>
           </cell>
           <cell r="G36">
-            <v>-0.58581274163724995</v>
+            <v>-0.53774888409062171</v>
           </cell>
           <cell r="H36" t="str">
             <v>BAJO</v>
@@ -745,10 +746,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>354.44444444444446</v>
+            <v>364.31578947368422</v>
           </cell>
           <cell r="G37">
-            <v>-0.2165399600343838</v>
+            <v>-0.19472044926946119</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -756,10 +757,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>270.88888888888891</v>
+            <v>273.94736842105266</v>
           </cell>
           <cell r="G38">
-            <v>-0.20539259259259257</v>
+            <v>-0.19642105263157894</v>
           </cell>
           <cell r="H38" t="str">
             <v>BAJO</v>
@@ -767,10 +768,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>407.22222222222223</v>
+            <v>417.26315789473682</v>
           </cell>
           <cell r="G39">
-            <v>-0.1957909435467784</v>
+            <v>-0.17596144760464905</v>
           </cell>
           <cell r="H39" t="str">
             <v>BAJO</v>
@@ -778,10 +779,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>242.72222222222223</v>
+            <v>243.68421052631578</v>
           </cell>
           <cell r="G40">
-            <v>-0.12432127109070368</v>
+            <v>-0.12085066717301618</v>
           </cell>
           <cell r="H40" t="str">
             <v>BAJO</v>
@@ -789,10 +790,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>256.77777777777777</v>
+            <v>263.68421052631578</v>
           </cell>
           <cell r="G41">
-            <v>-0.1283581066022047</v>
+            <v>-0.10491395902191825</v>
           </cell>
           <cell r="H41" t="str">
             <v>BAJO</v>
@@ -800,10 +801,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>52.111111111111114</v>
+            <v>51.368421052631582</v>
           </cell>
           <cell r="G42">
-            <v>-0.27070964093864847</v>
+            <v>-0.28110352216418899</v>
           </cell>
           <cell r="H42" t="str">
             <v>BAJO</v>
@@ -811,10 +812,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>85.222222222222229</v>
+            <v>85.315789473684205</v>
           </cell>
           <cell r="G43">
-            <v>-0.18518518518518512</v>
+            <v>-0.18429058304169821</v>
           </cell>
           <cell r="H43" t="str">
             <v>BAJO</v>
@@ -822,10 +823,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>35.444444444444443</v>
+            <v>34.421052631578945</v>
           </cell>
           <cell r="G44">
-            <v>-0.27191617387695821</v>
+            <v>-0.29293822792274804</v>
           </cell>
           <cell r="H44" t="str">
             <v>BAJO</v>
@@ -833,10 +834,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>41.666666666666664</v>
+            <v>41.421052631578945</v>
           </cell>
           <cell r="G45">
-            <v>-0.12531806615776075</v>
+            <v>-0.13047408597830457</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -844,21 +845,21 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>0.55555555555555558</v>
+            <v>0.52631578947368418</v>
           </cell>
           <cell r="G46">
-            <v>1.8518518518518601E-2</v>
+            <v>-3.5087719298245612E-2</v>
           </cell>
           <cell r="H46" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="47">
           <cell r="F47">
-            <v>3.0555555555555554</v>
+            <v>2.8947368421052633</v>
           </cell>
           <cell r="G47">
-            <v>0.10200364298725062</v>
+            <v>4.4003451251079628E-2</v>
           </cell>
           <cell r="H47" t="str">
             <v>SUBIÓ</v>
@@ -882,6 +883,7 @@
       <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
       <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1135,11 +1137,11 @@
       </c>
       <c r="E2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!$F$4</f>
-        <v>1128.9444444444443</v>
+        <v>1133.578947368421</v>
       </c>
       <c r="F2" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>8.0235637516430813E-2</v>
+        <v>8.4670182763799007E-2</v>
       </c>
       <c r="G2" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1164,11 +1166,11 @@
       </c>
       <c r="E3" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>76.833333333333329</v>
+        <v>77.15789473684211</v>
       </c>
       <c r="F3" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>1.1569918212646968E-2</v>
+        <v>1.5843018677753617E-2</v>
       </c>
       <c r="G3" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1193,11 +1195,11 @@
       </c>
       <c r="E4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>541.22222222222217</v>
+        <v>543.84210526315792</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>0.1073085547185797</v>
+        <v>0.11266867997670182</v>
       </c>
       <c r="G4" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1222,11 +1224,11 @@
       </c>
       <c r="E5" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>94.888888888888886</v>
+        <v>95.15789473684211</v>
       </c>
       <c r="F5" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>3.8584853510226669E-2</v>
+        <v>4.1529196124640011E-2</v>
       </c>
       <c r="G5" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1251,11 +1253,11 @@
       </c>
       <c r="E6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>17.111111111111111</v>
+        <v>17.315789473684209</v>
       </c>
       <c r="F6" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>7.2491294713516785E-2</v>
+        <v>8.5320137951716779E-2</v>
       </c>
       <c r="G6" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1280,11 +1282,11 @@
       </c>
       <c r="E7" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1261.8333333333333</v>
+        <v>1256.9473684210527</v>
       </c>
       <c r="F7" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>-0.1245834778678272</v>
+        <v>-0.12797319210169478</v>
       </c>
       <c r="G7" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1309,11 +1311,11 @@
       </c>
       <c r="E8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>117.05555555555556</v>
+        <v>121.26315789473684</v>
       </c>
       <c r="F8" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-0.11928104575163401</v>
+        <v>-8.762329901360788E-2</v>
       </c>
       <c r="G8" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1338,11 +1340,11 @@
       </c>
       <c r="E9" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>283</v>
+        <v>287.78947368421052</v>
       </c>
       <c r="F9" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-0.14910482438157713</v>
+        <v>-0.13470432949943534</v>
       </c>
       <c r="G9" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1367,11 +1369,11 @@
       </c>
       <c r="E10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>635.83333333333337</v>
+        <v>671.10526315789468</v>
       </c>
       <c r="F10" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>-0.10919357235347804</v>
+        <v>-5.9777380788786583E-2</v>
       </c>
       <c r="G10" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1396,11 +1398,11 @@
       </c>
       <c r="E11" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>364.27777777777777</v>
+        <v>393.31578947368422</v>
       </c>
       <c r="F11" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.23856426497756666</v>
+        <v>-0.17786723340417554</v>
       </c>
       <c r="G11" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1425,11 +1427,11 @@
       </c>
       <c r="E12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3228.2777777777778</v>
+        <v>3267.8421052631579</v>
       </c>
       <c r="F12" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-7.5774466639194293E-2</v>
+        <v>-6.4447572180500012E-2</v>
       </c>
       <c r="G12" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1454,11 +1456,11 @@
       </c>
       <c r="E13" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2163</v>
+        <v>2184.6842105263158</v>
       </c>
       <c r="F13" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-2.9926203775431093E-2</v>
+        <v>-2.0201153186713561E-2</v>
       </c>
       <c r="G13" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1483,11 +1485,11 @@
       </c>
       <c r="E14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2146.5555555555557</v>
+        <v>2175.8947368421054</v>
       </c>
       <c r="F14" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-6.9124948804040409E-2</v>
+        <v>-5.6401722604988658E-2</v>
       </c>
       <c r="G14" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1512,11 +1514,11 @@
       </c>
       <c r="E15" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2385.1111111111113</v>
+        <v>2428.3684210526317</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-0.11930910114894933</v>
+        <v>-0.10333654582571794</v>
       </c>
       <c r="G15" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1541,11 +1543,11 @@
       </c>
       <c r="E16" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>132.61111111111111</v>
+        <v>136.10526315789474</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.23806621978468401</v>
+        <v>-0.21799013071985263</v>
       </c>
       <c r="G16" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1570,15 +1572,15 @@
       </c>
       <c r="E17" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>214.33333333333334</v>
+        <v>224</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>-1.2003106686435672E-3</v>
+        <v>4.384664266045335E-2</v>
       </c>
       <c r="G17" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H17">
         <v>3.68</v>
@@ -1599,11 +1601,11 @@
       </c>
       <c r="E18" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>150.66666666666666</v>
+        <v>153.52631578947367</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>0.18423246397522908</v>
+        <v>0.20670916304695264</v>
       </c>
       <c r="G18" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1628,15 +1630,15 @@
       </c>
       <c r="E19" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>476.11111111111109</v>
+        <v>493.42105263157896</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>-1.6668752868527648E-2</v>
+        <v>1.908215902128596E-2</v>
       </c>
       <c r="G19" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H19">
         <v>4.1500000000000004</v>
@@ -1657,11 +1659,11 @@
       </c>
       <c r="E20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>795</v>
+        <v>823.63157894736844</v>
       </c>
       <c r="F20" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>2.0777401657523065E-2</v>
+        <v>5.7540255447770861E-2</v>
       </c>
       <c r="G20" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1686,11 +1688,11 @@
       </c>
       <c r="E21" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>6.1111111111111107</v>
+        <v>5.7894736842105265</v>
       </c>
       <c r="F21" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>-0.88842784693407095</v>
+        <v>-0.89430006551648833</v>
       </c>
       <c r="G21" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
@@ -1715,11 +1717,11 @@
       </c>
       <c r="E22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>49.444444444444443</v>
+        <v>53.157894736842103</v>
       </c>
       <c r="F22" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>0.1888281724347296</v>
+        <v>0.2781133160770779</v>
       </c>
       <c r="G22" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1744,11 +1746,11 @@
       </c>
       <c r="E23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>691</v>
+        <v>688.84210526315792</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-0.20379196564185831</v>
+        <v>-0.20627841010896797</v>
       </c>
       <c r="G23" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1773,11 +1775,11 @@
       </c>
       <c r="E24" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>1094.5</v>
+        <v>1093.6842105263158</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.2083442924776433</v>
+        <v>-0.20893435587917708</v>
       </c>
       <c r="G24" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1802,11 +1804,11 @@
       </c>
       <c r="E25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>466.72222222222223</v>
+        <v>476.5263157894737</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.14455645347922286</v>
+        <v>-0.12658677435904186</v>
       </c>
       <c r="G25" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1831,11 +1833,11 @@
       </c>
       <c r="E26" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>367.77777777777777</v>
+        <v>377.68421052631578</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-0.27028218694885364</v>
+        <v>-0.25062656641604009</v>
       </c>
       <c r="G26" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1860,11 +1862,11 @@
       </c>
       <c r="E27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>106.72222222222223</v>
+        <v>111.26315789473684</v>
       </c>
       <c r="F27" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>-0.18077847561448401</v>
+        <v>-0.14592132809343672</v>
       </c>
       <c r="G27" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1889,11 +1891,11 @@
       </c>
       <c r="E28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>118</v>
+        <v>124.47368421052632</v>
       </c>
       <c r="F28" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>-0.1735116205030246</v>
+        <v>-0.12816903768494781</v>
       </c>
       <c r="G28" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1918,11 +1920,11 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>792.33333333333337</v>
+        <v>801.31578947368416</v>
       </c>
       <c r="F29" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-6.9832799715403793E-2</v>
+        <v>-5.9287760489805219E-2</v>
       </c>
       <c r="G29" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1947,11 +1949,11 @@
       </c>
       <c r="E30" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>655.38888888888891</v>
+        <v>658.10526315789468</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-0.23561705160602464</v>
+        <v>-0.23244893232923269</v>
       </c>
       <c r="G30" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -1976,11 +1978,11 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>825.94444444444446</v>
+        <v>841.47368421052636</v>
       </c>
       <c r="F31" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-0.22644624189962637</v>
+        <v>-0.21190204118213796</v>
       </c>
       <c r="G31" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2005,11 +2007,11 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>560.27777777777783</v>
+        <v>562.0526315789474</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-0.18218477235196973</v>
+        <v>-0.17959408872499716</v>
       </c>
       <c r="G32" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2034,11 +2036,11 @@
       </c>
       <c r="E33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>211.27777777777777</v>
+        <v>213.21052631578948</v>
       </c>
       <c r="F33" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>1.2219318621757624E-2</v>
+        <v>2.1479002384008794E-2</v>
       </c>
       <c r="G33" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2063,11 +2065,11 @@
       </c>
       <c r="E34" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>211.55555555555554</v>
+        <v>236.10526315789474</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-0.58581274163724995</v>
+        <v>-0.53774888409062171</v>
       </c>
       <c r="G34" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2092,11 +2094,11 @@
       </c>
       <c r="E35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>354.44444444444446</v>
+        <v>364.31578947368422</v>
       </c>
       <c r="F35" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.2165399600343838</v>
+        <v>-0.19472044926946119</v>
       </c>
       <c r="G35" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2121,11 +2123,11 @@
       </c>
       <c r="E36" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>270.88888888888891</v>
+        <v>273.94736842105266</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>-0.20539259259259257</v>
+        <v>-0.19642105263157894</v>
       </c>
       <c r="G36" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2150,11 +2152,11 @@
       </c>
       <c r="E37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>407.22222222222223</v>
+        <v>417.26315789473682</v>
       </c>
       <c r="F37" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>-0.1957909435467784</v>
+        <v>-0.17596144760464905</v>
       </c>
       <c r="G37" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2179,11 +2181,11 @@
       </c>
       <c r="E38" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>242.72222222222223</v>
+        <v>243.68421052631578</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>-0.12432127109070368</v>
+        <v>-0.12085066717301618</v>
       </c>
       <c r="G38" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2208,11 +2210,11 @@
       </c>
       <c r="E39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>256.77777777777777</v>
+        <v>263.68421052631578</v>
       </c>
       <c r="F39" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-0.1283581066022047</v>
+        <v>-0.10491395902191825</v>
       </c>
       <c r="G39" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2237,11 +2239,11 @@
       </c>
       <c r="E40" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>52.111111111111114</v>
+        <v>51.368421052631582</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>-0.27070964093864847</v>
+        <v>-0.28110352216418899</v>
       </c>
       <c r="G40" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2266,11 +2268,11 @@
       </c>
       <c r="E41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>85.222222222222229</v>
+        <v>85.315789473684205</v>
       </c>
       <c r="F41" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.18518518518518512</v>
+        <v>-0.18429058304169821</v>
       </c>
       <c r="G41" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2295,11 +2297,11 @@
       </c>
       <c r="E42" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>35.444444444444443</v>
+        <v>34.421052631578945</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-0.27191617387695821</v>
+        <v>-0.29293822792274804</v>
       </c>
       <c r="G42" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2324,11 +2326,11 @@
       </c>
       <c r="E43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>41.666666666666664</v>
+        <v>41.421052631578945</v>
       </c>
       <c r="F43" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-0.12531806615776075</v>
+        <v>-0.13047408597830457</v>
       </c>
       <c r="G43" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2353,15 +2355,15 @@
       </c>
       <c r="E44" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>0.55555555555555558</v>
+        <v>0.52631578947368418</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>1.8518518518518601E-2</v>
+        <v>-3.5087719298245612E-2</v>
       </c>
       <c r="G44" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H44">
         <v>18</v>
@@ -2382,11 +2384,11 @@
       </c>
       <c r="E45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>3.0555555555555554</v>
+        <v>2.8947368421052633</v>
       </c>
       <c r="F45" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>0.10200364298725062</v>
+        <v>4.4003451251079628E-2</v>
       </c>
       <c r="G45" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B7FF445-DB7E-4D3F-801E-50BAFA15E06D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C176332A-6AFF-4973-A5A3-C5319B8E78ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -375,6 +375,7 @@
       <sheetName val="INVENTARIO NACIONAL 27-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 28-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 29-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 30-07-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -383,10 +384,10 @@
       <sheetData sheetId="3">
         <row r="4">
           <cell r="F4">
-            <v>1133.578947368421</v>
+            <v>1156.3499999999999</v>
           </cell>
           <cell r="G4">
-            <v>8.4670182763799007E-2</v>
+            <v>0.10645876826722334</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -394,10 +395,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>77.15789473684211</v>
+            <v>78.45</v>
           </cell>
           <cell r="G5">
-            <v>1.5843018677753617E-2</v>
+            <v>3.2854578096948028E-2</v>
           </cell>
           <cell r="H5" t="str">
             <v>SUBIÓ</v>
@@ -405,10 +406,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>543.84210526315792</v>
+            <v>572</v>
           </cell>
           <cell r="G6">
-            <v>0.11266867997670182</v>
+            <v>0.17027806193620387</v>
           </cell>
           <cell r="H6" t="str">
             <v>SUBIÓ</v>
@@ -416,10 +417,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>95.15789473684211</v>
+            <v>97.5</v>
           </cell>
           <cell r="G7">
-            <v>4.1529196124640011E-2</v>
+            <v>6.7164179104477695E-2</v>
           </cell>
           <cell r="H7" t="str">
             <v>SUBIÓ</v>
@@ -427,10 +428,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>17.315789473684209</v>
+            <v>17.95</v>
           </cell>
           <cell r="G8">
-            <v>8.5320137951716779E-2</v>
+            <v>0.12507122507122492</v>
           </cell>
           <cell r="H8" t="str">
             <v>SUBIÓ</v>
@@ -438,10 +439,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1256.9473684210527</v>
+            <v>1311.9</v>
           </cell>
           <cell r="G9">
-            <v>-0.12797319210169478</v>
+            <v>-8.9848948314464994E-2</v>
           </cell>
           <cell r="H9" t="str">
             <v>BAJO</v>
@@ -449,10 +450,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>121.26315789473684</v>
+            <v>121.65</v>
           </cell>
           <cell r="G10">
-            <v>-8.762329901360788E-2</v>
+            <v>-8.4712722298221577E-2</v>
           </cell>
           <cell r="H10" t="str">
             <v>BAJO</v>
@@ -460,10 +461,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>287.78947368421052</v>
+            <v>300.45</v>
           </cell>
           <cell r="G11">
-            <v>-0.13470432949943534</v>
+            <v>-9.6637966379663709E-2</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -471,10 +472,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>671.10526315789468</v>
+            <v>675.05</v>
           </cell>
           <cell r="G12">
-            <v>-5.9777380788786583E-2</v>
+            <v>-5.4250780105712271E-2</v>
           </cell>
           <cell r="H12" t="str">
             <v>BAJO</v>
@@ -482,10 +483,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>393.31578947368422</v>
+            <v>412.05</v>
           </cell>
           <cell r="G13">
-            <v>-0.17786723340417554</v>
+            <v>-0.13870783847981005</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -493,10 +494,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3267.8421052631579</v>
+            <v>3326.45</v>
           </cell>
           <cell r="G14">
-            <v>-6.4447572180500012E-2</v>
+            <v>-4.7668683713969706E-2</v>
           </cell>
           <cell r="H14" t="str">
             <v>BAJO</v>
@@ -504,10 +505,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2184.6842105263158</v>
+            <v>2229.5</v>
           </cell>
           <cell r="G15">
-            <v>-2.0201153186713561E-2</v>
+            <v>-1.0192848697343493E-4</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -515,10 +516,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2175.8947368421054</v>
+            <v>2216.85</v>
           </cell>
           <cell r="G16">
-            <v>-5.6401722604988658E-2</v>
+            <v>-3.8641067591807854E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -526,10 +527,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2428.3684210526317</v>
+            <v>2466.25</v>
           </cell>
           <cell r="G17">
-            <v>-0.10333654582571794</v>
+            <v>-8.934895352545269E-2</v>
           </cell>
           <cell r="H17" t="str">
             <v>BAJO</v>
@@ -537,10 +538,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>136.10526315789474</v>
+            <v>138.75</v>
           </cell>
           <cell r="G18">
-            <v>-0.21799013071985263</v>
+            <v>-0.20279446330634621</v>
           </cell>
           <cell r="H18" t="str">
             <v>BAJO</v>
@@ -548,10 +549,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>224</v>
+            <v>229.45</v>
           </cell>
           <cell r="G19">
-            <v>4.384664266045335E-2</v>
+            <v>6.9243804278754428E-2</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -559,10 +560,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>153.52631578947367</v>
+            <v>154.4</v>
           </cell>
           <cell r="G20">
-            <v>0.20670916304695264</v>
+            <v>0.21357627724187211</v>
           </cell>
           <cell r="H20" t="str">
             <v>SUBIÓ</v>
@@ -570,10 +571,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>493.42105263157896</v>
+            <v>497.65</v>
           </cell>
           <cell r="G21">
-            <v>1.908215902128596E-2</v>
+            <v>2.7816372512204257E-2</v>
           </cell>
           <cell r="H21" t="str">
             <v>SUBIÓ</v>
@@ -581,10 +582,10 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>823.63157894736844</v>
+            <v>821.9</v>
           </cell>
           <cell r="G22">
-            <v>5.7540255447770861E-2</v>
+            <v>5.5316913738765017E-2</v>
           </cell>
           <cell r="H22" t="str">
             <v>SUBIÓ</v>
@@ -592,10 +593,10 @@
         </row>
         <row r="23">
           <cell r="F23">
-            <v>5.7894736842105265</v>
+            <v>5.5</v>
           </cell>
           <cell r="G23">
-            <v>-0.89430006551648833</v>
+            <v>-0.89958506224066392</v>
           </cell>
           <cell r="H23" t="str">
             <v>BAJO</v>
@@ -603,10 +604,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>53.157894736842103</v>
+            <v>53.6</v>
           </cell>
           <cell r="G24">
-            <v>0.2781133160770779</v>
+            <v>0.2887431693989071</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -614,10 +615,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>688.84210526315792</v>
+            <v>695.3</v>
           </cell>
           <cell r="G25">
-            <v>-0.20627841010896797</v>
+            <v>-0.19883727020373965</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -625,10 +626,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>1093.6842105263158</v>
+            <v>1122.5999999999999</v>
           </cell>
           <cell r="G26">
-            <v>-0.20893435587917708</v>
+            <v>-0.18801946344029463</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -636,10 +637,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>476.5263157894737</v>
+            <v>483.4</v>
           </cell>
           <cell r="G27">
-            <v>-0.12658677435904186</v>
+            <v>-0.11398816962426073</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -647,10 +648,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>377.68421052631578</v>
+            <v>377.05</v>
           </cell>
           <cell r="G28">
-            <v>-0.25062656641604009</v>
+            <v>-0.25188492063492063</v>
           </cell>
           <cell r="H28" t="str">
             <v>BAJO</v>
@@ -658,10 +659,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>111.26315789473684</v>
+            <v>111.35</v>
           </cell>
           <cell r="G29">
-            <v>-0.14592132809343672</v>
+            <v>-0.14525471039776705</v>
           </cell>
           <cell r="H29" t="str">
             <v>BAJO</v>
@@ -669,10 +670,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>124.47368421052632</v>
+            <v>125</v>
           </cell>
           <cell r="G30">
-            <v>-0.12816903768494781</v>
+            <v>-0.12448264883794979</v>
           </cell>
           <cell r="H30" t="str">
             <v>BAJO</v>
@@ -680,10 +681,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>801.31578947368416</v>
+            <v>806.7</v>
           </cell>
           <cell r="G31">
-            <v>-5.9287760489805219E-2</v>
+            <v>-5.2966915688367089E-2</v>
           </cell>
           <cell r="H31" t="str">
             <v>BAJO</v>
@@ -691,10 +692,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>658.10526315789468</v>
+            <v>657.95</v>
           </cell>
           <cell r="G32">
-            <v>-0.23244893232923269</v>
+            <v>-0.23263001643428927</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -702,10 +703,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>841.47368421052636</v>
+            <v>845.65</v>
           </cell>
           <cell r="G33">
-            <v>-0.21190204118213796</v>
+            <v>-0.20799063431247344</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -713,10 +714,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>562.0526315789474</v>
+            <v>573.95000000000005</v>
           </cell>
           <cell r="G34">
-            <v>-0.17959408872499716</v>
+            <v>-0.16222797239915077</v>
           </cell>
           <cell r="H34" t="str">
             <v>BAJO</v>
@@ -724,10 +725,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>213.21052631578948</v>
+            <v>216.95</v>
           </cell>
           <cell r="G35">
-            <v>2.1479002384008794E-2</v>
+            <v>3.9394599303135935E-2</v>
           </cell>
           <cell r="H35" t="str">
             <v>SUBIÓ</v>
@@ -735,10 +736,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>236.10526315789474</v>
+            <v>273.75</v>
           </cell>
           <cell r="G36">
-            <v>-0.53774888409062171</v>
+            <v>-0.46404734359704547</v>
           </cell>
           <cell r="H36" t="str">
             <v>BAJO</v>
@@ -746,10 +747,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>364.31578947368422</v>
+            <v>380.05</v>
           </cell>
           <cell r="G37">
-            <v>-0.19472044926946119</v>
+            <v>-0.15994172611272983</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -757,10 +758,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>273.94736842105266</v>
+            <v>277.89999999999998</v>
           </cell>
           <cell r="G38">
-            <v>-0.19642105263157894</v>
+            <v>-0.18482666666666681</v>
           </cell>
           <cell r="H38" t="str">
             <v>BAJO</v>
@@ -768,10 +769,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>417.26315789473682</v>
+            <v>428.65</v>
           </cell>
           <cell r="G39">
-            <v>-0.17596144760464905</v>
+            <v>-0.15347396768402166</v>
           </cell>
           <cell r="H39" t="str">
             <v>BAJO</v>
@@ -779,10 +780,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>243.68421052631578</v>
+            <v>245.9</v>
           </cell>
           <cell r="G40">
-            <v>-0.12085066717301618</v>
+            <v>-0.11285667431944901</v>
           </cell>
           <cell r="H40" t="str">
             <v>BAJO</v>
@@ -790,10 +791,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>263.68421052631578</v>
+            <v>269</v>
           </cell>
           <cell r="G41">
-            <v>-0.10491395902191825</v>
+            <v>-8.6869310291621593E-2</v>
           </cell>
           <cell r="H41" t="str">
             <v>BAJO</v>
@@ -801,10 +802,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>51.368421052631582</v>
+            <v>50.65</v>
           </cell>
           <cell r="G42">
-            <v>-0.28110352216418899</v>
+            <v>-0.29115776081424938</v>
           </cell>
           <cell r="H42" t="str">
             <v>BAJO</v>
@@ -812,10 +813,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>85.315789473684205</v>
+            <v>83.35</v>
           </cell>
           <cell r="G43">
-            <v>-0.18429058304169821</v>
+            <v>-0.20308561495002175</v>
           </cell>
           <cell r="H43" t="str">
             <v>BAJO</v>
@@ -823,10 +824,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>34.421052631578945</v>
+            <v>34.4</v>
           </cell>
           <cell r="G44">
-            <v>-0.29293822792274804</v>
+            <v>-0.29337068160597568</v>
           </cell>
           <cell r="H44" t="str">
             <v>BAJO</v>
@@ -834,10 +835,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>41.421052631578945</v>
+            <v>39.75</v>
           </cell>
           <cell r="G45">
-            <v>-0.13047408597830457</v>
+            <v>-0.16555343511450371</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -845,21 +846,21 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>0.52631578947368418</v>
+            <v>0.9</v>
           </cell>
           <cell r="G46">
-            <v>-3.5087719298245612E-2</v>
+            <v>0.65000000000000013</v>
           </cell>
           <cell r="H46" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="47">
           <cell r="F47">
-            <v>2.8947368421052633</v>
+            <v>3.45</v>
           </cell>
           <cell r="G47">
-            <v>4.4003451251079628E-2</v>
+            <v>0.24426229508196862</v>
           </cell>
           <cell r="H47" t="str">
             <v>SUBIÓ</v>
@@ -884,6 +885,7 @@
       <sheetData sheetId="19"/>
       <sheetData sheetId="20"/>
       <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1137,11 +1139,11 @@
       </c>
       <c r="E2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!$F$4</f>
-        <v>1133.578947368421</v>
+        <v>1156.3499999999999</v>
       </c>
       <c r="F2" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>8.4670182763799007E-2</v>
+        <v>0.10645876826722334</v>
       </c>
       <c r="G2" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1166,11 +1168,11 @@
       </c>
       <c r="E3" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>77.15789473684211</v>
+        <v>78.45</v>
       </c>
       <c r="F3" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>1.5843018677753617E-2</v>
+        <v>3.2854578096948028E-2</v>
       </c>
       <c r="G3" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1195,11 +1197,11 @@
       </c>
       <c r="E4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>543.84210526315792</v>
+        <v>572</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>0.11266867997670182</v>
+        <v>0.17027806193620387</v>
       </c>
       <c r="G4" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1224,11 +1226,11 @@
       </c>
       <c r="E5" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>95.15789473684211</v>
+        <v>97.5</v>
       </c>
       <c r="F5" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>4.1529196124640011E-2</v>
+        <v>6.7164179104477695E-2</v>
       </c>
       <c r="G5" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1253,11 +1255,11 @@
       </c>
       <c r="E6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>17.315789473684209</v>
+        <v>17.95</v>
       </c>
       <c r="F6" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>8.5320137951716779E-2</v>
+        <v>0.12507122507122492</v>
       </c>
       <c r="G6" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1282,11 +1284,11 @@
       </c>
       <c r="E7" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1256.9473684210527</v>
+        <v>1311.9</v>
       </c>
       <c r="F7" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>-0.12797319210169478</v>
+        <v>-8.9848948314464994E-2</v>
       </c>
       <c r="G7" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1311,11 +1313,11 @@
       </c>
       <c r="E8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>121.26315789473684</v>
+        <v>121.65</v>
       </c>
       <c r="F8" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-8.762329901360788E-2</v>
+        <v>-8.4712722298221577E-2</v>
       </c>
       <c r="G8" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1340,11 +1342,11 @@
       </c>
       <c r="E9" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>287.78947368421052</v>
+        <v>300.45</v>
       </c>
       <c r="F9" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-0.13470432949943534</v>
+        <v>-9.6637966379663709E-2</v>
       </c>
       <c r="G9" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1369,11 +1371,11 @@
       </c>
       <c r="E10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>671.10526315789468</v>
+        <v>675.05</v>
       </c>
       <c r="F10" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>-5.9777380788786583E-2</v>
+        <v>-5.4250780105712271E-2</v>
       </c>
       <c r="G10" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1398,11 +1400,11 @@
       </c>
       <c r="E11" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>393.31578947368422</v>
+        <v>412.05</v>
       </c>
       <c r="F11" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.17786723340417554</v>
+        <v>-0.13870783847981005</v>
       </c>
       <c r="G11" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1427,11 +1429,11 @@
       </c>
       <c r="E12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3267.8421052631579</v>
+        <v>3326.45</v>
       </c>
       <c r="F12" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-6.4447572180500012E-2</v>
+        <v>-4.7668683713969706E-2</v>
       </c>
       <c r="G12" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1456,11 +1458,11 @@
       </c>
       <c r="E13" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2184.6842105263158</v>
+        <v>2229.5</v>
       </c>
       <c r="F13" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-2.0201153186713561E-2</v>
+        <v>-1.0192848697343493E-4</v>
       </c>
       <c r="G13" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1485,11 +1487,11 @@
       </c>
       <c r="E14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2175.8947368421054</v>
+        <v>2216.85</v>
       </c>
       <c r="F14" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-5.6401722604988658E-2</v>
+        <v>-3.8641067591807854E-2</v>
       </c>
       <c r="G14" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1514,11 +1516,11 @@
       </c>
       <c r="E15" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2428.3684210526317</v>
+        <v>2466.25</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-0.10333654582571794</v>
+        <v>-8.934895352545269E-2</v>
       </c>
       <c r="G15" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1543,11 +1545,11 @@
       </c>
       <c r="E16" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>136.10526315789474</v>
+        <v>138.75</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.21799013071985263</v>
+        <v>-0.20279446330634621</v>
       </c>
       <c r="G16" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1572,11 +1574,11 @@
       </c>
       <c r="E17" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>224</v>
+        <v>229.45</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>4.384664266045335E-2</v>
+        <v>6.9243804278754428E-2</v>
       </c>
       <c r="G17" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1601,11 +1603,11 @@
       </c>
       <c r="E18" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>153.52631578947367</v>
+        <v>154.4</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>0.20670916304695264</v>
+        <v>0.21357627724187211</v>
       </c>
       <c r="G18" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1630,11 +1632,11 @@
       </c>
       <c r="E19" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>493.42105263157896</v>
+        <v>497.65</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>1.908215902128596E-2</v>
+        <v>2.7816372512204257E-2</v>
       </c>
       <c r="G19" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1659,11 +1661,11 @@
       </c>
       <c r="E20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>823.63157894736844</v>
+        <v>821.9</v>
       </c>
       <c r="F20" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>5.7540255447770861E-2</v>
+        <v>5.5316913738765017E-2</v>
       </c>
       <c r="G20" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1688,11 +1690,11 @@
       </c>
       <c r="E21" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>5.7894736842105265</v>
+        <v>5.5</v>
       </c>
       <c r="F21" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>-0.89430006551648833</v>
+        <v>-0.89958506224066392</v>
       </c>
       <c r="G21" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
@@ -1717,11 +1719,11 @@
       </c>
       <c r="E22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>53.157894736842103</v>
+        <v>53.6</v>
       </c>
       <c r="F22" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>0.2781133160770779</v>
+        <v>0.2887431693989071</v>
       </c>
       <c r="G22" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1746,11 +1748,11 @@
       </c>
       <c r="E23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>688.84210526315792</v>
+        <v>695.3</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-0.20627841010896797</v>
+        <v>-0.19883727020373965</v>
       </c>
       <c r="G23" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1775,11 +1777,11 @@
       </c>
       <c r="E24" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>1093.6842105263158</v>
+        <v>1122.5999999999999</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.20893435587917708</v>
+        <v>-0.18801946344029463</v>
       </c>
       <c r="G24" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1804,11 +1806,11 @@
       </c>
       <c r="E25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>476.5263157894737</v>
+        <v>483.4</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.12658677435904186</v>
+        <v>-0.11398816962426073</v>
       </c>
       <c r="G25" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1833,11 +1835,11 @@
       </c>
       <c r="E26" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>377.68421052631578</v>
+        <v>377.05</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-0.25062656641604009</v>
+        <v>-0.25188492063492063</v>
       </c>
       <c r="G26" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1862,11 +1864,11 @@
       </c>
       <c r="E27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>111.26315789473684</v>
+        <v>111.35</v>
       </c>
       <c r="F27" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>-0.14592132809343672</v>
+        <v>-0.14525471039776705</v>
       </c>
       <c r="G27" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1891,11 +1893,11 @@
       </c>
       <c r="E28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>124.47368421052632</v>
+        <v>125</v>
       </c>
       <c r="F28" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>-0.12816903768494781</v>
+        <v>-0.12448264883794979</v>
       </c>
       <c r="G28" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1920,11 +1922,11 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>801.31578947368416</v>
+        <v>806.7</v>
       </c>
       <c r="F29" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-5.9287760489805219E-2</v>
+        <v>-5.2966915688367089E-2</v>
       </c>
       <c r="G29" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1949,11 +1951,11 @@
       </c>
       <c r="E30" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>658.10526315789468</v>
+        <v>657.95</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-0.23244893232923269</v>
+        <v>-0.23263001643428927</v>
       </c>
       <c r="G30" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -1978,11 +1980,11 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>841.47368421052636</v>
+        <v>845.65</v>
       </c>
       <c r="F31" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-0.21190204118213796</v>
+        <v>-0.20799063431247344</v>
       </c>
       <c r="G31" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2007,11 +2009,11 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>562.0526315789474</v>
+        <v>573.95000000000005</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-0.17959408872499716</v>
+        <v>-0.16222797239915077</v>
       </c>
       <c r="G32" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2036,11 +2038,11 @@
       </c>
       <c r="E33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>213.21052631578948</v>
+        <v>216.95</v>
       </c>
       <c r="F33" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>2.1479002384008794E-2</v>
+        <v>3.9394599303135935E-2</v>
       </c>
       <c r="G33" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2065,11 +2067,11 @@
       </c>
       <c r="E34" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>236.10526315789474</v>
+        <v>273.75</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-0.53774888409062171</v>
+        <v>-0.46404734359704547</v>
       </c>
       <c r="G34" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2094,11 +2096,11 @@
       </c>
       <c r="E35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>364.31578947368422</v>
+        <v>380.05</v>
       </c>
       <c r="F35" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.19472044926946119</v>
+        <v>-0.15994172611272983</v>
       </c>
       <c r="G35" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2123,11 +2125,11 @@
       </c>
       <c r="E36" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>273.94736842105266</v>
+        <v>277.89999999999998</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>-0.19642105263157894</v>
+        <v>-0.18482666666666681</v>
       </c>
       <c r="G36" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2152,11 +2154,11 @@
       </c>
       <c r="E37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>417.26315789473682</v>
+        <v>428.65</v>
       </c>
       <c r="F37" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>-0.17596144760464905</v>
+        <v>-0.15347396768402166</v>
       </c>
       <c r="G37" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2181,11 +2183,11 @@
       </c>
       <c r="E38" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>243.68421052631578</v>
+        <v>245.9</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>-0.12085066717301618</v>
+        <v>-0.11285667431944901</v>
       </c>
       <c r="G38" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2210,11 +2212,11 @@
       </c>
       <c r="E39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>263.68421052631578</v>
+        <v>269</v>
       </c>
       <c r="F39" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-0.10491395902191825</v>
+        <v>-8.6869310291621593E-2</v>
       </c>
       <c r="G39" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2239,11 +2241,11 @@
       </c>
       <c r="E40" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>51.368421052631582</v>
+        <v>50.65</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>-0.28110352216418899</v>
+        <v>-0.29115776081424938</v>
       </c>
       <c r="G40" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2268,11 +2270,11 @@
       </c>
       <c r="E41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>85.315789473684205</v>
+        <v>83.35</v>
       </c>
       <c r="F41" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.18429058304169821</v>
+        <v>-0.20308561495002175</v>
       </c>
       <c r="G41" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2297,11 +2299,11 @@
       </c>
       <c r="E42" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>34.421052631578945</v>
+        <v>34.4</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-0.29293822792274804</v>
+        <v>-0.29337068160597568</v>
       </c>
       <c r="G42" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2326,11 +2328,11 @@
       </c>
       <c r="E43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>41.421052631578945</v>
+        <v>39.75</v>
       </c>
       <c r="F43" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-0.13047408597830457</v>
+        <v>-0.16555343511450371</v>
       </c>
       <c r="G43" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2355,15 +2357,15 @@
       </c>
       <c r="E44" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>0.52631578947368418</v>
+        <v>0.9</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>-3.5087719298245612E-2</v>
+        <v>0.65000000000000013</v>
       </c>
       <c r="G44" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H44">
         <v>18</v>
@@ -2384,11 +2386,11 @@
       </c>
       <c r="E45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>2.8947368421052633</v>
+        <v>3.45</v>
       </c>
       <c r="F45" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>4.4003451251079628E-2</v>
+        <v>0.24426229508196862</v>
       </c>
       <c r="G45" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C176332A-6AFF-4973-A5A3-C5319B8E78ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39404E47-9101-4E74-B923-CEB4BDF8C78A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -376,6 +376,7 @@
       <sheetName val="INVENTARIO NACIONAL 28-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 29-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 30-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 31-07-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -384,10 +385,10 @@
       <sheetData sheetId="3">
         <row r="4">
           <cell r="F4">
-            <v>1156.3499999999999</v>
+            <v>1051.2272727272727</v>
           </cell>
           <cell r="G4">
-            <v>0.10645876826722334</v>
+            <v>5.8716075156577396E-3</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -395,21 +396,21 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>78.45</v>
+            <v>71.318181818181813</v>
           </cell>
           <cell r="G5">
-            <v>3.2854578096948028E-2</v>
+            <v>-6.1041292639138267E-2</v>
           </cell>
           <cell r="H5" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="6">
           <cell r="F6">
-            <v>572</v>
+            <v>520</v>
           </cell>
           <cell r="G6">
-            <v>0.17027806193620387</v>
+            <v>6.3889147214730713E-2</v>
           </cell>
           <cell r="H6" t="str">
             <v>SUBIÓ</v>
@@ -417,21 +418,21 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>97.5</v>
+            <v>88.63636363636364</v>
           </cell>
           <cell r="G7">
-            <v>6.7164179104477695E-2</v>
+            <v>-2.9850746268656581E-2</v>
           </cell>
           <cell r="H7" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="8">
           <cell r="F8">
-            <v>17.95</v>
+            <v>16.318181818181817</v>
           </cell>
           <cell r="G8">
-            <v>0.12507122507122492</v>
+            <v>2.2792022792022637E-2</v>
           </cell>
           <cell r="H8" t="str">
             <v>SUBIÓ</v>
@@ -439,10 +440,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1311.9</v>
+            <v>1192.6363636363637</v>
           </cell>
           <cell r="G9">
-            <v>-8.9848948314464994E-2</v>
+            <v>-0.17258995301314994</v>
           </cell>
           <cell r="H9" t="str">
             <v>BAJO</v>
@@ -450,10 +451,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>121.65</v>
+            <v>110.59090909090909</v>
           </cell>
           <cell r="G10">
-            <v>-8.4712722298221577E-2</v>
+            <v>-0.16792065663474687</v>
           </cell>
           <cell r="H10" t="str">
             <v>BAJO</v>
@@ -461,10 +462,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>300.45</v>
+            <v>273.13636363636363</v>
           </cell>
           <cell r="G11">
-            <v>-9.6637966379663709E-2</v>
+            <v>-0.1787617876178762</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -472,10 +473,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>675.05</v>
+            <v>613.68181818181813</v>
           </cell>
           <cell r="G12">
-            <v>-5.4250780105712271E-2</v>
+            <v>-0.14022798191428398</v>
           </cell>
           <cell r="H12" t="str">
             <v>BAJO</v>
@@ -483,10 +484,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>412.05</v>
+            <v>374.59090909090907</v>
           </cell>
           <cell r="G13">
-            <v>-0.13870783847981005</v>
+            <v>-0.21700712589073645</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -494,10 +495,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3326.45</v>
+            <v>3024.0454545454545</v>
           </cell>
           <cell r="G14">
-            <v>-4.7668683713969706E-2</v>
+            <v>-0.13424425792179062</v>
           </cell>
           <cell r="H14" t="str">
             <v>BAJO</v>
@@ -505,10 +506,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2229.5</v>
+            <v>2026.8181818181818</v>
           </cell>
           <cell r="G15">
-            <v>-1.0192848697343493E-4</v>
+            <v>-9.1001753169975941E-2</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -516,10 +517,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2216.85</v>
+            <v>2015.3181818181818</v>
           </cell>
           <cell r="G16">
-            <v>-3.8641067591807854E-2</v>
+            <v>-0.1260373341743708</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -527,10 +528,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2466.25</v>
+            <v>2242.0454545454545</v>
           </cell>
           <cell r="G17">
-            <v>-8.934895352545269E-2</v>
+            <v>-0.17213541229586604</v>
           </cell>
           <cell r="H17" t="str">
             <v>BAJO</v>
@@ -538,10 +539,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>138.75</v>
+            <v>126.13636363636364</v>
           </cell>
           <cell r="G18">
-            <v>-0.20279446330634621</v>
+            <v>-0.27526769391486017</v>
           </cell>
           <cell r="H18" t="str">
             <v>BAJO</v>
@@ -549,21 +550,21 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>229.45</v>
+            <v>208.59090909090909</v>
           </cell>
           <cell r="G19">
-            <v>6.9243804278754428E-2</v>
+            <v>-2.7960177928404994E-2</v>
           </cell>
           <cell r="H19" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="20">
           <cell r="F20">
-            <v>154.4</v>
+            <v>140.36363636363637</v>
           </cell>
           <cell r="G20">
-            <v>0.21357627724187211</v>
+            <v>0.10325116112897459</v>
           </cell>
           <cell r="H20" t="str">
             <v>SUBIÓ</v>
@@ -571,32 +572,32 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>497.65</v>
+            <v>452.40909090909093</v>
           </cell>
           <cell r="G21">
-            <v>2.7816372512204257E-2</v>
+            <v>-6.5621479534359706E-2</v>
           </cell>
           <cell r="H21" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="22">
           <cell r="F22">
-            <v>821.9</v>
+            <v>747.18181818181813</v>
           </cell>
           <cell r="G22">
-            <v>5.5316913738765017E-2</v>
+            <v>-4.0620987510213702E-2</v>
           </cell>
           <cell r="H22" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="23">
           <cell r="F23">
-            <v>5.5</v>
+            <v>5</v>
           </cell>
           <cell r="G23">
-            <v>-0.89958506224066392</v>
+            <v>-0.90871369294605808</v>
           </cell>
           <cell r="H23" t="str">
             <v>BAJO</v>
@@ -604,10 +605,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>53.6</v>
+            <v>48.727272727272727</v>
           </cell>
           <cell r="G24">
-            <v>0.2887431693989071</v>
+            <v>0.17158469945355193</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -615,10 +616,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>695.3</v>
+            <v>632.09090909090912</v>
           </cell>
           <cell r="G25">
-            <v>-0.19883727020373965</v>
+            <v>-0.27167024563976327</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -626,10 +627,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>1122.5999999999999</v>
+            <v>1020.5454545454545</v>
           </cell>
           <cell r="G26">
-            <v>-0.18801946344029463</v>
+            <v>-0.26183587585481327</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -637,10 +638,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>483.4</v>
+            <v>439.45454545454544</v>
           </cell>
           <cell r="G27">
-            <v>-0.11398816962426073</v>
+            <v>-0.19453469965841885</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -648,10 +649,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>377.05</v>
+            <v>342.77272727272725</v>
           </cell>
           <cell r="G28">
-            <v>-0.25188492063492063</v>
+            <v>-0.3198953823953824</v>
           </cell>
           <cell r="H28" t="str">
             <v>BAJO</v>
@@ -659,10 +660,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>111.35</v>
+            <v>101.22727272727273</v>
           </cell>
           <cell r="G29">
-            <v>-0.14525471039776705</v>
+            <v>-0.22295882763433361</v>
           </cell>
           <cell r="H29" t="str">
             <v>BAJO</v>
@@ -670,10 +671,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>125</v>
+            <v>113.63636363636364</v>
           </cell>
           <cell r="G30">
-            <v>-0.12448264883794979</v>
+            <v>-0.20407513530722698</v>
           </cell>
           <cell r="H30" t="str">
             <v>BAJO</v>
@@ -681,10 +682,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>806.7</v>
+            <v>733.36363636363637</v>
           </cell>
           <cell r="G31">
-            <v>-5.2966915688367089E-2</v>
+            <v>-0.13906083244397016</v>
           </cell>
           <cell r="H31" t="str">
             <v>BAJO</v>
@@ -692,10 +693,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>657.95</v>
+            <v>598.13636363636363</v>
           </cell>
           <cell r="G32">
-            <v>-0.23263001643428927</v>
+            <v>-0.30239092403117207</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -703,10 +704,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>845.65</v>
+            <v>768.77272727272725</v>
           </cell>
           <cell r="G33">
-            <v>-0.20799063431247344</v>
+            <v>-0.27999148573861221</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -714,10 +715,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>573.95000000000005</v>
+            <v>521.77272727272725</v>
           </cell>
           <cell r="G34">
-            <v>-0.16222797239915077</v>
+            <v>-0.23838906581740982</v>
           </cell>
           <cell r="H34" t="str">
             <v>BAJO</v>
@@ -725,21 +726,21 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>216.95</v>
+            <v>197.22727272727272</v>
           </cell>
           <cell r="G35">
-            <v>3.9394599303135935E-2</v>
+            <v>-5.5095818815330988E-2</v>
           </cell>
           <cell r="H35" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="36">
           <cell r="F36">
-            <v>273.75</v>
+            <v>248.86363636363637</v>
           </cell>
           <cell r="G36">
-            <v>-0.46404734359704547</v>
+            <v>-0.51277031236095039</v>
           </cell>
           <cell r="H36" t="str">
             <v>BAJO</v>
@@ -747,10 +748,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>380.05</v>
+            <v>345.5</v>
           </cell>
           <cell r="G37">
-            <v>-0.15994172611272983</v>
+            <v>-0.2363106601024817</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -758,10 +759,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>277.89999999999998</v>
+            <v>252.63636363636363</v>
           </cell>
           <cell r="G38">
-            <v>-0.18482666666666681</v>
+            <v>-0.25893333333333346</v>
           </cell>
           <cell r="H38" t="str">
             <v>BAJO</v>
@@ -769,10 +770,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>428.65</v>
+            <v>389.68181818181819</v>
           </cell>
           <cell r="G39">
-            <v>-0.15347396768402166</v>
+            <v>-0.23043087971274689</v>
           </cell>
           <cell r="H39" t="str">
             <v>BAJO</v>
@@ -780,10 +781,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>245.9</v>
+            <v>223.54545454545453</v>
           </cell>
           <cell r="G40">
-            <v>-0.11285667431944901</v>
+            <v>-0.19350606756313549</v>
           </cell>
           <cell r="H40" t="str">
             <v>BAJO</v>
@@ -791,10 +792,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>269</v>
+            <v>244.54545454545453</v>
           </cell>
           <cell r="G41">
-            <v>-8.6869310291621593E-2</v>
+            <v>-0.16988119117420153</v>
           </cell>
           <cell r="H41" t="str">
             <v>BAJO</v>
@@ -802,10 +803,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>50.65</v>
+            <v>46.045454545454547</v>
           </cell>
           <cell r="G42">
-            <v>-0.29115776081424938</v>
+            <v>-0.3555979643765903</v>
           </cell>
           <cell r="H42" t="str">
             <v>BAJO</v>
@@ -813,10 +814,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>83.35</v>
+            <v>75.772727272727266</v>
           </cell>
           <cell r="G43">
-            <v>-0.20308561495002175</v>
+            <v>-0.27553237722729251</v>
           </cell>
           <cell r="H43" t="str">
             <v>BAJO</v>
@@ -824,10 +825,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>34.4</v>
+            <v>31.272727272727273</v>
           </cell>
           <cell r="G44">
-            <v>-0.29337068160597568</v>
+            <v>-0.35760971055088697</v>
           </cell>
           <cell r="H44" t="str">
             <v>BAJO</v>
@@ -835,10 +836,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>39.75</v>
+            <v>36.136363636363633</v>
           </cell>
           <cell r="G45">
-            <v>-0.16555343511450371</v>
+            <v>-0.24141221374045807</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -846,10 +847,10 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>0.9</v>
+            <v>0.81818181818181823</v>
           </cell>
           <cell r="G46">
-            <v>0.65000000000000013</v>
+            <v>0.50000000000000022</v>
           </cell>
           <cell r="H46" t="str">
             <v>SUBIÓ</v>
@@ -857,10 +858,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>3.45</v>
+            <v>3.1363636363636362</v>
           </cell>
           <cell r="G47">
-            <v>0.24426229508196862</v>
+            <v>0.13114754098360759</v>
           </cell>
           <cell r="H47" t="str">
             <v>SUBIÓ</v>
@@ -886,6 +887,7 @@
       <sheetData sheetId="20"/>
       <sheetData sheetId="21"/>
       <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1139,11 +1141,11 @@
       </c>
       <c r="E2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!$F$4</f>
-        <v>1156.3499999999999</v>
+        <v>1051.2272727272727</v>
       </c>
       <c r="F2" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>0.10645876826722334</v>
+        <v>5.8716075156577396E-3</v>
       </c>
       <c r="G2" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1168,15 +1170,15 @@
       </c>
       <c r="E3" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>78.45</v>
+        <v>71.318181818181813</v>
       </c>
       <c r="F3" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>3.2854578096948028E-2</v>
+        <v>-6.1041292639138267E-2</v>
       </c>
       <c r="G3" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H3">
         <v>1.59</v>
@@ -1197,11 +1199,11 @@
       </c>
       <c r="E4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>572</v>
+        <v>520</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>0.17027806193620387</v>
+        <v>6.3889147214730713E-2</v>
       </c>
       <c r="G4" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1226,15 +1228,15 @@
       </c>
       <c r="E5" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>97.5</v>
+        <v>88.63636363636364</v>
       </c>
       <c r="F5" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>6.7164179104477695E-2</v>
+        <v>-2.9850746268656581E-2</v>
       </c>
       <c r="G5" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H5">
         <v>3.61</v>
@@ -1255,11 +1257,11 @@
       </c>
       <c r="E6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>17.95</v>
+        <v>16.318181818181817</v>
       </c>
       <c r="F6" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>0.12507122507122492</v>
+        <v>2.2792022792022637E-2</v>
       </c>
       <c r="G6" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1284,11 +1286,11 @@
       </c>
       <c r="E7" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1311.9</v>
+        <v>1192.6363636363637</v>
       </c>
       <c r="F7" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>-8.9848948314464994E-2</v>
+        <v>-0.17258995301314994</v>
       </c>
       <c r="G7" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1313,11 +1315,11 @@
       </c>
       <c r="E8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>121.65</v>
+        <v>110.59090909090909</v>
       </c>
       <c r="F8" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-8.4712722298221577E-2</v>
+        <v>-0.16792065663474687</v>
       </c>
       <c r="G8" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1342,11 +1344,11 @@
       </c>
       <c r="E9" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>300.45</v>
+        <v>273.13636363636363</v>
       </c>
       <c r="F9" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-9.6637966379663709E-2</v>
+        <v>-0.1787617876178762</v>
       </c>
       <c r="G9" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1371,11 +1373,11 @@
       </c>
       <c r="E10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>675.05</v>
+        <v>613.68181818181813</v>
       </c>
       <c r="F10" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>-5.4250780105712271E-2</v>
+        <v>-0.14022798191428398</v>
       </c>
       <c r="G10" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1400,11 +1402,11 @@
       </c>
       <c r="E11" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>412.05</v>
+        <v>374.59090909090907</v>
       </c>
       <c r="F11" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.13870783847981005</v>
+        <v>-0.21700712589073645</v>
       </c>
       <c r="G11" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1429,11 +1431,11 @@
       </c>
       <c r="E12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3326.45</v>
+        <v>3024.0454545454545</v>
       </c>
       <c r="F12" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-4.7668683713969706E-2</v>
+        <v>-0.13424425792179062</v>
       </c>
       <c r="G12" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1458,11 +1460,11 @@
       </c>
       <c r="E13" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2229.5</v>
+        <v>2026.8181818181818</v>
       </c>
       <c r="F13" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-1.0192848697343493E-4</v>
+        <v>-9.1001753169975941E-2</v>
       </c>
       <c r="G13" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1487,11 +1489,11 @@
       </c>
       <c r="E14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2216.85</v>
+        <v>2015.3181818181818</v>
       </c>
       <c r="F14" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-3.8641067591807854E-2</v>
+        <v>-0.1260373341743708</v>
       </c>
       <c r="G14" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1516,11 +1518,11 @@
       </c>
       <c r="E15" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2466.25</v>
+        <v>2242.0454545454545</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-8.934895352545269E-2</v>
+        <v>-0.17213541229586604</v>
       </c>
       <c r="G15" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1545,11 +1547,11 @@
       </c>
       <c r="E16" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>138.75</v>
+        <v>126.13636363636364</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.20279446330634621</v>
+        <v>-0.27526769391486017</v>
       </c>
       <c r="G16" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1574,15 +1576,15 @@
       </c>
       <c r="E17" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>229.45</v>
+        <v>208.59090909090909</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>6.9243804278754428E-2</v>
+        <v>-2.7960177928404994E-2</v>
       </c>
       <c r="G17" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H17">
         <v>3.68</v>
@@ -1603,11 +1605,11 @@
       </c>
       <c r="E18" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>154.4</v>
+        <v>140.36363636363637</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>0.21357627724187211</v>
+        <v>0.10325116112897459</v>
       </c>
       <c r="G18" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1632,15 +1634,15 @@
       </c>
       <c r="E19" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>497.65</v>
+        <v>452.40909090909093</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>2.7816372512204257E-2</v>
+        <v>-6.5621479534359706E-2</v>
       </c>
       <c r="G19" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H19">
         <v>4.1500000000000004</v>
@@ -1661,15 +1663,15 @@
       </c>
       <c r="E20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>821.9</v>
+        <v>747.18181818181813</v>
       </c>
       <c r="F20" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>5.5316913738765017E-2</v>
+        <v>-4.0620987510213702E-2</v>
       </c>
       <c r="G20" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H20">
         <v>4.1500000000000004</v>
@@ -1690,11 +1692,11 @@
       </c>
       <c r="E21" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="F21" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>-0.89958506224066392</v>
+        <v>-0.90871369294605808</v>
       </c>
       <c r="G21" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
@@ -1719,11 +1721,11 @@
       </c>
       <c r="E22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>53.6</v>
+        <v>48.727272727272727</v>
       </c>
       <c r="F22" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>0.2887431693989071</v>
+        <v>0.17158469945355193</v>
       </c>
       <c r="G22" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1748,11 +1750,11 @@
       </c>
       <c r="E23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>695.3</v>
+        <v>632.09090909090912</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-0.19883727020373965</v>
+        <v>-0.27167024563976327</v>
       </c>
       <c r="G23" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1777,11 +1779,11 @@
       </c>
       <c r="E24" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>1122.5999999999999</v>
+        <v>1020.5454545454545</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.18801946344029463</v>
+        <v>-0.26183587585481327</v>
       </c>
       <c r="G24" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1806,11 +1808,11 @@
       </c>
       <c r="E25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>483.4</v>
+        <v>439.45454545454544</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.11398816962426073</v>
+        <v>-0.19453469965841885</v>
       </c>
       <c r="G25" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1835,11 +1837,11 @@
       </c>
       <c r="E26" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>377.05</v>
+        <v>342.77272727272725</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-0.25188492063492063</v>
+        <v>-0.3198953823953824</v>
       </c>
       <c r="G26" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1864,11 +1866,11 @@
       </c>
       <c r="E27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>111.35</v>
+        <v>101.22727272727273</v>
       </c>
       <c r="F27" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>-0.14525471039776705</v>
+        <v>-0.22295882763433361</v>
       </c>
       <c r="G27" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1893,11 +1895,11 @@
       </c>
       <c r="E28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>125</v>
+        <v>113.63636363636364</v>
       </c>
       <c r="F28" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>-0.12448264883794979</v>
+        <v>-0.20407513530722698</v>
       </c>
       <c r="G28" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1922,11 +1924,11 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>806.7</v>
+        <v>733.36363636363637</v>
       </c>
       <c r="F29" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-5.2966915688367089E-2</v>
+        <v>-0.13906083244397016</v>
       </c>
       <c r="G29" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1951,11 +1953,11 @@
       </c>
       <c r="E30" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>657.95</v>
+        <v>598.13636363636363</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-0.23263001643428927</v>
+        <v>-0.30239092403117207</v>
       </c>
       <c r="G30" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -1980,11 +1982,11 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>845.65</v>
+        <v>768.77272727272725</v>
       </c>
       <c r="F31" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-0.20799063431247344</v>
+        <v>-0.27999148573861221</v>
       </c>
       <c r="G31" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2009,11 +2011,11 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>573.95000000000005</v>
+        <v>521.77272727272725</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-0.16222797239915077</v>
+        <v>-0.23838906581740982</v>
       </c>
       <c r="G32" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2038,15 +2040,15 @@
       </c>
       <c r="E33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>216.95</v>
+        <v>197.22727272727272</v>
       </c>
       <c r="F33" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>3.9394599303135935E-2</v>
+        <v>-5.5095818815330988E-2</v>
       </c>
       <c r="G33" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H33">
         <v>1.1599999999999999</v>
@@ -2067,11 +2069,11 @@
       </c>
       <c r="E34" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>273.75</v>
+        <v>248.86363636363637</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-0.46404734359704547</v>
+        <v>-0.51277031236095039</v>
       </c>
       <c r="G34" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2096,11 +2098,11 @@
       </c>
       <c r="E35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>380.05</v>
+        <v>345.5</v>
       </c>
       <c r="F35" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.15994172611272983</v>
+        <v>-0.2363106601024817</v>
       </c>
       <c r="G35" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2125,11 +2127,11 @@
       </c>
       <c r="E36" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>277.89999999999998</v>
+        <v>252.63636363636363</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>-0.18482666666666681</v>
+        <v>-0.25893333333333346</v>
       </c>
       <c r="G36" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2154,11 +2156,11 @@
       </c>
       <c r="E37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>428.65</v>
+        <v>389.68181818181819</v>
       </c>
       <c r="F37" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>-0.15347396768402166</v>
+        <v>-0.23043087971274689</v>
       </c>
       <c r="G37" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2183,11 +2185,11 @@
       </c>
       <c r="E38" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>245.9</v>
+        <v>223.54545454545453</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>-0.11285667431944901</v>
+        <v>-0.19350606756313549</v>
       </c>
       <c r="G38" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2212,11 +2214,11 @@
       </c>
       <c r="E39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>269</v>
+        <v>244.54545454545453</v>
       </c>
       <c r="F39" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-8.6869310291621593E-2</v>
+        <v>-0.16988119117420153</v>
       </c>
       <c r="G39" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2241,11 +2243,11 @@
       </c>
       <c r="E40" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>50.65</v>
+        <v>46.045454545454547</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>-0.29115776081424938</v>
+        <v>-0.3555979643765903</v>
       </c>
       <c r="G40" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2270,11 +2272,11 @@
       </c>
       <c r="E41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>83.35</v>
+        <v>75.772727272727266</v>
       </c>
       <c r="F41" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.20308561495002175</v>
+        <v>-0.27553237722729251</v>
       </c>
       <c r="G41" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2299,11 +2301,11 @@
       </c>
       <c r="E42" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>34.4</v>
+        <v>31.272727272727273</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-0.29337068160597568</v>
+        <v>-0.35760971055088697</v>
       </c>
       <c r="G42" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2328,11 +2330,11 @@
       </c>
       <c r="E43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>39.75</v>
+        <v>36.136363636363633</v>
       </c>
       <c r="F43" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-0.16555343511450371</v>
+        <v>-0.24141221374045807</v>
       </c>
       <c r="G43" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2357,11 +2359,11 @@
       </c>
       <c r="E44" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>0.9</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>0.65000000000000013</v>
+        <v>0.50000000000000022</v>
       </c>
       <c r="G44" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
@@ -2386,11 +2388,11 @@
       </c>
       <c r="E45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>3.45</v>
+        <v>3.1363636363636362</v>
       </c>
       <c r="F45" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>0.24426229508196862</v>
+        <v>0.13114754098360759</v>
       </c>
       <c r="G45" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39404E47-9101-4E74-B923-CEB4BDF8C78A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD94D3FF-CDF1-413F-A978-2C2CF6C30FD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -385,10 +385,10 @@
       <sheetData sheetId="3">
         <row r="4">
           <cell r="F4">
-            <v>1051.2272727272727</v>
+            <v>1118.5454545454545</v>
           </cell>
           <cell r="G4">
-            <v>5.8716075156577396E-3</v>
+            <v>7.0285316631871986E-2</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -396,21 +396,21 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>71.318181818181813</v>
+            <v>77.954545454545453</v>
           </cell>
           <cell r="G5">
-            <v>-6.1041292639138267E-2</v>
+            <v>2.6331538001196808E-2</v>
           </cell>
           <cell r="H5" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="6">
           <cell r="F6">
-            <v>520</v>
+            <v>547.5</v>
           </cell>
           <cell r="G6">
-            <v>6.3889147214730713E-2</v>
+            <v>0.1201525155770482</v>
           </cell>
           <cell r="H6" t="str">
             <v>SUBIÓ</v>
@@ -418,21 +418,21 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>88.63636363636364</v>
+            <v>97.772727272727266</v>
           </cell>
           <cell r="G7">
-            <v>-2.9850746268656581E-2</v>
+            <v>7.0149253731343286E-2</v>
           </cell>
           <cell r="H7" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="8">
           <cell r="F8">
-            <v>16.318181818181817</v>
+            <v>16.681818181818183</v>
           </cell>
           <cell r="G8">
-            <v>2.2792022792022637E-2</v>
+            <v>4.5584045584045718E-2</v>
           </cell>
           <cell r="H8" t="str">
             <v>SUBIÓ</v>
@@ -440,10 +440,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1192.6363636363637</v>
+            <v>1294.909090909091</v>
           </cell>
           <cell r="G9">
-            <v>-0.17258995301314994</v>
+            <v>-0.10163665604995109</v>
           </cell>
           <cell r="H9" t="str">
             <v>BAJO</v>
@@ -451,10 +451,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>110.59090909090909</v>
+            <v>122.18181818181819</v>
           </cell>
           <cell r="G10">
-            <v>-0.16792065663474687</v>
+            <v>-8.0711354309165428E-2</v>
           </cell>
           <cell r="H10" t="str">
             <v>BAJO</v>
@@ -462,10 +462,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>273.13636363636363</v>
+            <v>303.72727272727275</v>
           </cell>
           <cell r="G11">
-            <v>-0.1787617876178762</v>
+            <v>-8.6784201175344911E-2</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -473,10 +473,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>613.68181818181813</v>
+            <v>662</v>
           </cell>
           <cell r="G12">
-            <v>-0.14022798191428398</v>
+            <v>-7.2533910717697214E-2</v>
           </cell>
           <cell r="H12" t="str">
             <v>BAJO</v>
@@ -484,10 +484,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>374.59090909090907</v>
+            <v>405.22727272727275</v>
           </cell>
           <cell r="G13">
-            <v>-0.21700712589073645</v>
+            <v>-0.15296912114014249</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -495,10 +495,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3024.0454545454545</v>
+            <v>3250.0454545454545</v>
           </cell>
           <cell r="G14">
-            <v>-0.13424425792179062</v>
+            <v>-6.9542585724510442E-2</v>
           </cell>
           <cell r="H14" t="str">
             <v>BAJO</v>
@@ -506,10 +506,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2026.8181818181818</v>
+            <v>2178.5454545454545</v>
           </cell>
           <cell r="G15">
-            <v>-9.1001753169975941E-2</v>
+            <v>-2.2954295266440994E-2</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -517,10 +517,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2015.3181818181818</v>
+            <v>2162.5454545454545</v>
           </cell>
           <cell r="G16">
-            <v>-0.1260373341743708</v>
+            <v>-6.2190770929017813E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -528,10 +528,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2242.0454545454545</v>
+            <v>2404.681818181818</v>
           </cell>
           <cell r="G17">
-            <v>-0.17213541229586604</v>
+            <v>-0.11208271093133715</v>
           </cell>
           <cell r="H17" t="str">
             <v>BAJO</v>
@@ -539,10 +539,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>126.13636363636364</v>
+            <v>133.13636363636363</v>
           </cell>
           <cell r="G18">
-            <v>-0.27526769391486017</v>
+            <v>-0.23504831548707239</v>
           </cell>
           <cell r="H18" t="str">
             <v>BAJO</v>
@@ -550,21 +550,21 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>208.59090909090909</v>
+            <v>225.86363636363637</v>
           </cell>
           <cell r="G19">
-            <v>-2.7960177928404994E-2</v>
+            <v>5.2531243380639747E-2</v>
           </cell>
           <cell r="H19" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="20">
           <cell r="F20">
-            <v>140.36363636363637</v>
+            <v>147.90909090909091</v>
           </cell>
           <cell r="G20">
-            <v>0.10325116112897459</v>
+            <v>0.16255805644873167</v>
           </cell>
           <cell r="H20" t="str">
             <v>SUBIÓ</v>
@@ -572,24 +572,24 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>452.40909090909093</v>
+            <v>486.59090909090907</v>
           </cell>
           <cell r="G21">
-            <v>-6.5621479534359706E-2</v>
+            <v>4.9755914382274558E-3</v>
           </cell>
           <cell r="H21" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="22">
           <cell r="F22">
-            <v>747.18181818181813</v>
+            <v>796.40909090909088</v>
           </cell>
           <cell r="G22">
-            <v>-4.0620987510213702E-2</v>
+            <v>2.2586669779385948E-2</v>
           </cell>
           <cell r="H22" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="23">
@@ -605,10 +605,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>48.727272727272727</v>
+            <v>49.18181818181818</v>
           </cell>
           <cell r="G24">
-            <v>0.17158469945355193</v>
+            <v>0.1825136612021856</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -616,10 +616,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>632.09090909090912</v>
+            <v>684.72727272727275</v>
           </cell>
           <cell r="G25">
-            <v>-0.27167024563976327</v>
+            <v>-0.21101974545644997</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -627,10 +627,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>1020.5454545454545</v>
+            <v>1109.590909090909</v>
           </cell>
           <cell r="G26">
-            <v>-0.26183587585481327</v>
+            <v>-0.19742898474487114</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -638,10 +638,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>439.45454545454544</v>
+            <v>482.90909090909093</v>
           </cell>
           <cell r="G27">
-            <v>-0.19453469965841885</v>
+            <v>-0.11488794468049657</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -649,10 +649,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>342.77272727272725</v>
+            <v>366.40909090909093</v>
           </cell>
           <cell r="G28">
-            <v>-0.3198953823953824</v>
+            <v>-0.27299783549783541</v>
           </cell>
           <cell r="H28" t="str">
             <v>BAJO</v>
@@ -660,10 +660,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>101.22727272727273</v>
+            <v>107.04545454545455</v>
           </cell>
           <cell r="G29">
-            <v>-0.22295882763433361</v>
+            <v>-0.17829727843684584</v>
           </cell>
           <cell r="H29" t="str">
             <v>BAJO</v>
@@ -671,10 +671,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>113.63636363636364</v>
+            <v>122.54545454545455</v>
           </cell>
           <cell r="G30">
-            <v>-0.20407513530722698</v>
+            <v>-0.14167462591531366</v>
           </cell>
           <cell r="H30" t="str">
             <v>BAJO</v>
@@ -682,10 +682,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>733.36363636363637</v>
+            <v>790.72727272727275</v>
           </cell>
           <cell r="G31">
-            <v>-0.13906083244397016</v>
+            <v>-7.1718249733191075E-2</v>
           </cell>
           <cell r="H31" t="str">
             <v>BAJO</v>
@@ -693,10 +693,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>598.13636363636363</v>
+            <v>651.5454545454545</v>
           </cell>
           <cell r="G32">
-            <v>-0.30239092403117207</v>
+            <v>-0.24009966601282939</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -704,10 +704,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>768.77272727272725</v>
+            <v>842.63636363636363</v>
           </cell>
           <cell r="G33">
-            <v>-0.27999148573861221</v>
+            <v>-0.21081311196253727</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -715,10 +715,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>521.77272727272725</v>
+            <v>572.36363636363637</v>
           </cell>
           <cell r="G34">
-            <v>-0.23838906581740982</v>
+            <v>-0.16454352441613596</v>
           </cell>
           <cell r="H34" t="str">
             <v>BAJO</v>
@@ -726,21 +726,21 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>197.22727272727272</v>
+            <v>212.54545454545453</v>
           </cell>
           <cell r="G35">
-            <v>-5.5095818815330988E-2</v>
+            <v>1.8292682926829285E-2</v>
           </cell>
           <cell r="H35" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="36">
           <cell r="F36">
-            <v>248.86363636363637</v>
+            <v>291.45454545454544</v>
           </cell>
           <cell r="G36">
-            <v>-0.51277031236095039</v>
+            <v>-0.42938506718875147</v>
           </cell>
           <cell r="H36" t="str">
             <v>BAJO</v>
@@ -748,10 +748,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>345.5</v>
+            <v>374.22727272727275</v>
           </cell>
           <cell r="G37">
-            <v>-0.2363106601024817</v>
+            <v>-0.1728122174218828</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -759,10 +759,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>252.63636363636363</v>
+            <v>272.95454545454544</v>
           </cell>
           <cell r="G38">
-            <v>-0.25893333333333346</v>
+            <v>-0.19933333333333347</v>
           </cell>
           <cell r="H38" t="str">
             <v>BAJO</v>
@@ -770,10 +770,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>389.68181818181819</v>
+            <v>420.40909090909093</v>
           </cell>
           <cell r="G39">
-            <v>-0.23043087971274689</v>
+            <v>-0.16974865350089763</v>
           </cell>
           <cell r="H39" t="str">
             <v>BAJO</v>
@@ -781,10 +781,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>223.54545454545453</v>
+            <v>246.45454545454547</v>
           </cell>
           <cell r="G40">
-            <v>-0.19350606756313549</v>
+            <v>-0.11085601836667758</v>
           </cell>
           <cell r="H40" t="str">
             <v>BAJO</v>
@@ -792,10 +792,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>244.54545454545453</v>
+            <v>263.40909090909093</v>
           </cell>
           <cell r="G41">
-            <v>-0.16988119117420153</v>
+            <v>-0.1058478629841072</v>
           </cell>
           <cell r="H41" t="str">
             <v>BAJO</v>
@@ -803,10 +803,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>46.045454545454547</v>
+            <v>49.909090909090907</v>
           </cell>
           <cell r="G42">
-            <v>-0.3555979643765903</v>
+            <v>-0.30152671755725191</v>
           </cell>
           <cell r="H42" t="str">
             <v>BAJO</v>
@@ -814,10 +814,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>75.772727272727266</v>
+            <v>79.409090909090907</v>
           </cell>
           <cell r="G43">
-            <v>-0.27553237722729251</v>
+            <v>-0.24076488483268144</v>
           </cell>
           <cell r="H43" t="str">
             <v>BAJO</v>
@@ -825,10 +825,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>31.272727272727273</v>
+            <v>34.272727272727273</v>
           </cell>
           <cell r="G44">
-            <v>-0.35760971055088697</v>
+            <v>-0.29598506069094299</v>
           </cell>
           <cell r="H44" t="str">
             <v>BAJO</v>
@@ -836,10 +836,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>36.136363636363633</v>
+            <v>37.5</v>
           </cell>
           <cell r="G45">
-            <v>-0.24141221374045807</v>
+            <v>-0.21278625954198471</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -858,10 +858,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>3.1363636363636362</v>
+            <v>3.2727272727272729</v>
           </cell>
           <cell r="G47">
-            <v>0.13114754098360759</v>
+            <v>0.18032786885246033</v>
           </cell>
           <cell r="H47" t="str">
             <v>SUBIÓ</v>
@@ -1141,11 +1141,11 @@
       </c>
       <c r="E2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!$F$4</f>
-        <v>1051.2272727272727</v>
+        <v>1118.5454545454545</v>
       </c>
       <c r="F2" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>5.8716075156577396E-3</v>
+        <v>7.0285316631871986E-2</v>
       </c>
       <c r="G2" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1170,15 +1170,15 @@
       </c>
       <c r="E3" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>71.318181818181813</v>
+        <v>77.954545454545453</v>
       </c>
       <c r="F3" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-6.1041292639138267E-2</v>
+        <v>2.6331538001196808E-2</v>
       </c>
       <c r="G3" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H3">
         <v>1.59</v>
@@ -1199,11 +1199,11 @@
       </c>
       <c r="E4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>520</v>
+        <v>547.5</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>6.3889147214730713E-2</v>
+        <v>0.1201525155770482</v>
       </c>
       <c r="G4" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1228,15 +1228,15 @@
       </c>
       <c r="E5" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>88.63636363636364</v>
+        <v>97.772727272727266</v>
       </c>
       <c r="F5" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>-2.9850746268656581E-2</v>
+        <v>7.0149253731343286E-2</v>
       </c>
       <c r="G5" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H5">
         <v>3.61</v>
@@ -1257,11 +1257,11 @@
       </c>
       <c r="E6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>16.318181818181817</v>
+        <v>16.681818181818183</v>
       </c>
       <c r="F6" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>2.2792022792022637E-2</v>
+        <v>4.5584045584045718E-2</v>
       </c>
       <c r="G6" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1286,11 +1286,11 @@
       </c>
       <c r="E7" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1192.6363636363637</v>
+        <v>1294.909090909091</v>
       </c>
       <c r="F7" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>-0.17258995301314994</v>
+        <v>-0.10163665604995109</v>
       </c>
       <c r="G7" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1315,11 +1315,11 @@
       </c>
       <c r="E8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>110.59090909090909</v>
+        <v>122.18181818181819</v>
       </c>
       <c r="F8" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-0.16792065663474687</v>
+        <v>-8.0711354309165428E-2</v>
       </c>
       <c r="G8" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1344,11 +1344,11 @@
       </c>
       <c r="E9" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>273.13636363636363</v>
+        <v>303.72727272727275</v>
       </c>
       <c r="F9" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-0.1787617876178762</v>
+        <v>-8.6784201175344911E-2</v>
       </c>
       <c r="G9" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1373,11 +1373,11 @@
       </c>
       <c r="E10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>613.68181818181813</v>
+        <v>662</v>
       </c>
       <c r="F10" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>-0.14022798191428398</v>
+        <v>-7.2533910717697214E-2</v>
       </c>
       <c r="G10" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1402,11 +1402,11 @@
       </c>
       <c r="E11" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>374.59090909090907</v>
+        <v>405.22727272727275</v>
       </c>
       <c r="F11" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.21700712589073645</v>
+        <v>-0.15296912114014249</v>
       </c>
       <c r="G11" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1431,11 +1431,11 @@
       </c>
       <c r="E12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3024.0454545454545</v>
+        <v>3250.0454545454545</v>
       </c>
       <c r="F12" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-0.13424425792179062</v>
+        <v>-6.9542585724510442E-2</v>
       </c>
       <c r="G12" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1460,11 +1460,11 @@
       </c>
       <c r="E13" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2026.8181818181818</v>
+        <v>2178.5454545454545</v>
       </c>
       <c r="F13" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-9.1001753169975941E-2</v>
+        <v>-2.2954295266440994E-2</v>
       </c>
       <c r="G13" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1489,11 +1489,11 @@
       </c>
       <c r="E14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2015.3181818181818</v>
+        <v>2162.5454545454545</v>
       </c>
       <c r="F14" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-0.1260373341743708</v>
+        <v>-6.2190770929017813E-2</v>
       </c>
       <c r="G14" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1518,11 +1518,11 @@
       </c>
       <c r="E15" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2242.0454545454545</v>
+        <v>2404.681818181818</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-0.17213541229586604</v>
+        <v>-0.11208271093133715</v>
       </c>
       <c r="G15" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1547,11 +1547,11 @@
       </c>
       <c r="E16" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>126.13636363636364</v>
+        <v>133.13636363636363</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.27526769391486017</v>
+        <v>-0.23504831548707239</v>
       </c>
       <c r="G16" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1576,15 +1576,15 @@
       </c>
       <c r="E17" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>208.59090909090909</v>
+        <v>225.86363636363637</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>-2.7960177928404994E-2</v>
+        <v>5.2531243380639747E-2</v>
       </c>
       <c r="G17" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H17">
         <v>3.68</v>
@@ -1605,11 +1605,11 @@
       </c>
       <c r="E18" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>140.36363636363637</v>
+        <v>147.90909090909091</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>0.10325116112897459</v>
+        <v>0.16255805644873167</v>
       </c>
       <c r="G18" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1634,15 +1634,15 @@
       </c>
       <c r="E19" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>452.40909090909093</v>
+        <v>486.59090909090907</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>-6.5621479534359706E-2</v>
+        <v>4.9755914382274558E-3</v>
       </c>
       <c r="G19" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H19">
         <v>4.1500000000000004</v>
@@ -1663,15 +1663,15 @@
       </c>
       <c r="E20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>747.18181818181813</v>
+        <v>796.40909090909088</v>
       </c>
       <c r="F20" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-4.0620987510213702E-2</v>
+        <v>2.2586669779385948E-2</v>
       </c>
       <c r="G20" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H20">
         <v>4.1500000000000004</v>
@@ -1721,11 +1721,11 @@
       </c>
       <c r="E22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>48.727272727272727</v>
+        <v>49.18181818181818</v>
       </c>
       <c r="F22" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>0.17158469945355193</v>
+        <v>0.1825136612021856</v>
       </c>
       <c r="G22" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1750,11 +1750,11 @@
       </c>
       <c r="E23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>632.09090909090912</v>
+        <v>684.72727272727275</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-0.27167024563976327</v>
+        <v>-0.21101974545644997</v>
       </c>
       <c r="G23" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1779,11 +1779,11 @@
       </c>
       <c r="E24" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>1020.5454545454545</v>
+        <v>1109.590909090909</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.26183587585481327</v>
+        <v>-0.19742898474487114</v>
       </c>
       <c r="G24" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1808,11 +1808,11 @@
       </c>
       <c r="E25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>439.45454545454544</v>
+        <v>482.90909090909093</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.19453469965841885</v>
+        <v>-0.11488794468049657</v>
       </c>
       <c r="G25" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1837,11 +1837,11 @@
       </c>
       <c r="E26" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>342.77272727272725</v>
+        <v>366.40909090909093</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-0.3198953823953824</v>
+        <v>-0.27299783549783541</v>
       </c>
       <c r="G26" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1866,11 +1866,11 @@
       </c>
       <c r="E27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>101.22727272727273</v>
+        <v>107.04545454545455</v>
       </c>
       <c r="F27" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>-0.22295882763433361</v>
+        <v>-0.17829727843684584</v>
       </c>
       <c r="G27" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1895,11 +1895,11 @@
       </c>
       <c r="E28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>113.63636363636364</v>
+        <v>122.54545454545455</v>
       </c>
       <c r="F28" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>-0.20407513530722698</v>
+        <v>-0.14167462591531366</v>
       </c>
       <c r="G28" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1924,11 +1924,11 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>733.36363636363637</v>
+        <v>790.72727272727275</v>
       </c>
       <c r="F29" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-0.13906083244397016</v>
+        <v>-7.1718249733191075E-2</v>
       </c>
       <c r="G29" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1953,11 +1953,11 @@
       </c>
       <c r="E30" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>598.13636363636363</v>
+        <v>651.5454545454545</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-0.30239092403117207</v>
+        <v>-0.24009966601282939</v>
       </c>
       <c r="G30" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -1982,11 +1982,11 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>768.77272727272725</v>
+        <v>842.63636363636363</v>
       </c>
       <c r="F31" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-0.27999148573861221</v>
+        <v>-0.21081311196253727</v>
       </c>
       <c r="G31" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2011,11 +2011,11 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>521.77272727272725</v>
+        <v>572.36363636363637</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-0.23838906581740982</v>
+        <v>-0.16454352441613596</v>
       </c>
       <c r="G32" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2040,15 +2040,15 @@
       </c>
       <c r="E33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>197.22727272727272</v>
+        <v>212.54545454545453</v>
       </c>
       <c r="F33" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-5.5095818815330988E-2</v>
+        <v>1.8292682926829285E-2</v>
       </c>
       <c r="G33" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H33">
         <v>1.1599999999999999</v>
@@ -2069,11 +2069,11 @@
       </c>
       <c r="E34" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>248.86363636363637</v>
+        <v>291.45454545454544</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-0.51277031236095039</v>
+        <v>-0.42938506718875147</v>
       </c>
       <c r="G34" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2098,11 +2098,11 @@
       </c>
       <c r="E35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>345.5</v>
+        <v>374.22727272727275</v>
       </c>
       <c r="F35" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.2363106601024817</v>
+        <v>-0.1728122174218828</v>
       </c>
       <c r="G35" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2127,11 +2127,11 @@
       </c>
       <c r="E36" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>252.63636363636363</v>
+        <v>272.95454545454544</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>-0.25893333333333346</v>
+        <v>-0.19933333333333347</v>
       </c>
       <c r="G36" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2156,11 +2156,11 @@
       </c>
       <c r="E37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>389.68181818181819</v>
+        <v>420.40909090909093</v>
       </c>
       <c r="F37" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>-0.23043087971274689</v>
+        <v>-0.16974865350089763</v>
       </c>
       <c r="G37" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2185,11 +2185,11 @@
       </c>
       <c r="E38" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>223.54545454545453</v>
+        <v>246.45454545454547</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>-0.19350606756313549</v>
+        <v>-0.11085601836667758</v>
       </c>
       <c r="G38" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2214,11 +2214,11 @@
       </c>
       <c r="E39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>244.54545454545453</v>
+        <v>263.40909090909093</v>
       </c>
       <c r="F39" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-0.16988119117420153</v>
+        <v>-0.1058478629841072</v>
       </c>
       <c r="G39" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2243,11 +2243,11 @@
       </c>
       <c r="E40" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>46.045454545454547</v>
+        <v>49.909090909090907</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>-0.3555979643765903</v>
+        <v>-0.30152671755725191</v>
       </c>
       <c r="G40" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2272,11 +2272,11 @@
       </c>
       <c r="E41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>75.772727272727266</v>
+        <v>79.409090909090907</v>
       </c>
       <c r="F41" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.27553237722729251</v>
+        <v>-0.24076488483268144</v>
       </c>
       <c r="G41" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2301,11 +2301,11 @@
       </c>
       <c r="E42" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>31.272727272727273</v>
+        <v>34.272727272727273</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-0.35760971055088697</v>
+        <v>-0.29598506069094299</v>
       </c>
       <c r="G42" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2330,11 +2330,11 @@
       </c>
       <c r="E43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>36.136363636363633</v>
+        <v>37.5</v>
       </c>
       <c r="F43" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-0.24141221374045807</v>
+        <v>-0.21278625954198471</v>
       </c>
       <c r="G43" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2388,11 +2388,11 @@
       </c>
       <c r="E45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>3.1363636363636362</v>
+        <v>3.2727272727272729</v>
       </c>
       <c r="F45" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>0.13114754098360759</v>
+        <v>0.18032786885246033</v>
       </c>
       <c r="G45" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD94D3FF-CDF1-413F-A978-2C2CF6C30FD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE499B70-28FC-4603-A1B5-0F7D9DBDBDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,9 +43,6 @@
     <t>PRODUCTO</t>
   </si>
   <si>
-    <t>PROMD VTA DIA JUNIO</t>
-  </si>
-  <si>
     <t>PROMD VTA DIA JULIO</t>
   </si>
   <si>
@@ -221,6 +218,9 @@
   </si>
   <si>
     <t>CATEGORÍA</t>
+  </si>
+  <si>
+    <t>PROMD VTA DIA AGOSTO</t>
   </si>
 </sst>
 </file>
@@ -353,42 +353,21 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="INVENTARIO NACIONAL 03-07-26"/>
-      <sheetName val="VINCULO VTS BY SKU JUNIO"/>
+      <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
-      <sheetName val="INVENTARIO NACIONAL 03-07-26-2"/>
-      <sheetName val="INVENTARIO NACIONAL 06-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 07-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 08-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 09-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 10-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 13-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 14-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 15-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 16-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 17-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 20-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 21-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 22-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 23-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 27-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 28-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 29-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 30-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 31-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 04-08-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
+      <sheetData sheetId="2">
         <row r="4">
           <cell r="F4">
-            <v>1118.5454545454545</v>
+            <v>1224</v>
           </cell>
           <cell r="G4">
-            <v>7.0285316631871986E-2</v>
+            <v>9.4278283485045522E-2</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -396,65 +375,65 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>77.954545454545453</v>
+            <v>65</v>
           </cell>
           <cell r="G5">
-            <v>2.6331538001196808E-2</v>
+            <v>-0.16618075801749266</v>
           </cell>
           <cell r="H5" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="6">
           <cell r="F6">
-            <v>547.5</v>
+            <v>469</v>
           </cell>
           <cell r="G6">
-            <v>0.1201525155770482</v>
+            <v>-0.14337899543378996</v>
           </cell>
           <cell r="H6" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="7">
           <cell r="F7">
-            <v>97.772727272727266</v>
+            <v>62</v>
           </cell>
           <cell r="G7">
-            <v>7.0149253731343286E-2</v>
+            <v>-0.36587633658763363</v>
           </cell>
           <cell r="H7" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="8">
           <cell r="F8">
-            <v>16.681818181818183</v>
+            <v>6</v>
           </cell>
           <cell r="G8">
-            <v>4.5584045584045718E-2</v>
+            <v>-0.64032697547683926</v>
           </cell>
           <cell r="H8" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1294.909090909091</v>
+            <v>1400</v>
           </cell>
           <cell r="G9">
-            <v>-0.10163665604995109</v>
+            <v>8.1156978376860422E-2</v>
           </cell>
           <cell r="H9" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="10">
           <cell r="F10">
-            <v>122.18181818181819</v>
+            <v>74</v>
           </cell>
           <cell r="G10">
-            <v>-8.0711354309165428E-2</v>
+            <v>-0.39434523809523814</v>
           </cell>
           <cell r="H10" t="str">
             <v>BAJO</v>
@@ -462,10 +441,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>303.72727272727275</v>
+            <v>239</v>
           </cell>
           <cell r="G11">
-            <v>-8.6784201175344911E-2</v>
+            <v>-0.21310984735109251</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -473,10 +452,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>662</v>
+            <v>528</v>
           </cell>
           <cell r="G12">
-            <v>-7.2533910717697214E-2</v>
+            <v>-0.202416918429003</v>
           </cell>
           <cell r="H12" t="str">
             <v>BAJO</v>
@@ -484,10 +463,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>405.22727272727275</v>
+            <v>269</v>
           </cell>
           <cell r="G13">
-            <v>-0.15296912114014249</v>
+            <v>-0.33617498597868767</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -495,10 +474,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3250.0454545454545</v>
+            <v>2798</v>
           </cell>
           <cell r="G14">
-            <v>-6.9542585724510442E-2</v>
+            <v>-0.13908896379071622</v>
           </cell>
           <cell r="H14" t="str">
             <v>BAJO</v>
@@ -506,10 +485,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2178.5454545454545</v>
+            <v>1945</v>
           </cell>
           <cell r="G15">
-            <v>-2.2954295266440994E-2</v>
+            <v>-0.10720247037222497</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -517,10 +496,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2162.5454545454545</v>
+            <v>1938</v>
           </cell>
           <cell r="G16">
-            <v>-6.2190770929017813E-2</v>
+            <v>-0.10383386581469645</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -528,10 +507,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2404.681818181818</v>
+            <v>2026</v>
           </cell>
           <cell r="G17">
-            <v>-0.11208271093133715</v>
+            <v>-0.1574768916696595</v>
           </cell>
           <cell r="H17" t="str">
             <v>BAJO</v>
@@ -539,10 +518,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>133.13636363636363</v>
+            <v>40</v>
           </cell>
           <cell r="G18">
-            <v>-0.23504831548707239</v>
+            <v>-0.69955616251280306</v>
           </cell>
           <cell r="H18" t="str">
             <v>BAJO</v>
@@ -550,54 +529,54 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>225.86363636363637</v>
+            <v>57</v>
           </cell>
           <cell r="G19">
-            <v>5.2531243380639747E-2</v>
+            <v>-0.74763533910243507</v>
           </cell>
           <cell r="H19" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="20">
           <cell r="F20">
-            <v>147.90909090909091</v>
+            <v>36</v>
           </cell>
           <cell r="G20">
-            <v>0.16255805644873167</v>
+            <v>-0.75660725261216966</v>
           </cell>
           <cell r="H20" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="21">
           <cell r="F21">
-            <v>486.59090909090907</v>
+            <v>244</v>
           </cell>
           <cell r="G21">
-            <v>4.9755914382274558E-3</v>
+            <v>-0.49855207846800553</v>
           </cell>
           <cell r="H21" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="22">
           <cell r="F22">
-            <v>796.40909090909088</v>
+            <v>392</v>
           </cell>
           <cell r="G22">
-            <v>2.2586669779385948E-2</v>
+            <v>-0.50779065121853773</v>
           </cell>
           <cell r="H22" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="23">
           <cell r="F23">
-            <v>5</v>
+            <v>0</v>
           </cell>
           <cell r="G23">
-            <v>-0.90871369294605808</v>
+            <v>-1</v>
           </cell>
           <cell r="H23" t="str">
             <v>BAJO</v>
@@ -605,10 +584,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>49.18181818181818</v>
+            <v>50</v>
           </cell>
           <cell r="G24">
-            <v>0.1825136612021856</v>
+            <v>1.6635859519408491E-2</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -616,10 +595,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>684.72727272727275</v>
+            <v>606</v>
           </cell>
           <cell r="G25">
-            <v>-0.21101974545644997</v>
+            <v>-0.11497610196494956</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -627,10 +606,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>1109.590909090909</v>
+            <v>866</v>
           </cell>
           <cell r="G26">
-            <v>-0.19742898474487114</v>
+            <v>-0.21953217811642289</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -638,10 +617,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>482.90909090909093</v>
+            <v>358</v>
           </cell>
           <cell r="G27">
-            <v>-0.11488794468049657</v>
+            <v>-0.25865963855421692</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -649,10 +628,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>366.40909090909093</v>
+            <v>188</v>
           </cell>
           <cell r="G28">
-            <v>-0.27299783549783541</v>
+            <v>-0.48691229376007938</v>
           </cell>
           <cell r="H28" t="str">
             <v>BAJO</v>
@@ -660,10 +639,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>107.04545454545455</v>
+            <v>84</v>
           </cell>
           <cell r="G29">
-            <v>-0.17829727843684584</v>
+            <v>-0.21528662420382172</v>
           </cell>
           <cell r="H29" t="str">
             <v>BAJO</v>
@@ -671,10 +650,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>122.54545454545455</v>
+            <v>50</v>
           </cell>
           <cell r="G30">
-            <v>-0.14167462591531366</v>
+            <v>-0.59198813056379818</v>
           </cell>
           <cell r="H30" t="str">
             <v>BAJO</v>
@@ -682,10 +661,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>790.72727272727275</v>
+            <v>370</v>
           </cell>
           <cell r="G31">
-            <v>-7.1718249733191075E-2</v>
+            <v>-0.53207633938836518</v>
           </cell>
           <cell r="H31" t="str">
             <v>BAJO</v>
@@ -693,10 +672,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>651.5454545454545</v>
+            <v>402</v>
           </cell>
           <cell r="G32">
-            <v>-0.24009966601282939</v>
+            <v>-0.38300544160736705</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -704,10 +683,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>842.63636363636363</v>
+            <v>467</v>
           </cell>
           <cell r="G33">
-            <v>-0.21081311196253727</v>
+            <v>-0.44578703204229153</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -715,10 +694,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>572.36363636363637</v>
+            <v>307</v>
           </cell>
           <cell r="G34">
-            <v>-0.16454352441613596</v>
+            <v>-0.46362770012706478</v>
           </cell>
           <cell r="H34" t="str">
             <v>BAJO</v>
@@ -726,32 +705,32 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>212.54545454545453</v>
+            <v>43</v>
           </cell>
           <cell r="G35">
-            <v>1.8292682926829285E-2</v>
+            <v>-0.7976903336184773</v>
           </cell>
           <cell r="H35" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="36">
           <cell r="F36">
-            <v>291.45454545454544</v>
+            <v>315</v>
           </cell>
           <cell r="G36">
-            <v>-0.42938506718875147</v>
+            <v>8.0786026200873495E-2</v>
           </cell>
           <cell r="H36" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="37">
           <cell r="F37">
-            <v>374.22727272727275</v>
+            <v>70</v>
           </cell>
           <cell r="G37">
-            <v>-0.1728122174218828</v>
+            <v>-0.81294789262723188</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -759,10 +738,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>272.95454545454544</v>
+            <v>261</v>
           </cell>
           <cell r="G38">
-            <v>-0.19933333333333347</v>
+            <v>-4.3796835970024928E-2</v>
           </cell>
           <cell r="H38" t="str">
             <v>BAJO</v>
@@ -770,43 +749,43 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>420.40909090909093</v>
+            <v>1192</v>
           </cell>
           <cell r="G39">
-            <v>-0.16974865350089763</v>
+            <v>1.8353335495729266</v>
           </cell>
           <cell r="H39" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="40">
           <cell r="F40">
-            <v>246.45454545454547</v>
+            <v>591</v>
           </cell>
           <cell r="G40">
-            <v>-0.11085601836667758</v>
+            <v>1.3980081150866837</v>
           </cell>
           <cell r="H40" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="41">
           <cell r="F41">
-            <v>263.40909090909093</v>
+            <v>267</v>
           </cell>
           <cell r="G41">
-            <v>-0.1058478629841072</v>
+            <v>1.3632441760137892E-2</v>
           </cell>
           <cell r="H41" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="42">
           <cell r="F42">
-            <v>49.909090909090907</v>
+            <v>13</v>
           </cell>
           <cell r="G42">
-            <v>-0.30152671755725191</v>
+            <v>-0.73952641165755917</v>
           </cell>
           <cell r="H42" t="str">
             <v>BAJO</v>
@@ -814,32 +793,32 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>79.409090909090907</v>
+            <v>230</v>
           </cell>
           <cell r="G43">
-            <v>-0.24076488483268144</v>
+            <v>1.8963938179736695</v>
           </cell>
           <cell r="H43" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="44">
           <cell r="F44">
-            <v>34.272727272727273</v>
+            <v>223</v>
           </cell>
           <cell r="G44">
-            <v>-0.29598506069094299</v>
+            <v>5.5066312997347477</v>
           </cell>
           <cell r="H44" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="45">
           <cell r="F45">
-            <v>37.5</v>
+            <v>19</v>
           </cell>
           <cell r="G45">
-            <v>-0.21278625954198471</v>
+            <v>-0.49333333333333329</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -847,47 +826,28 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>0.81818181818181823</v>
+            <v>0</v>
           </cell>
           <cell r="G46">
-            <v>0.50000000000000022</v>
+            <v>-1</v>
           </cell>
           <cell r="H46" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="47">
           <cell r="F47">
-            <v>3.2727272727272729</v>
+            <v>1</v>
           </cell>
           <cell r="G47">
-            <v>0.18032786885246033</v>
+            <v>-0.69444444444444442</v>
           </cell>
           <cell r="H47" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1096,7 +1056,10 @@
   <cols>
     <col min="1" max="1" width="17.7109375" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
-    <col min="3" max="8" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" customWidth="1"/>
+    <col min="4" max="4" width="26.140625" customWidth="1"/>
+    <col min="5" max="5" width="29.5703125" customWidth="1"/>
+    <col min="6" max="8" width="17.7109375" customWidth="1"/>
     <col min="10" max="10" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1108,22 +1071,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
       <c r="H1" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -1131,21 +1094,21 @@
         <v>110150</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D2" s="5">
-        <v>1045</v>
+        <v>1118.5454545454545</v>
       </c>
       <c r="E2" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!$F$4</f>
-        <v>1118.5454545454545</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
+        <v>1224</v>
       </c>
       <c r="F2" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>7.0285316631871986E-2</v>
+        <v>9.4278283485045522E-2</v>
       </c>
       <c r="G2" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1160,25 +1123,25 @@
         <v>110151</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D3" s="5">
-        <v>76</v>
+        <v>77.954545454545453</v>
       </c>
       <c r="E3" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>77.954545454545453</v>
+        <v>65</v>
       </c>
       <c r="F3" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>2.6331538001196808E-2</v>
+        <v>-0.16618075801749266</v>
       </c>
       <c r="G3" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H3">
         <v>1.59</v>
@@ -1189,25 +1152,25 @@
         <v>110230</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D4" s="5">
-        <v>489</v>
+        <v>547.5</v>
       </c>
       <c r="E4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>547.5</v>
+        <v>469</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>0.1201525155770482</v>
+        <v>-0.14337899543378996</v>
       </c>
       <c r="G4" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H4">
         <v>2.0299999999999998</v>
@@ -1218,25 +1181,25 @@
         <v>110400</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D5" s="5">
-        <v>91</v>
+        <v>97.772727272727266</v>
       </c>
       <c r="E5" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>97.772727272727266</v>
+        <v>62</v>
       </c>
       <c r="F5" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>7.0149253731343286E-2</v>
+        <v>-0.36587633658763363</v>
       </c>
       <c r="G5" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H5">
         <v>3.61</v>
@@ -1247,25 +1210,25 @@
         <v>111000</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D6" s="5">
-        <v>16</v>
+        <v>16.681818181818183</v>
       </c>
       <c r="E6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>16.681818181818183</v>
+        <v>6</v>
       </c>
       <c r="F6" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>4.5584045584045718E-2</v>
+        <v>-0.64032697547683926</v>
       </c>
       <c r="G6" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H6">
         <v>8.7799999999999994</v>
@@ -1276,25 +1239,25 @@
         <v>120130</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D7" s="5">
-        <v>1441</v>
+        <v>1294.909090909091</v>
       </c>
       <c r="E7" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1294.909090909091</v>
+        <v>1400</v>
       </c>
       <c r="F7" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>-0.10163665604995109</v>
+        <v>8.1156978376860422E-2</v>
       </c>
       <c r="G7" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H7">
         <v>0.63</v>
@@ -1305,21 +1268,21 @@
         <v>120131</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D8" s="5">
-        <v>133</v>
+        <v>122.18181818181819</v>
       </c>
       <c r="E8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>122.18181818181819</v>
+        <v>74</v>
       </c>
       <c r="F8" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-8.0711354309165428E-2</v>
+        <v>-0.39434523809523814</v>
       </c>
       <c r="G8" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1334,21 +1297,21 @@
         <v>120132</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D9" s="5">
-        <v>333</v>
+        <v>303.72727272727275</v>
       </c>
       <c r="E9" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>303.72727272727275</v>
+        <v>239</v>
       </c>
       <c r="F9" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-8.6784201175344911E-2</v>
+        <v>-0.21310984735109251</v>
       </c>
       <c r="G9" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1363,21 +1326,21 @@
         <v>130150</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D10" s="5">
-        <v>714</v>
+        <v>662</v>
       </c>
       <c r="E10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>662</v>
+        <v>528</v>
       </c>
       <c r="F10" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>-7.2533910717697214E-2</v>
+        <v>-0.202416918429003</v>
       </c>
       <c r="G10" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1392,21 +1355,21 @@
         <v>130151</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D11" s="5">
-        <v>478</v>
+        <v>405.22727272727275</v>
       </c>
       <c r="E11" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>405.22727272727275</v>
+        <v>269</v>
       </c>
       <c r="F11" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.15296912114014249</v>
+        <v>-0.33617498597868767</v>
       </c>
       <c r="G11" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1421,21 +1384,21 @@
         <v>130152</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D12" s="5">
-        <v>3493</v>
+        <v>3250.0454545454545</v>
       </c>
       <c r="E12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3250.0454545454545</v>
+        <v>2798</v>
       </c>
       <c r="F12" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-6.9542585724510442E-2</v>
+        <v>-0.13908896379071622</v>
       </c>
       <c r="G12" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1450,21 +1413,21 @@
         <v>130153</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D13" s="5">
-        <v>2230</v>
+        <v>2178.5454545454545</v>
       </c>
       <c r="E13" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2178.5454545454545</v>
+        <v>1945</v>
       </c>
       <c r="F13" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-2.2954295266440994E-2</v>
+        <v>-0.10720247037222497</v>
       </c>
       <c r="G13" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1479,21 +1442,21 @@
         <v>130154</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" s="5">
-        <v>2306</v>
+        <v>2162.5454545454545</v>
       </c>
       <c r="E14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2162.5454545454545</v>
+        <v>1938</v>
       </c>
       <c r="F14" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-6.2190770929017813E-2</v>
+        <v>-0.10383386581469645</v>
       </c>
       <c r="G14" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1508,21 +1471,21 @@
         <v>130155</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D15" s="5">
-        <v>2708</v>
+        <v>2404.681818181818</v>
       </c>
       <c r="E15" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2404.681818181818</v>
+        <v>2026</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-0.11208271093133715</v>
+        <v>-0.1574768916696595</v>
       </c>
       <c r="G15" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1537,21 +1500,21 @@
         <v>130156</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D16" s="5">
-        <v>174</v>
+        <v>133.13636363636363</v>
       </c>
       <c r="E16" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>133.13636363636363</v>
+        <v>40</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.23504831548707239</v>
+        <v>-0.69955616251280306</v>
       </c>
       <c r="G16" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1566,25 +1529,25 @@
         <v>130700</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D17" s="5">
-        <v>215</v>
+        <v>225.86363636363637</v>
       </c>
       <c r="E17" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>225.86363636363637</v>
+        <v>57</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>5.2531243380639747E-2</v>
+        <v>-0.74763533910243507</v>
       </c>
       <c r="G17" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H17">
         <v>3.68</v>
@@ -1595,25 +1558,25 @@
         <v>130701</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D18" s="5">
-        <v>127</v>
+        <v>147.90909090909091</v>
       </c>
       <c r="E18" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>147.90909090909091</v>
+        <v>36</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>0.16255805644873167</v>
+        <v>-0.75660725261216966</v>
       </c>
       <c r="G18" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H18">
         <v>3.68</v>
@@ -1624,25 +1587,25 @@
         <v>130702</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D19" s="5">
-        <v>484</v>
+        <v>486.59090909090907</v>
       </c>
       <c r="E19" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>486.59090909090907</v>
+        <v>244</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>4.9755914382274558E-3</v>
+        <v>-0.49855207846800553</v>
       </c>
       <c r="G19" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H19">
         <v>4.1500000000000004</v>
@@ -1653,25 +1616,25 @@
         <v>130703</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D20" s="5">
-        <v>779</v>
+        <v>796.40909090909088</v>
       </c>
       <c r="E20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>796.40909090909088</v>
+        <v>392</v>
       </c>
       <c r="F20" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>2.2586669779385948E-2</v>
+        <v>-0.50779065121853773</v>
       </c>
       <c r="G20" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H20">
         <v>4.1500000000000004</v>
@@ -1682,21 +1645,21 @@
         <v>130704</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D21" s="5">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="E21" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F21" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>-0.90871369294605808</v>
+        <v>-1</v>
       </c>
       <c r="G21" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
@@ -1711,21 +1674,21 @@
         <v>130707</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D22" s="5">
-        <v>42</v>
+        <v>49.18181818181818</v>
       </c>
       <c r="E22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>49.18181818181818</v>
+        <v>50</v>
       </c>
       <c r="F22" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>0.1825136612021856</v>
+        <v>1.6635859519408491E-2</v>
       </c>
       <c r="G22" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1740,21 +1703,21 @@
         <v>131150</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D23" s="5">
-        <v>868</v>
+        <v>684.72727272727275</v>
       </c>
       <c r="E23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>684.72727272727275</v>
+        <v>606</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-0.21101974545644997</v>
+        <v>-0.11497610196494956</v>
       </c>
       <c r="G23" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1769,21 +1732,21 @@
         <v>131151</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D24" s="5">
-        <v>1383</v>
+        <v>1109.590909090909</v>
       </c>
       <c r="E24" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>1109.590909090909</v>
+        <v>866</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.19742898474487114</v>
+        <v>-0.21953217811642289</v>
       </c>
       <c r="G24" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1798,21 +1761,21 @@
         <v>131152</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D25" s="5">
-        <v>546</v>
+        <v>482.90909090909093</v>
       </c>
       <c r="E25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>482.90909090909093</v>
+        <v>358</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.11488794468049657</v>
+        <v>-0.25865963855421692</v>
       </c>
       <c r="G25" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1827,21 +1790,21 @@
         <v>131153</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D26" s="5">
-        <v>504</v>
+        <v>366.40909090909093</v>
       </c>
       <c r="E26" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>366.40909090909093</v>
+        <v>188</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-0.27299783549783541</v>
+        <v>-0.48691229376007938</v>
       </c>
       <c r="G26" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1856,21 +1819,21 @@
         <v>131700</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D27" s="5">
-        <v>130</v>
+        <v>107.04545454545455</v>
       </c>
       <c r="E27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>107.04545454545455</v>
+        <v>84</v>
       </c>
       <c r="F27" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>-0.17829727843684584</v>
+        <v>-0.21528662420382172</v>
       </c>
       <c r="G27" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1885,21 +1848,21 @@
         <v>131701</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D28" s="5">
-        <v>143</v>
+        <v>122.54545454545455</v>
       </c>
       <c r="E28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>122.54545454545455</v>
+        <v>50</v>
       </c>
       <c r="F28" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>-0.14167462591531366</v>
+        <v>-0.59198813056379818</v>
       </c>
       <c r="G28" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1914,21 +1877,21 @@
         <v>132150</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D29" s="5">
-        <v>852</v>
+        <v>790.72727272727275</v>
       </c>
       <c r="E29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>790.72727272727275</v>
+        <v>370</v>
       </c>
       <c r="F29" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-7.1718249733191075E-2</v>
+        <v>-0.53207633938836518</v>
       </c>
       <c r="G29" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1943,21 +1906,21 @@
         <v>132151</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D30" s="5">
-        <v>857</v>
+        <v>651.5454545454545</v>
       </c>
       <c r="E30" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>651.5454545454545</v>
+        <v>402</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-0.24009966601282939</v>
+        <v>-0.38300544160736705</v>
       </c>
       <c r="G30" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -1972,21 +1935,21 @@
         <v>132152</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D31" s="5">
-        <v>1068</v>
+        <v>842.63636363636363</v>
       </c>
       <c r="E31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>842.63636363636363</v>
+        <v>467</v>
       </c>
       <c r="F31" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-0.21081311196253727</v>
+        <v>-0.44578703204229153</v>
       </c>
       <c r="G31" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2001,21 +1964,21 @@
         <v>132153</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D32" s="5">
-        <v>685</v>
+        <v>572.36363636363637</v>
       </c>
       <c r="E32" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>572.36363636363637</v>
+        <v>307</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-0.16454352441613596</v>
+        <v>-0.46362770012706478</v>
       </c>
       <c r="G32" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2030,25 +1993,25 @@
         <v>140230</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D33" s="5">
-        <v>209</v>
+        <v>212.54545454545453</v>
       </c>
       <c r="E33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>212.54545454545453</v>
+        <v>43</v>
       </c>
       <c r="F33" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>1.8292682926829285E-2</v>
+        <v>-0.7976903336184773</v>
       </c>
       <c r="G33" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H33">
         <v>1.1599999999999999</v>
@@ -2059,25 +2022,25 @@
         <v>140231</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D34" s="5">
-        <v>511</v>
+        <v>291.45454545454544</v>
       </c>
       <c r="E34" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>291.45454545454544</v>
+        <v>315</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-0.42938506718875147</v>
+        <v>8.0786026200873495E-2</v>
       </c>
       <c r="G34" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H34">
         <v>1.1599999999999999</v>
@@ -2088,21 +2051,21 @@
         <v>140232</v>
       </c>
       <c r="B35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D35" s="5">
-        <v>452</v>
+        <v>374.22727272727275</v>
       </c>
       <c r="E35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>374.22727272727275</v>
+        <v>70</v>
       </c>
       <c r="F35" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.1728122174218828</v>
+        <v>-0.81294789262723188</v>
       </c>
       <c r="G35" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2117,21 +2080,21 @@
         <v>150360</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D36" s="5">
-        <v>341</v>
+        <v>272.95454545454544</v>
       </c>
       <c r="E36" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>272.95454545454544</v>
+        <v>261</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>-0.19933333333333347</v>
+        <v>-4.3796835970024928E-2</v>
       </c>
       <c r="G36" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2146,25 +2109,25 @@
         <v>150361</v>
       </c>
       <c r="B37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D37" s="5">
-        <v>506</v>
+        <v>420.40909090909093</v>
       </c>
       <c r="E37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>420.40909090909093</v>
+        <v>1192</v>
       </c>
       <c r="F37" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>-0.16974865350089763</v>
+        <v>1.8353335495729266</v>
       </c>
       <c r="G37" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H37">
         <v>0.81</v>
@@ -2175,25 +2138,25 @@
         <v>150362</v>
       </c>
       <c r="B38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D38" s="5">
-        <v>277</v>
+        <v>246.45454545454547</v>
       </c>
       <c r="E38" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>246.45454545454547</v>
+        <v>591</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>-0.11085601836667758</v>
+        <v>1.3980081150866837</v>
       </c>
       <c r="G38" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H38">
         <v>0.81</v>
@@ -2204,25 +2167,25 @@
         <v>150363</v>
       </c>
       <c r="B39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D39" s="5">
-        <v>295</v>
+        <v>263.40909090909093</v>
       </c>
       <c r="E39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>263.40909090909093</v>
+        <v>267</v>
       </c>
       <c r="F39" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-0.1058478629841072</v>
+        <v>1.3632441760137892E-2</v>
       </c>
       <c r="G39" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H39">
         <v>0.81</v>
@@ -2233,21 +2196,21 @@
         <v>151500</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D40" s="5">
-        <v>71</v>
+        <v>49.909090909090907</v>
       </c>
       <c r="E40" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>49.909090909090907</v>
+        <v>13</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>-0.30152671755725191</v>
+        <v>-0.73952641165755917</v>
       </c>
       <c r="G40" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2262,25 +2225,25 @@
         <v>151501</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D41" s="5">
-        <v>105</v>
+        <v>79.409090909090907</v>
       </c>
       <c r="E41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>79.409090909090907</v>
+        <v>230</v>
       </c>
       <c r="F41" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.24076488483268144</v>
+        <v>1.8963938179736695</v>
       </c>
       <c r="G41" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H41">
         <v>2.62</v>
@@ -2291,25 +2254,25 @@
         <v>151502</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D42" s="5">
-        <v>49</v>
+        <v>34.272727272727273</v>
       </c>
       <c r="E42" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>34.272727272727273</v>
+        <v>223</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-0.29598506069094299</v>
+        <v>5.5066312997347477</v>
       </c>
       <c r="G42" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H42">
         <v>2.62</v>
@@ -2320,21 +2283,21 @@
         <v>151503</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D43" s="5">
-        <v>48</v>
+        <v>37.5</v>
       </c>
       <c r="E43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>37.5</v>
+        <v>19</v>
       </c>
       <c r="F43" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-0.21278625954198471</v>
+        <v>-0.49333333333333329</v>
       </c>
       <c r="G43" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2346,28 +2309,28 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B44" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D44" s="5">
-        <v>1</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="E44" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>0.81818181818181823</v>
+        <v>0</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>0.50000000000000022</v>
+        <v>-1</v>
       </c>
       <c r="G44" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H44">
         <v>18</v>
@@ -2375,28 +2338,28 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B45" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D45" s="5">
-        <v>3</v>
+        <v>3.2727272727272729</v>
       </c>
       <c r="E45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>3.2727272727272729</v>
+        <v>1</v>
       </c>
       <c r="F45" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>0.18032786885246033</v>
+        <v>-0.69444444444444442</v>
       </c>
       <c r="G45" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H45">
         <v>18</v>
@@ -2417,18 +2380,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE499B70-28FC-4603-A1B5-0F7D9DBDBDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF7A873-E1AD-4940-B85A-2E6187D213FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,9 +43,6 @@
     <t>PRODUCTO</t>
   </si>
   <si>
-    <t>PROMD VTA DIA JULIO</t>
-  </si>
-  <si>
     <t>Porcentaje de desviación</t>
   </si>
   <si>
@@ -221,6 +218,9 @@
   </si>
   <si>
     <t>PROMD VTA DIA AGOSTO</t>
+  </si>
+  <si>
+    <t>PROMD VTA DIA JUNIO</t>
   </si>
 </sst>
 </file>
@@ -1057,8 +1057,8 @@
     <col min="1" max="1" width="17.7109375" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
     <col min="3" max="3" width="17.7109375" customWidth="1"/>
-    <col min="4" max="4" width="26.140625" customWidth="1"/>
-    <col min="5" max="5" width="29.5703125" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="24.7109375" customWidth="1"/>
     <col min="6" max="8" width="17.7109375" customWidth="1"/>
     <col min="10" max="10" width="17.7109375" customWidth="1"/>
   </cols>
@@ -1071,22 +1071,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
-        <v>4</v>
-      </c>
       <c r="H1" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -1094,10 +1094,10 @@
         <v>110150</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D2" s="5">
         <v>1118.5454545454545</v>
@@ -1123,10 +1123,10 @@
         <v>110151</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D3" s="5">
         <v>77.954545454545453</v>
@@ -1152,10 +1152,10 @@
         <v>110230</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D4" s="5">
         <v>547.5</v>
@@ -1181,10 +1181,10 @@
         <v>110400</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D5" s="5">
         <v>97.772727272727266</v>
@@ -1210,10 +1210,10 @@
         <v>111000</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D6" s="5">
         <v>16.681818181818183</v>
@@ -1239,10 +1239,10 @@
         <v>120130</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D7" s="5">
         <v>1294.909090909091</v>
@@ -1268,10 +1268,10 @@
         <v>120131</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D8" s="5">
         <v>122.18181818181819</v>
@@ -1297,10 +1297,10 @@
         <v>120132</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D9" s="5">
         <v>303.72727272727275</v>
@@ -1326,10 +1326,10 @@
         <v>130150</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D10" s="5">
         <v>662</v>
@@ -1355,10 +1355,10 @@
         <v>130151</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D11" s="5">
         <v>405.22727272727275</v>
@@ -1384,10 +1384,10 @@
         <v>130152</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D12" s="5">
         <v>3250.0454545454545</v>
@@ -1413,10 +1413,10 @@
         <v>130153</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D13" s="5">
         <v>2178.5454545454545</v>
@@ -1442,10 +1442,10 @@
         <v>130154</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" s="5">
         <v>2162.5454545454545</v>
@@ -1471,10 +1471,10 @@
         <v>130155</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" s="5">
         <v>2404.681818181818</v>
@@ -1500,10 +1500,10 @@
         <v>130156</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D16" s="5">
         <v>133.13636363636363</v>
@@ -1529,10 +1529,10 @@
         <v>130700</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D17" s="5">
         <v>225.86363636363637</v>
@@ -1558,10 +1558,10 @@
         <v>130701</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D18" s="5">
         <v>147.90909090909091</v>
@@ -1587,10 +1587,10 @@
         <v>130702</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D19" s="5">
         <v>486.59090909090907</v>
@@ -1616,10 +1616,10 @@
         <v>130703</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D20" s="5">
         <v>796.40909090909088</v>
@@ -1645,10 +1645,10 @@
         <v>130704</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D21" s="5">
         <v>5</v>
@@ -1674,10 +1674,10 @@
         <v>130707</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D22" s="5">
         <v>49.18181818181818</v>
@@ -1703,10 +1703,10 @@
         <v>131150</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D23" s="5">
         <v>684.72727272727275</v>
@@ -1732,10 +1732,10 @@
         <v>131151</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D24" s="5">
         <v>1109.590909090909</v>
@@ -1761,10 +1761,10 @@
         <v>131152</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D25" s="5">
         <v>482.90909090909093</v>
@@ -1790,10 +1790,10 @@
         <v>131153</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D26" s="5">
         <v>366.40909090909093</v>
@@ -1819,10 +1819,10 @@
         <v>131700</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D27" s="5">
         <v>107.04545454545455</v>
@@ -1848,10 +1848,10 @@
         <v>131701</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D28" s="5">
         <v>122.54545454545455</v>
@@ -1877,10 +1877,10 @@
         <v>132150</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D29" s="5">
         <v>790.72727272727275</v>
@@ -1906,10 +1906,10 @@
         <v>132151</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D30" s="5">
         <v>651.5454545454545</v>
@@ -1935,10 +1935,10 @@
         <v>132152</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D31" s="5">
         <v>842.63636363636363</v>
@@ -1964,10 +1964,10 @@
         <v>132153</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D32" s="5">
         <v>572.36363636363637</v>
@@ -1993,10 +1993,10 @@
         <v>140230</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D33" s="5">
         <v>212.54545454545453</v>
@@ -2022,10 +2022,10 @@
         <v>140231</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D34" s="5">
         <v>291.45454545454544</v>
@@ -2051,10 +2051,10 @@
         <v>140232</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D35" s="5">
         <v>374.22727272727275</v>
@@ -2080,10 +2080,10 @@
         <v>150360</v>
       </c>
       <c r="B36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D36" s="5">
         <v>272.95454545454544</v>
@@ -2109,10 +2109,10 @@
         <v>150361</v>
       </c>
       <c r="B37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D37" s="5">
         <v>420.40909090909093</v>
@@ -2138,10 +2138,10 @@
         <v>150362</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D38" s="5">
         <v>246.45454545454547</v>
@@ -2167,10 +2167,10 @@
         <v>150363</v>
       </c>
       <c r="B39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D39" s="5">
         <v>263.40909090909093</v>
@@ -2196,10 +2196,10 @@
         <v>151500</v>
       </c>
       <c r="B40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D40" s="5">
         <v>49.909090909090907</v>
@@ -2225,10 +2225,10 @@
         <v>151501</v>
       </c>
       <c r="B41" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D41" s="5">
         <v>79.409090909090907</v>
@@ -2254,10 +2254,10 @@
         <v>151502</v>
       </c>
       <c r="B42" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D42" s="5">
         <v>34.272727272727273</v>
@@ -2283,10 +2283,10 @@
         <v>151503</v>
       </c>
       <c r="B43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D43" s="5">
         <v>37.5</v>
@@ -2309,13 +2309,13 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B44" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D44" s="5">
         <v>0.81818181818181823</v>
@@ -2338,13 +2338,13 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B45" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D45" s="5">
         <v>3.2727272727272729</v>
@@ -2380,18 +2380,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
+++ b/Comparación de Venta Diaria por SKU (Junio vs Julio).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF7A873-E1AD-4940-B85A-2E6187D213FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17889072-1866-44D9-B239-EC10100F67AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -220,7 +220,7 @@
     <t>PROMD VTA DIA AGOSTO</t>
   </si>
   <si>
-    <t>PROMD VTA DIA JUNIO</t>
+    <t>PROMD VTA DIA JULIO</t>
   </si>
 </sst>
 </file>
